--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="410" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20DDDE7C-ADB0-49B9-996F-32EDC5F54743}"/>
+  <xr:revisionPtr revIDLastSave="519" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15EB6805-8694-40BC-99DA-921536F80D33}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>
@@ -88,16 +88,16 @@
     <t>Segment-5</t>
   </si>
   <si>
-    <t>25-09-2026 (6/11 flue cans assembled)</t>
-  </si>
-  <si>
-    <t>Daily- 125 - (SH-85 and RH-40); Sep-876 NDHT Balance joints - 11361 (SH - 6474; RH - 4887)</t>
-  </si>
-  <si>
-    <t>Daily-1; MS Joints - 54/146; MS to PRDS - 7/26; HRH - 8/95; CRH -14/87; LPBP - 6/49; HPBP-8/23; BFD- 157/661</t>
-  </si>
-  <si>
-    <t>Daily- 3; June - 1229; July - 832; Aug - 642; Sep- 378MT; Total - 3871 MT</t>
+    <t>30-09-2026 (10/11 flue cans assembled)</t>
+  </si>
+  <si>
+    <t>Daily- 3; June - 1229; July - 832; Aug - 642; Sep- 529 MT; Total - 4023 MT</t>
+  </si>
+  <si>
+    <t>Daily- 121 - (SH-84 and RH-37); Sep-1731 NDHT Balance joints - 10506 (SH - 5880; RH - 4626)</t>
+  </si>
+  <si>
+    <t>Daily-2; MS Joints - 59/146; MS to PRDS - 9/26; HRH - 10/95; CRH -14/87; LPBP - 7/49; HPBP-8/23; BFD- 160/661</t>
   </si>
 </sst>
 </file>
@@ -157,6 +157,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -482,13 +486,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="93" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -499,37 +503,37 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A2" s="1">
-        <v>46280</v>
+        <v>46289</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A3" s="1">
-        <v>46280</v>
+        <v>46290</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A4" s="1">
-        <v>46280</v>
+        <v>46290</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -542,14 +546,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
-  <dimension ref="A1:D45"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D54"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -563,7 +567,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -577,593 +581,716 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A3" s="1">
+        <v>46290</v>
+      </c>
+      <c r="C3">
+        <v>121</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A4" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>133</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A5" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>143</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A6" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A7" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>131</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A8" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B8">
+        <v>42</v>
+      </c>
+      <c r="C8">
+        <v>111</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A9" s="1">
+        <v>46284</v>
+      </c>
+      <c r="B9">
+        <v>16</v>
+      </c>
+      <c r="C9">
+        <v>118</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A10" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B10">
+        <v>16</v>
+      </c>
+      <c r="C10">
+        <v>118</v>
+      </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A11" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B11">
+        <v>33</v>
+      </c>
+      <c r="C11">
+        <v>98</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A12" s="1">
         <v>46280</v>
       </c>
-      <c r="B3">
+      <c r="B12">
         <v>3</v>
       </c>
-      <c r="C3">
+      <c r="C12">
         <v>125</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+      <c r="D12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A13" s="1">
         <v>46279</v>
       </c>
-      <c r="B4">
+      <c r="B13">
         <v>58</v>
       </c>
-      <c r="C4">
+      <c r="C13">
         <v>100</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>46278</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>46277</v>
-      </c>
-      <c r="B6">
-        <v>63</v>
-      </c>
-      <c r="C6">
-        <v>42</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>46276</v>
-      </c>
-      <c r="B7">
-        <v>19</v>
-      </c>
-      <c r="C7">
-        <v>73</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>46275</v>
-      </c>
-      <c r="B8">
-        <v>21</v>
-      </c>
-      <c r="C8">
-        <v>16</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>46274</v>
-      </c>
-      <c r="B9">
-        <v>47</v>
-      </c>
-      <c r="C9">
-        <v>84</v>
-      </c>
-      <c r="D9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>46273</v>
-      </c>
-      <c r="B10">
-        <v>45</v>
-      </c>
-      <c r="C10">
-        <v>105</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>46272</v>
-      </c>
-      <c r="B11">
-        <v>38</v>
-      </c>
-      <c r="C11">
-        <v>92</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>46271</v>
-      </c>
-      <c r="B12">
-        <v>13</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>46270</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>90</v>
       </c>
       <c r="D13">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A14" s="1">
+        <v>46278</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A15" s="1">
+        <v>46277</v>
+      </c>
+      <c r="B15">
+        <v>63</v>
+      </c>
+      <c r="C15">
+        <v>42</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A16" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B16">
+        <v>19</v>
+      </c>
+      <c r="C16">
+        <v>73</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A17" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B17">
+        <v>21</v>
+      </c>
+      <c r="C17">
+        <v>16</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A18" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B18">
+        <v>47</v>
+      </c>
+      <c r="C18">
+        <v>84</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A19" s="1">
+        <v>46273</v>
+      </c>
+      <c r="B19">
+        <v>45</v>
+      </c>
+      <c r="C19">
+        <v>105</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A20" s="1">
+        <v>46272</v>
+      </c>
+      <c r="B20">
+        <v>38</v>
+      </c>
+      <c r="C20">
+        <v>92</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A21" s="1">
+        <v>46271</v>
+      </c>
+      <c r="B21">
+        <v>13</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A22" s="1">
+        <v>46270</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>90</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A23" s="1">
         <v>46269</v>
       </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A24" s="1">
         <v>46268</v>
       </c>
-      <c r="B15">
+      <c r="B24">
         <v>23</v>
       </c>
-      <c r="C15">
+      <c r="C24">
         <v>74</v>
       </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+      <c r="D24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A25" s="1">
         <v>46267</v>
       </c>
-      <c r="B16">
+      <c r="B25">
         <v>7</v>
       </c>
-      <c r="C16">
+      <c r="C25">
         <v>75</v>
       </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+      <c r="D25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A26" s="1">
         <v>46266</v>
       </c>
-      <c r="B17">
+      <c r="B26">
         <v>17</v>
       </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A27" s="1">
         <v>46265</v>
       </c>
-      <c r="C18">
+      <c r="C27">
         <v>62</v>
       </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+      <c r="D27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A28" s="1">
         <v>46264</v>
       </c>
-      <c r="B19">
+      <c r="B28">
         <v>5</v>
       </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A29" s="1">
         <v>46263</v>
       </c>
-      <c r="B20">
+      <c r="B29">
         <v>73</v>
       </c>
-      <c r="C20">
+      <c r="C29">
         <v>62</v>
       </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+      <c r="D29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A30" s="1">
         <v>46262</v>
       </c>
-      <c r="B21">
+      <c r="B30">
         <v>67</v>
       </c>
-      <c r="C21">
+      <c r="C30">
         <v>54</v>
       </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+      <c r="D30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A31" s="1">
         <v>46261</v>
       </c>
-      <c r="B22">
+      <c r="B31">
         <v>29</v>
       </c>
-      <c r="C22">
+      <c r="C31">
         <v>64</v>
       </c>
-      <c r="D22">
+      <c r="D31">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A32" s="1">
         <v>46260</v>
       </c>
-      <c r="B23">
+      <c r="B32">
         <v>85</v>
       </c>
-      <c r="C23">
+      <c r="C32">
         <v>62</v>
       </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+      <c r="D32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A33" s="1">
         <v>46259</v>
       </c>
-      <c r="B24">
+      <c r="B33">
         <v>13</v>
       </c>
-      <c r="C24">
+      <c r="C33">
         <v>62</v>
       </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+      <c r="D33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A34" s="1">
         <v>46258</v>
       </c>
-      <c r="B25">
+      <c r="B34">
         <v>18</v>
       </c>
-      <c r="C25">
+      <c r="C34">
         <v>56</v>
       </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
+      <c r="D34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A35" s="1">
         <v>46257</v>
       </c>
-      <c r="B26">
+      <c r="B35">
         <v>3</v>
       </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A36" s="1">
         <v>46256</v>
       </c>
-      <c r="B27">
+      <c r="B36">
         <v>69</v>
       </c>
-      <c r="C27">
+      <c r="C36">
         <v>53</v>
       </c>
-      <c r="D27">
+      <c r="D36">
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A37" s="1">
         <v>46255</v>
       </c>
-      <c r="B28">
+      <c r="B37">
         <v>15</v>
       </c>
-      <c r="C28">
+      <c r="C37">
         <v>60</v>
       </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+      <c r="D37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A38" s="1">
         <v>46254</v>
       </c>
-      <c r="B29">
+      <c r="B38">
         <v>48</v>
       </c>
-      <c r="C29">
+      <c r="C38">
         <v>43</v>
       </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+      <c r="D38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A39" s="1">
         <v>46253</v>
       </c>
-      <c r="B30">
+      <c r="B39">
         <v>27</v>
       </c>
-      <c r="C30">
+      <c r="C39">
         <v>51</v>
       </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+      <c r="D39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A40" s="1">
         <v>46252</v>
       </c>
-      <c r="B31">
-        <v>0</v>
-      </c>
-      <c r="C31">
-        <v>0</v>
-      </c>
-      <c r="D31">
+      <c r="B40">
+        <v>0</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A41" s="1">
         <v>46251</v>
       </c>
-      <c r="B32">
+      <c r="B41">
         <v>12</v>
       </c>
-      <c r="C32">
-        <v>0</v>
-      </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A42" s="1">
         <v>46250</v>
       </c>
-      <c r="B33">
+      <c r="B42">
         <v>12</v>
       </c>
-      <c r="C33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
+      <c r="C42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A43" s="1">
         <v>46249</v>
       </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
+      <c r="C43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A44" s="1">
         <v>46248</v>
       </c>
-      <c r="B35">
+      <c r="B44">
         <v>7</v>
       </c>
-      <c r="C35">
+      <c r="C44">
         <v>16</v>
       </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
+      <c r="D44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A45" s="1">
         <v>46247</v>
       </c>
-      <c r="B36">
+      <c r="B45">
         <v>35</v>
       </c>
-      <c r="C36">
+      <c r="C45">
         <v>21</v>
       </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
+      <c r="D45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A46" s="1">
         <v>46246</v>
       </c>
-      <c r="B37">
+      <c r="B46">
         <v>28</v>
       </c>
-      <c r="C37">
+      <c r="C46">
         <v>21</v>
       </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
+      <c r="D46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A47" s="1">
         <v>46245</v>
       </c>
-      <c r="B38">
+      <c r="B47">
         <v>21</v>
       </c>
-      <c r="C38">
+      <c r="C47">
         <v>25</v>
       </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
+      <c r="D47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A48" s="1">
         <v>46244</v>
       </c>
-      <c r="B39">
+      <c r="B48">
         <v>19</v>
       </c>
-      <c r="C39">
+      <c r="C48">
         <v>11</v>
       </c>
-      <c r="D39">
+      <c r="D48">
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A49" s="1">
         <v>46243</v>
       </c>
-      <c r="B40">
+      <c r="B49">
         <v>13</v>
       </c>
-      <c r="C40">
-        <v>0</v>
-      </c>
-      <c r="D40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A50" s="1">
         <v>46242</v>
       </c>
-      <c r="B41">
-        <v>0</v>
-      </c>
-      <c r="C41">
-        <v>0</v>
-      </c>
-      <c r="D41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A51" s="1">
         <v>46241</v>
       </c>
-      <c r="B42">
+      <c r="B51">
         <v>32</v>
       </c>
-      <c r="C42">
-        <v>0</v>
-      </c>
-      <c r="D42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A52" s="1">
         <v>46240</v>
       </c>
-      <c r="B43">
+      <c r="B52">
         <v>16</v>
       </c>
-      <c r="C43">
-        <v>0</v>
-      </c>
-      <c r="D43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A53" s="1">
         <v>46239</v>
       </c>
-      <c r="B44">
-        <v>0</v>
-      </c>
-      <c r="C44">
-        <v>0</v>
-      </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="1">
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A54" s="1">
         <v>46238</v>
       </c>
-      <c r="B45">
-        <v>0</v>
-      </c>
-      <c r="C45">
-        <v>0</v>
-      </c>
-      <c r="D45">
+      <c r="B54">
+        <v>0</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
         <v>1</v>
       </c>
     </row>
@@ -1175,13 +1302,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E384ED-EF07-4058-B570-9E7F8CBFADFB}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="9.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -1189,7 +1316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1197,7 +1324,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1205,7 +1332,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1213,7 +1340,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1221,7 +1348,7 @@
         <v>46326</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
         <v>15</v>
       </c>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="519" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15EB6805-8694-40BC-99DA-921536F80D33}"/>
+  <xr:revisionPtr revIDLastSave="546" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46D32B33-9684-4277-B1E0-289F17894E2E}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,12 +52,18 @@
     <t>ACC</t>
   </si>
   <si>
+    <t>Daily- 13; June - 1229; July - 832; Aug - 642; Sep- 579 MT; Total - 4073 MT</t>
+  </si>
+  <si>
     <t>Boiler</t>
   </si>
   <si>
     <t>PCP Joint</t>
   </si>
   <si>
+    <t>Daily-0; MS Joints - 59/146; MS to PRDS - 9/26; HRH - 10/95; CRH -14/87; LPBP - 7/49; HPBP-8/23; BFD- 163/661</t>
+  </si>
+  <si>
     <t>Boiler - NDHT Joints</t>
   </si>
   <si>
@@ -82,22 +88,16 @@
     <t>Segment-3</t>
   </si>
   <si>
+    <t>30-09-2026 (10/11 flue cans assembled)</t>
+  </si>
+  <si>
     <t>Segment-4</t>
   </si>
   <si>
     <t>Segment-5</t>
   </si>
   <si>
-    <t>30-09-2026 (10/11 flue cans assembled)</t>
-  </si>
-  <si>
-    <t>Daily- 3; June - 1229; July - 832; Aug - 642; Sep- 529 MT; Total - 4023 MT</t>
-  </si>
-  <si>
-    <t>Daily- 121 - (SH-84 and RH-37); Sep-1731 NDHT Balance joints - 10506 (SH - 5880; RH - 4626)</t>
-  </si>
-  <si>
-    <t>Daily-2; MS Joints - 59/146; MS to PRDS - 9/26; HRH - 10/95; CRH -14/87; LPBP - 7/49; HPBP-8/23; BFD- 160/661</t>
+    <t>Daily- 0 - (SH-0 and RH-0); Sep-1770 NDHT Balance joints - 10467 (SH - 5847; RH - 4620)</t>
   </si>
 </sst>
 </file>
@@ -157,10 +157,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -505,35 +501,35 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A2" s="1">
-        <v>46289</v>
+        <v>46292</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A3" s="1">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A4" s="1">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -546,7 +542,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -561,15 +557,15 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>30</v>
@@ -583,52 +579,55 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A3" s="1">
-        <v>46290</v>
+        <v>46292</v>
+      </c>
+      <c r="B3">
+        <v>13</v>
       </c>
       <c r="C3">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A4" s="1">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C4">
-        <v>133</v>
+        <v>39</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A5" s="1">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C5">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A6" s="1">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -636,125 +635,125 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A7" s="1">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="B7">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A8" s="1">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="B8">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C8">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A9" s="1">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="B9">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C9">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A10" s="1">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="B10">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C10">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A11" s="1">
-        <v>46281</v>
+        <v>46284</v>
       </c>
       <c r="B11">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C11">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A12" s="1">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C12">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A13" s="1">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="B13">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C13">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A14" s="1">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="B14">
         <v>3</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A15" s="1">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="B15">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C15">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -762,55 +761,55 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A16" s="1">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="B16">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C16">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A17" s="1">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B17">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="C17">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A18" s="1">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B18">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="C18">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A19" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B19">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="C19">
-        <v>105</v>
+        <v>16</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -818,52 +817,52 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A20" s="1">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="B20">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C20">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A21" s="1">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="B21">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A22" s="1">
-        <v>46270</v>
+        <v>46272</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C22">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A23" s="1">
-        <v>46269</v>
+        <v>46271</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -874,52 +873,55 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A24" s="1">
-        <v>46268</v>
+        <v>46270</v>
       </c>
       <c r="B24">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A25" s="1">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B25">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A26" s="1">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B26">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A27" s="1">
-        <v>46265</v>
+        <v>46267</v>
+      </c>
+      <c r="B27">
+        <v>7</v>
       </c>
       <c r="C27">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -927,24 +929,21 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A28" s="1">
-        <v>46264</v>
+        <v>46266</v>
       </c>
       <c r="B28">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A29" s="1">
-        <v>46263</v>
-      </c>
-      <c r="B29">
-        <v>73</v>
+        <v>46265</v>
       </c>
       <c r="C29">
         <v>62</v>
@@ -955,13 +954,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A30" s="1">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="B30">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="C30">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -969,27 +968,27 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A31" s="1">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="B31">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="C31">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A32" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B32">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="C32">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -997,97 +996,97 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A33" s="1">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B33">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C33">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A34" s="1">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B34">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="C34">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A35" s="1">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A36" s="1">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="B36">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="C36">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A37" s="1">
-        <v>46255</v>
+        <v>46257</v>
       </c>
       <c r="B37">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C37">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A38" s="1">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="B38">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="C38">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A39" s="1">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B39">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C39">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1095,27 +1094,27 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A40" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A41" s="1">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B41">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -1123,74 +1122,74 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A42" s="1">
-        <v>46250</v>
+        <v>46252</v>
       </c>
       <c r="B42">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C42">
         <v>0</v>
+      </c>
+      <c r="D42">
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A43" s="1">
-        <v>46249</v>
+        <v>46251</v>
+      </c>
+      <c r="B43">
+        <v>12</v>
       </c>
       <c r="C43">
         <v>0</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A44" s="1">
-        <v>46248</v>
+        <v>46250</v>
       </c>
       <c r="B44">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C44">
-        <v>16</v>
-      </c>
-      <c r="D44">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A45" s="1">
-        <v>46247</v>
-      </c>
-      <c r="B45">
-        <v>35</v>
+        <v>46249</v>
       </c>
       <c r="C45">
-        <v>21</v>
-      </c>
-      <c r="D45">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A46" s="1">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B46">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C46">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A47" s="1">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B47">
+        <v>35</v>
+      </c>
+      <c r="C47">
         <v>21</v>
-      </c>
-      <c r="C47">
-        <v>25</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -1198,27 +1197,27 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A48" s="1">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B48">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C48">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D48">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A49" s="1">
-        <v>46243</v>
+        <v>46245</v>
       </c>
       <c r="B49">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -1226,24 +1225,24 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A50" s="1">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A51" s="1">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B51">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -1254,10 +1253,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A52" s="1">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="B52">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -1268,29 +1267,57 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A53" s="1">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A54" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B54">
+        <v>16</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A55" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A56" s="1">
         <v>46238</v>
       </c>
-      <c r="B54">
-        <v>0</v>
-      </c>
-      <c r="C54">
-        <v>0</v>
-      </c>
-      <c r="D54">
+      <c r="B56">
+        <v>0</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56">
         <v>1</v>
       </c>
     </row>
@@ -1310,7 +1337,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1318,23 +1345,23 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>16</v>
@@ -1342,7 +1369,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B5" s="1">
         <v>46326</v>
@@ -1350,7 +1377,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1">
         <v>46361</v>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="546" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46D32B33-9684-4277-B1E0-289F17894E2E}"/>
+  <xr:revisionPtr revIDLastSave="559" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDB75462-DD27-42B3-9E95-DC27F3ED0E50}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>
@@ -52,18 +52,12 @@
     <t>ACC</t>
   </si>
   <si>
-    <t>Daily- 13; June - 1229; July - 832; Aug - 642; Sep- 579 MT; Total - 4073 MT</t>
-  </si>
-  <si>
     <t>Boiler</t>
   </si>
   <si>
     <t>PCP Joint</t>
   </si>
   <si>
-    <t>Daily-0; MS Joints - 59/146; MS to PRDS - 9/26; HRH - 10/95; CRH -14/87; LPBP - 7/49; HPBP-8/23; BFD- 163/661</t>
-  </si>
-  <si>
     <t>Boiler - NDHT Joints</t>
   </si>
   <si>
@@ -98,6 +92,12 @@
   </si>
   <si>
     <t>Daily- 0 - (SH-0 and RH-0); Sep-1770 NDHT Balance joints - 10467 (SH - 5847; RH - 4620)</t>
+  </si>
+  <si>
+    <t>Daily- 43; June - 1229; July - 832; Aug - 642; Sep- 622 MT; Total - 4115 MT</t>
+  </si>
+  <si>
+    <t>Daily-4; MS Joints - 63/146; MS to PRDS - 9/26; HRH - 10/95; CRH -14/87; LPBP - 7/49; HPBP-8/23; BFD- 163/661</t>
   </si>
 </sst>
 </file>
@@ -482,13 +482,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="93" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -499,37 +499,37 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A3" s="1">
-        <v>46292</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A4" s="1">
-        <v>46292</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -542,14 +542,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
-  <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:D57"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -557,15 +557,15 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>8</v>
-      </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A2" t="s">
-        <v>10</v>
       </c>
       <c r="B2">
         <v>30</v>
@@ -577,135 +577,135 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B3">
+        <v>43</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>46292</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>13</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A4" s="1">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>46291</v>
       </c>
-      <c r="B4">
+      <c r="B5">
         <v>17</v>
       </c>
-      <c r="C4">
+      <c r="C5">
         <v>39</v>
       </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A5" s="1">
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>46290</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>20</v>
       </c>
-      <c r="C5">
+      <c r="C6">
         <v>121</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A6" s="1">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>46289</v>
       </c>
-      <c r="B6">
+      <c r="B7">
         <v>3</v>
       </c>
-      <c r="C6">
+      <c r="C7">
         <v>133</v>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A7" s="1">
+      <c r="D7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>46288</v>
       </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
         <v>143</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A8" s="1">
+      <c r="D8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>46287</v>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>9</v>
       </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A9" s="1">
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>46286</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>32</v>
       </c>
-      <c r="C9">
+      <c r="C10">
         <v>131</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A10" s="1">
+      <c r="D10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>46285</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>42</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>111</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A11" s="1">
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>46284</v>
-      </c>
-      <c r="B11">
-        <v>16</v>
-      </c>
-      <c r="C11">
-        <v>118</v>
-      </c>
-      <c r="D11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A12" s="1">
-        <v>46283</v>
       </c>
       <c r="B12">
         <v>16</v>
@@ -717,440 +717,440 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B13">
+        <v>16</v>
+      </c>
+      <c r="C13">
+        <v>118</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>46281</v>
       </c>
-      <c r="B13">
+      <c r="B14">
         <v>33</v>
       </c>
-      <c r="C13">
+      <c r="C14">
         <v>98</v>
       </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A14" s="1">
+      <c r="D14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>46280</v>
       </c>
-      <c r="B14">
+      <c r="B15">
         <v>3</v>
       </c>
-      <c r="C14">
+      <c r="C15">
         <v>125</v>
       </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A15" s="1">
+      <c r="D15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>46279</v>
       </c>
-      <c r="B15">
+      <c r="B16">
         <v>58</v>
       </c>
-      <c r="C15">
+      <c r="C16">
         <v>100</v>
       </c>
-      <c r="D15">
+      <c r="D16">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A16" s="1">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
         <v>46278</v>
       </c>
-      <c r="B16">
+      <c r="B17">
         <v>3</v>
       </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A17" s="1">
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>46277</v>
       </c>
-      <c r="B17">
+      <c r="B18">
         <v>63</v>
       </c>
-      <c r="C17">
+      <c r="C18">
         <v>42</v>
       </c>
-      <c r="D17">
+      <c r="D18">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A18" s="1">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>46276</v>
       </c>
-      <c r="B18">
+      <c r="B19">
         <v>19</v>
       </c>
-      <c r="C18">
+      <c r="C19">
         <v>73</v>
       </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A19" s="1">
+      <c r="D19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>46275</v>
       </c>
-      <c r="B19">
+      <c r="B20">
         <v>21</v>
       </c>
-      <c r="C19">
+      <c r="C20">
         <v>16</v>
       </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A20" s="1">
+      <c r="D20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
         <v>46274</v>
       </c>
-      <c r="B20">
+      <c r="B21">
         <v>47</v>
       </c>
-      <c r="C20">
+      <c r="C21">
         <v>84</v>
       </c>
-      <c r="D20">
+      <c r="D21">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A21" s="1">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
         <v>46273</v>
       </c>
-      <c r="B21">
+      <c r="B22">
         <v>45</v>
       </c>
-      <c r="C21">
+      <c r="C22">
         <v>105</v>
       </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A22" s="1">
+      <c r="D22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
         <v>46272</v>
       </c>
-      <c r="B22">
+      <c r="B23">
         <v>38</v>
       </c>
-      <c r="C22">
+      <c r="C23">
         <v>92</v>
       </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A23" s="1">
+      <c r="D23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
         <v>46271</v>
       </c>
-      <c r="B23">
+      <c r="B24">
         <v>13</v>
       </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A24" s="1">
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
         <v>46270</v>
       </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-      <c r="C24">
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
         <v>90</v>
       </c>
-      <c r="D24">
+      <c r="D25">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A25" s="1">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
         <v>46269</v>
       </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A26" s="1">
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
         <v>46268</v>
       </c>
-      <c r="B26">
+      <c r="B27">
         <v>23</v>
       </c>
-      <c r="C26">
+      <c r="C27">
         <v>74</v>
       </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A27" s="1">
+      <c r="D27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
         <v>46267</v>
       </c>
-      <c r="B27">
+      <c r="B28">
         <v>7</v>
       </c>
-      <c r="C27">
+      <c r="C28">
         <v>75</v>
       </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A28" s="1">
+      <c r="D28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
         <v>46266</v>
       </c>
-      <c r="B28">
+      <c r="B29">
         <v>17</v>
       </c>
-      <c r="C28">
-        <v>0</v>
-      </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A29" s="1">
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
         <v>46265</v>
       </c>
-      <c r="C29">
+      <c r="C30">
         <v>62</v>
       </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A30" s="1">
+      <c r="D30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
         <v>46264</v>
       </c>
-      <c r="B30">
+      <c r="B31">
         <v>5</v>
       </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A31" s="1">
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
         <v>46263</v>
       </c>
-      <c r="B31">
+      <c r="B32">
         <v>73</v>
       </c>
-      <c r="C31">
+      <c r="C32">
         <v>62</v>
       </c>
-      <c r="D31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A32" s="1">
+      <c r="D32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
         <v>46262</v>
       </c>
-      <c r="B32">
+      <c r="B33">
         <v>67</v>
       </c>
-      <c r="C32">
+      <c r="C33">
         <v>54</v>
       </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A33" s="1">
+      <c r="D33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
         <v>46261</v>
       </c>
-      <c r="B33">
+      <c r="B34">
         <v>29</v>
       </c>
-      <c r="C33">
+      <c r="C34">
         <v>64</v>
       </c>
-      <c r="D33">
+      <c r="D34">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A34" s="1">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
         <v>46260</v>
       </c>
-      <c r="B34">
+      <c r="B35">
         <v>85</v>
-      </c>
-      <c r="C34">
-        <v>62</v>
-      </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A35" s="1">
-        <v>46259</v>
-      </c>
-      <c r="B35">
-        <v>13</v>
       </c>
       <c r="C35">
         <v>62</v>
       </c>
       <c r="D35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B36">
+        <v>13</v>
+      </c>
+      <c r="C36">
+        <v>62</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
         <v>46258</v>
       </c>
-      <c r="B36">
+      <c r="B37">
         <v>18</v>
       </c>
-      <c r="C36">
+      <c r="C37">
         <v>56</v>
       </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A37" s="1">
+      <c r="D37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
         <v>46257</v>
       </c>
-      <c r="B37">
+      <c r="B38">
         <v>3</v>
       </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A38" s="1">
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
         <v>46256</v>
       </c>
-      <c r="B38">
+      <c r="B39">
         <v>69</v>
       </c>
-      <c r="C38">
+      <c r="C39">
         <v>53</v>
       </c>
-      <c r="D38">
+      <c r="D39">
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A39" s="1">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
         <v>46255</v>
       </c>
-      <c r="B39">
+      <c r="B40">
         <v>15</v>
       </c>
-      <c r="C39">
+      <c r="C40">
         <v>60</v>
       </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A40" s="1">
+      <c r="D40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
         <v>46254</v>
       </c>
-      <c r="B40">
+      <c r="B41">
         <v>48</v>
       </c>
-      <c r="C40">
+      <c r="C41">
         <v>43</v>
       </c>
-      <c r="D40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A41" s="1">
+      <c r="D41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
         <v>46253</v>
       </c>
-      <c r="B41">
+      <c r="B42">
         <v>27</v>
       </c>
-      <c r="C41">
+      <c r="C42">
         <v>51</v>
       </c>
-      <c r="D41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A42" s="1">
+      <c r="D42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
         <v>46252</v>
       </c>
-      <c r="B42">
-        <v>0</v>
-      </c>
-      <c r="C42">
-        <v>0</v>
-      </c>
-      <c r="D42">
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A43" s="1">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
         <v>46251</v>
-      </c>
-      <c r="B43">
-        <v>12</v>
-      </c>
-      <c r="C43">
-        <v>0</v>
-      </c>
-      <c r="D43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A44" s="1">
-        <v>46250</v>
       </c>
       <c r="B44">
         <v>12</v>
@@ -1158,166 +1158,180 @@
       <c r="C44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="D44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
+        <v>46250</v>
+      </c>
+      <c r="B45">
+        <v>12</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
         <v>46249</v>
       </c>
-      <c r="C45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A46" s="1">
+      <c r="C46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
         <v>46248</v>
       </c>
-      <c r="B46">
+      <c r="B47">
         <v>7</v>
       </c>
-      <c r="C46">
+      <c r="C47">
         <v>16</v>
       </c>
-      <c r="D46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A47" s="1">
+      <c r="D47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
         <v>46247</v>
       </c>
-      <c r="B47">
+      <c r="B48">
         <v>35</v>
-      </c>
-      <c r="C47">
-        <v>21</v>
-      </c>
-      <c r="D47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A48" s="1">
-        <v>46246</v>
-      </c>
-      <c r="B48">
-        <v>28</v>
       </c>
       <c r="C48">
         <v>21</v>
       </c>
       <c r="D48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B49">
+        <v>28</v>
+      </c>
+      <c r="C49">
+        <v>21</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
         <v>46245</v>
       </c>
-      <c r="B49">
+      <c r="B50">
         <v>21</v>
       </c>
-      <c r="C49">
+      <c r="C50">
         <v>25</v>
       </c>
-      <c r="D49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A50" s="1">
+      <c r="D50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
         <v>46244</v>
       </c>
-      <c r="B50">
+      <c r="B51">
         <v>19</v>
       </c>
-      <c r="C50">
+      <c r="C51">
         <v>11</v>
       </c>
-      <c r="D50">
+      <c r="D51">
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A51" s="1">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
         <v>46243</v>
       </c>
-      <c r="B51">
+      <c r="B52">
         <v>13</v>
       </c>
-      <c r="C51">
-        <v>0</v>
-      </c>
-      <c r="D51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A52" s="1">
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
         <v>46242</v>
       </c>
-      <c r="B52">
-        <v>0</v>
-      </c>
-      <c r="C52">
-        <v>0</v>
-      </c>
-      <c r="D52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A53" s="1">
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
         <v>46241</v>
       </c>
-      <c r="B53">
+      <c r="B54">
         <v>32</v>
       </c>
-      <c r="C53">
-        <v>0</v>
-      </c>
-      <c r="D53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A54" s="1">
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
         <v>46240</v>
       </c>
-      <c r="B54">
+      <c r="B55">
         <v>16</v>
       </c>
-      <c r="C54">
-        <v>0</v>
-      </c>
-      <c r="D54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A55" s="1">
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
         <v>46239</v>
       </c>
-      <c r="B55">
-        <v>0</v>
-      </c>
-      <c r="C55">
-        <v>0</v>
-      </c>
-      <c r="D55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A56" s="1">
+      <c r="B56">
+        <v>0</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
         <v>46238</v>
       </c>
-      <c r="B56">
-        <v>0</v>
-      </c>
-      <c r="C56">
-        <v>0</v>
-      </c>
-      <c r="D56">
+      <c r="B57">
+        <v>0</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="D57">
         <v>1</v>
       </c>
     </row>
@@ -1329,55 +1343,55 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E384ED-EF07-4058-B570-9E7F8CBFADFB}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A2" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A3" t="s">
+      <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A4" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>15</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A5" t="s">
-        <v>17</v>
       </c>
       <c r="B5" s="1">
         <v>46326</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1">
         <v>46361</v>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="559" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDB75462-DD27-42B3-9E95-DC27F3ED0E50}"/>
+  <xr:revisionPtr revIDLastSave="589" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4870BB39-A5A6-4C10-A757-CC26B588E8F6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>
@@ -52,12 +52,21 @@
     <t>ACC</t>
   </si>
   <si>
+    <t>Daily- 43; June - 1229; July - 832; Aug - 642; Sep- 622 MT; Total - 4115 MT</t>
+  </si>
+  <si>
     <t>Boiler</t>
   </si>
   <si>
+    <t>Daily- 139 - (SH-93 and RH-46); Sep-2023 NDHT Balance joints - 10214 (SH - 5670; RH - 4544)</t>
+  </si>
+  <si>
     <t>PCP Joint</t>
   </si>
   <si>
+    <t>Daily-0; MS Joints - 63/146; MS to PRDS - 9/26; HRH - 10/95; CRH -14/87; LPBP - 8/49; HPBP-8/23; BFD- 167/661</t>
+  </si>
+  <si>
     <t>Boiler - NDHT Joints</t>
   </si>
   <si>
@@ -82,22 +91,13 @@
     <t>Segment-3</t>
   </si>
   <si>
-    <t>30-09-2026 (10/11 flue cans assembled)</t>
+    <t>05-10-2026 (10/11 flue cans assembled)</t>
   </si>
   <si>
     <t>Segment-4</t>
   </si>
   <si>
     <t>Segment-5</t>
-  </si>
-  <si>
-    <t>Daily- 0 - (SH-0 and RH-0); Sep-1770 NDHT Balance joints - 10467 (SH - 5847; RH - 4620)</t>
-  </si>
-  <si>
-    <t>Daily- 43; June - 1229; July - 832; Aug - 642; Sep- 622 MT; Total - 4115 MT</t>
-  </si>
-  <si>
-    <t>Daily-4; MS Joints - 63/146; MS to PRDS - 9/26; HRH - 10/95; CRH -14/87; LPBP - 7/49; HPBP-8/23; BFD- 163/661</t>
   </si>
 </sst>
 </file>
@@ -482,13 +482,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="93" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -499,37 +499,37 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A2" s="1">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A3" s="1">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A4" s="1">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -542,14 +542,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
-  <dimension ref="A1:D57"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D61"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -557,15 +557,15 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>30</v>
@@ -577,471 +577,459 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A3" s="1">
+        <v>46298</v>
+      </c>
+      <c r="C3">
+        <v>65</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A4" s="1">
+        <v>46296</v>
+      </c>
+      <c r="C4">
+        <v>101</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A5" s="1">
+        <v>46295</v>
+      </c>
+      <c r="C5">
+        <v>139</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A6" s="1">
+        <v>46294</v>
+      </c>
+      <c r="C6">
+        <v>114</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A7" s="1">
         <v>46293</v>
       </c>
-      <c r="B3">
+      <c r="B7">
         <v>43</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A8" s="1">
         <v>46292</v>
       </c>
-      <c r="B4">
+      <c r="B8">
         <v>13</v>
       </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A9" s="1">
         <v>46291</v>
       </c>
-      <c r="B5">
+      <c r="B9">
         <v>17</v>
       </c>
-      <c r="C5">
+      <c r="C9">
         <v>39</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+      <c r="D9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A10" s="1">
         <v>46290</v>
       </c>
-      <c r="B6">
+      <c r="B10">
         <v>20</v>
       </c>
-      <c r="C6">
+      <c r="C10">
         <v>121</v>
       </c>
-      <c r="D6">
+      <c r="D10">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A11" s="1">
         <v>46289</v>
       </c>
-      <c r="B7">
+      <c r="B11">
         <v>3</v>
       </c>
-      <c r="C7">
+      <c r="C11">
         <v>133</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+      <c r="D11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A12" s="1">
         <v>46288</v>
       </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
         <v>143</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+      <c r="D12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A13" s="1">
         <v>46287</v>
       </c>
-      <c r="B9">
+      <c r="B13">
         <v>9</v>
       </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A14" s="1">
         <v>46286</v>
       </c>
-      <c r="B10">
+      <c r="B14">
         <v>32</v>
       </c>
-      <c r="C10">
+      <c r="C14">
         <v>131</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+      <c r="D14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A15" s="1">
         <v>46285</v>
       </c>
-      <c r="B11">
+      <c r="B15">
         <v>42</v>
       </c>
-      <c r="C11">
+      <c r="C15">
         <v>111</v>
       </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+      <c r="D15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A16" s="1">
         <v>46284</v>
       </c>
-      <c r="B12">
+      <c r="B16">
         <v>16</v>
       </c>
-      <c r="C12">
+      <c r="C16">
         <v>118</v>
       </c>
-      <c r="D12">
+      <c r="D16">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A17" s="1">
         <v>46283</v>
       </c>
-      <c r="B13">
+      <c r="B17">
         <v>16</v>
       </c>
-      <c r="C13">
+      <c r="C17">
         <v>118</v>
       </c>
-      <c r="D13">
+      <c r="D17">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A18" s="1">
         <v>46281</v>
       </c>
-      <c r="B14">
+      <c r="B18">
         <v>33</v>
       </c>
-      <c r="C14">
+      <c r="C18">
         <v>98</v>
       </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+      <c r="D18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A19" s="1">
         <v>46280</v>
       </c>
-      <c r="B15">
+      <c r="B19">
         <v>3</v>
       </c>
-      <c r="C15">
+      <c r="C19">
         <v>125</v>
       </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+      <c r="D19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A20" s="1">
         <v>46279</v>
       </c>
-      <c r="B16">
+      <c r="B20">
         <v>58</v>
       </c>
-      <c r="C16">
+      <c r="C20">
         <v>100</v>
       </c>
-      <c r="D16">
+      <c r="D20">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A21" s="1">
         <v>46278</v>
       </c>
-      <c r="B17">
+      <c r="B21">
         <v>3</v>
       </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A22" s="1">
         <v>46277</v>
       </c>
-      <c r="B18">
+      <c r="B22">
         <v>63</v>
       </c>
-      <c r="C18">
+      <c r="C22">
         <v>42</v>
       </c>
-      <c r="D18">
+      <c r="D22">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A23" s="1">
         <v>46276</v>
       </c>
-      <c r="B19">
+      <c r="B23">
         <v>19</v>
       </c>
-      <c r="C19">
+      <c r="C23">
         <v>73</v>
       </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+      <c r="D23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A24" s="1">
         <v>46275</v>
       </c>
-      <c r="B20">
+      <c r="B24">
         <v>21</v>
       </c>
-      <c r="C20">
+      <c r="C24">
         <v>16</v>
       </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+      <c r="D24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A25" s="1">
         <v>46274</v>
       </c>
-      <c r="B21">
+      <c r="B25">
         <v>47</v>
       </c>
-      <c r="C21">
+      <c r="C25">
         <v>84</v>
       </c>
-      <c r="D21">
+      <c r="D25">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A26" s="1">
         <v>46273</v>
       </c>
-      <c r="B22">
+      <c r="B26">
         <v>45</v>
       </c>
-      <c r="C22">
+      <c r="C26">
         <v>105</v>
       </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+      <c r="D26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A27" s="1">
         <v>46272</v>
       </c>
-      <c r="B23">
+      <c r="B27">
         <v>38</v>
       </c>
-      <c r="C23">
+      <c r="C27">
         <v>92</v>
       </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+      <c r="D27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A28" s="1">
         <v>46271</v>
       </c>
-      <c r="B24">
+      <c r="B28">
         <v>13</v>
       </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A29" s="1">
         <v>46270</v>
       </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="C25">
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29">
         <v>90</v>
       </c>
-      <c r="D25">
+      <c r="D29">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A30" s="1">
         <v>46269</v>
       </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A31" s="1">
         <v>46268</v>
       </c>
-      <c r="B27">
+      <c r="B31">
         <v>23</v>
       </c>
-      <c r="C27">
+      <c r="C31">
         <v>74</v>
       </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+      <c r="D31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A32" s="1">
         <v>46267</v>
       </c>
-      <c r="B28">
+      <c r="B32">
         <v>7</v>
       </c>
-      <c r="C28">
+      <c r="C32">
         <v>75</v>
       </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+      <c r="D32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A33" s="1">
         <v>46266</v>
       </c>
-      <c r="B29">
+      <c r="B33">
         <v>17</v>
       </c>
-      <c r="C29">
-        <v>0</v>
-      </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A34" s="1">
         <v>46265</v>
       </c>
-      <c r="C30">
+      <c r="C34">
         <v>62</v>
       </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+      <c r="D34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A35" s="1">
         <v>46264</v>
       </c>
-      <c r="B31">
+      <c r="B35">
         <v>5</v>
       </c>
-      <c r="C31">
-        <v>0</v>
-      </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A36" s="1">
         <v>46263</v>
       </c>
-      <c r="B32">
+      <c r="B36">
         <v>73</v>
-      </c>
-      <c r="C32">
-        <v>62</v>
-      </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
-        <v>46262</v>
-      </c>
-      <c r="B33">
-        <v>67</v>
-      </c>
-      <c r="C33">
-        <v>54</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
-        <v>46261</v>
-      </c>
-      <c r="B34">
-        <v>29</v>
-      </c>
-      <c r="C34">
-        <v>64</v>
-      </c>
-      <c r="D34">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
-        <v>46260</v>
-      </c>
-      <c r="B35">
-        <v>85</v>
-      </c>
-      <c r="C35">
-        <v>62</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
-        <v>46259</v>
-      </c>
-      <c r="B36">
-        <v>13</v>
       </c>
       <c r="C36">
         <v>62</v>
@@ -1050,288 +1038,344 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A37" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B37">
+        <v>67</v>
+      </c>
+      <c r="C37">
+        <v>54</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A38" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B38">
+        <v>29</v>
+      </c>
+      <c r="C38">
+        <v>64</v>
+      </c>
+      <c r="D38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A39" s="1">
+        <v>46260</v>
+      </c>
+      <c r="B39">
+        <v>85</v>
+      </c>
+      <c r="C39">
+        <v>62</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A40" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B40">
+        <v>13</v>
+      </c>
+      <c r="C40">
+        <v>62</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A41" s="1">
         <v>46258</v>
       </c>
-      <c r="B37">
+      <c r="B41">
         <v>18</v>
       </c>
-      <c r="C37">
+      <c r="C41">
         <v>56</v>
       </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
+      <c r="D41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A42" s="1">
         <v>46257</v>
       </c>
-      <c r="B38">
+      <c r="B42">
         <v>3</v>
       </c>
-      <c r="C38">
-        <v>0</v>
-      </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A43" s="1">
         <v>46256</v>
       </c>
-      <c r="B39">
+      <c r="B43">
         <v>69</v>
       </c>
-      <c r="C39">
+      <c r="C43">
         <v>53</v>
       </c>
-      <c r="D39">
+      <c r="D43">
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A44" s="1">
         <v>46255</v>
       </c>
-      <c r="B40">
+      <c r="B44">
         <v>15</v>
       </c>
-      <c r="C40">
+      <c r="C44">
         <v>60</v>
       </c>
-      <c r="D40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
+      <c r="D44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A45" s="1">
         <v>46254</v>
       </c>
-      <c r="B41">
+      <c r="B45">
         <v>48</v>
       </c>
-      <c r="C41">
+      <c r="C45">
         <v>43</v>
       </c>
-      <c r="D41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
+      <c r="D45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A46" s="1">
         <v>46253</v>
       </c>
-      <c r="B42">
+      <c r="B46">
         <v>27</v>
       </c>
-      <c r="C42">
+      <c r="C46">
         <v>51</v>
       </c>
-      <c r="D42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
+      <c r="D46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A47" s="1">
         <v>46252</v>
       </c>
-      <c r="B43">
-        <v>0</v>
-      </c>
-      <c r="C43">
-        <v>0</v>
-      </c>
-      <c r="D43">
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A48" s="1">
         <v>46251</v>
       </c>
-      <c r="B44">
+      <c r="B48">
         <v>12</v>
       </c>
-      <c r="C44">
-        <v>0</v>
-      </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="1">
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A49" s="1">
         <v>46250</v>
       </c>
-      <c r="B45">
+      <c r="B49">
         <v>12</v>
       </c>
-      <c r="C45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
+      <c r="C49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A50" s="1">
         <v>46249</v>
       </c>
-      <c r="C46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
+      <c r="C50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A51" s="1">
         <v>46248</v>
       </c>
-      <c r="B47">
+      <c r="B51">
         <v>7</v>
       </c>
-      <c r="C47">
+      <c r="C51">
         <v>16</v>
       </c>
-      <c r="D47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
+      <c r="D51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A52" s="1">
         <v>46247</v>
       </c>
-      <c r="B48">
+      <c r="B52">
         <v>35</v>
       </c>
-      <c r="C48">
+      <c r="C52">
         <v>21</v>
       </c>
-      <c r="D48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="1">
+      <c r="D52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A53" s="1">
         <v>46246</v>
       </c>
-      <c r="B49">
+      <c r="B53">
         <v>28</v>
       </c>
-      <c r="C49">
+      <c r="C53">
         <v>21</v>
       </c>
-      <c r="D49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
+      <c r="D53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A54" s="1">
         <v>46245</v>
       </c>
-      <c r="B50">
+      <c r="B54">
         <v>21</v>
       </c>
-      <c r="C50">
+      <c r="C54">
         <v>25</v>
       </c>
-      <c r="D50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
+      <c r="D54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A55" s="1">
         <v>46244</v>
       </c>
-      <c r="B51">
+      <c r="B55">
         <v>19</v>
       </c>
-      <c r="C51">
+      <c r="C55">
         <v>11</v>
       </c>
-      <c r="D51">
+      <c r="D55">
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A56" s="1">
         <v>46243</v>
       </c>
-      <c r="B52">
+      <c r="B56">
         <v>13</v>
       </c>
-      <c r="C52">
-        <v>0</v>
-      </c>
-      <c r="D52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A57" s="1">
         <v>46242</v>
       </c>
-      <c r="B53">
-        <v>0</v>
-      </c>
-      <c r="C53">
-        <v>0</v>
-      </c>
-      <c r="D53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="1">
+      <c r="B57">
+        <v>0</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A58" s="1">
         <v>46241</v>
       </c>
-      <c r="B54">
+      <c r="B58">
         <v>32</v>
       </c>
-      <c r="C54">
-        <v>0</v>
-      </c>
-      <c r="D54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="1">
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A59" s="1">
         <v>46240</v>
       </c>
-      <c r="B55">
+      <c r="B59">
         <v>16</v>
       </c>
-      <c r="C55">
-        <v>0</v>
-      </c>
-      <c r="D55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A60" s="1">
         <v>46239</v>
       </c>
-      <c r="B56">
-        <v>0</v>
-      </c>
-      <c r="C56">
-        <v>0</v>
-      </c>
-      <c r="D56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
+      <c r="B60">
+        <v>0</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A61" s="1">
         <v>46238</v>
       </c>
-      <c r="B57">
-        <v>0</v>
-      </c>
-      <c r="C57">
-        <v>0</v>
-      </c>
-      <c r="D57">
+      <c r="B61">
+        <v>0</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
         <v>1</v>
       </c>
     </row>
@@ -1343,55 +1387,55 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E384ED-EF07-4058-B570-9E7F8CBFADFB}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="9.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B5" s="1">
         <v>46326</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B6" s="1">
         <v>46361</v>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="589" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4870BB39-A5A6-4C10-A757-CC26B588E8F6}"/>
+  <xr:revisionPtr revIDLastSave="612" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B16A8FCE-9740-4E02-A37C-543C44DB948E}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>
@@ -52,15 +52,9 @@
     <t>ACC</t>
   </si>
   <si>
-    <t>Daily- 43; June - 1229; July - 832; Aug - 642; Sep- 622 MT; Total - 4115 MT</t>
-  </si>
-  <si>
     <t>Boiler</t>
   </si>
   <si>
-    <t>Daily- 139 - (SH-93 and RH-46); Sep-2023 NDHT Balance joints - 10214 (SH - 5670; RH - 4544)</t>
-  </si>
-  <si>
     <t>PCP Joint</t>
   </si>
   <si>
@@ -98,6 +92,12 @@
   </si>
   <si>
     <t>Segment-5</t>
+  </si>
+  <si>
+    <t>Daily- 66; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Total - 4722 MT</t>
+  </si>
+  <si>
+    <t>Daily- 0 - (SH-0 and RH-0); Oct-166 NDHT Balance joints - 10048 (SH - 5548; RH - 4500)</t>
   </si>
 </sst>
 </file>
@@ -501,35 +501,35 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A2" s="1">
-        <v>46295</v>
+        <v>46299</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A3" s="1">
-        <v>46295</v>
+        <v>46299</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A4" s="1">
-        <v>46295</v>
+        <v>46299</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -542,7 +542,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -557,15 +557,15 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>30</v>
@@ -579,21 +579,27 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A3" s="1">
-        <v>46298</v>
+        <v>46299</v>
+      </c>
+      <c r="B3">
+        <v>66</v>
       </c>
       <c r="C3">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A4" s="1">
-        <v>46296</v>
+        <v>46298</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -601,10 +607,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A5" s="1">
-        <v>46295</v>
+        <v>46297</v>
+      </c>
+      <c r="B5">
+        <v>40</v>
       </c>
       <c r="C5">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -612,10 +621,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A6" s="1">
-        <v>46294</v>
+        <v>46296</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -623,97 +635,97 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A7" s="1">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="B7">
-        <v>43</v>
+        <v>321</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A8" s="1">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="B8">
-        <v>13</v>
+        <v>200</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A9" s="1">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="B9">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C9">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A10" s="1">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="B10">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C10">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A11" s="1">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C11">
-        <v>133</v>
+        <v>39</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A12" s="1">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C12">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A13" s="1">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B13">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -721,125 +733,125 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A14" s="1">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="B14">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A15" s="1">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="B15">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C15">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A16" s="1">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="B16">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C16">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A17" s="1">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="B17">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C17">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D17">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A18" s="1">
-        <v>46281</v>
+        <v>46284</v>
       </c>
       <c r="B18">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C18">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A19" s="1">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C19">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A20" s="1">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="B20">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C20">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A21" s="1">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="B21">
         <v>3</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A22" s="1">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="B22">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C22">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="D22">
         <v>2</v>
@@ -847,55 +859,55 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A23" s="1">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="B23">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C23">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A24" s="1">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B24">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="C24">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A25" s="1">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B25">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="C25">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A26" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B26">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="C26">
-        <v>105</v>
+        <v>16</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -903,52 +915,52 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A27" s="1">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="B27">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C27">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A28" s="1">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="B28">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A29" s="1">
-        <v>46270</v>
+        <v>46272</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C29">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A30" s="1">
-        <v>46269</v>
+        <v>46271</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -959,52 +971,55 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A31" s="1">
-        <v>46268</v>
+        <v>46270</v>
       </c>
       <c r="B31">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A32" s="1">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B32">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A33" s="1">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B33">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A34" s="1">
-        <v>46265</v>
+        <v>46267</v>
+      </c>
+      <c r="B34">
+        <v>7</v>
       </c>
       <c r="C34">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1012,24 +1027,21 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A35" s="1">
-        <v>46264</v>
+        <v>46266</v>
       </c>
       <c r="B35">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A36" s="1">
-        <v>46263</v>
-      </c>
-      <c r="B36">
-        <v>73</v>
+        <v>46265</v>
       </c>
       <c r="C36">
         <v>62</v>
@@ -1040,13 +1052,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A37" s="1">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="B37">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="C37">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -1054,27 +1066,27 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A38" s="1">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="B38">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="C38">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D38">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A39" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B39">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="C39">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -1082,97 +1094,97 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A40" s="1">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B40">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C40">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A41" s="1">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B41">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="C41">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A42" s="1">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A43" s="1">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="B43">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="C43">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A44" s="1">
-        <v>46255</v>
+        <v>46257</v>
       </c>
       <c r="B44">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C44">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A45" s="1">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="B45">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="C45">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A46" s="1">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B46">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C46">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -1180,27 +1192,27 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A47" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A48" s="1">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B48">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -1208,74 +1220,74 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A49" s="1">
-        <v>46250</v>
+        <v>46252</v>
       </c>
       <c r="B49">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C49">
         <v>0</v>
+      </c>
+      <c r="D49">
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A50" s="1">
-        <v>46249</v>
+        <v>46251</v>
+      </c>
+      <c r="B50">
+        <v>12</v>
       </c>
       <c r="C50">
         <v>0</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A51" s="1">
-        <v>46248</v>
+        <v>46250</v>
       </c>
       <c r="B51">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C51">
-        <v>16</v>
-      </c>
-      <c r="D51">
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A52" s="1">
-        <v>46247</v>
-      </c>
-      <c r="B52">
-        <v>35</v>
+        <v>46249</v>
       </c>
       <c r="C52">
-        <v>21</v>
-      </c>
-      <c r="D52">
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A53" s="1">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B53">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C53">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A54" s="1">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B54">
+        <v>35</v>
+      </c>
+      <c r="C54">
         <v>21</v>
-      </c>
-      <c r="C54">
-        <v>25</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -1283,27 +1295,27 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A55" s="1">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B55">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C55">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D55">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A56" s="1">
-        <v>46243</v>
+        <v>46245</v>
       </c>
       <c r="B56">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -1311,24 +1323,24 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A57" s="1">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A58" s="1">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B58">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -1339,10 +1351,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A59" s="1">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="B59">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -1353,29 +1365,57 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A60" s="1">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A61" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B61">
+        <v>16</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A62" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B62">
+        <v>0</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A63" s="1">
         <v>46238</v>
       </c>
-      <c r="B61">
-        <v>0</v>
-      </c>
-      <c r="C61">
-        <v>0</v>
-      </c>
-      <c r="D61">
+      <c r="B63">
+        <v>0</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
         <v>1</v>
       </c>
     </row>
@@ -1395,7 +1435,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1403,31 +1443,31 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1">
         <v>46326</v>
@@ -1435,7 +1475,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1">
         <v>46361</v>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="612" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B16A8FCE-9740-4E02-A37C-543C44DB948E}"/>
+  <xr:revisionPtr revIDLastSave="634" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABF478E2-1D2E-40AB-BC15-796985F67F20}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>
@@ -58,9 +58,6 @@
     <t>PCP Joint</t>
   </si>
   <si>
-    <t>Daily-0; MS Joints - 63/146; MS to PRDS - 9/26; HRH - 10/95; CRH -14/87; LPBP - 8/49; HPBP-8/23; BFD- 167/661</t>
-  </si>
-  <si>
     <t>Boiler - NDHT Joints</t>
   </si>
   <si>
@@ -94,10 +91,13 @@
     <t>Segment-5</t>
   </si>
   <si>
-    <t>Daily- 66; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Total - 4722 MT</t>
-  </si>
-  <si>
-    <t>Daily- 0 - (SH-0 and RH-0); Oct-166 NDHT Balance joints - 10048 (SH - 5548; RH - 4500)</t>
+    <t>Daily- 65; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 211 ;Total - 4826 MT</t>
+  </si>
+  <si>
+    <t>Daily-123  - (SH-89 and RH-34); Oct-289 NDHT Balance joints - 9925 (SH - 5459; RH - 4466)</t>
+  </si>
+  <si>
+    <t>Daily-2; MS Joints - 65/146; MS to PRDS - 9/26; HRH - 10/95; CRH -14/87; LPBP - 8/49; HPBP-8/23; BFD- 169/661</t>
   </si>
 </sst>
 </file>
@@ -482,13 +482,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="93" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -499,37 +499,37 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -542,14 +542,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
-  <dimension ref="A1:D63"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:D64"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -557,15 +557,15 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A2" t="s">
-        <v>9</v>
       </c>
       <c r="B2">
         <v>30</v>
@@ -577,233 +577,233 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B3">
+        <v>65</v>
+      </c>
+      <c r="C3">
+        <v>123</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>46299</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>66</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A4" s="1">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>46298</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>65</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A5" s="1">
-        <v>46297</v>
       </c>
       <c r="B5">
         <v>40</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>46296</v>
       </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
+      <c r="B7">
+        <v>40</v>
+      </c>
+      <c r="C7">
         <v>101</v>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A7" s="1">
+      <c r="D7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>46295</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>321</v>
       </c>
-      <c r="C7">
+      <c r="C8">
         <v>139</v>
       </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A8" s="1">
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>46294</v>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>200</v>
       </c>
-      <c r="C8">
+      <c r="C9">
         <v>114</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A9" s="1">
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>46293</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>43</v>
       </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A10" s="1">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>46292</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>13</v>
       </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A11" s="1">
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>46291</v>
       </c>
-      <c r="B11">
+      <c r="B12">
         <v>17</v>
       </c>
-      <c r="C11">
+      <c r="C12">
         <v>39</v>
       </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A12" s="1">
+      <c r="D12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>46290</v>
       </c>
-      <c r="B12">
+      <c r="B13">
         <v>20</v>
       </c>
-      <c r="C12">
+      <c r="C13">
         <v>121</v>
       </c>
-      <c r="D12">
+      <c r="D13">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A13" s="1">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>46289</v>
       </c>
-      <c r="B13">
+      <c r="B14">
         <v>3</v>
       </c>
-      <c r="C13">
+      <c r="C14">
         <v>133</v>
       </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A14" s="1">
+      <c r="D14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>46288</v>
       </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14">
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
         <v>143</v>
       </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A15" s="1">
+      <c r="D15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>46287</v>
       </c>
-      <c r="B15">
+      <c r="B16">
         <v>9</v>
       </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A16" s="1">
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
         <v>46286</v>
       </c>
-      <c r="B16">
+      <c r="B17">
         <v>32</v>
       </c>
-      <c r="C16">
+      <c r="C17">
         <v>131</v>
       </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A17" s="1">
+      <c r="D17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>46285</v>
       </c>
-      <c r="B17">
+      <c r="B18">
         <v>42</v>
       </c>
-      <c r="C17">
+      <c r="C18">
         <v>111</v>
       </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A18" s="1">
+      <c r="D18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>46284</v>
-      </c>
-      <c r="B18">
-        <v>16</v>
-      </c>
-      <c r="C18">
-        <v>118</v>
-      </c>
-      <c r="D18">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A19" s="1">
-        <v>46283</v>
       </c>
       <c r="B19">
         <v>16</v>
@@ -815,440 +815,440 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B20">
+        <v>16</v>
+      </c>
+      <c r="C20">
+        <v>118</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
         <v>46281</v>
       </c>
-      <c r="B20">
+      <c r="B21">
         <v>33</v>
       </c>
-      <c r="C20">
+      <c r="C21">
         <v>98</v>
       </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A21" s="1">
+      <c r="D21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
         <v>46280</v>
       </c>
-      <c r="B21">
+      <c r="B22">
         <v>3</v>
       </c>
-      <c r="C21">
+      <c r="C22">
         <v>125</v>
       </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A22" s="1">
+      <c r="D22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
         <v>46279</v>
       </c>
-      <c r="B22">
+      <c r="B23">
         <v>58</v>
       </c>
-      <c r="C22">
+      <c r="C23">
         <v>100</v>
       </c>
-      <c r="D22">
+      <c r="D23">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A23" s="1">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
         <v>46278</v>
       </c>
-      <c r="B23">
+      <c r="B24">
         <v>3</v>
       </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A24" s="1">
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
         <v>46277</v>
       </c>
-      <c r="B24">
+      <c r="B25">
         <v>63</v>
       </c>
-      <c r="C24">
+      <c r="C25">
         <v>42</v>
       </c>
-      <c r="D24">
+      <c r="D25">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A25" s="1">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
         <v>46276</v>
       </c>
-      <c r="B25">
+      <c r="B26">
         <v>19</v>
       </c>
-      <c r="C25">
+      <c r="C26">
         <v>73</v>
       </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A26" s="1">
+      <c r="D26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
         <v>46275</v>
       </c>
-      <c r="B26">
+      <c r="B27">
         <v>21</v>
       </c>
-      <c r="C26">
+      <c r="C27">
         <v>16</v>
       </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A27" s="1">
+      <c r="D27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
         <v>46274</v>
       </c>
-      <c r="B27">
+      <c r="B28">
         <v>47</v>
       </c>
-      <c r="C27">
+      <c r="C28">
         <v>84</v>
       </c>
-      <c r="D27">
+      <c r="D28">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A28" s="1">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
         <v>46273</v>
       </c>
-      <c r="B28">
+      <c r="B29">
         <v>45</v>
       </c>
-      <c r="C28">
+      <c r="C29">
         <v>105</v>
       </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A29" s="1">
+      <c r="D29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
         <v>46272</v>
       </c>
-      <c r="B29">
+      <c r="B30">
         <v>38</v>
       </c>
-      <c r="C29">
+      <c r="C30">
         <v>92</v>
       </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A30" s="1">
+      <c r="D30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
         <v>46271</v>
       </c>
-      <c r="B30">
+      <c r="B31">
         <v>13</v>
       </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A31" s="1">
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
         <v>46270</v>
       </c>
-      <c r="B31">
-        <v>0</v>
-      </c>
-      <c r="C31">
+      <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32">
         <v>90</v>
       </c>
-      <c r="D31">
+      <c r="D32">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A32" s="1">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
         <v>46269</v>
       </c>
-      <c r="B32">
-        <v>0</v>
-      </c>
-      <c r="C32">
-        <v>0</v>
-      </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A33" s="1">
+      <c r="B33">
+        <v>0</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
         <v>46268</v>
       </c>
-      <c r="B33">
+      <c r="B34">
         <v>23</v>
       </c>
-      <c r="C33">
+      <c r="C34">
         <v>74</v>
       </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A34" s="1">
+      <c r="D34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
         <v>46267</v>
       </c>
-      <c r="B34">
+      <c r="B35">
         <v>7</v>
       </c>
-      <c r="C34">
+      <c r="C35">
         <v>75</v>
       </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A35" s="1">
+      <c r="D35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
         <v>46266</v>
       </c>
-      <c r="B35">
+      <c r="B36">
         <v>17</v>
       </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A36" s="1">
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
         <v>46265</v>
       </c>
-      <c r="C36">
+      <c r="C37">
         <v>62</v>
       </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A37" s="1">
+      <c r="D37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
         <v>46264</v>
       </c>
-      <c r="B37">
+      <c r="B38">
         <v>5</v>
       </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A38" s="1">
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
         <v>46263</v>
       </c>
-      <c r="B38">
+      <c r="B39">
         <v>73</v>
       </c>
-      <c r="C38">
+      <c r="C39">
         <v>62</v>
       </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A39" s="1">
+      <c r="D39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
         <v>46262</v>
       </c>
-      <c r="B39">
+      <c r="B40">
         <v>67</v>
       </c>
-      <c r="C39">
+      <c r="C40">
         <v>54</v>
       </c>
-      <c r="D39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A40" s="1">
+      <c r="D40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
         <v>46261</v>
       </c>
-      <c r="B40">
+      <c r="B41">
         <v>29</v>
       </c>
-      <c r="C40">
+      <c r="C41">
         <v>64</v>
       </c>
-      <c r="D40">
+      <c r="D41">
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A41" s="1">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
         <v>46260</v>
       </c>
-      <c r="B41">
+      <c r="B42">
         <v>85</v>
-      </c>
-      <c r="C41">
-        <v>62</v>
-      </c>
-      <c r="D41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A42" s="1">
-        <v>46259</v>
-      </c>
-      <c r="B42">
-        <v>13</v>
       </c>
       <c r="C42">
         <v>62</v>
       </c>
       <c r="D42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B43">
+        <v>13</v>
+      </c>
+      <c r="C43">
+        <v>62</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
         <v>46258</v>
       </c>
-      <c r="B43">
+      <c r="B44">
         <v>18</v>
       </c>
-      <c r="C43">
+      <c r="C44">
         <v>56</v>
       </c>
-      <c r="D43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A44" s="1">
+      <c r="D44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
         <v>46257</v>
       </c>
-      <c r="B44">
+      <c r="B45">
         <v>3</v>
       </c>
-      <c r="C44">
-        <v>0</v>
-      </c>
-      <c r="D44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A45" s="1">
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
         <v>46256</v>
       </c>
-      <c r="B45">
+      <c r="B46">
         <v>69</v>
       </c>
-      <c r="C45">
+      <c r="C46">
         <v>53</v>
       </c>
-      <c r="D45">
+      <c r="D46">
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A46" s="1">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
         <v>46255</v>
       </c>
-      <c r="B46">
+      <c r="B47">
         <v>15</v>
       </c>
-      <c r="C46">
+      <c r="C47">
         <v>60</v>
       </c>
-      <c r="D46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A47" s="1">
+      <c r="D47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
         <v>46254</v>
       </c>
-      <c r="B47">
+      <c r="B48">
         <v>48</v>
       </c>
-      <c r="C47">
+      <c r="C48">
         <v>43</v>
       </c>
-      <c r="D47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A48" s="1">
+      <c r="D48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
         <v>46253</v>
       </c>
-      <c r="B48">
+      <c r="B49">
         <v>27</v>
       </c>
-      <c r="C48">
+      <c r="C49">
         <v>51</v>
       </c>
-      <c r="D48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A49" s="1">
+      <c r="D49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
         <v>46252</v>
       </c>
-      <c r="B49">
-        <v>0</v>
-      </c>
-      <c r="C49">
-        <v>0</v>
-      </c>
-      <c r="D49">
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A50" s="1">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
         <v>46251</v>
-      </c>
-      <c r="B50">
-        <v>12</v>
-      </c>
-      <c r="C50">
-        <v>0</v>
-      </c>
-      <c r="D50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A51" s="1">
-        <v>46250</v>
       </c>
       <c r="B51">
         <v>12</v>
@@ -1256,166 +1256,180 @@
       <c r="C51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="D51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
+        <v>46250</v>
+      </c>
+      <c r="B52">
+        <v>12</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
         <v>46249</v>
       </c>
-      <c r="C52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A53" s="1">
+      <c r="C53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
         <v>46248</v>
       </c>
-      <c r="B53">
+      <c r="B54">
         <v>7</v>
       </c>
-      <c r="C53">
+      <c r="C54">
         <v>16</v>
       </c>
-      <c r="D53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A54" s="1">
+      <c r="D54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
         <v>46247</v>
       </c>
-      <c r="B54">
+      <c r="B55">
         <v>35</v>
-      </c>
-      <c r="C54">
-        <v>21</v>
-      </c>
-      <c r="D54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A55" s="1">
-        <v>46246</v>
-      </c>
-      <c r="B55">
-        <v>28</v>
       </c>
       <c r="C55">
         <v>21</v>
       </c>
       <c r="D55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B56">
+        <v>28</v>
+      </c>
+      <c r="C56">
+        <v>21</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
         <v>46245</v>
       </c>
-      <c r="B56">
+      <c r="B57">
         <v>21</v>
       </c>
-      <c r="C56">
+      <c r="C57">
         <v>25</v>
       </c>
-      <c r="D56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A57" s="1">
+      <c r="D57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
         <v>46244</v>
       </c>
-      <c r="B57">
+      <c r="B58">
         <v>19</v>
       </c>
-      <c r="C57">
+      <c r="C58">
         <v>11</v>
       </c>
-      <c r="D57">
+      <c r="D58">
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A58" s="1">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
         <v>46243</v>
       </c>
-      <c r="B58">
+      <c r="B59">
         <v>13</v>
       </c>
-      <c r="C58">
-        <v>0</v>
-      </c>
-      <c r="D58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A59" s="1">
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
         <v>46242</v>
       </c>
-      <c r="B59">
-        <v>0</v>
-      </c>
-      <c r="C59">
-        <v>0</v>
-      </c>
-      <c r="D59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A60" s="1">
+      <c r="B60">
+        <v>0</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
         <v>46241</v>
       </c>
-      <c r="B60">
+      <c r="B61">
         <v>32</v>
       </c>
-      <c r="C60">
-        <v>0</v>
-      </c>
-      <c r="D60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A61" s="1">
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
         <v>46240</v>
       </c>
-      <c r="B61">
+      <c r="B62">
         <v>16</v>
       </c>
-      <c r="C61">
-        <v>0</v>
-      </c>
-      <c r="D61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A62" s="1">
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
         <v>46239</v>
       </c>
-      <c r="B62">
-        <v>0</v>
-      </c>
-      <c r="C62">
-        <v>0</v>
-      </c>
-      <c r="D62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A63" s="1">
+      <c r="B63">
+        <v>0</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
         <v>46238</v>
       </c>
-      <c r="B63">
-        <v>0</v>
-      </c>
-      <c r="C63">
-        <v>0</v>
-      </c>
-      <c r="D63">
+      <c r="B64">
+        <v>0</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
         <v>1</v>
       </c>
     </row>
@@ -1427,55 +1441,55 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E384ED-EF07-4058-B570-9E7F8CBFADFB}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A4" t="s">
+      <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A5" t="s">
-        <v>16</v>
       </c>
       <c r="B5" s="1">
         <v>46326</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1">
         <v>46361</v>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="634" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABF478E2-1D2E-40AB-BC15-796985F67F20}"/>
+  <xr:revisionPtr revIDLastSave="664" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0F581D2-0B2B-4772-821E-3C497C13EB45}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t>Date</t>
   </si>
@@ -55,9 +55,15 @@
     <t>Boiler</t>
   </si>
   <si>
+    <t>Daily-104  - (SH-89 and RH-24); Oct-393NDHT Balance joints - 9821 (SH - 5379; RH - 4442)</t>
+  </si>
+  <si>
     <t>PCP Joint</t>
   </si>
   <si>
+    <t>Daily-4; MS Joints - 68/146; MS to PRDS - 9/26; HRH - 10/95; CRH -14/87; LPBP - 9/49; HPBP-8/23; BFD- 169/661</t>
+  </si>
+  <si>
     <t>Boiler - NDHT Joints</t>
   </si>
   <si>
@@ -82,22 +88,13 @@
     <t>Segment-3</t>
   </si>
   <si>
-    <t>05-10-2026 (10/11 flue cans assembled)</t>
-  </si>
-  <si>
     <t>Segment-4</t>
   </si>
   <si>
     <t>Segment-5</t>
   </si>
   <si>
-    <t>Daily- 65; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 211 ;Total - 4826 MT</t>
-  </si>
-  <si>
-    <t>Daily-123  - (SH-89 and RH-34); Oct-289 NDHT Balance joints - 9925 (SH - 5459; RH - 4466)</t>
-  </si>
-  <si>
-    <t>Daily-2; MS Joints - 65/146; MS to PRDS - 9/26; HRH - 10/95; CRH -14/87; LPBP - 8/49; HPBP-8/23; BFD- 169/661</t>
+    <t>Daily- 45; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 235 ;Total - 4851 MT</t>
   </si>
 </sst>
 </file>
@@ -501,35 +498,35 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -542,7 +539,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -557,15 +554,15 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>30</v>
@@ -579,139 +576,139 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B3">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="C3">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B4">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B5">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C5">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B7">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B8">
-        <v>321</v>
+        <v>40</v>
       </c>
       <c r="C8">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B9">
-        <v>200</v>
+        <v>321</v>
       </c>
       <c r="C9">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B10">
-        <v>43</v>
+        <v>200</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B11">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B12">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C12">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -719,41 +716,41 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B13">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C13">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C14">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C15">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -761,13 +758,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B16">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -775,27 +772,27 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B17">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C17">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B18">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C18">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -803,21 +800,21 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B19">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C19">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D19">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B20">
         <v>16</v>
@@ -831,97 +828,97 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B21">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C21">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C22">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B23">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="C23">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B24">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B25">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="C25">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B26">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="C26">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B27">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C27">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -929,55 +926,55 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B28">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="C28">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B29">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C29">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B30">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C30">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B31">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -985,41 +982,41 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C32">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B34">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -1027,27 +1024,27 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B35">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C35">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B36">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1055,10 +1052,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>46265</v>
+        <v>46266</v>
+      </c>
+      <c r="B37">
+        <v>17</v>
       </c>
       <c r="C37">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1066,97 +1066,94 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>46264</v>
-      </c>
-      <c r="B38">
-        <v>5</v>
+        <v>46265</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B39">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="C39">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B40">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C40">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B41">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C41">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B42">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="C42">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B43">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="C43">
         <v>62</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B44">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C44">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -1164,105 +1161,105 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B46">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="C46">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B47">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="C47">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B48">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="C48">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B49">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C49">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B51">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C51">
         <v>0</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B52">
         <v>12</v>
@@ -1270,10 +1267,16 @@
       <c r="C52">
         <v>0</v>
       </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>46249</v>
+        <v>46250</v>
+      </c>
+      <c r="B53">
+        <v>12</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -1281,27 +1284,21 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>46248</v>
-      </c>
-      <c r="B54">
-        <v>7</v>
+        <v>46249</v>
       </c>
       <c r="C54">
-        <v>16</v>
-      </c>
-      <c r="D54">
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B55">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="C55">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -1309,66 +1306,66 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B56">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C56">
         <v>21</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B57">
+        <v>28</v>
+      </c>
+      <c r="C57">
         <v>21</v>
       </c>
-      <c r="C57">
-        <v>25</v>
-      </c>
       <c r="D57">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B58">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C58">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D58">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B59">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -1379,10 +1376,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B61">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -1393,10 +1390,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B62">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -1407,29 +1404,43 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B64">
+        <v>0</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
         <v>46238</v>
       </c>
-      <c r="B64">
-        <v>0</v>
-      </c>
-      <c r="C64">
-        <v>0</v>
-      </c>
-      <c r="D64">
+      <c r="B65">
+        <v>0</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
         <v>1</v>
       </c>
     </row>
@@ -1449,7 +1460,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1457,42 +1468,42 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1">
-        <v>46326</v>
+        <v>46336</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1">
-        <v>46361</v>
+        <v>46371</v>
       </c>
     </row>
   </sheetData>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="664" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0F581D2-0B2B-4772-821E-3C497C13EB45}"/>
+  <xr:revisionPtr revIDLastSave="680" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E362AF0-BE6C-411F-8062-BB50AB4B69D6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>
@@ -52,18 +52,18 @@
     <t>ACC</t>
   </si>
   <si>
+    <t>Daily- 26; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 262 ;Total - 4877 MT</t>
+  </si>
+  <si>
     <t>Boiler</t>
   </si>
   <si>
-    <t>Daily-104  - (SH-89 and RH-24); Oct-393NDHT Balance joints - 9821 (SH - 5379; RH - 4442)</t>
+    <t>Daily-91  - (SH-57 and RH-34); Oct-448NDHT Balance joints - 9730 (SH - 5322; RH - 4408)</t>
   </si>
   <si>
     <t>PCP Joint</t>
   </si>
   <si>
-    <t>Daily-4; MS Joints - 68/146; MS to PRDS - 9/26; HRH - 10/95; CRH -14/87; LPBP - 9/49; HPBP-8/23; BFD- 169/661</t>
-  </si>
-  <si>
     <t>Boiler - NDHT Joints</t>
   </si>
   <si>
@@ -94,7 +94,7 @@
     <t>Segment-5</t>
   </si>
   <si>
-    <t>Daily- 45; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 235 ;Total - 4851 MT</t>
+    <t>Daily-0; MS Joints - 68/146; MS to PRDS - 9/26; HRH - 10/95; CRH -14/87; LPBP - 9/49; HPBP-8/23; BFD- 170/661</t>
   </si>
 </sst>
 </file>
@@ -479,13 +479,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="93" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -496,7 +496,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A2" s="1">
         <v>46301</v>
       </c>
@@ -504,29 +504,29 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A3" s="1">
         <v>46301</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A4" s="1">
         <v>46301</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -539,14 +539,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
-  <dimension ref="A1:D65"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D66"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -560,7 +560,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -574,261 +574,261 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A3" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B3">
+        <v>26</v>
+      </c>
+      <c r="C3">
+        <v>91</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A4" s="1">
         <v>46301</v>
-      </c>
-      <c r="B3">
-        <v>45</v>
-      </c>
-      <c r="C3">
-        <v>104</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>46300</v>
       </c>
       <c r="B4">
         <v>45</v>
       </c>
       <c r="C4">
+        <v>104</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A5" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B5">
+        <v>45</v>
+      </c>
+      <c r="C5">
         <v>123</v>
       </c>
-      <c r="D4">
+      <c r="D5">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A6" s="1">
         <v>46299</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>66</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A7" s="1">
         <v>46298</v>
       </c>
-      <c r="B6">
+      <c r="B7">
         <v>40</v>
       </c>
-      <c r="C6">
+      <c r="C7">
         <v>65</v>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+      <c r="D7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A8" s="1">
         <v>46297</v>
       </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A9" s="1">
         <v>46296</v>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>40</v>
       </c>
-      <c r="C8">
+      <c r="C9">
         <v>101</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A10" s="1">
         <v>46295</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>321</v>
       </c>
-      <c r="C9">
+      <c r="C10">
         <v>139</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+      <c r="D10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A11" s="1">
         <v>46294</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>200</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>114</v>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+      <c r="D11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A12" s="1">
         <v>46293</v>
       </c>
-      <c r="B11">
+      <c r="B12">
         <v>43</v>
       </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A13" s="1">
         <v>46292</v>
       </c>
-      <c r="B12">
+      <c r="B13">
         <v>13</v>
       </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A14" s="1">
         <v>46291</v>
       </c>
-      <c r="B13">
+      <c r="B14">
         <v>17</v>
       </c>
-      <c r="C13">
+      <c r="C14">
         <v>39</v>
       </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+      <c r="D14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A15" s="1">
         <v>46290</v>
       </c>
-      <c r="B14">
+      <c r="B15">
         <v>20</v>
       </c>
-      <c r="C14">
+      <c r="C15">
         <v>121</v>
       </c>
-      <c r="D14">
+      <c r="D15">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A16" s="1">
         <v>46289</v>
       </c>
-      <c r="B15">
+      <c r="B16">
         <v>3</v>
       </c>
-      <c r="C15">
+      <c r="C16">
         <v>133</v>
       </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+      <c r="D16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A17" s="1">
         <v>46288</v>
       </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16">
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
         <v>143</v>
       </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+      <c r="D17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A18" s="1">
         <v>46287</v>
       </c>
-      <c r="B17">
+      <c r="B18">
         <v>9</v>
       </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A19" s="1">
         <v>46286</v>
       </c>
-      <c r="B18">
+      <c r="B19">
         <v>32</v>
       </c>
-      <c r="C18">
+      <c r="C19">
         <v>131</v>
       </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+      <c r="D19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A20" s="1">
         <v>46285</v>
       </c>
-      <c r="B19">
+      <c r="B20">
         <v>42</v>
       </c>
-      <c r="C19">
+      <c r="C20">
         <v>111</v>
       </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+      <c r="D20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A21" s="1">
         <v>46284</v>
-      </c>
-      <c r="B20">
-        <v>16</v>
-      </c>
-      <c r="C20">
-        <v>118</v>
-      </c>
-      <c r="D20">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>46283</v>
       </c>
       <c r="B21">
         <v>16</v>
@@ -840,440 +840,440 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A22" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B22">
+        <v>16</v>
+      </c>
+      <c r="C22">
+        <v>118</v>
+      </c>
+      <c r="D22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A23" s="1">
         <v>46281</v>
       </c>
-      <c r="B22">
+      <c r="B23">
         <v>33</v>
       </c>
-      <c r="C22">
+      <c r="C23">
         <v>98</v>
       </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+      <c r="D23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A24" s="1">
         <v>46280</v>
       </c>
-      <c r="B23">
+      <c r="B24">
         <v>3</v>
       </c>
-      <c r="C23">
+      <c r="C24">
         <v>125</v>
       </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+      <c r="D24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A25" s="1">
         <v>46279</v>
       </c>
-      <c r="B24">
+      <c r="B25">
         <v>58</v>
       </c>
-      <c r="C24">
+      <c r="C25">
         <v>100</v>
       </c>
-      <c r="D24">
+      <c r="D25">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A26" s="1">
         <v>46278</v>
       </c>
-      <c r="B25">
+      <c r="B26">
         <v>3</v>
       </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A27" s="1">
         <v>46277</v>
       </c>
-      <c r="B26">
+      <c r="B27">
         <v>63</v>
       </c>
-      <c r="C26">
+      <c r="C27">
         <v>42</v>
       </c>
-      <c r="D26">
+      <c r="D27">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A28" s="1">
         <v>46276</v>
       </c>
-      <c r="B27">
+      <c r="B28">
         <v>19</v>
       </c>
-      <c r="C27">
+      <c r="C28">
         <v>73</v>
       </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+      <c r="D28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A29" s="1">
         <v>46275</v>
       </c>
-      <c r="B28">
+      <c r="B29">
         <v>21</v>
       </c>
-      <c r="C28">
+      <c r="C29">
         <v>16</v>
       </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+      <c r="D29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A30" s="1">
         <v>46274</v>
       </c>
-      <c r="B29">
+      <c r="B30">
         <v>47</v>
       </c>
-      <c r="C29">
+      <c r="C30">
         <v>84</v>
       </c>
-      <c r="D29">
+      <c r="D30">
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A31" s="1">
         <v>46273</v>
       </c>
-      <c r="B30">
+      <c r="B31">
         <v>45</v>
       </c>
-      <c r="C30">
+      <c r="C31">
         <v>105</v>
       </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+      <c r="D31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A32" s="1">
         <v>46272</v>
       </c>
-      <c r="B31">
+      <c r="B32">
         <v>38</v>
       </c>
-      <c r="C31">
+      <c r="C32">
         <v>92</v>
       </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+      <c r="D32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A33" s="1">
         <v>46271</v>
       </c>
-      <c r="B32">
+      <c r="B33">
         <v>13</v>
       </c>
-      <c r="C32">
-        <v>0</v>
-      </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A34" s="1">
         <v>46270</v>
       </c>
-      <c r="B33">
-        <v>0</v>
-      </c>
-      <c r="C33">
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34">
         <v>90</v>
       </c>
-      <c r="D33">
+      <c r="D34">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A35" s="1">
         <v>46269</v>
       </c>
-      <c r="B34">
-        <v>0</v>
-      </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A36" s="1">
         <v>46268</v>
       </c>
-      <c r="B35">
+      <c r="B36">
         <v>23</v>
       </c>
-      <c r="C35">
+      <c r="C36">
         <v>74</v>
       </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
+      <c r="D36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A37" s="1">
         <v>46267</v>
       </c>
-      <c r="B36">
+      <c r="B37">
         <v>7</v>
       </c>
-      <c r="C36">
+      <c r="C37">
         <v>75</v>
       </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
+      <c r="D37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A38" s="1">
         <v>46266</v>
       </c>
-      <c r="B37">
+      <c r="B38">
         <v>17</v>
       </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A39" s="1">
         <v>46265</v>
       </c>
-      <c r="C38">
+      <c r="C39">
         <v>62</v>
       </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
+      <c r="D39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A40" s="1">
         <v>46264</v>
       </c>
-      <c r="B39">
+      <c r="B40">
         <v>5</v>
       </c>
-      <c r="C39">
-        <v>0</v>
-      </c>
-      <c r="D39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A41" s="1">
         <v>46263</v>
       </c>
-      <c r="B40">
+      <c r="B41">
         <v>73</v>
       </c>
-      <c r="C40">
+      <c r="C41">
         <v>62</v>
       </c>
-      <c r="D40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
+      <c r="D41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A42" s="1">
         <v>46262</v>
       </c>
-      <c r="B41">
+      <c r="B42">
         <v>67</v>
       </c>
-      <c r="C41">
+      <c r="C42">
         <v>54</v>
       </c>
-      <c r="D41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
+      <c r="D42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A43" s="1">
         <v>46261</v>
       </c>
-      <c r="B42">
+      <c r="B43">
         <v>29</v>
       </c>
-      <c r="C42">
+      <c r="C43">
         <v>64</v>
       </c>
-      <c r="D42">
+      <c r="D43">
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A44" s="1">
         <v>46260</v>
       </c>
-      <c r="B43">
+      <c r="B44">
         <v>85</v>
-      </c>
-      <c r="C43">
-        <v>62</v>
-      </c>
-      <c r="D43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
-        <v>46259</v>
-      </c>
-      <c r="B44">
-        <v>13</v>
       </c>
       <c r="C44">
         <v>62</v>
       </c>
       <c r="D44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A45" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B45">
+        <v>13</v>
+      </c>
+      <c r="C45">
+        <v>62</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A46" s="1">
         <v>46258</v>
       </c>
-      <c r="B45">
+      <c r="B46">
         <v>18</v>
       </c>
-      <c r="C45">
+      <c r="C46">
         <v>56</v>
       </c>
-      <c r="D45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
+      <c r="D46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A47" s="1">
         <v>46257</v>
       </c>
-      <c r="B46">
+      <c r="B47">
         <v>3</v>
       </c>
-      <c r="C46">
-        <v>0</v>
-      </c>
-      <c r="D46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A48" s="1">
         <v>46256</v>
       </c>
-      <c r="B47">
+      <c r="B48">
         <v>69</v>
       </c>
-      <c r="C47">
+      <c r="C48">
         <v>53</v>
       </c>
-      <c r="D47">
+      <c r="D48">
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A49" s="1">
         <v>46255</v>
       </c>
-      <c r="B48">
+      <c r="B49">
         <v>15</v>
       </c>
-      <c r="C48">
+      <c r="C49">
         <v>60</v>
       </c>
-      <c r="D48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="1">
+      <c r="D49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A50" s="1">
         <v>46254</v>
       </c>
-      <c r="B49">
+      <c r="B50">
         <v>48</v>
       </c>
-      <c r="C49">
+      <c r="C50">
         <v>43</v>
       </c>
-      <c r="D49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
+      <c r="D50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A51" s="1">
         <v>46253</v>
       </c>
-      <c r="B50">
+      <c r="B51">
         <v>27</v>
       </c>
-      <c r="C50">
+      <c r="C51">
         <v>51</v>
       </c>
-      <c r="D50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
+      <c r="D51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A52" s="1">
         <v>46252</v>
       </c>
-      <c r="B51">
-        <v>0</v>
-      </c>
-      <c r="C51">
-        <v>0</v>
-      </c>
-      <c r="D51">
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A53" s="1">
         <v>46251</v>
-      </c>
-      <c r="B52">
-        <v>12</v>
-      </c>
-      <c r="C52">
-        <v>0</v>
-      </c>
-      <c r="D52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
-        <v>46250</v>
       </c>
       <c r="B53">
         <v>12</v>
@@ -1281,166 +1281,180 @@
       <c r="C53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A54" s="1">
+        <v>46250</v>
+      </c>
+      <c r="B54">
+        <v>12</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A55" s="1">
         <v>46249</v>
       </c>
-      <c r="C54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="1">
+      <c r="C55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A56" s="1">
         <v>46248</v>
       </c>
-      <c r="B55">
+      <c r="B56">
         <v>7</v>
       </c>
-      <c r="C55">
+      <c r="C56">
         <v>16</v>
       </c>
-      <c r="D55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
+      <c r="D56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A57" s="1">
         <v>46247</v>
       </c>
-      <c r="B56">
+      <c r="B57">
         <v>35</v>
-      </c>
-      <c r="C56">
-        <v>21</v>
-      </c>
-      <c r="D56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
-        <v>46246</v>
-      </c>
-      <c r="B57">
-        <v>28</v>
       </c>
       <c r="C57">
         <v>21</v>
       </c>
       <c r="D57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A58" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B58">
+        <v>28</v>
+      </c>
+      <c r="C58">
+        <v>21</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A59" s="1">
         <v>46245</v>
       </c>
-      <c r="B58">
+      <c r="B59">
         <v>21</v>
       </c>
-      <c r="C58">
+      <c r="C59">
         <v>25</v>
       </c>
-      <c r="D58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
+      <c r="D59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A60" s="1">
         <v>46244</v>
       </c>
-      <c r="B59">
+      <c r="B60">
         <v>19</v>
       </c>
-      <c r="C59">
+      <c r="C60">
         <v>11</v>
       </c>
-      <c r="D59">
+      <c r="D60">
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A61" s="1">
         <v>46243</v>
       </c>
-      <c r="B60">
+      <c r="B61">
         <v>13</v>
       </c>
-      <c r="C60">
-        <v>0</v>
-      </c>
-      <c r="D60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A62" s="1">
         <v>46242</v>
       </c>
-      <c r="B61">
-        <v>0</v>
-      </c>
-      <c r="C61">
-        <v>0</v>
-      </c>
-      <c r="D61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="1">
+      <c r="B62">
+        <v>0</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A63" s="1">
         <v>46241</v>
       </c>
-      <c r="B62">
+      <c r="B63">
         <v>32</v>
       </c>
-      <c r="C62">
-        <v>0</v>
-      </c>
-      <c r="D62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="1">
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A64" s="1">
         <v>46240</v>
       </c>
-      <c r="B63">
+      <c r="B64">
         <v>16</v>
       </c>
-      <c r="C63">
-        <v>0</v>
-      </c>
-      <c r="D63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="1">
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A65" s="1">
         <v>46239</v>
       </c>
-      <c r="B64">
-        <v>0</v>
-      </c>
-      <c r="C64">
-        <v>0</v>
-      </c>
-      <c r="D64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="1">
+      <c r="B65">
+        <v>0</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A66" s="1">
         <v>46238</v>
       </c>
-      <c r="B65">
-        <v>0</v>
-      </c>
-      <c r="C65">
-        <v>0</v>
-      </c>
-      <c r="D65">
+      <c r="B66">
+        <v>0</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66">
         <v>1</v>
       </c>
     </row>
@@ -1452,13 +1466,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E384ED-EF07-4058-B570-9E7F8CBFADFB}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="9.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -1466,7 +1480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1474,7 +1488,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1482,7 +1496,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1490,7 +1504,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1498,7 +1512,7 @@
         <v>46336</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
         <v>17</v>
       </c>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="680" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E362AF0-BE6C-411F-8062-BB50AB4B69D6}"/>
+  <xr:revisionPtr revIDLastSave="769" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F5E03AC-CAC8-4A5A-8CF3-6EFD27395600}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>
     <sheet name="Critical areas" sheetId="2" r:id="rId2"/>
-    <sheet name="Chimney" sheetId="3" r:id="rId3"/>
+    <sheet name="Joints" sheetId="5" r:id="rId3"/>
+    <sheet name="Chimney" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
   <si>
     <t>Date</t>
   </si>
@@ -52,18 +53,18 @@
     <t>ACC</t>
   </si>
   <si>
-    <t>Daily- 26; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 262 ;Total - 4877 MT</t>
+    <t>Daily- 70; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 323 ;Total - 4948 MT</t>
   </si>
   <si>
     <t>Boiler</t>
   </si>
   <si>
-    <t>Daily-91  - (SH-57 and RH-34); Oct-448NDHT Balance joints - 9730 (SH - 5322; RH - 4408)</t>
-  </si>
-  <si>
     <t>PCP Joint</t>
   </si>
   <si>
+    <t>Daily-1; MS Joints - 68/146; MS to PRDS - 10/26; HRH - 10/95; CRH -14/87; LPBP - 9/49; HPBP-8/23; BFD- 171/661</t>
+  </si>
+  <si>
     <t>Boiler - NDHT Joints</t>
   </si>
   <si>
@@ -73,6 +74,39 @@
     <t>Daily Target</t>
   </si>
   <si>
+    <t>SH</t>
+  </si>
+  <si>
+    <t>RH</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>HRH</t>
+  </si>
+  <si>
+    <t>CRH</t>
+  </si>
+  <si>
+    <t>LPBP</t>
+  </si>
+  <si>
+    <t>HPBP</t>
+  </si>
+  <si>
+    <t>BFD</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Balance</t>
+  </si>
+  <si>
     <t>Segment</t>
   </si>
   <si>
@@ -94,7 +128,7 @@
     <t>Segment-5</t>
   </si>
   <si>
-    <t>Daily-0; MS Joints - 68/146; MS to PRDS - 9/26; HRH - 10/95; CRH -14/87; LPBP - 9/49; HPBP-8/23; BFD- 170/661</t>
+    <t>Daily-134  - (SH-94 and RH-40); Oct-618 NDHT Balance joints - 9596 (SH - 5228; RH - 4368)</t>
   </si>
 </sst>
 </file>
@@ -479,13 +513,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="93" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -496,7 +530,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46301</v>
       </c>
@@ -507,7 +541,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46301</v>
       </c>
@@ -515,18 +549,18 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46301</v>
       </c>
       <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
         <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -539,14 +573,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
-  <dimension ref="A1:D66"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:D67"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -560,7 +596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -574,275 +610,275 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B3">
+        <v>70</v>
+      </c>
+      <c r="C3">
+        <v>134</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>46302</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>26</v>
       </c>
-      <c r="C3">
+      <c r="C4">
         <v>91</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A4" s="1">
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>46301</v>
-      </c>
-      <c r="B4">
-        <v>45</v>
-      </c>
-      <c r="C4">
-        <v>104</v>
-      </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A5" s="1">
-        <v>46300</v>
       </c>
       <c r="B5">
         <v>45</v>
       </c>
       <c r="C5">
+        <v>104</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B6">
+        <v>45</v>
+      </c>
+      <c r="C6">
         <v>123</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A6" s="1">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>46299</v>
       </c>
-      <c r="B6">
+      <c r="B7">
         <v>66</v>
       </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A7" s="1">
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>46298</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>40</v>
       </c>
-      <c r="C7">
+      <c r="C8">
         <v>65</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A8" s="1">
+      <c r="D8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>46297</v>
       </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A9" s="1">
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>46296</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>40</v>
       </c>
-      <c r="C9">
+      <c r="C10">
         <v>101</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A10" s="1">
+      <c r="D10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>46295</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>321</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>139</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A11" s="1">
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>46294</v>
       </c>
-      <c r="B11">
+      <c r="B12">
         <v>200</v>
       </c>
-      <c r="C11">
+      <c r="C12">
         <v>114</v>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A12" s="1">
+      <c r="D12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>46293</v>
       </c>
-      <c r="B12">
+      <c r="B13">
         <v>43</v>
       </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A13" s="1">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>46292</v>
       </c>
-      <c r="B13">
+      <c r="B14">
         <v>13</v>
       </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A14" s="1">
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>46291</v>
       </c>
-      <c r="B14">
+      <c r="B15">
         <v>17</v>
       </c>
-      <c r="C14">
+      <c r="C15">
         <v>39</v>
       </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A15" s="1">
+      <c r="D15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>46290</v>
       </c>
-      <c r="B15">
+      <c r="B16">
         <v>20</v>
       </c>
-      <c r="C15">
+      <c r="C16">
         <v>121</v>
       </c>
-      <c r="D15">
+      <c r="D16">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A16" s="1">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
         <v>46289</v>
       </c>
-      <c r="B16">
+      <c r="B17">
         <v>3</v>
       </c>
-      <c r="C16">
+      <c r="C17">
         <v>133</v>
       </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A17" s="1">
+      <c r="D17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>46288</v>
       </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
         <v>143</v>
       </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A18" s="1">
+      <c r="D18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>46287</v>
       </c>
-      <c r="B18">
+      <c r="B19">
         <v>9</v>
       </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A19" s="1">
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>46286</v>
       </c>
-      <c r="B19">
+      <c r="B20">
         <v>32</v>
       </c>
-      <c r="C19">
+      <c r="C20">
         <v>131</v>
       </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A20" s="1">
+      <c r="D20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
         <v>46285</v>
       </c>
-      <c r="B20">
+      <c r="B21">
         <v>42</v>
       </c>
-      <c r="C20">
+      <c r="C21">
         <v>111</v>
       </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A21" s="1">
+      <c r="D21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
         <v>46284</v>
-      </c>
-      <c r="B21">
-        <v>16</v>
-      </c>
-      <c r="C21">
-        <v>118</v>
-      </c>
-      <c r="D21">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A22" s="1">
-        <v>46283</v>
       </c>
       <c r="B22">
         <v>16</v>
@@ -854,440 +890,440 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B23">
+        <v>16</v>
+      </c>
+      <c r="C23">
+        <v>118</v>
+      </c>
+      <c r="D23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
         <v>46281</v>
       </c>
-      <c r="B23">
+      <c r="B24">
         <v>33</v>
       </c>
-      <c r="C23">
+      <c r="C24">
         <v>98</v>
       </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A24" s="1">
+      <c r="D24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
         <v>46280</v>
       </c>
-      <c r="B24">
+      <c r="B25">
         <v>3</v>
       </c>
-      <c r="C24">
+      <c r="C25">
         <v>125</v>
       </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A25" s="1">
+      <c r="D25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
         <v>46279</v>
       </c>
-      <c r="B25">
+      <c r="B26">
         <v>58</v>
       </c>
-      <c r="C25">
+      <c r="C26">
         <v>100</v>
       </c>
-      <c r="D25">
+      <c r="D26">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A26" s="1">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
         <v>46278</v>
       </c>
-      <c r="B26">
+      <c r="B27">
         <v>3</v>
       </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A27" s="1">
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
         <v>46277</v>
       </c>
-      <c r="B27">
+      <c r="B28">
         <v>63</v>
       </c>
-      <c r="C27">
+      <c r="C28">
         <v>42</v>
       </c>
-      <c r="D27">
+      <c r="D28">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A28" s="1">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
         <v>46276</v>
       </c>
-      <c r="B28">
+      <c r="B29">
         <v>19</v>
       </c>
-      <c r="C28">
+      <c r="C29">
         <v>73</v>
       </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A29" s="1">
+      <c r="D29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
         <v>46275</v>
       </c>
-      <c r="B29">
+      <c r="B30">
         <v>21</v>
       </c>
-      <c r="C29">
+      <c r="C30">
         <v>16</v>
       </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A30" s="1">
+      <c r="D30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
         <v>46274</v>
       </c>
-      <c r="B30">
+      <c r="B31">
         <v>47</v>
       </c>
-      <c r="C30">
+      <c r="C31">
         <v>84</v>
       </c>
-      <c r="D30">
+      <c r="D31">
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A31" s="1">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
         <v>46273</v>
       </c>
-      <c r="B31">
+      <c r="B32">
         <v>45</v>
       </c>
-      <c r="C31">
+      <c r="C32">
         <v>105</v>
       </c>
-      <c r="D31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A32" s="1">
+      <c r="D32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
         <v>46272</v>
       </c>
-      <c r="B32">
+      <c r="B33">
         <v>38</v>
       </c>
-      <c r="C32">
+      <c r="C33">
         <v>92</v>
       </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A33" s="1">
+      <c r="D33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
         <v>46271</v>
       </c>
-      <c r="B33">
+      <c r="B34">
         <v>13</v>
       </c>
-      <c r="C33">
-        <v>0</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A34" s="1">
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
         <v>46270</v>
       </c>
-      <c r="B34">
-        <v>0</v>
-      </c>
-      <c r="C34">
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
         <v>90</v>
       </c>
-      <c r="D34">
+      <c r="D35">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A35" s="1">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
         <v>46269</v>
       </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A36" s="1">
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
         <v>46268</v>
       </c>
-      <c r="B36">
+      <c r="B37">
         <v>23</v>
       </c>
-      <c r="C36">
+      <c r="C37">
         <v>74</v>
       </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A37" s="1">
+      <c r="D37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
         <v>46267</v>
       </c>
-      <c r="B37">
+      <c r="B38">
         <v>7</v>
       </c>
-      <c r="C37">
+      <c r="C38">
         <v>75</v>
       </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A38" s="1">
+      <c r="D38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
         <v>46266</v>
       </c>
-      <c r="B38">
+      <c r="B39">
         <v>17</v>
       </c>
-      <c r="C38">
-        <v>0</v>
-      </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A39" s="1">
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
         <v>46265</v>
       </c>
-      <c r="C39">
+      <c r="C40">
         <v>62</v>
       </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A40" s="1">
+      <c r="D40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
         <v>46264</v>
       </c>
-      <c r="B40">
+      <c r="B41">
         <v>5</v>
       </c>
-      <c r="C40">
-        <v>0</v>
-      </c>
-      <c r="D40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A41" s="1">
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
         <v>46263</v>
       </c>
-      <c r="B41">
+      <c r="B42">
         <v>73</v>
       </c>
-      <c r="C41">
+      <c r="C42">
         <v>62</v>
       </c>
-      <c r="D41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A42" s="1">
+      <c r="D42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
         <v>46262</v>
       </c>
-      <c r="B42">
+      <c r="B43">
         <v>67</v>
       </c>
-      <c r="C42">
+      <c r="C43">
         <v>54</v>
       </c>
-      <c r="D42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A43" s="1">
+      <c r="D43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
         <v>46261</v>
       </c>
-      <c r="B43">
+      <c r="B44">
         <v>29</v>
       </c>
-      <c r="C43">
+      <c r="C44">
         <v>64</v>
       </c>
-      <c r="D43">
+      <c r="D44">
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A44" s="1">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
         <v>46260</v>
       </c>
-      <c r="B44">
+      <c r="B45">
         <v>85</v>
-      </c>
-      <c r="C44">
-        <v>62</v>
-      </c>
-      <c r="D44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A45" s="1">
-        <v>46259</v>
-      </c>
-      <c r="B45">
-        <v>13</v>
       </c>
       <c r="C45">
         <v>62</v>
       </c>
       <c r="D45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B46">
+        <v>13</v>
+      </c>
+      <c r="C46">
+        <v>62</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
         <v>46258</v>
       </c>
-      <c r="B46">
+      <c r="B47">
         <v>18</v>
       </c>
-      <c r="C46">
+      <c r="C47">
         <v>56</v>
       </c>
-      <c r="D46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A47" s="1">
+      <c r="D47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
         <v>46257</v>
       </c>
-      <c r="B47">
+      <c r="B48">
         <v>3</v>
       </c>
-      <c r="C47">
-        <v>0</v>
-      </c>
-      <c r="D47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A48" s="1">
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
         <v>46256</v>
       </c>
-      <c r="B48">
+      <c r="B49">
         <v>69</v>
       </c>
-      <c r="C48">
+      <c r="C49">
         <v>53</v>
       </c>
-      <c r="D48">
+      <c r="D49">
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A49" s="1">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
         <v>46255</v>
       </c>
-      <c r="B49">
+      <c r="B50">
         <v>15</v>
       </c>
-      <c r="C49">
+      <c r="C50">
         <v>60</v>
       </c>
-      <c r="D49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A50" s="1">
+      <c r="D50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
         <v>46254</v>
       </c>
-      <c r="B50">
+      <c r="B51">
         <v>48</v>
       </c>
-      <c r="C50">
+      <c r="C51">
         <v>43</v>
       </c>
-      <c r="D50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A51" s="1">
+      <c r="D51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
         <v>46253</v>
       </c>
-      <c r="B51">
+      <c r="B52">
         <v>27</v>
       </c>
-      <c r="C51">
+      <c r="C52">
         <v>51</v>
       </c>
-      <c r="D51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A52" s="1">
+      <c r="D52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
         <v>46252</v>
       </c>
-      <c r="B52">
-        <v>0</v>
-      </c>
-      <c r="C52">
-        <v>0</v>
-      </c>
-      <c r="D52">
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53">
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A53" s="1">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
         <v>46251</v>
-      </c>
-      <c r="B53">
-        <v>12</v>
-      </c>
-      <c r="C53">
-        <v>0</v>
-      </c>
-      <c r="D53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A54" s="1">
-        <v>46250</v>
       </c>
       <c r="B54">
         <v>12</v>
@@ -1295,166 +1331,180 @@
       <c r="C54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="D54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
+        <v>46250</v>
+      </c>
+      <c r="B55">
+        <v>12</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
         <v>46249</v>
       </c>
-      <c r="C55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A56" s="1">
+      <c r="C56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
         <v>46248</v>
       </c>
-      <c r="B56">
+      <c r="B57">
         <v>7</v>
       </c>
-      <c r="C56">
+      <c r="C57">
         <v>16</v>
       </c>
-      <c r="D56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A57" s="1">
+      <c r="D57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
         <v>46247</v>
       </c>
-      <c r="B57">
+      <c r="B58">
         <v>35</v>
-      </c>
-      <c r="C57">
-        <v>21</v>
-      </c>
-      <c r="D57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A58" s="1">
-        <v>46246</v>
-      </c>
-      <c r="B58">
-        <v>28</v>
       </c>
       <c r="C58">
         <v>21</v>
       </c>
       <c r="D58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B59">
+        <v>28</v>
+      </c>
+      <c r="C59">
+        <v>21</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
         <v>46245</v>
       </c>
-      <c r="B59">
+      <c r="B60">
         <v>21</v>
       </c>
-      <c r="C59">
+      <c r="C60">
         <v>25</v>
       </c>
-      <c r="D59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A60" s="1">
+      <c r="D60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
         <v>46244</v>
       </c>
-      <c r="B60">
+      <c r="B61">
         <v>19</v>
       </c>
-      <c r="C60">
+      <c r="C61">
         <v>11</v>
       </c>
-      <c r="D60">
+      <c r="D61">
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A61" s="1">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
         <v>46243</v>
       </c>
-      <c r="B61">
+      <c r="B62">
         <v>13</v>
       </c>
-      <c r="C61">
-        <v>0</v>
-      </c>
-      <c r="D61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A62" s="1">
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
         <v>46242</v>
       </c>
-      <c r="B62">
-        <v>0</v>
-      </c>
-      <c r="C62">
-        <v>0</v>
-      </c>
-      <c r="D62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A63" s="1">
+      <c r="B63">
+        <v>0</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
         <v>46241</v>
       </c>
-      <c r="B63">
+      <c r="B64">
         <v>32</v>
       </c>
-      <c r="C63">
-        <v>0</v>
-      </c>
-      <c r="D63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A64" s="1">
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
         <v>46240</v>
       </c>
-      <c r="B64">
+      <c r="B65">
         <v>16</v>
       </c>
-      <c r="C64">
-        <v>0</v>
-      </c>
-      <c r="D64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A65" s="1">
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
         <v>46239</v>
       </c>
-      <c r="B65">
-        <v>0</v>
-      </c>
-      <c r="C65">
-        <v>0</v>
-      </c>
-      <c r="D65">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A66" s="1">
+      <c r="B66">
+        <v>0</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
         <v>46238</v>
       </c>
-      <c r="B66">
-        <v>0</v>
-      </c>
-      <c r="C66">
-        <v>0</v>
-      </c>
-      <c r="D66">
+      <c r="B67">
+        <v>0</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67">
         <v>1</v>
       </c>
     </row>
@@ -1464,57 +1514,254 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D41FB4CD-150C-4CE3-A76E-CB540C2892DD}">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2">
+        <v>9697</v>
+      </c>
+      <c r="C2">
+        <v>11870</v>
+      </c>
+      <c r="D2">
+        <f>26+146</f>
+        <v>172</v>
+      </c>
+      <c r="E2">
+        <v>95</v>
+      </c>
+      <c r="F2">
+        <v>87</v>
+      </c>
+      <c r="G2">
+        <v>49</v>
+      </c>
+      <c r="H2">
+        <v>23</v>
+      </c>
+      <c r="I2">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3">
+        <f>4375+B6</f>
+        <v>4469</v>
+      </c>
+      <c r="C3">
+        <f>7462+C6</f>
+        <v>7502</v>
+      </c>
+      <c r="D3">
+        <f>D6+75</f>
+        <v>76</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <f>I6+170</f>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4">
+        <f>B2-B3</f>
+        <v>5228</v>
+      </c>
+      <c r="C4">
+        <f>C2-C3</f>
+        <v>4368</v>
+      </c>
+      <c r="D4">
+        <f t="shared" ref="D4:I4" si="0">D2-D3</f>
+        <v>96</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>73</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B5">
+        <v>57</v>
+      </c>
+      <c r="C5">
+        <v>34</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B6">
+        <v>94</v>
+      </c>
+      <c r="C6">
+        <v>40</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E384ED-EF07-4058-B570-9E7F8CBFADFB}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B5" s="1">
         <v>46336</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B6" s="1">
         <v>46371</v>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="769" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F5E03AC-CAC8-4A5A-8CF3-6EFD27395600}"/>
+  <xr:revisionPtr revIDLastSave="887" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25E75F83-C2A8-435D-97DF-9283C3DF20EA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>
@@ -53,16 +53,19 @@
     <t>ACC</t>
   </si>
   <si>
-    <t>Daily- 70; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 323 ;Total - 4948 MT</t>
+    <t>Daily-102; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 613;Total - 5228 MT</t>
   </si>
   <si>
     <t>Boiler</t>
   </si>
   <si>
+    <t>Daily-118  - (SH-92 and RH-26); Oct-948 NDHT Balance joints - 9266 (SH - 4962; RH - 4304)</t>
+  </si>
+  <si>
     <t>PCP Joint</t>
   </si>
   <si>
-    <t>Daily-1; MS Joints - 68/146; MS to PRDS - 10/26; HRH - 10/95; CRH -14/87; LPBP - 9/49; HPBP-8/23; BFD- 171/661</t>
+    <t>Daily-3; MS Joints - 71/146; MS to PRDS - 11/26; HRH - 10/95; CRH -14/87; LPBP - 10/49; HPBP-8/23; BFD- 174/661</t>
   </si>
   <si>
     <t>Boiler - NDHT Joints</t>
@@ -126,16 +129,13 @@
   </si>
   <si>
     <t>Segment-5</t>
-  </si>
-  <si>
-    <t>Daily-134  - (SH-94 and RH-40); Oct-618 NDHT Balance joints - 9596 (SH - 5228; RH - 4368)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -513,13 +513,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="93" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -530,9 +530,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="1">
-        <v>46301</v>
+        <v>46306</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -541,26 +541,26 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" s="1">
-        <v>46301</v>
+        <v>46305</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="1">
-        <v>46301</v>
+        <v>46305</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -573,16 +573,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
-  <dimension ref="A1:D67"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D71"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.25" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="11.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -590,15 +590,15 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>30</v>
@@ -610,611 +610,611 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B3">
+        <v>102</v>
+      </c>
+      <c r="C3">
+        <v>118</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1">
+        <v>46306</v>
+      </c>
+      <c r="B4">
+        <v>21</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1">
+        <v>46305</v>
+      </c>
+      <c r="B5">
+        <v>83</v>
+      </c>
+      <c r="C5">
+        <v>82</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B6">
+        <v>74</v>
+      </c>
+      <c r="C6">
+        <v>130</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1">
         <v>46303</v>
       </c>
-      <c r="B3">
+      <c r="B7">
         <v>70</v>
       </c>
-      <c r="C3">
+      <c r="C7">
         <v>134</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+      <c r="D7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1">
         <v>46302</v>
       </c>
-      <c r="B4">
+      <c r="B8">
         <v>26</v>
       </c>
-      <c r="C4">
+      <c r="C8">
         <v>91</v>
       </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1">
         <v>46301</v>
       </c>
-      <c r="B5">
+      <c r="B9">
         <v>45</v>
       </c>
-      <c r="C5">
+      <c r="C9">
         <v>104</v>
       </c>
-      <c r="D5">
+      <c r="D9">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+    <row r="10" spans="1:4">
+      <c r="A10" s="1">
         <v>46300</v>
       </c>
-      <c r="B6">
+      <c r="B10">
         <v>45</v>
       </c>
-      <c r="C6">
+      <c r="C10">
         <v>123</v>
       </c>
-      <c r="D6">
+      <c r="D10">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+    <row r="11" spans="1:4">
+      <c r="A11" s="1">
         <v>46299</v>
       </c>
-      <c r="B7">
+      <c r="B11">
         <v>66</v>
       </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1">
         <v>46298</v>
       </c>
-      <c r="B8">
+      <c r="B12">
         <v>40</v>
       </c>
-      <c r="C8">
+      <c r="C12">
         <v>65</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+      <c r="D12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1">
         <v>46297</v>
       </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1">
         <v>46296</v>
       </c>
-      <c r="B10">
+      <c r="B14">
         <v>40</v>
       </c>
-      <c r="C10">
+      <c r="C14">
         <v>101</v>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+      <c r="D14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1">
         <v>46295</v>
       </c>
-      <c r="B11">
+      <c r="B15">
         <v>321</v>
       </c>
-      <c r="C11">
+      <c r="C15">
         <v>139</v>
       </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+      <c r="D15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1">
         <v>46294</v>
       </c>
-      <c r="B12">
+      <c r="B16">
         <v>200</v>
       </c>
-      <c r="C12">
+      <c r="C16">
         <v>114</v>
       </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+      <c r="D16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1">
         <v>46293</v>
       </c>
-      <c r="B13">
+      <c r="B17">
         <v>43</v>
       </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+    <row r="18" spans="1:4">
+      <c r="A18" s="1">
         <v>46292</v>
       </c>
-      <c r="B14">
+      <c r="B18">
         <v>13</v>
       </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="1">
         <v>46291</v>
       </c>
-      <c r="B15">
+      <c r="B19">
         <v>17</v>
       </c>
-      <c r="C15">
+      <c r="C19">
         <v>39</v>
       </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+      <c r="D19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="1">
         <v>46290</v>
       </c>
-      <c r="B16">
+      <c r="B20">
         <v>20</v>
       </c>
-      <c r="C16">
+      <c r="C20">
         <v>121</v>
       </c>
-      <c r="D16">
+      <c r="D20">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+    <row r="21" spans="1:4">
+      <c r="A21" s="1">
         <v>46289</v>
       </c>
-      <c r="B17">
+      <c r="B21">
         <v>3</v>
       </c>
-      <c r="C17">
+      <c r="C21">
         <v>133</v>
       </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+      <c r="D21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="1">
         <v>46288</v>
       </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18">
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
         <v>143</v>
       </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+      <c r="D22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="1">
         <v>46287</v>
       </c>
-      <c r="B19">
+      <c r="B23">
         <v>9</v>
       </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="1">
         <v>46286</v>
       </c>
-      <c r="B20">
+      <c r="B24">
         <v>32</v>
       </c>
-      <c r="C20">
+      <c r="C24">
         <v>131</v>
       </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+      <c r="D24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="1">
         <v>46285</v>
       </c>
-      <c r="B21">
+      <c r="B25">
         <v>42</v>
       </c>
-      <c r="C21">
+      <c r="C25">
         <v>111</v>
       </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+      <c r="D25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="1">
         <v>46284</v>
       </c>
-      <c r="B22">
+      <c r="B26">
         <v>16</v>
       </c>
-      <c r="C22">
+      <c r="C26">
         <v>118</v>
       </c>
-      <c r="D22">
+      <c r="D26">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+    <row r="27" spans="1:4">
+      <c r="A27" s="1">
         <v>46283</v>
       </c>
-      <c r="B23">
+      <c r="B27">
         <v>16</v>
       </c>
-      <c r="C23">
+      <c r="C27">
         <v>118</v>
       </c>
-      <c r="D23">
+      <c r="D27">
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+    <row r="28" spans="1:4">
+      <c r="A28" s="1">
         <v>46281</v>
       </c>
-      <c r="B24">
+      <c r="B28">
         <v>33</v>
       </c>
-      <c r="C24">
+      <c r="C28">
         <v>98</v>
       </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+      <c r="D28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="1">
         <v>46280</v>
       </c>
-      <c r="B25">
+      <c r="B29">
         <v>3</v>
       </c>
-      <c r="C25">
+      <c r="C29">
         <v>125</v>
       </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
+      <c r="D29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="1">
         <v>46279</v>
       </c>
-      <c r="B26">
+      <c r="B30">
         <v>58</v>
       </c>
-      <c r="C26">
+      <c r="C30">
         <v>100</v>
       </c>
-      <c r="D26">
+      <c r="D30">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+    <row r="31" spans="1:4">
+      <c r="A31" s="1">
         <v>46278</v>
       </c>
-      <c r="B27">
+      <c r="B31">
         <v>3</v>
       </c>
-      <c r="C27">
-        <v>0</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="1">
         <v>46277</v>
       </c>
-      <c r="B28">
+      <c r="B32">
         <v>63</v>
       </c>
-      <c r="C28">
+      <c r="C32">
         <v>42</v>
       </c>
-      <c r="D28">
+      <c r="D32">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+    <row r="33" spans="1:4">
+      <c r="A33" s="1">
         <v>46276</v>
       </c>
-      <c r="B29">
+      <c r="B33">
         <v>19</v>
       </c>
-      <c r="C29">
+      <c r="C33">
         <v>73</v>
       </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+      <c r="D33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="1">
         <v>46275</v>
       </c>
-      <c r="B30">
+      <c r="B34">
         <v>21</v>
       </c>
-      <c r="C30">
+      <c r="C34">
         <v>16</v>
       </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+      <c r="D34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="1">
         <v>46274</v>
       </c>
-      <c r="B31">
+      <c r="B35">
         <v>47</v>
       </c>
-      <c r="C31">
+      <c r="C35">
         <v>84</v>
       </c>
-      <c r="D31">
+      <c r="D35">
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+    <row r="36" spans="1:4">
+      <c r="A36" s="1">
         <v>46273</v>
       </c>
-      <c r="B32">
+      <c r="B36">
         <v>45</v>
       </c>
-      <c r="C32">
+      <c r="C36">
         <v>105</v>
       </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+      <c r="D36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="1">
         <v>46272</v>
       </c>
-      <c r="B33">
+      <c r="B37">
         <v>38</v>
       </c>
-      <c r="C33">
+      <c r="C37">
         <v>92</v>
       </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
+      <c r="D37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="1">
         <v>46271</v>
       </c>
-      <c r="B34">
+      <c r="B38">
         <v>13</v>
       </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="1">
         <v>46270</v>
       </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-      <c r="C35">
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39">
         <v>90</v>
       </c>
-      <c r="D35">
+      <c r="D39">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
+    <row r="40" spans="1:4">
+      <c r="A40" s="1">
         <v>46269</v>
       </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-      <c r="C36">
-        <v>0</v>
-      </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
+      <c r="B40">
+        <v>0</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="1">
         <v>46268</v>
       </c>
-      <c r="B37">
+      <c r="B41">
         <v>23</v>
       </c>
-      <c r="C37">
+      <c r="C41">
         <v>74</v>
       </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
+      <c r="D41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="1">
         <v>46267</v>
       </c>
-      <c r="B38">
+      <c r="B42">
         <v>7</v>
       </c>
-      <c r="C38">
+      <c r="C42">
         <v>75</v>
       </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
+      <c r="D42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="1">
         <v>46266</v>
       </c>
-      <c r="B39">
+      <c r="B43">
         <v>17</v>
       </c>
-      <c r="C39">
-        <v>0</v>
-      </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="1">
         <v>46265</v>
       </c>
-      <c r="C40">
+      <c r="C44">
         <v>62</v>
       </c>
-      <c r="D40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
+      <c r="D44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="1">
         <v>46264</v>
       </c>
-      <c r="B41">
+      <c r="B45">
         <v>5</v>
       </c>
-      <c r="C41">
-        <v>0</v>
-      </c>
-      <c r="D41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="1">
         <v>46263</v>
       </c>
-      <c r="B42">
+      <c r="B46">
         <v>73</v>
-      </c>
-      <c r="C42">
-        <v>62</v>
-      </c>
-      <c r="D42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
-        <v>46262</v>
-      </c>
-      <c r="B43">
-        <v>67</v>
-      </c>
-      <c r="C43">
-        <v>54</v>
-      </c>
-      <c r="D43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
-        <v>46261</v>
-      </c>
-      <c r="B44">
-        <v>29</v>
-      </c>
-      <c r="C44">
-        <v>64</v>
-      </c>
-      <c r="D44">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="1">
-        <v>46260</v>
-      </c>
-      <c r="B45">
-        <v>85</v>
-      </c>
-      <c r="C45">
-        <v>62</v>
-      </c>
-      <c r="D45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
-        <v>46259</v>
-      </c>
-      <c r="B46">
-        <v>13</v>
       </c>
       <c r="C46">
         <v>62</v>
@@ -1223,288 +1223,344 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4">
       <c r="A47" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B47">
+        <v>67</v>
+      </c>
+      <c r="C47">
+        <v>54</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B48">
+        <v>29</v>
+      </c>
+      <c r="C48">
+        <v>64</v>
+      </c>
+      <c r="D48">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="1">
+        <v>46260</v>
+      </c>
+      <c r="B49">
+        <v>85</v>
+      </c>
+      <c r="C49">
+        <v>62</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B50">
+        <v>13</v>
+      </c>
+      <c r="C50">
+        <v>62</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="1">
         <v>46258</v>
       </c>
-      <c r="B47">
+      <c r="B51">
         <v>18</v>
       </c>
-      <c r="C47">
+      <c r="C51">
         <v>56</v>
       </c>
-      <c r="D47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
+      <c r="D51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="1">
         <v>46257</v>
       </c>
-      <c r="B48">
+      <c r="B52">
         <v>3</v>
       </c>
-      <c r="C48">
-        <v>0</v>
-      </c>
-      <c r="D48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="1">
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="1">
         <v>46256</v>
       </c>
-      <c r="B49">
+      <c r="B53">
         <v>69</v>
       </c>
-      <c r="C49">
+      <c r="C53">
         <v>53</v>
       </c>
-      <c r="D49">
+      <c r="D53">
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
+    <row r="54" spans="1:4">
+      <c r="A54" s="1">
         <v>46255</v>
       </c>
-      <c r="B50">
+      <c r="B54">
         <v>15</v>
       </c>
-      <c r="C50">
+      <c r="C54">
         <v>60</v>
       </c>
-      <c r="D50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
+      <c r="D54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="1">
         <v>46254</v>
       </c>
-      <c r="B51">
+      <c r="B55">
         <v>48</v>
       </c>
-      <c r="C51">
+      <c r="C55">
         <v>43</v>
       </c>
-      <c r="D51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
+      <c r="D55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="1">
         <v>46253</v>
       </c>
-      <c r="B52">
+      <c r="B56">
         <v>27</v>
       </c>
-      <c r="C52">
+      <c r="C56">
         <v>51</v>
       </c>
-      <c r="D52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
+      <c r="D56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="1">
         <v>46252</v>
       </c>
-      <c r="B53">
-        <v>0</v>
-      </c>
-      <c r="C53">
-        <v>0</v>
-      </c>
-      <c r="D53">
+      <c r="B57">
+        <v>0</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="D57">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="1">
+    <row r="58" spans="1:4">
+      <c r="A58" s="1">
         <v>46251</v>
       </c>
-      <c r="B54">
+      <c r="B58">
         <v>12</v>
       </c>
-      <c r="C54">
-        <v>0</v>
-      </c>
-      <c r="D54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="1">
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="1">
         <v>46250</v>
       </c>
-      <c r="B55">
+      <c r="B59">
         <v>12</v>
       </c>
-      <c r="C55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
+      <c r="C59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="1">
         <v>46249</v>
       </c>
-      <c r="C56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
+      <c r="C60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="1">
         <v>46248</v>
       </c>
-      <c r="B57">
+      <c r="B61">
         <v>7</v>
       </c>
-      <c r="C57">
+      <c r="C61">
         <v>16</v>
       </c>
-      <c r="D57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="1">
+      <c r="D61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="1">
         <v>46247</v>
       </c>
-      <c r="B58">
+      <c r="B62">
         <v>35</v>
       </c>
-      <c r="C58">
+      <c r="C62">
         <v>21</v>
       </c>
-      <c r="D58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
+      <c r="D62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="1">
         <v>46246</v>
       </c>
-      <c r="B59">
+      <c r="B63">
         <v>28</v>
       </c>
-      <c r="C59">
+      <c r="C63">
         <v>21</v>
       </c>
-      <c r="D59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
+      <c r="D63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="1">
         <v>46245</v>
       </c>
-      <c r="B60">
+      <c r="B64">
         <v>21</v>
       </c>
-      <c r="C60">
+      <c r="C64">
         <v>25</v>
       </c>
-      <c r="D60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
+      <c r="D64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="1">
         <v>46244</v>
       </c>
-      <c r="B61">
+      <c r="B65">
         <v>19</v>
       </c>
-      <c r="C61">
+      <c r="C65">
         <v>11</v>
       </c>
-      <c r="D61">
+      <c r="D65">
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="1">
+    <row r="66" spans="1:4">
+      <c r="A66" s="1">
         <v>46243</v>
       </c>
-      <c r="B62">
+      <c r="B66">
         <v>13</v>
       </c>
-      <c r="C62">
-        <v>0</v>
-      </c>
-      <c r="D62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="1">
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="1">
         <v>46242</v>
       </c>
-      <c r="B63">
-        <v>0</v>
-      </c>
-      <c r="C63">
-        <v>0</v>
-      </c>
-      <c r="D63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="1">
+      <c r="B67">
+        <v>0</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="1">
         <v>46241</v>
       </c>
-      <c r="B64">
+      <c r="B68">
         <v>32</v>
       </c>
-      <c r="C64">
-        <v>0</v>
-      </c>
-      <c r="D64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="1">
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="1">
         <v>46240</v>
       </c>
-      <c r="B65">
+      <c r="B69">
         <v>16</v>
       </c>
-      <c r="C65">
-        <v>0</v>
-      </c>
-      <c r="D65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="1">
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="1">
         <v>46239</v>
       </c>
-      <c r="B66">
-        <v>0</v>
-      </c>
-      <c r="C66">
-        <v>0</v>
-      </c>
-      <c r="D66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="1">
+      <c r="B70">
+        <v>0</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="1">
         <v>46238</v>
       </c>
-      <c r="B67">
-        <v>0</v>
-      </c>
-      <c r="C67">
-        <v>0</v>
-      </c>
-      <c r="D67">
+      <c r="B71">
+        <v>0</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
         <v>1</v>
       </c>
     </row>
@@ -1515,41 +1571,41 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D41FB4CD-150C-4CE3-A76E-CB540C2892DD}">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="B1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2">
         <v>9697</v>
@@ -1577,17 +1633,17 @@
         <v>661</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3">
-        <f>4375+B6</f>
-        <v>4469</v>
+        <f>4375+B6+B7</f>
+        <v>4571</v>
       </c>
       <c r="C3">
-        <f>7462+C6</f>
-        <v>7502</v>
+        <f>7462+C6+C7</f>
+        <v>7530</v>
       </c>
       <c r="D3">
         <f>D6+75</f>
@@ -1600,27 +1656,27 @@
         <v>14</v>
       </c>
       <c r="G3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H3">
         <v>8</v>
       </c>
       <c r="I3">
-        <f>I6+170</f>
-        <v>171</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <f>I6+170+I7</f>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <f>B2-B3</f>
-        <v>5228</v>
+        <v>5126</v>
       </c>
       <c r="C4">
         <f>C2-C3</f>
-        <v>4368</v>
+        <v>4340</v>
       </c>
       <c r="D4">
         <f t="shared" ref="D4:I4" si="0">D2-D3</f>
@@ -1636,18 +1692,18 @@
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H4">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="I4">
-        <f t="shared" si="0"/>
-        <v>490</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <f>I2-I3</f>
+        <v>489</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>46302</v>
       </c>
@@ -1676,7 +1732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>46303</v>
       </c>
@@ -1703,6 +1759,122 @@
       </c>
       <c r="I6">
         <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B7">
+        <v>102</v>
+      </c>
+      <c r="C7">
+        <v>28</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1">
+        <v>46305</v>
+      </c>
+      <c r="B8">
+        <v>72</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1">
+        <v>46306</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B10">
+        <v>92</v>
+      </c>
+      <c r="C10">
+        <v>26</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1713,55 +1885,55 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E384ED-EF07-4058-B570-9E7F8CBFADFB}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="9.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
         <v>25</v>
       </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1">
         <v>46336</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" s="1">
         <v>46371</v>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="887" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25E75F83-C2A8-435D-97DF-9283C3DF20EA}"/>
+  <xr:revisionPtr revIDLastSave="918" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32B96FFA-0E0C-4C6E-B4E9-84C99A8DF15B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>
@@ -53,19 +53,19 @@
     <t>ACC</t>
   </si>
   <si>
-    <t>Daily-102; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 613;Total - 5228 MT</t>
+    <t>Daily-44; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 657;Total - 5272 MT</t>
   </si>
   <si>
     <t>Boiler</t>
   </si>
   <si>
-    <t>Daily-118  - (SH-92 and RH-26); Oct-948 NDHT Balance joints - 9266 (SH - 4962; RH - 4304)</t>
+    <t>Daily-127  - (SH-93and RH-34); Oct-1075 NDHT Balance joints - 9139 (SH - 4869; RH - 4270)</t>
   </si>
   <si>
     <t>PCP Joint</t>
   </si>
   <si>
-    <t>Daily-3; MS Joints - 71/146; MS to PRDS - 11/26; HRH - 10/95; CRH -14/87; LPBP - 10/49; HPBP-8/23; BFD- 174/661</t>
+    <t>Daily-1; MS Joints - 71/146; MS to PRDS - 11/26; HRH - 10/95; CRH -14/87; LPBP - 10/49; HPBP-8/23; BFD- 174/661</t>
   </si>
   <si>
     <t>Boiler - NDHT Joints</t>
@@ -532,7 +532,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -543,7 +543,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1">
-        <v>46305</v>
+        <v>46308</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1">
-        <v>46305</v>
+        <v>46308</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -573,7 +573,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
@@ -612,55 +612,55 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B3">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="C3">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B4">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="B5">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="C5">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B6">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C6">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -668,13 +668,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B7">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C7">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -682,167 +682,167 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B8">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="C8">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B9">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C9">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B10">
         <v>45</v>
       </c>
       <c r="C10">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B11">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B12">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C12">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B14">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B15">
-        <v>321</v>
+        <v>40</v>
       </c>
       <c r="C15">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B16">
-        <v>200</v>
+        <v>321</v>
       </c>
       <c r="C16">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B17">
-        <v>43</v>
+        <v>200</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="D17">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B18">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B19">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C19">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -850,41 +850,41 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B20">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C20">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C21">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C22">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -892,13 +892,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="1">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B23">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -906,27 +906,27 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B24">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C24">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B25">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C25">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -934,21 +934,21 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="1">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B26">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C26">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D26">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="1">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B27">
         <v>16</v>
@@ -962,97 +962,97 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="1">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B28">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C28">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="1">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B29">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C29">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B30">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="C30">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="1">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="1">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B32">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="C32">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="1">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B33">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="C33">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B34">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C34">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1060,55 +1060,55 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B35">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="C35">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B36">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C36">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B37">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C37">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B38">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -1116,41 +1116,41 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="1">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C39">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="1">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="1">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B41">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -1158,27 +1158,27 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="1">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B42">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C42">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B43">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -1186,10 +1186,13 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="1">
-        <v>46265</v>
+        <v>46266</v>
+      </c>
+      <c r="B44">
+        <v>17</v>
       </c>
       <c r="C44">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -1197,97 +1200,94 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="1">
-        <v>46264</v>
-      </c>
-      <c r="B45">
-        <v>5</v>
+        <v>46265</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="1">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B46">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="C46">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B47">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C47">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B48">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C48">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B49">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="C49">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B50">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="C50">
         <v>62</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B51">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C51">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -1295,105 +1295,105 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="1">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="1">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B53">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="C53">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="1">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B54">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="C54">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B55">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="C55">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B56">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C56">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D57">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="1">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B58">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C58">
         <v>0</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="1">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B59">
         <v>12</v>
@@ -1401,10 +1401,16 @@
       <c r="C59">
         <v>0</v>
       </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="1">
-        <v>46249</v>
+        <v>46250</v>
+      </c>
+      <c r="B60">
+        <v>12</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -1412,27 +1418,21 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="1">
-        <v>46248</v>
-      </c>
-      <c r="B61">
-        <v>7</v>
+        <v>46249</v>
       </c>
       <c r="C61">
-        <v>16</v>
-      </c>
-      <c r="D61">
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B62">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="C62">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -1440,66 +1440,66 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="1">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B63">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C63">
         <v>21</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="1">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B64">
+        <v>28</v>
+      </c>
+      <c r="C64">
         <v>21</v>
       </c>
-      <c r="C64">
-        <v>25</v>
-      </c>
       <c r="D64">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="1">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B65">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C65">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D65">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="1">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B66">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="1">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B67">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -1510,10 +1510,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="1">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B68">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -1524,10 +1524,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="1">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B69">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -1538,29 +1538,43 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="1">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B70">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B71">
+        <v>0</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="1">
         <v>46238</v>
       </c>
-      <c r="B71">
-        <v>0</v>
-      </c>
-      <c r="C71">
-        <v>0</v>
-      </c>
-      <c r="D71">
+      <c r="B72">
+        <v>0</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
         <v>1</v>
       </c>
     </row>
@@ -1571,7 +1585,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D41FB4CD-150C-4CE3-A76E-CB540C2892DD}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
@@ -1875,6 +1889,35 @@
       </c>
       <c r="I10">
         <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B11">
+        <v>93</v>
+      </c>
+      <c r="C11">
+        <v>34</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="918" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32B96FFA-0E0C-4C6E-B4E9-84C99A8DF15B}"/>
+  <xr:revisionPtr revIDLastSave="945" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D51447E-2553-40BB-98F1-F3FD0BE02019}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>
@@ -53,19 +53,19 @@
     <t>ACC</t>
   </si>
   <si>
-    <t>Daily-44; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 657;Total - 5272 MT</t>
+    <t>Daily-23; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 680;Total - 5296 MT</t>
   </si>
   <si>
     <t>Boiler</t>
   </si>
   <si>
-    <t>Daily-127  - (SH-93and RH-34); Oct-1075 NDHT Balance joints - 9139 (SH - 4869; RH - 4270)</t>
+    <t>Daily-135  - (SH-101and RH-34); Oct-1210 NDHT Balance joints - 9004 (SH - 4768; RH - 4236)</t>
   </si>
   <si>
     <t>PCP Joint</t>
   </si>
   <si>
-    <t>Daily-1; MS Joints - 71/146; MS to PRDS - 11/26; HRH - 10/95; CRH -14/87; LPBP - 10/49; HPBP-8/23; BFD- 174/661</t>
+    <t>Daily-2; MS Joints - 71/146; MS to PRDS - 11/26; HRH - 10/95; CRH -14/87; LPBP - 11/49; HPBP-8/23; BFD- 174/661</t>
   </si>
   <si>
     <t>Boiler - NDHT Joints</t>
@@ -532,7 +532,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -543,7 +543,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -573,7 +573,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
@@ -612,69 +612,69 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B3">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="C3">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B4">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="C4">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B5">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="B6">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="C6">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B7">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C7">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -682,13 +682,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B8">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C8">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -696,167 +696,167 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B9">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="C9">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B10">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C10">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B11">
         <v>45</v>
       </c>
       <c r="C11">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B12">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B13">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C13">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B15">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B16">
-        <v>321</v>
+        <v>40</v>
       </c>
       <c r="C16">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B17">
-        <v>200</v>
+        <v>321</v>
       </c>
       <c r="C17">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B18">
-        <v>43</v>
+        <v>200</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="D18">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B19">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B20">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C20">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -864,41 +864,41 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B21">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C21">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C22">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C23">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -906,13 +906,13 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="1">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B24">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -920,27 +920,27 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B25">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C25">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="1">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B26">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C26">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -948,21 +948,21 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="1">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B27">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C27">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D27">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="1">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B28">
         <v>16</v>
@@ -976,97 +976,97 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="1">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B29">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C29">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="1">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C30">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B31">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="C31">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="1">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="1">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B33">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="C33">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B34">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="C34">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B35">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C35">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1074,55 +1074,55 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B36">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="C36">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="D36">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B37">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C37">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B38">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C38">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="1">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B39">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -1130,41 +1130,41 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="1">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C40">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="1">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="1">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B42">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -1172,27 +1172,27 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B43">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C43">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B44">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -1200,10 +1200,13 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="1">
-        <v>46265</v>
+        <v>46266</v>
+      </c>
+      <c r="B45">
+        <v>17</v>
       </c>
       <c r="C45">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -1211,97 +1214,94 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="1">
-        <v>46264</v>
-      </c>
-      <c r="B46">
-        <v>5</v>
+        <v>46265</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B47">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="C47">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="1">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B48">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C48">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B49">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C49">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B50">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="C50">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B51">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="C51">
         <v>62</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B52">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C52">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -1309,105 +1309,105 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="1">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="1">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B54">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="C54">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="1">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B55">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="C55">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B56">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="C56">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B57">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C57">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D58">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="1">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B59">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="1">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B60">
         <v>12</v>
@@ -1415,10 +1415,16 @@
       <c r="C60">
         <v>0</v>
       </c>
+      <c r="D60">
+        <v>1</v>
+      </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="1">
-        <v>46249</v>
+        <v>46250</v>
+      </c>
+      <c r="B61">
+        <v>12</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -1426,27 +1432,21 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="1">
-        <v>46248</v>
-      </c>
-      <c r="B62">
-        <v>7</v>
+        <v>46249</v>
       </c>
       <c r="C62">
-        <v>16</v>
-      </c>
-      <c r="D62">
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B63">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="C63">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -1454,66 +1454,66 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="1">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B64">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C64">
         <v>21</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="1">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B65">
+        <v>28</v>
+      </c>
+      <c r="C65">
         <v>21</v>
       </c>
-      <c r="C65">
-        <v>25</v>
-      </c>
       <c r="D65">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="1">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B66">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C66">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="1">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B67">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="1">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -1524,10 +1524,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="1">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B69">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -1538,10 +1538,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="1">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B70">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -1552,29 +1552,43 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="1">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B71">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B72">
+        <v>0</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="1">
         <v>46238</v>
       </c>
-      <c r="B72">
-        <v>0</v>
-      </c>
-      <c r="C72">
-        <v>0</v>
-      </c>
-      <c r="D72">
+      <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
         <v>1</v>
       </c>
     </row>
@@ -1585,7 +1599,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D41FB4CD-150C-4CE3-A76E-CB540C2892DD}">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
@@ -1917,6 +1931,32 @@
         <v>0</v>
       </c>
       <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B12">
+        <v>101</v>
+      </c>
+      <c r="C12">
+        <v>34</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
         <v>0</v>
       </c>
     </row>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="945" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D51447E-2553-40BB-98F1-F3FD0BE02019}"/>
+  <xr:revisionPtr revIDLastSave="1050" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BC890AD-59E6-460D-936A-78C357212D7D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>
@@ -53,21 +53,12 @@
     <t>ACC</t>
   </si>
   <si>
-    <t>Daily-23; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 680;Total - 5296 MT</t>
-  </si>
-  <si>
     <t>Boiler</t>
   </si>
   <si>
-    <t>Daily-135  - (SH-101and RH-34); Oct-1210 NDHT Balance joints - 9004 (SH - 4768; RH - 4236)</t>
-  </si>
-  <si>
     <t>PCP Joint</t>
   </si>
   <si>
-    <t>Daily-2; MS Joints - 71/146; MS to PRDS - 11/26; HRH - 10/95; CRH -14/87; LPBP - 11/49; HPBP-8/23; BFD- 174/661</t>
-  </si>
-  <si>
     <t>Boiler - NDHT Joints</t>
   </si>
   <si>
@@ -129,15 +120,36 @@
   </si>
   <si>
     <t>Segment-5</t>
+  </si>
+  <si>
+    <t>Daily-1; MS Joints - 72/146; MS to PRDS - 11/26; HRH - 10/95; CRH -14/87; LPBP - 11/49; HPBP-8/23; BFD- 176/661</t>
+  </si>
+  <si>
+    <t>Daily-26; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 436;Total - 5351 MT</t>
+  </si>
+  <si>
+    <t>Daily-122  - (SH-84and RH-38); Oct-1332 NDHT Balance joints - 8882 (SH - 4684; RH - 4198)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -149,13 +161,69 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -167,15 +235,97 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="22" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="22" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="34">
+    <cellStyle name="20% - Accent5 9" xfId="29" xr:uid="{83B76E04-2387-4B96-B399-6CA28CB9C921}"/>
+    <cellStyle name="20% - Accent5 9 98 9 51" xfId="32" xr:uid="{E9B08F62-33F7-462D-93D0-323D948290BA}"/>
+    <cellStyle name="Bad" xfId="1" builtinId="27"/>
+    <cellStyle name="Comma 2" xfId="6" xr:uid="{F6BFF238-A680-4EFF-88CD-3B1B0161DFB8}"/>
+    <cellStyle name="Comma 2 2" xfId="20" xr:uid="{F8181E47-271F-44A7-A3FE-D1D71E72085E}"/>
+    <cellStyle name="Comma 2 3" xfId="14" xr:uid="{9342E52E-E1A0-4A09-806F-16FE3F3ED1E4}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 10" xfId="22" xr:uid="{3BEC51BE-D192-4742-A0BF-B4BA433E0670}"/>
+    <cellStyle name="Normal 12 2" xfId="33" xr:uid="{8959DB9C-3142-494E-A942-A0F807A479B3}"/>
+    <cellStyle name="Normal 2" xfId="7" xr:uid="{A9838CAC-2E1D-4D9F-9EF9-E0E63D3517C4}"/>
+    <cellStyle name="Normal 2 11" xfId="4" xr:uid="{1602A16A-A7C7-4745-9ACA-2163ED8C3A54}"/>
+    <cellStyle name="Normal 2 2 2 17" xfId="28" xr:uid="{A65F04AB-0239-4174-B67B-5165C6E9BECA}"/>
+    <cellStyle name="Normal 2 2 2 17 98 9 51" xfId="31" xr:uid="{DDD75516-4494-4991-A2F3-537C0F984288}"/>
+    <cellStyle name="Normal 2 2 2 2" xfId="10" xr:uid="{D7BE154F-0C63-4FBB-874D-BB96EA40BC46}"/>
+    <cellStyle name="Normal 2_Du Detail" xfId="19" xr:uid="{B1CF3FC9-38B2-48DA-A19B-B20509994EF2}"/>
+    <cellStyle name="Normal 22" xfId="26" xr:uid="{DC7FA359-8D69-4F24-9A51-EB83B2A0A99D}"/>
+    <cellStyle name="Normal 22 98 9 51" xfId="30" xr:uid="{6ECBDAC6-51EC-4D63-B322-705D3CCC1112}"/>
+    <cellStyle name="Normal 3" xfId="8" xr:uid="{898637E5-8B84-4EE7-8C2F-9FFC90D6F088}"/>
+    <cellStyle name="Normal 3 2" xfId="11" xr:uid="{2317BB1C-FE94-4760-8167-2D6E649F7297}"/>
+    <cellStyle name="Normal 4" xfId="5" xr:uid="{7FD18CA3-00B3-4DBC-AB80-C925C182656E}"/>
+    <cellStyle name="Normal 5" xfId="9" xr:uid="{94863BD6-9710-47E7-B69A-61DE818B594A}"/>
+    <cellStyle name="Normal 5 2" xfId="12" xr:uid="{36C27247-C288-428B-8BF8-0C6CED851065}"/>
+    <cellStyle name="Normal 5 2 2" xfId="16" xr:uid="{84B96D50-22C1-4046-912A-04F5F34289C3}"/>
+    <cellStyle name="Normal 6" xfId="13" xr:uid="{D2B614C2-AB2F-491F-B9D6-F12C6596BFDB}"/>
+    <cellStyle name="Normal 6 2" xfId="15" xr:uid="{F84646AA-0A17-4A3B-A397-1461B63AEB18}"/>
+    <cellStyle name="Normal 6 3" xfId="23" xr:uid="{6D0328E3-CF7E-4A63-BA55-9751245311F1}"/>
+    <cellStyle name="Normal 6_Du Detail" xfId="25" xr:uid="{7FD08EAE-CE27-4C7E-BDBF-44673BDDB1F6}"/>
+    <cellStyle name="Normal 7" xfId="17" xr:uid="{754A35EA-F378-4CE0-A1A3-0973069E9DC0}"/>
+    <cellStyle name="Normal 7 2" xfId="24" xr:uid="{7EE310CB-54C3-4501-B37D-E34DE2A0F2A5}"/>
+    <cellStyle name="Normal 7_Du Detail" xfId="21" xr:uid="{CEFE62EF-08D5-4F02-9A50-430497EA831D}"/>
+    <cellStyle name="Normal 8" xfId="18" xr:uid="{AEC90A00-016F-4DCF-909E-72954C023E8A}"/>
+    <cellStyle name="Normal 9" xfId="2" xr:uid="{C0442E06-09A9-4EB8-A419-861957760B34}"/>
+    <cellStyle name="Percent 2" xfId="3" xr:uid="{D4ECF4DB-59CC-49E5-B26D-B71A761533FC}"/>
+    <cellStyle name="Title 2" xfId="27" xr:uid="{4CF40618-97A1-49D9-9269-557741BF9292}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
@@ -513,13 +663,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="93" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -530,37 +680,37 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1">
-        <v>46309</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1">
-        <v>46309</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -573,8 +723,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
-  <dimension ref="A1:D73"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <dimension ref="A1:AA74"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
@@ -582,7 +732,7 @@
     <col min="5" max="6" width="11.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -590,15 +740,15 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>30</v>
@@ -609,374 +759,440 @@
       <c r="D2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B3">
+        <v>56</v>
+      </c>
+      <c r="C3">
+        <v>122</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6">
+        <v>20.72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>46309</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>23</v>
       </c>
-      <c r="C3">
+      <c r="C4">
         <v>135</v>
       </c>
-      <c r="D3">
+      <c r="D4">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1">
+      <c r="E4" s="6">
+        <v>16.425999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>46308</v>
       </c>
-      <c r="B4">
+      <c r="B5">
         <v>44</v>
       </c>
-      <c r="C4">
+      <c r="C5">
         <v>127</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1">
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6">
+        <v>18.917999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>46307</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>102</v>
       </c>
-      <c r="C5">
+      <c r="C6">
         <v>118</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1">
+      <c r="E6" s="6">
+        <v>7.9720000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>46306</v>
       </c>
-      <c r="B6">
+      <c r="B7">
         <v>21</v>
       </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1">
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>46305</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>83</v>
       </c>
-      <c r="C7">
+      <c r="C8">
         <v>82</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1">
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>46304</v>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>74</v>
       </c>
-      <c r="C8">
+      <c r="C9">
         <v>130</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1">
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="6">
+        <v>4.3440000000000003</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="3"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="3"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="X9" s="3"/>
+      <c r="Y9" s="2"/>
+      <c r="Z9" s="2"/>
+      <c r="AA9" s="2"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>46303</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>70</v>
       </c>
-      <c r="C9">
+      <c r="C10">
         <v>134</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1">
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" s="6"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>46302</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>26</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>91</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1">
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>46301</v>
-      </c>
-      <c r="B11">
-        <v>45</v>
-      </c>
-      <c r="C11">
-        <v>104</v>
-      </c>
-      <c r="D11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1">
-        <v>46300</v>
       </c>
       <c r="B12">
         <v>45</v>
       </c>
       <c r="C12">
+        <v>104</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12" s="6">
+        <v>4.5679999999999996</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B13">
+        <v>45</v>
+      </c>
+      <c r="C13">
         <v>123</v>
       </c>
-      <c r="D12">
+      <c r="D13">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="1">
+      <c r="E13" s="6">
+        <v>6.4130000000000003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>46299</v>
       </c>
-      <c r="B13">
+      <c r="B14">
         <v>66</v>
       </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="1">
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6">
+        <v>4.3440000000000003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>46298</v>
       </c>
-      <c r="B14">
+      <c r="B15">
         <v>40</v>
       </c>
-      <c r="C14">
+      <c r="C15">
         <v>65</v>
       </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="1">
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="6"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>46297</v>
       </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="1">
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16" s="6"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
         <v>46296</v>
       </c>
-      <c r="B16">
+      <c r="B17">
         <v>40</v>
       </c>
-      <c r="C16">
+      <c r="C17">
         <v>101</v>
       </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="1">
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>46295</v>
       </c>
-      <c r="B17">
+      <c r="B18">
         <v>321</v>
       </c>
-      <c r="C17">
+      <c r="C18">
         <v>139</v>
       </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="1">
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5">
+        <v>37.679307999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>46294</v>
       </c>
-      <c r="B18">
+      <c r="B19">
         <v>200</v>
       </c>
-      <c r="C18">
+      <c r="C19">
         <v>114</v>
       </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="1">
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5">
+        <v>33.449338000000004</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>46293</v>
       </c>
-      <c r="B19">
+      <c r="B20">
         <v>43</v>
       </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="1">
+      <c r="E20" s="5">
+        <v>42.041217999999994</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
         <v>46292</v>
       </c>
-      <c r="B20">
+      <c r="B21">
         <v>13</v>
       </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="1">
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21" s="6"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
         <v>46291</v>
       </c>
-      <c r="B21">
+      <c r="B22">
         <v>17</v>
       </c>
-      <c r="C21">
+      <c r="C22">
         <v>39</v>
       </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="1">
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22" s="5">
+        <v>16.912866999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
         <v>46290</v>
       </c>
-      <c r="B22">
+      <c r="B23">
         <v>20</v>
       </c>
-      <c r="C22">
+      <c r="C23">
         <v>121</v>
       </c>
-      <c r="D22">
+      <c r="D23">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="1">
+      <c r="E23" s="5">
+        <v>11.657306</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
         <v>46289</v>
       </c>
-      <c r="B23">
+      <c r="B24">
         <v>3</v>
       </c>
-      <c r="C23">
+      <c r="C24">
         <v>133</v>
       </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="1">
+      <c r="D24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
         <v>46288</v>
       </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-      <c r="C24">
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
         <v>143</v>
       </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="1">
+      <c r="D25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
         <v>46287</v>
       </c>
-      <c r="B25">
+      <c r="B26">
         <v>9</v>
       </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="1">
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
         <v>46286</v>
       </c>
-      <c r="B26">
+      <c r="B27">
         <v>32</v>
       </c>
-      <c r="C26">
+      <c r="C27">
         <v>131</v>
       </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="1">
+      <c r="D27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
         <v>46285</v>
       </c>
-      <c r="B27">
+      <c r="B28">
         <v>42</v>
       </c>
-      <c r="C27">
+      <c r="C28">
         <v>111</v>
       </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="1">
+      <c r="D28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
         <v>46284</v>
-      </c>
-      <c r="B28">
-        <v>16</v>
-      </c>
-      <c r="C28">
-        <v>118</v>
-      </c>
-      <c r="D28">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="1">
-        <v>46283</v>
       </c>
       <c r="B29">
         <v>16</v>
@@ -988,440 +1204,473 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B30">
+        <v>16</v>
+      </c>
+      <c r="C30">
+        <v>118</v>
+      </c>
+      <c r="D30">
+        <v>4</v>
+      </c>
+      <c r="E30" s="5">
+        <v>30.143184999999992</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
         <v>46281</v>
       </c>
-      <c r="B30">
+      <c r="B31">
         <v>33</v>
       </c>
-      <c r="C30">
+      <c r="C31">
         <v>98</v>
       </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="1">
+      <c r="D31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
         <v>46280</v>
       </c>
-      <c r="B31">
+      <c r="B32">
         <v>3</v>
       </c>
-      <c r="C31">
+      <c r="C32">
         <v>125</v>
       </c>
-      <c r="D31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="1">
+      <c r="D32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
         <v>46279</v>
       </c>
-      <c r="B32">
+      <c r="B33">
         <v>58</v>
       </c>
-      <c r="C32">
+      <c r="C33">
         <v>100</v>
       </c>
-      <c r="D32">
+      <c r="D33">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="1">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
         <v>46278</v>
       </c>
-      <c r="B33">
+      <c r="B34">
         <v>3</v>
       </c>
-      <c r="C33">
-        <v>0</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="1">
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
         <v>46277</v>
       </c>
-      <c r="B34">
+      <c r="B35">
         <v>63</v>
       </c>
-      <c r="C34">
+      <c r="C35">
         <v>42</v>
       </c>
-      <c r="D34">
+      <c r="D35">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="1">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
         <v>46276</v>
       </c>
-      <c r="B35">
+      <c r="B36">
         <v>19</v>
       </c>
-      <c r="C35">
+      <c r="C36">
         <v>73</v>
       </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="1">
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36" s="5">
+        <v>5.3833070000000003</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
         <v>46275</v>
       </c>
-      <c r="B36">
+      <c r="B37">
         <v>21</v>
       </c>
-      <c r="C36">
+      <c r="C37">
         <v>16</v>
       </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="1">
+      <c r="D37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
         <v>46274</v>
       </c>
-      <c r="B37">
+      <c r="B38">
         <v>47</v>
       </c>
-      <c r="C37">
+      <c r="C38">
         <v>84</v>
       </c>
-      <c r="D37">
+      <c r="D38">
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="1">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
         <v>46273</v>
       </c>
-      <c r="B38">
+      <c r="B39">
         <v>45</v>
       </c>
-      <c r="C38">
+      <c r="C39">
         <v>105</v>
       </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="1">
+      <c r="D39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
         <v>46272</v>
       </c>
-      <c r="B39">
+      <c r="B40">
         <v>38</v>
       </c>
-      <c r="C39">
+      <c r="C40">
         <v>92</v>
       </c>
-      <c r="D39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="1">
+      <c r="D40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
         <v>46271</v>
       </c>
-      <c r="B40">
+      <c r="B41">
         <v>13</v>
       </c>
-      <c r="C40">
-        <v>0</v>
-      </c>
-      <c r="D40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="1">
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
         <v>46270</v>
       </c>
-      <c r="B41">
-        <v>0</v>
-      </c>
-      <c r="C41">
+      <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42">
         <v>90</v>
       </c>
-      <c r="D41">
+      <c r="D42">
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="1">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
         <v>46269</v>
       </c>
-      <c r="B42">
-        <v>0</v>
-      </c>
-      <c r="C42">
-        <v>0</v>
-      </c>
-      <c r="D42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="1">
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
         <v>46268</v>
       </c>
-      <c r="B43">
+      <c r="B44">
         <v>23</v>
       </c>
-      <c r="C43">
+      <c r="C44">
         <v>74</v>
       </c>
-      <c r="D43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="1">
+      <c r="D44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
         <v>46267</v>
       </c>
-      <c r="B44">
+      <c r="B45">
         <v>7</v>
       </c>
-      <c r="C44">
+      <c r="C45">
         <v>75</v>
       </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="1">
+      <c r="D45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
         <v>46266</v>
       </c>
-      <c r="B45">
+      <c r="B46">
         <v>17</v>
       </c>
-      <c r="C45">
-        <v>0</v>
-      </c>
-      <c r="D45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="1">
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
         <v>46265</v>
       </c>
-      <c r="C46">
+      <c r="C47">
         <v>62</v>
       </c>
-      <c r="D46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="1">
+      <c r="D47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
         <v>46264</v>
       </c>
-      <c r="B47">
+      <c r="B48">
         <v>5</v>
       </c>
-      <c r="C47">
-        <v>0</v>
-      </c>
-      <c r="D47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="1">
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
         <v>46263</v>
       </c>
-      <c r="B48">
+      <c r="B49">
         <v>73</v>
       </c>
-      <c r="C48">
+      <c r="C49">
         <v>62</v>
       </c>
-      <c r="D48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="1">
+      <c r="D49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
         <v>46262</v>
       </c>
-      <c r="B49">
+      <c r="B50">
         <v>67</v>
       </c>
-      <c r="C49">
+      <c r="C50">
         <v>54</v>
       </c>
-      <c r="D49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="1">
+      <c r="D50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
         <v>46261</v>
       </c>
-      <c r="B50">
+      <c r="B51">
         <v>29</v>
       </c>
-      <c r="C50">
+      <c r="C51">
         <v>64</v>
       </c>
-      <c r="D50">
+      <c r="D51">
         <v>3</v>
       </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="1">
+      <c r="E51" s="4">
+        <v>0.21422999999999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
         <v>46260</v>
       </c>
-      <c r="B51">
+      <c r="B52">
         <v>85</v>
-      </c>
-      <c r="C51">
-        <v>62</v>
-      </c>
-      <c r="D51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="1">
-        <v>46259</v>
-      </c>
-      <c r="B52">
-        <v>13</v>
       </c>
       <c r="C52">
         <v>62</v>
       </c>
       <c r="D52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B53">
+        <v>13</v>
+      </c>
+      <c r="C53">
+        <v>62</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53" s="4">
+        <v>10.703772000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
         <v>46258</v>
       </c>
-      <c r="B53">
+      <c r="B54">
         <v>18</v>
       </c>
-      <c r="C53">
+      <c r="C54">
         <v>56</v>
       </c>
-      <c r="D53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" s="1">
+      <c r="D54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
         <v>46257</v>
       </c>
-      <c r="B54">
+      <c r="B55">
         <v>3</v>
       </c>
-      <c r="C54">
-        <v>0</v>
-      </c>
-      <c r="D54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" s="1">
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
         <v>46256</v>
       </c>
-      <c r="B55">
+      <c r="B56">
         <v>69</v>
       </c>
-      <c r="C55">
+      <c r="C56">
         <v>53</v>
       </c>
-      <c r="D55">
+      <c r="D56">
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
-      <c r="A56" s="1">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
         <v>46255</v>
       </c>
-      <c r="B56">
+      <c r="B57">
         <v>15</v>
       </c>
-      <c r="C56">
+      <c r="C57">
         <v>60</v>
       </c>
-      <c r="D56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="1">
+      <c r="D57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
         <v>46254</v>
       </c>
-      <c r="B57">
+      <c r="B58">
         <v>48</v>
       </c>
-      <c r="C57">
+      <c r="C58">
         <v>43</v>
       </c>
-      <c r="D57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="1">
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58" s="4">
+        <v>8.4293359999999993</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
         <v>46253</v>
       </c>
-      <c r="B58">
+      <c r="B59">
         <v>27</v>
       </c>
-      <c r="C58">
+      <c r="C59">
         <v>51</v>
       </c>
-      <c r="D58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" s="1">
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="G59" s="7"/>
+      <c r="H59" s="7"/>
+      <c r="I59" s="3"/>
+      <c r="J59" s="3"/>
+      <c r="K59" s="7"/>
+      <c r="L59" s="7"/>
+      <c r="M59" s="7"/>
+      <c r="N59" s="7"/>
+      <c r="O59" s="7"/>
+      <c r="P59" s="7"/>
+      <c r="Q59" s="7"/>
+      <c r="R59" s="7"/>
+      <c r="S59" s="7"/>
+      <c r="T59" s="7"/>
+      <c r="U59" s="7"/>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
         <v>46252</v>
       </c>
-      <c r="B59">
-        <v>0</v>
-      </c>
-      <c r="C59">
-        <v>0</v>
-      </c>
-      <c r="D59">
+      <c r="B60">
+        <v>0</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
         <v>2</v>
       </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="1">
+      <c r="E60" s="4">
+        <v>6.2419820000000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
         <v>46251</v>
-      </c>
-      <c r="B60">
-        <v>12</v>
-      </c>
-      <c r="C60">
-        <v>0</v>
-      </c>
-      <c r="D60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="1">
-        <v>46250</v>
       </c>
       <c r="B61">
         <v>12</v>
@@ -1429,166 +1678,189 @@
       <c r="C61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:4">
+      <c r="D61">
+        <v>1</v>
+      </c>
+      <c r="E61" s="4">
+        <v>14.777381999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
+        <v>46250</v>
+      </c>
+      <c r="B62">
+        <v>12</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
         <v>46249</v>
       </c>
-      <c r="C62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="1">
+      <c r="C63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
         <v>46248</v>
       </c>
-      <c r="B63">
+      <c r="B64">
         <v>7</v>
       </c>
-      <c r="C63">
+      <c r="C64">
         <v>16</v>
       </c>
-      <c r="D63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" s="1">
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64" s="4">
+        <v>20.847041999999995</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
         <v>46247</v>
       </c>
-      <c r="B64">
+      <c r="B65">
         <v>35</v>
-      </c>
-      <c r="C64">
-        <v>21</v>
-      </c>
-      <c r="D64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="1">
-        <v>46246</v>
-      </c>
-      <c r="B65">
-        <v>28</v>
       </c>
       <c r="C65">
         <v>21</v>
       </c>
       <c r="D65">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="E65" s="4">
+        <v>5.4199330000000003</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B66">
+        <v>28</v>
+      </c>
+      <c r="C66">
+        <v>21</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
         <v>46245</v>
       </c>
-      <c r="B66">
+      <c r="B67">
         <v>21</v>
       </c>
-      <c r="C66">
+      <c r="C67">
         <v>25</v>
       </c>
-      <c r="D66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="1">
+      <c r="D67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
         <v>46244</v>
       </c>
-      <c r="B67">
+      <c r="B68">
         <v>19</v>
       </c>
-      <c r="C67">
+      <c r="C68">
         <v>11</v>
       </c>
-      <c r="D67">
+      <c r="D68">
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="1">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
         <v>46243</v>
       </c>
-      <c r="B68">
+      <c r="B69">
         <v>13</v>
       </c>
-      <c r="C68">
-        <v>0</v>
-      </c>
-      <c r="D68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="1">
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
         <v>46242</v>
       </c>
-      <c r="B69">
-        <v>0</v>
-      </c>
-      <c r="C69">
-        <v>0</v>
-      </c>
-      <c r="D69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" s="1">
+      <c r="B70">
+        <v>0</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
         <v>46241</v>
       </c>
-      <c r="B70">
+      <c r="B71">
         <v>32</v>
       </c>
-      <c r="C70">
-        <v>0</v>
-      </c>
-      <c r="D70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" s="1">
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
         <v>46240</v>
       </c>
-      <c r="B71">
+      <c r="B72">
         <v>16</v>
       </c>
-      <c r="C71">
-        <v>0</v>
-      </c>
-      <c r="D71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" s="1">
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
         <v>46239</v>
       </c>
-      <c r="B72">
-        <v>0</v>
-      </c>
-      <c r="C72">
-        <v>0</v>
-      </c>
-      <c r="D72">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="A73" s="1">
+      <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
         <v>46238</v>
       </c>
-      <c r="B73">
-        <v>0</v>
-      </c>
-      <c r="C73">
-        <v>0</v>
-      </c>
-      <c r="D73">
+      <c r="B74">
+        <v>0</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
         <v>1</v>
       </c>
     </row>
@@ -1599,41 +1871,41 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D41FB4CD-150C-4CE3-A76E-CB540C2892DD}">
-  <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>15</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>17</v>
-      </c>
-      <c r="H1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>20</v>
       </c>
       <c r="B2">
         <v>9697</v>
@@ -1661,9 +1933,9 @@
         <v>661</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B3">
         <f>4375+B6+B7</f>
@@ -1694,9 +1966,9 @@
         <v>172</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B4">
         <f>B2-B3</f>
@@ -1707,7 +1979,7 @@
         <v>4340</v>
       </c>
       <c r="D4">
-        <f t="shared" ref="D4:I4" si="0">D2-D3</f>
+        <f t="shared" ref="D4:H4" si="0">D2-D3</f>
         <v>96</v>
       </c>
       <c r="E4">
@@ -1731,7 +2003,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46302</v>
       </c>
@@ -1760,7 +2032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46303</v>
       </c>
@@ -1789,7 +2061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46304</v>
       </c>
@@ -1818,7 +2090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46305</v>
       </c>
@@ -1847,7 +2119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46306</v>
       </c>
@@ -1876,7 +2148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46307</v>
       </c>
@@ -1905,7 +2177,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46308</v>
       </c>
@@ -1934,7 +2206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46309</v>
       </c>
@@ -1958,6 +2230,35 @@
       </c>
       <c r="I12">
         <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B13">
+        <v>84</v>
+      </c>
+      <c r="C13">
+        <v>38</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1968,62 +2269,62 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E384ED-EF07-4058-B570-9E7F8CBFADFB}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>23</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B4" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>28</v>
       </c>
       <c r="B5" s="1">
         <v>46336</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B6" s="1">
         <v>46371</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30610"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1050" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BC890AD-59E6-460D-936A-78C357212D7D}"/>
+  <xr:revisionPtr revIDLastSave="1106" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0207D9D7-DA52-46AB-9D10-CE9F5CBC1122}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
   <si>
     <t>Date</t>
   </si>
@@ -53,18 +53,30 @@
     <t>ACC</t>
   </si>
   <si>
+    <t>Daily-117; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 852;Total - 5468 MT</t>
+  </si>
+  <si>
     <t>Boiler</t>
   </si>
   <si>
+    <t>Daily-148  - (SH-110and RH-38); Oct-1480 NDHT Balance joints - 8734 (SH - 4574; RH - 4160)</t>
+  </si>
+  <si>
     <t>PCP Joint</t>
   </si>
   <si>
+    <t>Daily-2; MS Joints - 74/146; MS to PRDS - 11/26; HRH - 10/95; CRH -14/87; LPBP - 11/49; HPBP-8/23; BFD- 176/661</t>
+  </si>
+  <si>
     <t>Boiler - NDHT Joints</t>
   </si>
   <si>
     <t>PCP - P91/92</t>
   </si>
   <si>
+    <t>Duct</t>
+  </si>
+  <si>
     <t>Daily Target</t>
   </si>
   <si>
@@ -80,15 +92,15 @@
     <t>HRH</t>
   </si>
   <si>
+    <t>LPBP</t>
+  </si>
+  <si>
+    <t>HPBP</t>
+  </si>
+  <si>
     <t>CRH</t>
   </si>
   <si>
-    <t>LPBP</t>
-  </si>
-  <si>
-    <t>HPBP</t>
-  </si>
-  <si>
     <t>BFD</t>
   </si>
   <si>
@@ -120,15 +132,6 @@
   </si>
   <si>
     <t>Segment-5</t>
-  </si>
-  <si>
-    <t>Daily-1; MS Joints - 72/146; MS to PRDS - 11/26; HRH - 10/95; CRH -14/87; LPBP - 11/49; HPBP-8/23; BFD- 176/661</t>
-  </si>
-  <si>
-    <t>Daily-26; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 436;Total - 5351 MT</t>
-  </si>
-  <si>
-    <t>Daily-122  - (SH-84and RH-38); Oct-1332 NDHT Balance joints - 8882 (SH - 4684; RH - 4198)</t>
   </si>
 </sst>
 </file>
@@ -140,7 +143,7 @@
     <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -660,16 +663,54 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="700" row="1">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{6F12D3FD-BB92-43D0-8C17-F82EDB98DE2D}">
+  <we:reference id="WA200005271" version="3.0.0.4" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200005271" version="3.0.0.4" store="WA200005271" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
+      <we:customFunctionIdList>
+        <we:customFunctionIds>_xldudf_AI_TABLE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_AI_FILL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_AI_LIST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_AI_ASK</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_AI_FORMAT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_AI_EXTRACT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_AI_TRANSLATE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_AI_CHOICE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_AI_WEB</we:customFunctionIds>
+      </we:customFunctionIdList>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="93" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -680,37 +721,37 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -723,8 +764,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
-  <dimension ref="A1:AA74"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AA75"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
@@ -732,7 +773,7 @@
     <col min="5" max="6" width="11.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -740,15 +781,18 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>30</v>
@@ -763,450 +807,450 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27">
       <c r="A3" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B3">
+        <v>117</v>
+      </c>
+      <c r="C3">
+        <v>148</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27">
+      <c r="A4" s="1">
         <v>46310</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>56</v>
       </c>
-      <c r="C3">
+      <c r="C4">
         <v>122</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" s="6">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6">
         <v>20.72</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+    <row r="5" spans="1:27">
+      <c r="A5" s="1">
         <v>46309</v>
       </c>
-      <c r="B4">
+      <c r="B5">
         <v>23</v>
       </c>
-      <c r="C4">
+      <c r="C5">
         <v>135</v>
       </c>
-      <c r="D4">
+      <c r="D5">
         <v>2</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E5" s="6">
         <v>16.425999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+    <row r="6" spans="1:27">
+      <c r="A6" s="1">
         <v>46308</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>44</v>
       </c>
-      <c r="C5">
+      <c r="C6">
         <v>127</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" s="6">
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6">
         <v>18.917999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+    <row r="7" spans="1:27">
+      <c r="A7" s="1">
         <v>46307</v>
       </c>
-      <c r="B6">
+      <c r="B7">
         <v>102</v>
       </c>
-      <c r="C6">
+      <c r="C7">
         <v>118</v>
       </c>
-      <c r="D6">
+      <c r="D7">
         <v>3</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E7" s="6">
         <v>7.9720000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+    <row r="8" spans="1:27">
+      <c r="A8" s="1">
         <v>46306</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>21</v>
       </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6"/>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" spans="1:27">
+      <c r="A9" s="1">
         <v>46305</v>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>83</v>
       </c>
-      <c r="C8">
+      <c r="C9">
         <v>82</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" s="6"/>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" spans="1:27">
+      <c r="A10" s="1">
         <v>46304</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>74</v>
       </c>
-      <c r="C9">
+      <c r="C10">
         <v>130</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" s="6">
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" s="6">
         <v>4.3440000000000003</v>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="3"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="2"/>
-      <c r="Z9" s="2"/>
-      <c r="AA9" s="2"/>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+      <c r="I10" s="2"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="3"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="3"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="X10" s="3"/>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="2"/>
+      <c r="AA10" s="2"/>
+    </row>
+    <row r="11" spans="1:27">
+      <c r="A11" s="1">
         <v>46303</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>70</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>134</v>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" spans="1:27">
+      <c r="A12" s="1">
         <v>46302</v>
       </c>
-      <c r="B11">
+      <c r="B12">
         <v>26</v>
       </c>
-      <c r="C11">
+      <c r="C12">
         <v>91</v>
       </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11" s="6"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6"/>
+    </row>
+    <row r="13" spans="1:27">
+      <c r="A13" s="1">
         <v>46301</v>
-      </c>
-      <c r="B12">
-        <v>45</v>
-      </c>
-      <c r="C12">
-        <v>104</v>
-      </c>
-      <c r="D12">
-        <v>4</v>
-      </c>
-      <c r="E12" s="6">
-        <v>4.5679999999999996</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>46300</v>
       </c>
       <c r="B13">
         <v>45</v>
       </c>
       <c r="C13">
+        <v>104</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13" s="6">
+        <v>4.5679999999999996</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27">
+      <c r="A14" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B14">
+        <v>45</v>
+      </c>
+      <c r="C14">
         <v>123</v>
       </c>
-      <c r="D13">
+      <c r="D14">
         <v>2</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E14" s="6">
         <v>6.4130000000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+    <row r="15" spans="1:27">
+      <c r="A15" s="1">
         <v>46299</v>
       </c>
-      <c r="B14">
+      <c r="B15">
         <v>66</v>
       </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14" s="6">
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15" s="6">
         <v>4.3440000000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+    <row r="16" spans="1:27">
+      <c r="A16" s="1">
         <v>46298</v>
       </c>
-      <c r="B15">
+      <c r="B16">
         <v>40</v>
       </c>
-      <c r="C15">
+      <c r="C16">
         <v>65</v>
       </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="6"/>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" s="6"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="1">
         <v>46297</v>
       </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16" s="6"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="1">
         <v>46296</v>
       </c>
-      <c r="B17">
+      <c r="B18">
         <v>40</v>
       </c>
-      <c r="C17">
+      <c r="C18">
         <v>101</v>
       </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17" s="6"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" s="6"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="1">
         <v>46295</v>
       </c>
-      <c r="B18">
+      <c r="B19">
         <v>321</v>
       </c>
-      <c r="C18">
+      <c r="C19">
         <v>139</v>
       </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18" s="5">
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5">
         <v>37.679307999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+    <row r="20" spans="1:5">
+      <c r="A20" s="1">
         <v>46294</v>
       </c>
-      <c r="B19">
+      <c r="B20">
         <v>200</v>
       </c>
-      <c r="C19">
+      <c r="C20">
         <v>114</v>
       </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19" s="5">
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" s="5">
         <v>33.449338000000004</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+    <row r="21" spans="1:5">
+      <c r="A21" s="1">
         <v>46293</v>
       </c>
-      <c r="B20">
+      <c r="B21">
         <v>43</v>
       </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
         <v>4</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E21" s="5">
         <v>42.041217999999994</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+    <row r="22" spans="1:5">
+      <c r="A22" s="1">
         <v>46292</v>
       </c>
-      <c r="B21">
+      <c r="B22">
         <v>13</v>
       </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21" s="6"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22" s="6"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="1">
         <v>46291</v>
       </c>
-      <c r="B22">
+      <c r="B23">
         <v>17</v>
       </c>
-      <c r="C22">
+      <c r="C23">
         <v>39</v>
       </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22" s="5">
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5">
         <v>16.912866999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+    <row r="24" spans="1:5">
+      <c r="A24" s="1">
         <v>46290</v>
       </c>
-      <c r="B23">
+      <c r="B24">
         <v>20</v>
       </c>
-      <c r="C23">
+      <c r="C24">
         <v>121</v>
       </c>
-      <c r="D23">
+      <c r="D24">
         <v>2</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E24" s="5">
         <v>11.657306</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+    <row r="25" spans="1:5">
+      <c r="A25" s="1">
         <v>46289</v>
       </c>
-      <c r="B24">
+      <c r="B25">
         <v>3</v>
       </c>
-      <c r="C24">
+      <c r="C25">
         <v>133</v>
       </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+      <c r="D25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="1">
         <v>46288</v>
       </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="C25">
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
         <v>143</v>
       </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
+      <c r="D26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="1">
         <v>46287</v>
       </c>
-      <c r="B26">
+      <c r="B27">
         <v>9</v>
       </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="1">
         <v>46286</v>
       </c>
-      <c r="B27">
+      <c r="B28">
         <v>32</v>
       </c>
-      <c r="C27">
+      <c r="C28">
         <v>131</v>
       </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+      <c r="D28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="1">
         <v>46285</v>
       </c>
-      <c r="B28">
+      <c r="B29">
         <v>42</v>
       </c>
-      <c r="C28">
+      <c r="C29">
         <v>111</v>
       </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+      <c r="D29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="1">
         <v>46284</v>
-      </c>
-      <c r="B29">
-        <v>16</v>
-      </c>
-      <c r="C29">
-        <v>118</v>
-      </c>
-      <c r="D29">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
-        <v>46283</v>
       </c>
       <c r="B30">
         <v>16</v>
@@ -1217,477 +1261,474 @@
       <c r="D30">
         <v>4</v>
       </c>
-      <c r="E30" s="5">
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B31">
+        <v>16</v>
+      </c>
+      <c r="C31">
+        <v>118</v>
+      </c>
+      <c r="D31">
+        <v>4</v>
+      </c>
+      <c r="E31" s="5">
         <v>30.143184999999992</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+    <row r="32" spans="1:5">
+      <c r="A32" s="1">
         <v>46281</v>
       </c>
-      <c r="B31">
+      <c r="B32">
         <v>33</v>
       </c>
-      <c r="C31">
+      <c r="C32">
         <v>98</v>
       </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+      <c r="D32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="1">
         <v>46280</v>
       </c>
-      <c r="B32">
+      <c r="B33">
         <v>3</v>
       </c>
-      <c r="C32">
+      <c r="C33">
         <v>125</v>
       </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+      <c r="D33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="1">
         <v>46279</v>
       </c>
-      <c r="B33">
+      <c r="B34">
         <v>58</v>
       </c>
-      <c r="C33">
+      <c r="C34">
         <v>100</v>
       </c>
-      <c r="D33">
+      <c r="D34">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
+    <row r="35" spans="1:5">
+      <c r="A35" s="1">
         <v>46278</v>
       </c>
-      <c r="B34">
+      <c r="B35">
         <v>3</v>
       </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="1">
         <v>46277</v>
       </c>
-      <c r="B35">
+      <c r="B36">
         <v>63</v>
       </c>
-      <c r="C35">
+      <c r="C36">
         <v>42</v>
       </c>
-      <c r="D35">
+      <c r="D36">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
+    <row r="37" spans="1:5">
+      <c r="A37" s="1">
         <v>46276</v>
       </c>
-      <c r="B36">
+      <c r="B37">
         <v>19</v>
       </c>
-      <c r="C36">
+      <c r="C37">
         <v>73</v>
       </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-      <c r="E36" s="5">
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37" s="5">
         <v>5.3833070000000003</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
+    <row r="38" spans="1:5">
+      <c r="A38" s="1">
         <v>46275</v>
       </c>
-      <c r="B37">
+      <c r="B38">
         <v>21</v>
       </c>
-      <c r="C37">
+      <c r="C38">
         <v>16</v>
       </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
+      <c r="D38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="1">
         <v>46274</v>
       </c>
-      <c r="B38">
+      <c r="B39">
         <v>47</v>
       </c>
-      <c r="C38">
+      <c r="C39">
         <v>84</v>
       </c>
-      <c r="D38">
+      <c r="D39">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
+    <row r="40" spans="1:5">
+      <c r="A40" s="1">
         <v>46273</v>
       </c>
-      <c r="B39">
+      <c r="B40">
         <v>45</v>
       </c>
-      <c r="C39">
+      <c r="C40">
         <v>105</v>
       </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
+      <c r="D40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="1">
         <v>46272</v>
       </c>
-      <c r="B40">
+      <c r="B41">
         <v>38</v>
       </c>
-      <c r="C40">
+      <c r="C41">
         <v>92</v>
       </c>
-      <c r="D40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
+      <c r="D41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="1">
         <v>46271</v>
       </c>
-      <c r="B41">
+      <c r="B42">
         <v>13</v>
       </c>
-      <c r="C41">
-        <v>0</v>
-      </c>
-      <c r="D41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="1">
         <v>46270</v>
       </c>
-      <c r="B42">
-        <v>0</v>
-      </c>
-      <c r="C42">
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
         <v>90</v>
       </c>
-      <c r="D42">
+      <c r="D43">
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
+    <row r="44" spans="1:5">
+      <c r="A44" s="1">
         <v>46269</v>
       </c>
-      <c r="B43">
-        <v>0</v>
-      </c>
-      <c r="C43">
-        <v>0</v>
-      </c>
-      <c r="D43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="1">
         <v>46268</v>
       </c>
-      <c r="B44">
+      <c r="B45">
         <v>23</v>
       </c>
-      <c r="C44">
+      <c r="C45">
         <v>74</v>
       </c>
-      <c r="D44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1">
+      <c r="D45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="1">
         <v>46267</v>
       </c>
-      <c r="B45">
+      <c r="B46">
         <v>7</v>
       </c>
-      <c r="C45">
+      <c r="C46">
         <v>75</v>
       </c>
-      <c r="D45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
+      <c r="D46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="1">
         <v>46266</v>
       </c>
-      <c r="B46">
+      <c r="B47">
         <v>17</v>
       </c>
-      <c r="C46">
-        <v>0</v>
-      </c>
-      <c r="D46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="1">
         <v>46265</v>
       </c>
-      <c r="C47">
+      <c r="C48">
         <v>62</v>
       </c>
-      <c r="D47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
+      <c r="D48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21">
+      <c r="A49" s="1">
         <v>46264</v>
       </c>
-      <c r="B48">
+      <c r="B49">
         <v>5</v>
       </c>
-      <c r="C48">
-        <v>0</v>
-      </c>
-      <c r="D48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A49" s="1">
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21">
+      <c r="A50" s="1">
         <v>46263</v>
       </c>
-      <c r="B49">
+      <c r="B50">
         <v>73</v>
       </c>
-      <c r="C49">
+      <c r="C50">
         <v>62</v>
       </c>
-      <c r="D49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
+      <c r="D50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21">
+      <c r="A51" s="1">
         <v>46262</v>
       </c>
-      <c r="B50">
+      <c r="B51">
         <v>67</v>
       </c>
-      <c r="C50">
+      <c r="C51">
         <v>54</v>
       </c>
-      <c r="D50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
+      <c r="D51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21">
+      <c r="A52" s="1">
         <v>46261</v>
       </c>
-      <c r="B51">
+      <c r="B52">
         <v>29</v>
       </c>
-      <c r="C51">
+      <c r="C52">
         <v>64</v>
       </c>
-      <c r="D51">
+      <c r="D52">
         <v>3</v>
       </c>
-      <c r="E51" s="4">
+      <c r="E52" s="4">
         <v>0.21422999999999998</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
+    <row r="53" spans="1:21">
+      <c r="A53" s="1">
         <v>46260</v>
       </c>
-      <c r="B52">
+      <c r="B53">
         <v>85</v>
-      </c>
-      <c r="C52">
-        <v>62</v>
-      </c>
-      <c r="D52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
-        <v>46259</v>
-      </c>
-      <c r="B53">
-        <v>13</v>
       </c>
       <c r="C53">
         <v>62</v>
       </c>
       <c r="D53">
-        <v>1</v>
-      </c>
-      <c r="E53" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21">
+      <c r="A54" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B54">
+        <v>13</v>
+      </c>
+      <c r="C54">
+        <v>62</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54" s="4">
         <v>10.703772000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A54" s="1">
+    <row r="55" spans="1:21">
+      <c r="A55" s="1">
         <v>46258</v>
       </c>
-      <c r="B54">
+      <c r="B55">
         <v>18</v>
       </c>
-      <c r="C54">
+      <c r="C55">
         <v>56</v>
       </c>
-      <c r="D54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A55" s="1">
+      <c r="D55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21">
+      <c r="A56" s="1">
         <v>46257</v>
       </c>
-      <c r="B55">
+      <c r="B56">
         <v>3</v>
       </c>
-      <c r="C55">
-        <v>0</v>
-      </c>
-      <c r="D55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21">
+      <c r="A57" s="1">
         <v>46256</v>
       </c>
-      <c r="B56">
+      <c r="B57">
         <v>69</v>
       </c>
-      <c r="C56">
+      <c r="C57">
         <v>53</v>
       </c>
-      <c r="D56">
+      <c r="D57">
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
+    <row r="58" spans="1:21">
+      <c r="A58" s="1">
         <v>46255</v>
       </c>
-      <c r="B57">
+      <c r="B58">
         <v>15</v>
       </c>
-      <c r="C57">
+      <c r="C58">
         <v>60</v>
       </c>
-      <c r="D57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A58" s="1">
+      <c r="D58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21">
+      <c r="A59" s="1">
         <v>46254</v>
       </c>
-      <c r="B58">
+      <c r="B59">
         <v>48</v>
       </c>
-      <c r="C58">
+      <c r="C59">
         <v>43</v>
       </c>
-      <c r="D58">
-        <v>0</v>
-      </c>
-      <c r="E58" s="4">
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59" s="4">
         <v>8.4293359999999993</v>
       </c>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
+    <row r="60" spans="1:21">
+      <c r="A60" s="1">
         <v>46253</v>
       </c>
-      <c r="B59">
+      <c r="B60">
         <v>27</v>
       </c>
-      <c r="C59">
+      <c r="C60">
         <v>51</v>
       </c>
-      <c r="D59">
-        <v>1</v>
-      </c>
-      <c r="G59" s="7"/>
-      <c r="H59" s="7"/>
-      <c r="I59" s="3"/>
-      <c r="J59" s="3"/>
-      <c r="K59" s="7"/>
-      <c r="L59" s="7"/>
-      <c r="M59" s="7"/>
-      <c r="N59" s="7"/>
-      <c r="O59" s="7"/>
-      <c r="P59" s="7"/>
-      <c r="Q59" s="7"/>
-      <c r="R59" s="7"/>
-      <c r="S59" s="7"/>
-      <c r="T59" s="7"/>
-      <c r="U59" s="7"/>
-    </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
+      <c r="D60">
+        <v>1</v>
+      </c>
+      <c r="G60" s="7"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="3"/>
+      <c r="J60" s="3"/>
+      <c r="K60" s="7"/>
+      <c r="L60" s="7"/>
+      <c r="M60" s="7"/>
+      <c r="N60" s="7"/>
+      <c r="O60" s="7"/>
+      <c r="P60" s="7"/>
+      <c r="Q60" s="7"/>
+      <c r="R60" s="7"/>
+      <c r="S60" s="7"/>
+      <c r="T60" s="7"/>
+      <c r="U60" s="7"/>
+    </row>
+    <row r="61" spans="1:21">
+      <c r="A61" s="1">
         <v>46252</v>
       </c>
-      <c r="B60">
-        <v>0</v>
-      </c>
-      <c r="C60">
-        <v>0</v>
-      </c>
-      <c r="D60">
+      <c r="B61">
+        <v>0</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
         <v>2</v>
       </c>
-      <c r="E60" s="4">
+      <c r="E61" s="4">
         <v>6.2419820000000001</v>
       </c>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
+    <row r="62" spans="1:21">
+      <c r="A62" s="1">
         <v>46251</v>
-      </c>
-      <c r="B61">
-        <v>12</v>
-      </c>
-      <c r="C61">
-        <v>0</v>
-      </c>
-      <c r="D61">
-        <v>1</v>
-      </c>
-      <c r="E61" s="4">
-        <v>14.777381999999999</v>
-      </c>
-    </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A62" s="1">
-        <v>46250</v>
       </c>
       <c r="B62">
         <v>12</v>
@@ -1695,172 +1736,189 @@
       <c r="C62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="E62" s="4">
+        <v>14.777381999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21">
       <c r="A63" s="1">
+        <v>46250</v>
+      </c>
+      <c r="B63">
+        <v>12</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21">
+      <c r="A64" s="1">
         <v>46249</v>
       </c>
-      <c r="C63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A64" s="1">
+      <c r="C64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="1">
         <v>46248</v>
       </c>
-      <c r="B64">
+      <c r="B65">
         <v>7</v>
       </c>
-      <c r="C64">
+      <c r="C65">
         <v>16</v>
       </c>
-      <c r="D64">
-        <v>0</v>
-      </c>
-      <c r="E64" s="4">
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65" s="4">
         <v>20.847041999999995</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="1">
+    <row r="66" spans="1:5">
+      <c r="A66" s="1">
         <v>46247</v>
       </c>
-      <c r="B65">
+      <c r="B66">
         <v>35</v>
-      </c>
-      <c r="C65">
-        <v>21</v>
-      </c>
-      <c r="D65">
-        <v>0</v>
-      </c>
-      <c r="E65" s="4">
-        <v>5.4199330000000003</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="1">
-        <v>46246</v>
-      </c>
-      <c r="B66">
-        <v>28</v>
       </c>
       <c r="C66">
         <v>21</v>
       </c>
       <c r="D66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E66" s="4">
+        <v>5.4199330000000003</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
       <c r="A67" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B67">
+        <v>28</v>
+      </c>
+      <c r="C67">
+        <v>21</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="1">
         <v>46245</v>
       </c>
-      <c r="B67">
+      <c r="B68">
         <v>21</v>
       </c>
-      <c r="C67">
+      <c r="C68">
         <v>25</v>
       </c>
-      <c r="D67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="1">
+      <c r="D68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="1">
         <v>46244</v>
       </c>
-      <c r="B68">
+      <c r="B69">
         <v>19</v>
       </c>
-      <c r="C68">
+      <c r="C69">
         <v>11</v>
       </c>
-      <c r="D68">
+      <c r="D69">
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="1">
+    <row r="70" spans="1:5">
+      <c r="A70" s="1">
         <v>46243</v>
       </c>
-      <c r="B69">
+      <c r="B70">
         <v>13</v>
       </c>
-      <c r="C69">
-        <v>0</v>
-      </c>
-      <c r="D69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="1">
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="1">
         <v>46242</v>
       </c>
-      <c r="B70">
-        <v>0</v>
-      </c>
-      <c r="C70">
-        <v>0</v>
-      </c>
-      <c r="D70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="1">
+      <c r="B71">
+        <v>0</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="1">
         <v>46241</v>
       </c>
-      <c r="B71">
+      <c r="B72">
         <v>32</v>
       </c>
-      <c r="C71">
-        <v>0</v>
-      </c>
-      <c r="D71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="1">
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="1">
         <v>46240</v>
       </c>
-      <c r="B72">
+      <c r="B73">
         <v>16</v>
       </c>
-      <c r="C72">
-        <v>0</v>
-      </c>
-      <c r="D72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="1">
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="1">
         <v>46239</v>
       </c>
-      <c r="B73">
-        <v>0</v>
-      </c>
-      <c r="C73">
-        <v>0</v>
-      </c>
-      <c r="D73">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="1">
+      <c r="B74">
+        <v>0</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="1">
         <v>46238</v>
       </c>
-      <c r="B74">
-        <v>0</v>
-      </c>
-      <c r="C74">
-        <v>0</v>
-      </c>
-      <c r="D74">
+      <c r="B75">
+        <v>0</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
         <v>1</v>
       </c>
     </row>
@@ -1871,41 +1929,44 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D41FB4CD-150C-4CE3-A76E-CB540C2892DD}">
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J14"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="B1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B2">
         <v>9697</v>
@@ -1921,66 +1982,77 @@
         <v>95</v>
       </c>
       <c r="F2">
+        <v>49</v>
+      </c>
+      <c r="G2">
+        <v>23</v>
+      </c>
+      <c r="H2">
         <v>87</v>
-      </c>
-      <c r="G2">
-        <v>49</v>
-      </c>
-      <c r="H2">
-        <v>23</v>
       </c>
       <c r="I2">
         <v>661</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J2">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B3">
-        <f>4375+B6+B7</f>
-        <v>4571</v>
+        <f>4375+SUM(B6:B500)</f>
+        <v>5123</v>
       </c>
       <c r="C3">
-        <f>7462+C6+C7</f>
-        <v>7530</v>
+        <f>7462+SUM(C6:C100)</f>
+        <v>7710</v>
       </c>
       <c r="D3">
-        <f>D6+75</f>
-        <v>76</v>
+        <f>75+SUM(D5:D100)</f>
+        <v>80</v>
       </c>
       <c r="E3">
+        <f>10+SUM(E5:E150)</f>
         <v>10</v>
       </c>
       <c r="F3">
+        <f>10+SUM(F5:F100)</f>
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <f>8+SUM(G5:G100)</f>
+        <v>8</v>
+      </c>
+      <c r="H3">
+        <f>14+SUM(H5:H100)</f>
         <v>14</v>
       </c>
-      <c r="G3">
-        <v>10</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
       <c r="I3">
-        <f>I6+170+I7</f>
-        <v>172</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <f>170+SUM(I5:I150)</f>
+        <v>177</v>
+      </c>
+      <c r="J3">
+        <f>1195+SUM(J5:J200)</f>
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <f>B2-B3</f>
-        <v>5126</v>
+        <v>4574</v>
       </c>
       <c r="C4">
         <f>C2-C3</f>
-        <v>4340</v>
+        <v>4160</v>
       </c>
       <c r="D4">
-        <f t="shared" ref="D4:H4" si="0">D2-D3</f>
-        <v>96</v>
+        <f t="shared" ref="D4:G4" si="0">D2-D3</f>
+        <v>92</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
@@ -1988,22 +2060,26 @@
       </c>
       <c r="F4">
         <f t="shared" si="0"/>
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H4">
-        <f t="shared" si="0"/>
-        <v>15</v>
+        <f>H2-H3</f>
+        <v>73</v>
       </c>
       <c r="I4">
         <f>I2-I3</f>
-        <v>489</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>484</v>
+      </c>
+      <c r="J4">
+        <f>J2-J3</f>
+        <v>3237</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="1">
         <v>46302</v>
       </c>
@@ -2031,8 +2107,11 @@
       <c r="I5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="1">
         <v>46303</v>
       </c>
@@ -2060,8 +2139,11 @@
       <c r="I6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J6" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="1">
         <v>46304</v>
       </c>
@@ -2078,10 +2160,10 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -2089,8 +2171,11 @@
       <c r="I7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J7" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="1">
         <v>46305</v>
       </c>
@@ -2118,8 +2203,11 @@
       <c r="I8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J8" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="1">
         <v>46306</v>
       </c>
@@ -2147,8 +2235,11 @@
       <c r="I9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="1">
         <v>46307</v>
       </c>
@@ -2176,8 +2267,11 @@
       <c r="I10">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J10" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="1">
         <v>46308</v>
       </c>
@@ -2205,8 +2299,11 @@
       <c r="I11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J11" s="6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="1">
         <v>46309</v>
       </c>
@@ -2220,10 +2317,10 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -2231,8 +2328,11 @@
       <c r="I12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J12" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="1">
         <v>46310</v>
       </c>
@@ -2260,6 +2360,21 @@
       <c r="I13">
         <v>2</v>
       </c>
+      <c r="J13" s="6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B14">
+        <v>110</v>
+      </c>
+      <c r="C14">
+        <v>38</v>
+      </c>
+      <c r="J14" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2269,55 +2384,55 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E384ED-EF07-4058-B570-9E7F8CBFADFB}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="9.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B5" s="1">
         <v>46336</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B6" s="1">
         <v>46371</v>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30610"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1106" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0207D9D7-DA52-46AB-9D10-CE9F5CBC1122}"/>
+  <xr:revisionPtr revIDLastSave="1115" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FC07B2B-5C12-41A0-B585-7C4A558E4EF0}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>
@@ -143,7 +143,7 @@
     <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -704,13 +704,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="93" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -721,7 +721,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46311</v>
       </c>
@@ -732,7 +732,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46311</v>
       </c>
@@ -743,7 +743,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46311</v>
       </c>
@@ -765,7 +765,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
   <dimension ref="A1:AA75"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
@@ -773,7 +773,7 @@
     <col min="5" max="6" width="11.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -790,7 +790,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -801,13 +801,13 @@
         <v>200</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:27">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46311</v>
       </c>
@@ -820,8 +820,11 @@
       <c r="D3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:27">
+      <c r="E3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46310</v>
       </c>
@@ -838,7 +841,7 @@
         <v>20.72</v>
       </c>
     </row>
-    <row r="5" spans="1:27">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46309</v>
       </c>
@@ -855,7 +858,7 @@
         <v>16.425999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:27">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46308</v>
       </c>
@@ -872,7 +875,7 @@
         <v>18.917999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46307</v>
       </c>
@@ -889,7 +892,7 @@
         <v>7.9720000000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46306</v>
       </c>
@@ -904,7 +907,7 @@
       </c>
       <c r="E8" s="6"/>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46305</v>
       </c>
@@ -919,7 +922,7 @@
       </c>
       <c r="E9" s="6"/>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46304</v>
       </c>
@@ -952,7 +955,7 @@
       <c r="Z10" s="2"/>
       <c r="AA10" s="2"/>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46303</v>
       </c>
@@ -967,7 +970,7 @@
       </c>
       <c r="E11" s="6"/>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46302</v>
       </c>
@@ -982,7 +985,7 @@
       </c>
       <c r="E12" s="6"/>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46301</v>
       </c>
@@ -999,7 +1002,7 @@
         <v>4.5679999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:27">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46300</v>
       </c>
@@ -1016,7 +1019,7 @@
         <v>6.4130000000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46299</v>
       </c>
@@ -1033,7 +1036,7 @@
         <v>4.3440000000000003</v>
       </c>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46298</v>
       </c>
@@ -1048,7 +1051,7 @@
       </c>
       <c r="E16" s="6"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46297</v>
       </c>
@@ -1063,7 +1066,7 @@
       </c>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46296</v>
       </c>
@@ -1078,7 +1081,7 @@
       </c>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46295</v>
       </c>
@@ -1095,7 +1098,7 @@
         <v>37.679307999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46294</v>
       </c>
@@ -1112,7 +1115,7 @@
         <v>33.449338000000004</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46293</v>
       </c>
@@ -1129,7 +1132,7 @@
         <v>42.041217999999994</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46292</v>
       </c>
@@ -1144,7 +1147,7 @@
       </c>
       <c r="E22" s="6"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46291</v>
       </c>
@@ -1161,7 +1164,7 @@
         <v>16.912866999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46290</v>
       </c>
@@ -1178,7 +1181,7 @@
         <v>11.657306</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46289</v>
       </c>
@@ -1192,7 +1195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46288</v>
       </c>
@@ -1206,7 +1209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46287</v>
       </c>
@@ -1220,7 +1223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46286</v>
       </c>
@@ -1234,7 +1237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46285</v>
       </c>
@@ -1248,7 +1251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46284</v>
       </c>
@@ -1262,7 +1265,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>46283</v>
       </c>
@@ -1279,7 +1282,7 @@
         <v>30.143184999999992</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>46281</v>
       </c>
@@ -1293,7 +1296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>46280</v>
       </c>
@@ -1307,7 +1310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>46279</v>
       </c>
@@ -1321,7 +1324,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>46278</v>
       </c>
@@ -1335,7 +1338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>46277</v>
       </c>
@@ -1349,7 +1352,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>46276</v>
       </c>
@@ -1366,7 +1369,7 @@
         <v>5.3833070000000003</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>46275</v>
       </c>
@@ -1380,7 +1383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>46274</v>
       </c>
@@ -1394,7 +1397,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>46273</v>
       </c>
@@ -1408,7 +1411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>46272</v>
       </c>
@@ -1422,7 +1425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>46271</v>
       </c>
@@ -1436,7 +1439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>46270</v>
       </c>
@@ -1450,7 +1453,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>46269</v>
       </c>
@@ -1464,7 +1467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>46268</v>
       </c>
@@ -1478,7 +1481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>46267</v>
       </c>
@@ -1492,7 +1495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46266</v>
       </c>
@@ -1506,7 +1509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46265</v>
       </c>
@@ -1517,7 +1520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:21">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>46264</v>
       </c>
@@ -1531,7 +1534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:21">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>46263</v>
       </c>
@@ -1545,7 +1548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:21">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>46262</v>
       </c>
@@ -1559,7 +1562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:21">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>46261</v>
       </c>
@@ -1576,7 +1579,7 @@
         <v>0.21422999999999998</v>
       </c>
     </row>
-    <row r="53" spans="1:21">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>46260</v>
       </c>
@@ -1590,7 +1593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:21">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>46259</v>
       </c>
@@ -1607,7 +1610,7 @@
         <v>10.703772000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:21">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>46258</v>
       </c>
@@ -1621,7 +1624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:21">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>46257</v>
       </c>
@@ -1635,7 +1638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:21">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>46256</v>
       </c>
@@ -1649,7 +1652,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:21">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>46255</v>
       </c>
@@ -1663,7 +1666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:21">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>46254</v>
       </c>
@@ -1680,7 +1683,7 @@
         <v>8.4293359999999993</v>
       </c>
     </row>
-    <row r="60" spans="1:21">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>46253</v>
       </c>
@@ -1709,7 +1712,7 @@
       <c r="T60" s="7"/>
       <c r="U60" s="7"/>
     </row>
-    <row r="61" spans="1:21">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>46252</v>
       </c>
@@ -1726,7 +1729,7 @@
         <v>6.2419820000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:21">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>46251</v>
       </c>
@@ -1743,7 +1746,7 @@
         <v>14.777381999999999</v>
       </c>
     </row>
-    <row r="63" spans="1:21">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>46250</v>
       </c>
@@ -1754,7 +1757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:21">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>46249</v>
       </c>
@@ -1762,7 +1765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>46248</v>
       </c>
@@ -1779,7 +1782,7 @@
         <v>20.847041999999995</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>46247</v>
       </c>
@@ -1796,7 +1799,7 @@
         <v>5.4199330000000003</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>46246</v>
       </c>
@@ -1810,7 +1813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>46245</v>
       </c>
@@ -1824,7 +1827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>46244</v>
       </c>
@@ -1838,7 +1841,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>46243</v>
       </c>
@@ -1852,7 +1855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>46242</v>
       </c>
@@ -1866,7 +1869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>46241</v>
       </c>
@@ -1880,7 +1883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>46240</v>
       </c>
@@ -1894,7 +1897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>46239</v>
       </c>
@@ -1908,7 +1911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>46238</v>
       </c>
@@ -1930,12 +1933,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D41FB4CD-150C-4CE3-A76E-CB540C2892DD}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>13</v>
       </c>
@@ -1964,7 +1967,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -1997,7 +2000,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -2011,7 +2014,7 @@
       </c>
       <c r="D3">
         <f>75+SUM(D5:D100)</f>
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E3">
         <f>10+SUM(E5:E150)</f>
@@ -2035,10 +2038,10 @@
       </c>
       <c r="J3">
         <f>1195+SUM(J5:J200)</f>
-        <v>1263</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -2052,7 +2055,7 @@
       </c>
       <c r="D4">
         <f t="shared" ref="D4:G4" si="0">D2-D3</f>
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
@@ -2076,10 +2079,10 @@
       </c>
       <c r="J4">
         <f>J2-J3</f>
-        <v>3237</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>3216</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46302</v>
       </c>
@@ -2111,7 +2114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46303</v>
       </c>
@@ -2143,7 +2146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46304</v>
       </c>
@@ -2175,7 +2178,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46305</v>
       </c>
@@ -2207,7 +2210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46306</v>
       </c>
@@ -2239,7 +2242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46307</v>
       </c>
@@ -2271,7 +2274,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46308</v>
       </c>
@@ -2303,7 +2306,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46309</v>
       </c>
@@ -2332,7 +2335,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46310</v>
       </c>
@@ -2364,7 +2367,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46311</v>
       </c>
@@ -2374,7 +2377,27 @@
       <c r="C14">
         <v>38</v>
       </c>
-      <c r="J14" s="6"/>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14" s="6">
+        <v>21</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2384,13 +2407,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E384ED-EF07-4058-B570-9E7F8CBFADFB}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>24</v>
       </c>
@@ -2398,7 +2421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -2406,7 +2429,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -2414,7 +2437,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -2422,7 +2445,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -2430,7 +2453,7 @@
         <v>46336</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>30</v>
       </c>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30610"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1115" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FC07B2B-5C12-41A0-B585-7C4A558E4EF0}"/>
+  <xr:revisionPtr revIDLastSave="1149" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3884AA94-BD12-45DA-97D0-630BD87A8DF3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>
@@ -53,19 +53,19 @@
     <t>ACC</t>
   </si>
   <si>
-    <t>Daily-117; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 852;Total - 5468 MT</t>
+    <t>Daily-18; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 885;Total - 5500 MT</t>
   </si>
   <si>
     <t>Boiler</t>
   </si>
   <si>
-    <t>Daily-148  - (SH-110and RH-38); Oct-1480 NDHT Balance joints - 8734 (SH - 4574; RH - 4160)</t>
+    <t>Daily-85  - (SH-61 and RH-24); Oct-1565 NDHT Balance joints - 8649 (SH - 4513; RH - 4136)</t>
   </si>
   <si>
     <t>PCP Joint</t>
   </si>
   <si>
-    <t>Daily-2; MS Joints - 74/146; MS to PRDS - 11/26; HRH - 10/95; CRH -14/87; LPBP - 11/49; HPBP-8/23; BFD- 176/661</t>
+    <t>Daily-0; MS Joints - 74/146; MS to PRDS - 11/26; HRH - 10/95; CRH -14/87; LPBP - 11/49; HPBP-8/23; BFD- 177/661</t>
   </si>
   <si>
     <t>Boiler - NDHT Joints</t>
@@ -143,7 +143,7 @@
     <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -704,13 +704,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="93" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -721,9 +721,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="1">
-        <v>46311</v>
+        <v>46313</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -732,9 +732,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" s="1">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -743,9 +743,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="1">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -764,8 +764,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
-  <dimension ref="A1:AA75"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AA77"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
@@ -773,7 +773,7 @@
     <col min="5" max="6" width="11.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -790,7 +790,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -807,739 +807,733 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27">
       <c r="A3" s="1">
+        <v>46313</v>
+      </c>
+      <c r="B3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27">
+      <c r="A4" s="1">
+        <v>46312</v>
+      </c>
+      <c r="B4">
+        <v>14</v>
+      </c>
+      <c r="C4">
+        <v>85</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27">
+      <c r="A5" s="1">
         <v>46311</v>
       </c>
-      <c r="B3">
+      <c r="B5">
         <v>117</v>
       </c>
-      <c r="C3">
+      <c r="C5">
         <v>148</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>46310</v>
-      </c>
-      <c r="B4">
-        <v>56</v>
-      </c>
-      <c r="C4">
-        <v>122</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="6">
-        <v>20.72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>46309</v>
-      </c>
-      <c r="B5">
-        <v>23</v>
-      </c>
-      <c r="C5">
-        <v>135</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27">
+      <c r="A6" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B6">
+        <v>56</v>
+      </c>
+      <c r="C6">
+        <v>122</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6">
+        <v>20.72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27">
+      <c r="A7" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B7">
+        <v>23</v>
+      </c>
+      <c r="C7">
+        <v>135</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" s="6">
         <v>16.425999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+    <row r="8" spans="1:27">
+      <c r="A8" s="1">
         <v>46308</v>
       </c>
-      <c r="B6">
+      <c r="B8">
         <v>44</v>
       </c>
-      <c r="C6">
+      <c r="C8">
         <v>127</v>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" s="6">
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="6">
         <v>18.917999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+    <row r="9" spans="1:27">
+      <c r="A9" s="1">
         <v>46307</v>
       </c>
-      <c r="B7">
+      <c r="B9">
         <v>102</v>
       </c>
-      <c r="C7">
+      <c r="C9">
         <v>118</v>
       </c>
-      <c r="D7">
+      <c r="D9">
         <v>3</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E9" s="6">
         <v>7.9720000000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+    <row r="10" spans="1:27">
+      <c r="A10" s="1">
         <v>46306</v>
       </c>
-      <c r="B8">
+      <c r="B10">
         <v>21</v>
       </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6"/>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6"/>
+    </row>
+    <row r="11" spans="1:27">
+      <c r="A11" s="1">
         <v>46305</v>
       </c>
-      <c r="B9">
+      <c r="B11">
         <v>83</v>
       </c>
-      <c r="C9">
+      <c r="C11">
         <v>82</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" s="6"/>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" spans="1:27">
+      <c r="A12" s="1">
         <v>46304</v>
       </c>
-      <c r="B10">
+      <c r="B12">
         <v>74</v>
       </c>
-      <c r="C10">
+      <c r="C12">
         <v>130</v>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" s="6">
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" s="6">
         <v>4.3440000000000003</v>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="3"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="2"/>
-      <c r="Z10" s="2"/>
-      <c r="AA10" s="2"/>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+      <c r="I12" s="2"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="3"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="3"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="X12" s="3"/>
+      <c r="Y12" s="2"/>
+      <c r="Z12" s="2"/>
+      <c r="AA12" s="2"/>
+    </row>
+    <row r="13" spans="1:27">
+      <c r="A13" s="1">
         <v>46303</v>
       </c>
-      <c r="B11">
+      <c r="B13">
         <v>70</v>
       </c>
-      <c r="C11">
+      <c r="C13">
         <v>134</v>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" s="6"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" spans="1:27">
+      <c r="A14" s="1">
         <v>46302</v>
       </c>
-      <c r="B12">
+      <c r="B14">
         <v>26</v>
       </c>
-      <c r="C12">
+      <c r="C14">
         <v>91</v>
       </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6"/>
+    </row>
+    <row r="15" spans="1:27">
+      <c r="A15" s="1">
         <v>46301</v>
       </c>
-      <c r="B13">
+      <c r="B15">
         <v>45</v>
       </c>
-      <c r="C13">
+      <c r="C15">
         <v>104</v>
       </c>
-      <c r="D13">
+      <c r="D15">
         <v>4</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E15" s="6">
         <v>4.5679999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+    <row r="16" spans="1:27">
+      <c r="A16" s="1">
         <v>46300</v>
       </c>
-      <c r="B14">
+      <c r="B16">
         <v>45</v>
       </c>
-      <c r="C14">
+      <c r="C16">
         <v>123</v>
       </c>
-      <c r="D14">
+      <c r="D16">
         <v>2</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E16" s="6">
         <v>6.4130000000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+    <row r="17" spans="1:5">
+      <c r="A17" s="1">
         <v>46299</v>
       </c>
-      <c r="B15">
+      <c r="B17">
         <v>66</v>
       </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15" s="6">
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17" s="6">
         <v>4.3440000000000003</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+    <row r="18" spans="1:5">
+      <c r="A18" s="1">
         <v>46298</v>
-      </c>
-      <c r="B16">
-        <v>40</v>
-      </c>
-      <c r="C16">
-        <v>65</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16" s="6"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>46297</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17" s="6"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>46296</v>
       </c>
       <c r="B18">
         <v>40</v>
       </c>
       <c r="C18">
+        <v>65</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" s="6"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19" s="6"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B20">
+        <v>40</v>
+      </c>
+      <c r="C20">
         <v>101</v>
       </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18" s="6"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" s="6"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="1">
         <v>46295</v>
       </c>
-      <c r="B19">
+      <c r="B21">
         <v>321</v>
       </c>
-      <c r="C19">
+      <c r="C21">
         <v>139</v>
       </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19" s="5">
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5">
         <v>37.679307999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+    <row r="22" spans="1:5">
+      <c r="A22" s="1">
         <v>46294</v>
       </c>
-      <c r="B20">
+      <c r="B22">
         <v>200</v>
       </c>
-      <c r="C20">
+      <c r="C22">
         <v>114</v>
       </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20" s="5">
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" s="5">
         <v>33.449338000000004</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+    <row r="23" spans="1:5">
+      <c r="A23" s="1">
         <v>46293</v>
       </c>
-      <c r="B21">
+      <c r="B23">
         <v>43</v>
       </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
         <v>4</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E23" s="5">
         <v>42.041217999999994</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+    <row r="24" spans="1:5">
+      <c r="A24" s="1">
         <v>46292</v>
       </c>
-      <c r="B22">
+      <c r="B24">
         <v>13</v>
       </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22" s="6"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24" s="6"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="1">
         <v>46291</v>
       </c>
-      <c r="B23">
+      <c r="B25">
         <v>17</v>
       </c>
-      <c r="C23">
+      <c r="C25">
         <v>39</v>
       </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23" s="5">
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5">
         <v>16.912866999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+    <row r="26" spans="1:5">
+      <c r="A26" s="1">
         <v>46290</v>
       </c>
-      <c r="B24">
+      <c r="B26">
         <v>20</v>
       </c>
-      <c r="C24">
+      <c r="C26">
         <v>121</v>
       </c>
-      <c r="D24">
+      <c r="D26">
         <v>2</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E26" s="5">
         <v>11.657306</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+    <row r="27" spans="1:5">
+      <c r="A27" s="1">
         <v>46289</v>
       </c>
-      <c r="B25">
+      <c r="B27">
         <v>3</v>
       </c>
-      <c r="C25">
+      <c r="C27">
         <v>133</v>
       </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
+      <c r="D27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="1">
         <v>46288</v>
       </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-      <c r="C26">
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
         <v>143</v>
       </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+      <c r="D28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="1">
         <v>46287</v>
       </c>
-      <c r="B27">
+      <c r="B29">
         <v>9</v>
       </c>
-      <c r="C27">
-        <v>0</v>
-      </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="1">
         <v>46286</v>
       </c>
-      <c r="B28">
+      <c r="B30">
         <v>32</v>
       </c>
-      <c r="C28">
+      <c r="C30">
         <v>131</v>
       </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+      <c r="D30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="1">
         <v>46285</v>
       </c>
-      <c r="B29">
+      <c r="B31">
         <v>42</v>
       </c>
-      <c r="C29">
+      <c r="C31">
         <v>111</v>
       </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+      <c r="D31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="1">
         <v>46284</v>
       </c>
-      <c r="B30">
+      <c r="B32">
         <v>16</v>
       </c>
-      <c r="C30">
+      <c r="C32">
         <v>118</v>
       </c>
-      <c r="D30">
+      <c r="D32">
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+    <row r="33" spans="1:5">
+      <c r="A33" s="1">
         <v>46283</v>
       </c>
-      <c r="B31">
+      <c r="B33">
         <v>16</v>
       </c>
-      <c r="C31">
+      <c r="C33">
         <v>118</v>
       </c>
-      <c r="D31">
+      <c r="D33">
         <v>4</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E33" s="5">
         <v>30.143184999999992</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+    <row r="34" spans="1:5">
+      <c r="A34" s="1">
         <v>46281</v>
       </c>
-      <c r="B32">
+      <c r="B34">
         <v>33</v>
       </c>
-      <c r="C32">
+      <c r="C34">
         <v>98</v>
       </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+      <c r="D34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="1">
         <v>46280</v>
-      </c>
-      <c r="B33">
-        <v>3</v>
-      </c>
-      <c r="C33">
-        <v>125</v>
-      </c>
-      <c r="D33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
-        <v>46279</v>
-      </c>
-      <c r="B34">
-        <v>58</v>
-      </c>
-      <c r="C34">
-        <v>100</v>
-      </c>
-      <c r="D34">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
-        <v>46278</v>
       </c>
       <c r="B35">
         <v>3</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="D35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" s="1">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="B36">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C36">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="D36">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5">
       <c r="A37" s="1">
+        <v>46278</v>
+      </c>
+      <c r="B37">
+        <v>3</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="1">
+        <v>46277</v>
+      </c>
+      <c r="B38">
+        <v>63</v>
+      </c>
+      <c r="C38">
+        <v>42</v>
+      </c>
+      <c r="D38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="1">
         <v>46276</v>
       </c>
-      <c r="B37">
+      <c r="B39">
         <v>19</v>
       </c>
-      <c r="C37">
+      <c r="C39">
         <v>73</v>
       </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-      <c r="E37" s="5">
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39" s="5">
         <v>5.3833070000000003</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
+    <row r="40" spans="1:5">
+      <c r="A40" s="1">
         <v>46275</v>
       </c>
-      <c r="B38">
+      <c r="B40">
         <v>21</v>
       </c>
-      <c r="C38">
+      <c r="C40">
         <v>16</v>
       </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
+      <c r="D40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="1">
         <v>46274</v>
       </c>
-      <c r="B39">
+      <c r="B41">
         <v>47</v>
       </c>
-      <c r="C39">
+      <c r="C41">
         <v>84</v>
       </c>
-      <c r="D39">
+      <c r="D41">
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
+    <row r="42" spans="1:5">
+      <c r="A42" s="1">
         <v>46273</v>
       </c>
-      <c r="B40">
+      <c r="B42">
         <v>45</v>
       </c>
-      <c r="C40">
+      <c r="C42">
         <v>105</v>
       </c>
-      <c r="D40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
+      <c r="D42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="1">
         <v>46272</v>
       </c>
-      <c r="B41">
+      <c r="B43">
         <v>38</v>
       </c>
-      <c r="C41">
+      <c r="C43">
         <v>92</v>
       </c>
-      <c r="D41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
+      <c r="D43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="1">
         <v>46271</v>
       </c>
-      <c r="B42">
+      <c r="B44">
         <v>13</v>
       </c>
-      <c r="C42">
-        <v>0</v>
-      </c>
-      <c r="D42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="1">
         <v>46270</v>
       </c>
-      <c r="B43">
-        <v>0</v>
-      </c>
-      <c r="C43">
+      <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45">
         <v>90</v>
       </c>
-      <c r="D43">
+      <c r="D45">
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
+    <row r="46" spans="1:5">
+      <c r="A46" s="1">
         <v>46269</v>
       </c>
-      <c r="B44">
-        <v>0</v>
-      </c>
-      <c r="C44">
-        <v>0</v>
-      </c>
-      <c r="D44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1">
+      <c r="B46">
+        <v>0</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="1">
         <v>46268</v>
       </c>
-      <c r="B45">
+      <c r="B47">
         <v>23</v>
       </c>
-      <c r="C45">
+      <c r="C47">
         <v>74</v>
       </c>
-      <c r="D45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
+      <c r="D47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="1">
         <v>46267</v>
       </c>
-      <c r="B46">
+      <c r="B48">
         <v>7</v>
       </c>
-      <c r="C46">
+      <c r="C48">
         <v>75</v>
       </c>
-      <c r="D46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
+      <c r="D48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21">
+      <c r="A49" s="1">
         <v>46266</v>
       </c>
-      <c r="B47">
+      <c r="B49">
         <v>17</v>
       </c>
-      <c r="C47">
-        <v>0</v>
-      </c>
-      <c r="D47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21">
+      <c r="A50" s="1">
         <v>46265</v>
-      </c>
-      <c r="C48">
-        <v>62</v>
-      </c>
-      <c r="D48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A49" s="1">
-        <v>46264</v>
-      </c>
-      <c r="B49">
-        <v>5</v>
-      </c>
-      <c r="C49">
-        <v>0</v>
-      </c>
-      <c r="D49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
-        <v>46263</v>
-      </c>
-      <c r="B50">
-        <v>73</v>
       </c>
       <c r="C50">
         <v>62</v>
@@ -1548,380 +1542,408 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21">
       <c r="A51" s="1">
+        <v>46264</v>
+      </c>
+      <c r="B51">
+        <v>5</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21">
+      <c r="A52" s="1">
+        <v>46263</v>
+      </c>
+      <c r="B52">
+        <v>73</v>
+      </c>
+      <c r="C52">
+        <v>62</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21">
+      <c r="A53" s="1">
         <v>46262</v>
       </c>
-      <c r="B51">
+      <c r="B53">
         <v>67</v>
       </c>
-      <c r="C51">
+      <c r="C53">
         <v>54</v>
       </c>
-      <c r="D51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
+      <c r="D53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21">
+      <c r="A54" s="1">
         <v>46261</v>
       </c>
-      <c r="B52">
+      <c r="B54">
         <v>29</v>
       </c>
-      <c r="C52">
+      <c r="C54">
         <v>64</v>
       </c>
-      <c r="D52">
+      <c r="D54">
         <v>3</v>
       </c>
-      <c r="E52" s="4">
+      <c r="E54" s="4">
         <v>0.21422999999999998</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
+    <row r="55" spans="1:21">
+      <c r="A55" s="1">
         <v>46260</v>
       </c>
-      <c r="B53">
+      <c r="B55">
         <v>85</v>
       </c>
-      <c r="C53">
+      <c r="C55">
         <v>62</v>
       </c>
-      <c r="D53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A54" s="1">
+      <c r="D55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21">
+      <c r="A56" s="1">
         <v>46259</v>
       </c>
-      <c r="B54">
+      <c r="B56">
         <v>13</v>
       </c>
-      <c r="C54">
+      <c r="C56">
         <v>62</v>
       </c>
-      <c r="D54">
-        <v>1</v>
-      </c>
-      <c r="E54" s="4">
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56" s="4">
         <v>10.703772000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A55" s="1">
+    <row r="57" spans="1:21">
+      <c r="A57" s="1">
         <v>46258</v>
       </c>
-      <c r="B55">
+      <c r="B57">
         <v>18</v>
       </c>
-      <c r="C55">
+      <c r="C57">
         <v>56</v>
       </c>
-      <c r="D55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
+      <c r="D57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21">
+      <c r="A58" s="1">
         <v>46257</v>
       </c>
-      <c r="B56">
+      <c r="B58">
         <v>3</v>
       </c>
-      <c r="C56">
-        <v>0</v>
-      </c>
-      <c r="D56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21">
+      <c r="A59" s="1">
         <v>46256</v>
       </c>
-      <c r="B57">
+      <c r="B59">
         <v>69</v>
       </c>
-      <c r="C57">
+      <c r="C59">
         <v>53</v>
       </c>
-      <c r="D57">
+      <c r="D59">
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A58" s="1">
+    <row r="60" spans="1:21">
+      <c r="A60" s="1">
         <v>46255</v>
       </c>
-      <c r="B58">
+      <c r="B60">
         <v>15</v>
       </c>
-      <c r="C58">
+      <c r="C60">
         <v>60</v>
       </c>
-      <c r="D58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
+      <c r="D60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21">
+      <c r="A61" s="1">
         <v>46254</v>
       </c>
-      <c r="B59">
+      <c r="B61">
         <v>48</v>
       </c>
-      <c r="C59">
+      <c r="C61">
         <v>43</v>
       </c>
-      <c r="D59">
-        <v>0</v>
-      </c>
-      <c r="E59" s="4">
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61" s="4">
         <v>8.4293359999999993</v>
       </c>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
+    <row r="62" spans="1:21">
+      <c r="A62" s="1">
         <v>46253</v>
       </c>
-      <c r="B60">
+      <c r="B62">
         <v>27</v>
       </c>
-      <c r="C60">
+      <c r="C62">
         <v>51</v>
       </c>
-      <c r="D60">
-        <v>1</v>
-      </c>
-      <c r="G60" s="7"/>
-      <c r="H60" s="7"/>
-      <c r="I60" s="3"/>
-      <c r="J60" s="3"/>
-      <c r="K60" s="7"/>
-      <c r="L60" s="7"/>
-      <c r="M60" s="7"/>
-      <c r="N60" s="7"/>
-      <c r="O60" s="7"/>
-      <c r="P60" s="7"/>
-      <c r="Q60" s="7"/>
-      <c r="R60" s="7"/>
-      <c r="S60" s="7"/>
-      <c r="T60" s="7"/>
-      <c r="U60" s="7"/>
-    </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="G62" s="7"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3"/>
+      <c r="K62" s="7"/>
+      <c r="L62" s="7"/>
+      <c r="M62" s="7"/>
+      <c r="N62" s="7"/>
+      <c r="O62" s="7"/>
+      <c r="P62" s="7"/>
+      <c r="Q62" s="7"/>
+      <c r="R62" s="7"/>
+      <c r="S62" s="7"/>
+      <c r="T62" s="7"/>
+      <c r="U62" s="7"/>
+    </row>
+    <row r="63" spans="1:21">
+      <c r="A63" s="1">
         <v>46252</v>
       </c>
-      <c r="B61">
-        <v>0</v>
-      </c>
-      <c r="C61">
-        <v>0</v>
-      </c>
-      <c r="D61">
+      <c r="B63">
+        <v>0</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
         <v>2</v>
       </c>
-      <c r="E61" s="4">
+      <c r="E63" s="4">
         <v>6.2419820000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A62" s="1">
+    <row r="64" spans="1:21">
+      <c r="A64" s="1">
         <v>46251</v>
       </c>
-      <c r="B62">
+      <c r="B64">
         <v>12</v>
       </c>
-      <c r="C62">
-        <v>0</v>
-      </c>
-      <c r="D62">
-        <v>1</v>
-      </c>
-      <c r="E62" s="4">
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+      <c r="E64" s="4">
         <v>14.777381999999999</v>
       </c>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A63" s="1">
+    <row r="65" spans="1:5">
+      <c r="A65" s="1">
         <v>46250</v>
       </c>
-      <c r="B63">
+      <c r="B65">
         <v>12</v>
       </c>
-      <c r="C63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A64" s="1">
+      <c r="C65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="1">
         <v>46249</v>
       </c>
-      <c r="C64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="1">
+      <c r="C66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="1">
         <v>46248</v>
       </c>
-      <c r="B65">
+      <c r="B67">
         <v>7</v>
       </c>
-      <c r="C65">
+      <c r="C67">
         <v>16</v>
       </c>
-      <c r="D65">
-        <v>0</v>
-      </c>
-      <c r="E65" s="4">
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67" s="4">
         <v>20.847041999999995</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="1">
+    <row r="68" spans="1:5">
+      <c r="A68" s="1">
         <v>46247</v>
       </c>
-      <c r="B66">
+      <c r="B68">
         <v>35</v>
       </c>
-      <c r="C66">
+      <c r="C68">
         <v>21</v>
       </c>
-      <c r="D66">
-        <v>0</v>
-      </c>
-      <c r="E66" s="4">
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68" s="4">
         <v>5.4199330000000003</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="1">
+    <row r="69" spans="1:5">
+      <c r="A69" s="1">
         <v>46246</v>
       </c>
-      <c r="B67">
+      <c r="B69">
         <v>28</v>
       </c>
-      <c r="C67">
+      <c r="C69">
         <v>21</v>
       </c>
-      <c r="D67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="1">
+      <c r="D69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="1">
         <v>46245</v>
       </c>
-      <c r="B68">
+      <c r="B70">
         <v>21</v>
       </c>
-      <c r="C68">
+      <c r="C70">
         <v>25</v>
       </c>
-      <c r="D68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="1">
+      <c r="D70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="1">
         <v>46244</v>
       </c>
-      <c r="B69">
+      <c r="B71">
         <v>19</v>
       </c>
-      <c r="C69">
+      <c r="C71">
         <v>11</v>
       </c>
-      <c r="D69">
+      <c r="D71">
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="1">
+    <row r="72" spans="1:5">
+      <c r="A72" s="1">
         <v>46243</v>
       </c>
-      <c r="B70">
+      <c r="B72">
         <v>13</v>
       </c>
-      <c r="C70">
-        <v>0</v>
-      </c>
-      <c r="D70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="1">
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="1">
         <v>46242</v>
       </c>
-      <c r="B71">
-        <v>0</v>
-      </c>
-      <c r="C71">
-        <v>0</v>
-      </c>
-      <c r="D71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="1">
+      <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="1">
         <v>46241</v>
       </c>
-      <c r="B72">
+      <c r="B74">
         <v>32</v>
       </c>
-      <c r="C72">
-        <v>0</v>
-      </c>
-      <c r="D72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="1">
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="1">
         <v>46240</v>
       </c>
-      <c r="B73">
+      <c r="B75">
         <v>16</v>
       </c>
-      <c r="C73">
-        <v>0</v>
-      </c>
-      <c r="D73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="1">
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="1">
         <v>46239</v>
       </c>
-      <c r="B74">
-        <v>0</v>
-      </c>
-      <c r="C74">
-        <v>0</v>
-      </c>
-      <c r="D74">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="1">
+      <c r="B76">
+        <v>0</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="1">
         <v>46238</v>
       </c>
-      <c r="B75">
-        <v>0</v>
-      </c>
-      <c r="C75">
-        <v>0</v>
-      </c>
-      <c r="D75">
+      <c r="B77">
+        <v>0</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+      <c r="D77">
         <v>1</v>
       </c>
     </row>
@@ -1932,13 +1954,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D41FB4CD-150C-4CE3-A76E-CB540C2892DD}">
-  <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="B1" t="s">
         <v>13</v>
       </c>
@@ -1967,7 +1989,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -2000,17 +2022,17 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>22</v>
       </c>
       <c r="B3">
         <f>4375+SUM(B6:B500)</f>
-        <v>5123</v>
+        <v>5184</v>
       </c>
       <c r="C3">
         <f>7462+SUM(C6:C100)</f>
-        <v>7710</v>
+        <v>7734</v>
       </c>
       <c r="D3">
         <f>75+SUM(D5:D100)</f>
@@ -2034,24 +2056,24 @@
       </c>
       <c r="I3">
         <f>170+SUM(I5:I150)</f>
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J3">
         <f>1195+SUM(J5:J200)</f>
         <v>1284</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>23</v>
       </c>
       <c r="B4">
         <f>B2-B3</f>
-        <v>4574</v>
+        <v>4513</v>
       </c>
       <c r="C4">
         <f>C2-C3</f>
-        <v>4160</v>
+        <v>4136</v>
       </c>
       <c r="D4">
         <f t="shared" ref="D4:G4" si="0">D2-D3</f>
@@ -2075,14 +2097,14 @@
       </c>
       <c r="I4">
         <f>I2-I3</f>
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J4">
         <f>J2-J3</f>
         <v>3216</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" s="1">
         <v>46302</v>
       </c>
@@ -2114,7 +2136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" s="1">
         <v>46303</v>
       </c>
@@ -2146,7 +2168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10">
       <c r="A7" s="1">
         <v>46304</v>
       </c>
@@ -2178,7 +2200,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10">
       <c r="A8" s="1">
         <v>46305</v>
       </c>
@@ -2210,7 +2232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9" s="1">
         <v>46306</v>
       </c>
@@ -2242,7 +2264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10">
       <c r="A10" s="1">
         <v>46307</v>
       </c>
@@ -2274,7 +2296,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10">
       <c r="A11" s="1">
         <v>46308</v>
       </c>
@@ -2306,7 +2328,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="A12" s="1">
         <v>46309</v>
       </c>
@@ -2335,7 +2357,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10">
       <c r="A13" s="1">
         <v>46310</v>
       </c>
@@ -2367,7 +2389,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10">
       <c r="A14" s="1">
         <v>46311</v>
       </c>
@@ -2398,6 +2420,41 @@
       <c r="J14" s="6">
         <v>21</v>
       </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="1">
+        <v>46312</v>
+      </c>
+      <c r="B15">
+        <v>61</v>
+      </c>
+      <c r="C15">
+        <v>24</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2407,13 +2464,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E384ED-EF07-4058-B570-9E7F8CBFADFB}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="9.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>24</v>
       </c>
@@ -2421,7 +2478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -2429,7 +2486,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -2437,7 +2494,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -2445,7 +2502,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -2453,7 +2510,7 @@
         <v>46336</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>30</v>
       </c>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1149" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3884AA94-BD12-45DA-97D0-630BD87A8DF3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30610"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30611"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1149" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3884AA94-BD12-45DA-97D0-630BD87A8DF3}"/>
+  <xr:revisionPtr revIDLastSave="1160" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88BB5AE2-34D2-4E28-BF51-F0BC16DD4EB1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
     <t>ACC</t>
   </si>
   <si>
-    <t>Daily-18; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 885;Total - 5500 MT</t>
+    <t>Daily-06; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 891;Total - 5506 MT</t>
   </si>
   <si>
     <t>Boiler</t>
@@ -723,7 +723,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -764,7 +764,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
-  <dimension ref="A1:AA77"/>
+  <dimension ref="A1:AA78"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
@@ -809,423 +809,417 @@
     </row>
     <row r="3" spans="1:27">
       <c r="A3" s="1">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B3">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:27">
       <c r="A4" s="1">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B4">
-        <v>14</v>
-      </c>
-      <c r="C4">
-        <v>85</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:27">
       <c r="A5" s="1">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B5">
-        <v>117</v>
+        <v>14</v>
       </c>
       <c r="C5">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:27">
       <c r="A6" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B6">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C6">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" s="6">
-        <v>20.72</v>
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:27">
       <c r="A7" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B7">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="C7">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="6">
-        <v>16.425999999999998</v>
+        <v>20.72</v>
       </c>
     </row>
     <row r="8" spans="1:27">
       <c r="A8" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B8">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="C8">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" s="6">
-        <v>18.917999999999999</v>
+        <v>16.425999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:27">
       <c r="A9" s="1">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B9">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="C9">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" s="6">
-        <v>7.9720000000000004</v>
+        <v>18.917999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:27">
       <c r="A10" s="1">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B10">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10" s="6"/>
+        <v>3</v>
+      </c>
+      <c r="E10" s="6">
+        <v>7.9720000000000004</v>
+      </c>
     </row>
     <row r="11" spans="1:27">
       <c r="A11" s="1">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="B11">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="C11">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="6"/>
     </row>
     <row r="12" spans="1:27">
       <c r="A12" s="1">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B12">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C12">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
-      <c r="E12" s="6">
-        <v>4.3440000000000003</v>
-      </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="3"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="2"/>
-      <c r="U12" s="2"/>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="2"/>
-      <c r="Z12" s="2"/>
-      <c r="AA12" s="2"/>
+      <c r="E12" s="6"/>
     </row>
     <row r="13" spans="1:27">
       <c r="A13" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B13">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C13">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
-      <c r="E13" s="6"/>
+      <c r="E13" s="6">
+        <v>4.3440000000000003</v>
+      </c>
+      <c r="I13" s="2"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="3"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="X13" s="3"/>
+      <c r="Y13" s="2"/>
+      <c r="Z13" s="2"/>
+      <c r="AA13" s="2"/>
     </row>
     <row r="14" spans="1:27">
       <c r="A14" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B14">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="C14">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="6"/>
     </row>
     <row r="15" spans="1:27">
       <c r="A15" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B15">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C15">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D15">
-        <v>4</v>
-      </c>
-      <c r="E15" s="6">
-        <v>4.5679999999999996</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E15" s="6"/>
     </row>
     <row r="16" spans="1:27">
       <c r="A16" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B16">
         <v>45</v>
       </c>
       <c r="C16">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="6">
-        <v>6.4130000000000003</v>
+        <v>4.5679999999999996</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B17">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E17" s="6">
-        <v>4.3440000000000003</v>
+        <v>6.4130000000000003</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B18">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C18">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18" s="6"/>
+        <v>0</v>
+      </c>
+      <c r="E18" s="6">
+        <v>4.3440000000000003</v>
+      </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="6"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B20">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="6"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B21">
-        <v>321</v>
+        <v>40</v>
       </c>
       <c r="C21">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21" s="5">
-        <v>37.679307999999999</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E21" s="6"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B22">
-        <v>200</v>
+        <v>321</v>
       </c>
       <c r="C22">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="5">
-        <v>33.449338000000004</v>
+        <v>37.679307999999999</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B23">
-        <v>43</v>
+        <v>200</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E23" s="5">
-        <v>42.041217999999994</v>
+        <v>33.449338000000004</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="1">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B24">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="E24" s="5">
+        <v>42.041217999999994</v>
+      </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="1">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B25">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C25">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
-      <c r="E25" s="5">
-        <v>16.912866999999999</v>
-      </c>
+      <c r="E25" s="6"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B26">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C26">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E26" s="5">
-        <v>11.657306</v>
+        <v>16.912866999999999</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C27">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="E27" s="5">
+        <v>11.657306</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C28">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -1233,13 +1227,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B29">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -1247,27 +1241,27 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B30">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C30">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B31">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C31">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1275,21 +1269,21 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B32">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C32">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B33">
         <v>16</v>
@@ -1300,162 +1294,162 @@
       <c r="D33">
         <v>4</v>
       </c>
-      <c r="E33" s="5">
-        <v>30.143184999999992</v>
-      </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B34">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C34">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="E34" s="5">
+        <v>30.143184999999992</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C35">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B36">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="C36">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B38">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="C38">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B39">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="C39">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="D39">
-        <v>1</v>
-      </c>
-      <c r="E39" s="5">
-        <v>5.3833070000000003</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B40">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C40">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="D40">
         <v>1</v>
+      </c>
+      <c r="E40" s="5">
+        <v>5.3833070000000003</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B41">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="C41">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B42">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C42">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="1">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B43">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C43">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="1">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B44">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -1463,41 +1457,41 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="1">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C45">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="1">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B46">
         <v>0</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="1">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B47">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -1505,27 +1499,27 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="1">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B48">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C48">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:21">
       <c r="A49" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B49">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -1533,10 +1527,13 @@
     </row>
     <row r="50" spans="1:21">
       <c r="A50" s="1">
-        <v>46265</v>
+        <v>46266</v>
+      </c>
+      <c r="B50">
+        <v>17</v>
       </c>
       <c r="C50">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -1544,233 +1541,227 @@
     </row>
     <row r="51" spans="1:21">
       <c r="A51" s="1">
-        <v>46264</v>
-      </c>
-      <c r="B51">
-        <v>5</v>
+        <v>46265</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:21">
       <c r="A52" s="1">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B52">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="C52">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:21">
       <c r="A53" s="1">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B53">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C53">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:21">
       <c r="A54" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B54">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C54">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D54">
-        <v>3</v>
-      </c>
-      <c r="E54" s="4">
-        <v>0.21422999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:21">
       <c r="A55" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B55">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="C55">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="E55" s="4">
+        <v>0.21422999999999998</v>
       </c>
     </row>
     <row r="56" spans="1:21">
       <c r="A56" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B56">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="C56">
         <v>62</v>
       </c>
       <c r="D56">
-        <v>1</v>
-      </c>
-      <c r="E56" s="4">
-        <v>10.703772000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:21">
       <c r="A57" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B57">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C57">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D57">
         <v>1</v>
+      </c>
+      <c r="E57" s="4">
+        <v>10.703772000000001</v>
       </c>
     </row>
     <row r="58" spans="1:21">
       <c r="A58" s="1">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B58">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:21">
       <c r="A59" s="1">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B59">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="C59">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:21">
       <c r="A60" s="1">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B60">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="C60">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:21">
       <c r="A61" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B61">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="C61">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D61">
-        <v>0</v>
-      </c>
-      <c r="E61" s="4">
-        <v>8.4293359999999993</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:21">
       <c r="A62" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B62">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C62">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D62">
-        <v>1</v>
-      </c>
-      <c r="G62" s="7"/>
-      <c r="H62" s="7"/>
-      <c r="I62" s="3"/>
-      <c r="J62" s="3"/>
-      <c r="K62" s="7"/>
-      <c r="L62" s="7"/>
-      <c r="M62" s="7"/>
-      <c r="N62" s="7"/>
-      <c r="O62" s="7"/>
-      <c r="P62" s="7"/>
-      <c r="Q62" s="7"/>
-      <c r="R62" s="7"/>
-      <c r="S62" s="7"/>
-      <c r="T62" s="7"/>
-      <c r="U62" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="E62" s="4">
+        <v>8.4293359999999993</v>
+      </c>
     </row>
     <row r="63" spans="1:21">
       <c r="A63" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D63">
-        <v>2</v>
-      </c>
-      <c r="E63" s="4">
-        <v>6.2419820000000001</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G63" s="7"/>
+      <c r="H63" s="7"/>
+      <c r="I63" s="3"/>
+      <c r="J63" s="3"/>
+      <c r="K63" s="7"/>
+      <c r="L63" s="7"/>
+      <c r="M63" s="7"/>
+      <c r="N63" s="7"/>
+      <c r="O63" s="7"/>
+      <c r="P63" s="7"/>
+      <c r="Q63" s="7"/>
+      <c r="R63" s="7"/>
+      <c r="S63" s="7"/>
+      <c r="T63" s="7"/>
+      <c r="U63" s="7"/>
     </row>
     <row r="64" spans="1:21">
       <c r="A64" s="1">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B64">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C64">
         <v>0</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" s="4">
-        <v>14.777381999999999</v>
+        <v>6.2419820000000001</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="1">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B65">
         <v>12</v>
@@ -1778,10 +1769,19 @@
       <c r="C65">
         <v>0</v>
       </c>
+      <c r="D65">
+        <v>1</v>
+      </c>
+      <c r="E65" s="4">
+        <v>14.777381999999999</v>
+      </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="1">
-        <v>46249</v>
+        <v>46250</v>
+      </c>
+      <c r="B66">
+        <v>12</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -1789,100 +1789,94 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="1">
-        <v>46248</v>
-      </c>
-      <c r="B67">
-        <v>7</v>
+        <v>46249</v>
       </c>
       <c r="C67">
-        <v>16</v>
-      </c>
-      <c r="D67">
-        <v>0</v>
-      </c>
-      <c r="E67" s="4">
-        <v>20.847041999999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B68">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="C68">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68" s="4">
-        <v>5.4199330000000003</v>
+        <v>20.847041999999995</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="1">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B69">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C69">
         <v>21</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E69" s="4">
+        <v>5.4199330000000003</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="1">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B70">
+        <v>28</v>
+      </c>
+      <c r="C70">
         <v>21</v>
       </c>
-      <c r="C70">
-        <v>25</v>
-      </c>
       <c r="D70">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="1">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B71">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C71">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D71">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="1">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B72">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="1">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -1893,10 +1887,10 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="1">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B74">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -1907,10 +1901,10 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="1">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B75">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -1921,29 +1915,43 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="1">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B77">
+        <v>0</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+      <c r="D77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="1">
         <v>46238</v>
       </c>
-      <c r="B77">
-        <v>0</v>
-      </c>
-      <c r="C77">
-        <v>0</v>
-      </c>
-      <c r="D77">
+      <c r="B78">
+        <v>0</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78">
         <v>1</v>
       </c>
     </row>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1160" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88BB5AE2-34D2-4E28-BF51-F0BC16DD4EB1}"/>
+  <xr:revisionPtr revIDLastSave="1167" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71CB0B80-5545-4446-928F-345209456295}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,13 +59,13 @@
     <t>Boiler</t>
   </si>
   <si>
-    <t>Daily-85  - (SH-61 and RH-24); Oct-1565 NDHT Balance joints - 8649 (SH - 4513; RH - 4136)</t>
+    <t>Daily-32  - (SH-32 and RH-); Oct-1597 NDHT Balance joints - 8617 (SH - 4481; RH - 4136)</t>
   </si>
   <si>
     <t>PCP Joint</t>
   </si>
   <si>
-    <t>Daily-0; MS Joints - 74/146; MS to PRDS - 11/26; HRH - 10/95; CRH -14/87; LPBP - 11/49; HPBP-8/23; BFD- 177/661</t>
+    <t>Daily-0; MS Joints - 74/146; MS to PRDS - 11/26; HRH - 10/95; CRH -15/87; LPBP - 11/49; HPBP-8/23; BFD- 177/661</t>
   </si>
   <si>
     <t>Boiler - NDHT Joints</t>
@@ -734,7 +734,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -745,7 +745,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1167" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71CB0B80-5545-4446-928F-345209456295}"/>
+  <xr:revisionPtr revIDLastSave="1189" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7836BCFD-65CA-4265-99ED-316BDBE5497B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
     <t>ACC</t>
   </si>
   <si>
-    <t>Daily-06; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 891;Total - 5506 MT</t>
+    <t>Daily-30; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 921;Total - 5536 MT</t>
   </si>
   <si>
     <t>Boiler</t>
@@ -723,7 +723,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -764,7 +764,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
-  <dimension ref="A1:AA78"/>
+  <dimension ref="A1:AA79"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
@@ -809,29 +809,41 @@
     </row>
     <row r="3" spans="1:27">
       <c r="A3" s="1">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>30</v>
+      </c>
+      <c r="C3">
+        <v>32</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:27">
       <c r="A4" s="1">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B4">
-        <v>18</v>
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:27">
       <c r="A5" s="1">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B5">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C5">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -839,401 +851,401 @@
     </row>
     <row r="6" spans="1:27">
       <c r="A6" s="1">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B6">
-        <v>117</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:27">
       <c r="A7" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B7">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C7">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" s="6">
-        <v>20.72</v>
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:27">
       <c r="A8" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="C8">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="6">
-        <v>16.425999999999998</v>
+        <v>20.72</v>
       </c>
     </row>
     <row r="9" spans="1:27">
       <c r="A9" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B9">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="C9">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="6">
-        <v>18.917999999999999</v>
+        <v>16.425999999999998</v>
       </c>
     </row>
     <row r="10" spans="1:27">
       <c r="A10" s="1">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B10">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="C10">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" s="6">
-        <v>7.9720000000000004</v>
+        <v>18.917999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:27">
       <c r="A11" s="1">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B11">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11" s="6"/>
+        <v>3</v>
+      </c>
+      <c r="E11" s="6">
+        <v>7.9720000000000004</v>
+      </c>
     </row>
     <row r="12" spans="1:27">
       <c r="A12" s="1">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="B12">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="C12">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="6"/>
     </row>
     <row r="13" spans="1:27">
       <c r="A13" s="1">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B13">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C13">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
-      <c r="E13" s="6">
-        <v>4.3440000000000003</v>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="3"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="2"/>
-      <c r="Z13" s="2"/>
-      <c r="AA13" s="2"/>
+      <c r="E13" s="6"/>
     </row>
     <row r="14" spans="1:27">
       <c r="A14" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B14">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C14">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
-      <c r="E14" s="6"/>
+      <c r="E14" s="6">
+        <v>4.3440000000000003</v>
+      </c>
+      <c r="I14" s="2"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="3"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="3"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="X14" s="3"/>
+      <c r="Y14" s="2"/>
+      <c r="Z14" s="2"/>
+      <c r="AA14" s="2"/>
     </row>
     <row r="15" spans="1:27">
       <c r="A15" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B15">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="C15">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="6"/>
     </row>
     <row r="16" spans="1:27">
       <c r="A16" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B16">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C16">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D16">
-        <v>4</v>
-      </c>
-      <c r="E16" s="6">
-        <v>4.5679999999999996</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E16" s="6"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B17">
         <v>45</v>
       </c>
       <c r="C17">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E17" s="6">
-        <v>6.4130000000000003</v>
+        <v>4.5679999999999996</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B18">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18" s="6">
-        <v>4.3440000000000003</v>
+        <v>6.4130000000000003</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B19">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C19">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19" s="6"/>
+        <v>0</v>
+      </c>
+      <c r="E19" s="6">
+        <v>4.3440000000000003</v>
+      </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="6"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B21">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="6"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B22">
-        <v>321</v>
+        <v>40</v>
       </c>
       <c r="C22">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22" s="5">
-        <v>37.679307999999999</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E22" s="6"/>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B23">
-        <v>200</v>
+        <v>321</v>
       </c>
       <c r="C23">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="5">
-        <v>33.449338000000004</v>
+        <v>37.679307999999999</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B24">
-        <v>43</v>
+        <v>200</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="D24">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E24" s="5">
-        <v>42.041217999999994</v>
+        <v>33.449338000000004</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="1">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B25">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="E25" s="5">
+        <v>42.041217999999994</v>
+      </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="1">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B26">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C26">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
-      <c r="E26" s="5">
-        <v>16.912866999999999</v>
-      </c>
+      <c r="E26" s="6"/>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B27">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C27">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E27" s="5">
-        <v>11.657306</v>
+        <v>16.912866999999999</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B28">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C28">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="E28" s="5">
+        <v>11.657306</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C29">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -1241,13 +1253,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="1">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B30">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1255,27 +1267,27 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B31">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C31">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B32">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C32">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -1283,21 +1295,21 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B33">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C33">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D33">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B34">
         <v>16</v>
@@ -1308,162 +1320,162 @@
       <c r="D34">
         <v>4</v>
       </c>
-      <c r="E34" s="5">
-        <v>30.143184999999992</v>
-      </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B35">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C35">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="E35" s="5">
+        <v>30.143184999999992</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C36">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B37">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="C37">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B39">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="C39">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B40">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="C40">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="D40">
-        <v>1</v>
-      </c>
-      <c r="E40" s="5">
-        <v>5.3833070000000003</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B41">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C41">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="D41">
         <v>1</v>
+      </c>
+      <c r="E41" s="5">
+        <v>5.3833070000000003</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="1">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B42">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="C42">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B43">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C43">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="1">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B44">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C44">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="1">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B45">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -1471,41 +1483,41 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="1">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C46">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="1">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B47">
         <v>0</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="1">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B48">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -1513,27 +1525,27 @@
     </row>
     <row r="49" spans="1:21">
       <c r="A49" s="1">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B49">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C49">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:21">
       <c r="A50" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B50">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -1541,10 +1553,13 @@
     </row>
     <row r="51" spans="1:21">
       <c r="A51" s="1">
-        <v>46265</v>
+        <v>46266</v>
+      </c>
+      <c r="B51">
+        <v>17</v>
       </c>
       <c r="C51">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -1552,233 +1567,227 @@
     </row>
     <row r="52" spans="1:21">
       <c r="A52" s="1">
-        <v>46264</v>
-      </c>
-      <c r="B52">
-        <v>5</v>
+        <v>46265</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:21">
       <c r="A53" s="1">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B53">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="C53">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:21">
       <c r="A54" s="1">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B54">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C54">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:21">
       <c r="A55" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B55">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C55">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D55">
-        <v>3</v>
-      </c>
-      <c r="E55" s="4">
-        <v>0.21422999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:21">
       <c r="A56" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B56">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="C56">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="E56" s="4">
+        <v>0.21422999999999998</v>
       </c>
     </row>
     <row r="57" spans="1:21">
       <c r="A57" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B57">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="C57">
         <v>62</v>
       </c>
       <c r="D57">
-        <v>1</v>
-      </c>
-      <c r="E57" s="4">
-        <v>10.703772000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:21">
       <c r="A58" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B58">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C58">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D58">
         <v>1</v>
+      </c>
+      <c r="E58" s="4">
+        <v>10.703772000000001</v>
       </c>
     </row>
     <row r="59" spans="1:21">
       <c r="A59" s="1">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B59">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:21">
       <c r="A60" s="1">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B60">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="C60">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:21">
       <c r="A61" s="1">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B61">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="C61">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62" spans="1:21">
       <c r="A62" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B62">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="C62">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D62">
-        <v>0</v>
-      </c>
-      <c r="E62" s="4">
-        <v>8.4293359999999993</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:21">
       <c r="A63" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B63">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C63">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D63">
-        <v>1</v>
-      </c>
-      <c r="G63" s="7"/>
-      <c r="H63" s="7"/>
-      <c r="I63" s="3"/>
-      <c r="J63" s="3"/>
-      <c r="K63" s="7"/>
-      <c r="L63" s="7"/>
-      <c r="M63" s="7"/>
-      <c r="N63" s="7"/>
-      <c r="O63" s="7"/>
-      <c r="P63" s="7"/>
-      <c r="Q63" s="7"/>
-      <c r="R63" s="7"/>
-      <c r="S63" s="7"/>
-      <c r="T63" s="7"/>
-      <c r="U63" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="E63" s="4">
+        <v>8.4293359999999993</v>
+      </c>
     </row>
     <row r="64" spans="1:21">
       <c r="A64" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D64">
-        <v>2</v>
-      </c>
-      <c r="E64" s="4">
-        <v>6.2419820000000001</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G64" s="7"/>
+      <c r="H64" s="7"/>
+      <c r="I64" s="3"/>
+      <c r="J64" s="3"/>
+      <c r="K64" s="7"/>
+      <c r="L64" s="7"/>
+      <c r="M64" s="7"/>
+      <c r="N64" s="7"/>
+      <c r="O64" s="7"/>
+      <c r="P64" s="7"/>
+      <c r="Q64" s="7"/>
+      <c r="R64" s="7"/>
+      <c r="S64" s="7"/>
+      <c r="T64" s="7"/>
+      <c r="U64" s="7"/>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="1">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B65">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" s="4">
-        <v>14.777381999999999</v>
+        <v>6.2419820000000001</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="1">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B66">
         <v>12</v>
@@ -1786,10 +1795,19 @@
       <c r="C66">
         <v>0</v>
       </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="E66" s="4">
+        <v>14.777381999999999</v>
+      </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="1">
-        <v>46249</v>
+        <v>46250</v>
+      </c>
+      <c r="B67">
+        <v>12</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -1797,100 +1815,94 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="1">
-        <v>46248</v>
-      </c>
-      <c r="B68">
-        <v>7</v>
+        <v>46249</v>
       </c>
       <c r="C68">
-        <v>16</v>
-      </c>
-      <c r="D68">
-        <v>0</v>
-      </c>
-      <c r="E68" s="4">
-        <v>20.847041999999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B69">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="C69">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69" s="4">
-        <v>5.4199330000000003</v>
+        <v>20.847041999999995</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="1">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B70">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C70">
         <v>21</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E70" s="4">
+        <v>5.4199330000000003</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="1">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B71">
+        <v>28</v>
+      </c>
+      <c r="C71">
         <v>21</v>
       </c>
-      <c r="C71">
-        <v>25</v>
-      </c>
       <c r="D71">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="1">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B72">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C72">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D72">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="1">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B73">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="1">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -1901,10 +1913,10 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="1">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B75">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -1915,10 +1927,10 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="1">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B76">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -1929,29 +1941,43 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="1">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B78">
+        <v>0</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="1">
         <v>46238</v>
       </c>
-      <c r="B78">
-        <v>0</v>
-      </c>
-      <c r="C78">
-        <v>0</v>
-      </c>
-      <c r="D78">
+      <c r="B79">
+        <v>0</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="D79">
         <v>1</v>
       </c>
     </row>
@@ -2036,7 +2062,7 @@
       </c>
       <c r="B3">
         <f>4375+SUM(B6:B500)</f>
-        <v>5184</v>
+        <v>5216</v>
       </c>
       <c r="C3">
         <f>7462+SUM(C6:C100)</f>
@@ -2060,7 +2086,7 @@
       </c>
       <c r="H3">
         <f>14+SUM(H5:H100)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I3">
         <f>170+SUM(I5:I150)</f>
@@ -2077,7 +2103,7 @@
       </c>
       <c r="B4">
         <f>B2-B3</f>
-        <v>4513</v>
+        <v>4481</v>
       </c>
       <c r="C4">
         <f>C2-C3</f>
@@ -2101,7 +2127,7 @@
       </c>
       <c r="H4">
         <f>H2-H3</f>
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I4">
         <f>I2-I3</f>
@@ -2462,7 +2488,36 @@
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="1"/>
+      <c r="A16" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B16">
+        <v>32</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30613"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1189" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7836BCFD-65CA-4265-99ED-316BDBE5497B}"/>
+  <xr:revisionPtr revIDLastSave="1216" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74C61ACF-6154-4441-A247-16A623C69BBF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>
@@ -53,19 +53,19 @@
     <t>ACC</t>
   </si>
   <si>
-    <t>Daily-30; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 921;Total - 5536 MT</t>
+    <t>Daily-10; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 931;Total - 5547 MT</t>
   </si>
   <si>
     <t>Boiler</t>
   </si>
   <si>
-    <t>Daily-32  - (SH-32 and RH-); Oct-1597 NDHT Balance joints - 8617 (SH - 4481; RH - 4136)</t>
+    <t>Daily-54  - (SH-54 and RH-); Oct-1651 NDHT Balance joints - 8563 (SH - 4427; RH - 4136)</t>
   </si>
   <si>
     <t>PCP Joint</t>
   </si>
   <si>
-    <t>Daily-0; MS Joints - 74/146; MS to PRDS - 11/26; HRH - 10/95; CRH -15/87; LPBP - 11/49; HPBP-8/23; BFD- 177/661</t>
+    <t>Daily-0; MS Joints - 74/146; MS to PRDS - 11/26; HRH - 11/95; CRH -15/87; LPBP - 11/49; HPBP-9/23; BFD- 180/661</t>
   </si>
   <si>
     <t>Boiler - NDHT Joints</t>
@@ -723,7 +723,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -734,7 +734,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -745,7 +745,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -764,7 +764,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
-  <dimension ref="A1:AA79"/>
+  <dimension ref="A1:AA80"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
@@ -809,27 +809,27 @@
     </row>
     <row r="3" spans="1:27">
       <c r="A3" s="1">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B3">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C3">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:27">
       <c r="A4" s="1">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -837,10 +837,10 @@
     </row>
     <row r="5" spans="1:27">
       <c r="A5" s="1">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B5">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -851,13 +851,13 @@
     </row>
     <row r="6" spans="1:27">
       <c r="A6" s="1">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C6">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -865,401 +865,401 @@
     </row>
     <row r="7" spans="1:27">
       <c r="A7" s="1">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B7">
-        <v>117</v>
+        <v>14</v>
       </c>
       <c r="C7">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:27">
       <c r="A8" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B8">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C8">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" s="6">
-        <v>20.72</v>
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:27">
       <c r="A9" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B9">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="C9">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="6">
-        <v>16.425999999999998</v>
+        <v>20.72</v>
       </c>
     </row>
     <row r="10" spans="1:27">
       <c r="A10" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B10">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="C10">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="6">
-        <v>18.917999999999999</v>
+        <v>16.425999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:27">
       <c r="A11" s="1">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B11">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="C11">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" s="6">
-        <v>7.9720000000000004</v>
+        <v>18.917999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:27">
       <c r="A12" s="1">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B12">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12" s="6"/>
+        <v>3</v>
+      </c>
+      <c r="E12" s="6">
+        <v>7.9720000000000004</v>
+      </c>
     </row>
     <row r="13" spans="1:27">
       <c r="A13" s="1">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="B13">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="C13">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="6"/>
     </row>
     <row r="14" spans="1:27">
       <c r="A14" s="1">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B14">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C14">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
-      <c r="E14" s="6">
-        <v>4.3440000000000003</v>
-      </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="3"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="2"/>
-      <c r="Z14" s="2"/>
-      <c r="AA14" s="2"/>
+      <c r="E14" s="6"/>
     </row>
     <row r="15" spans="1:27">
       <c r="A15" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B15">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C15">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
-      <c r="E15" s="6"/>
+      <c r="E15" s="6">
+        <v>4.3440000000000003</v>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="3"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="3"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="X15" s="3"/>
+      <c r="Y15" s="2"/>
+      <c r="Z15" s="2"/>
+      <c r="AA15" s="2"/>
     </row>
     <row r="16" spans="1:27">
       <c r="A16" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B16">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="C16">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="6"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B17">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C17">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D17">
-        <v>4</v>
-      </c>
-      <c r="E17" s="6">
-        <v>4.5679999999999996</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E17" s="6"/>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B18">
         <v>45</v>
       </c>
       <c r="C18">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" s="6">
-        <v>6.4130000000000003</v>
+        <v>4.5679999999999996</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B19">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E19" s="6">
-        <v>4.3440000000000003</v>
+        <v>6.4130000000000003</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B20">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C20">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20" s="6"/>
+        <v>0</v>
+      </c>
+      <c r="E20" s="6">
+        <v>4.3440000000000003</v>
+      </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="6"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B22">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="6"/>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B23">
-        <v>321</v>
+        <v>40</v>
       </c>
       <c r="C23">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23" s="5">
-        <v>37.679307999999999</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E23" s="6"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B24">
-        <v>200</v>
+        <v>321</v>
       </c>
       <c r="C24">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="5">
-        <v>33.449338000000004</v>
+        <v>37.679307999999999</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B25">
-        <v>43</v>
+        <v>200</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="D25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E25" s="5">
-        <v>42.041217999999994</v>
+        <v>33.449338000000004</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="1">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B26">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="E26" s="5">
+        <v>42.041217999999994</v>
+      </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B27">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C27">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
-      <c r="E27" s="5">
-        <v>16.912866999999999</v>
-      </c>
+      <c r="E27" s="6"/>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B28">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C28">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E28" s="5">
-        <v>11.657306</v>
+        <v>16.912866999999999</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B29">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C29">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="E29" s="5">
+        <v>11.657306</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C30">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1267,13 +1267,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B31">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -1281,27 +1281,27 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B32">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C32">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B33">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C33">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -1309,21 +1309,21 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B34">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C34">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D34">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B35">
         <v>16</v>
@@ -1334,162 +1334,162 @@
       <c r="D35">
         <v>4</v>
       </c>
-      <c r="E35" s="5">
-        <v>30.143184999999992</v>
-      </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B36">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C36">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="E36" s="5">
+        <v>30.143184999999992</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C37">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B38">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="C38">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B39">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B40">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="C40">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B41">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="C41">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="D41">
-        <v>1</v>
-      </c>
-      <c r="E41" s="5">
-        <v>5.3833070000000003</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="1">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B42">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C42">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="D42">
         <v>1</v>
+      </c>
+      <c r="E42" s="5">
+        <v>5.3833070000000003</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="1">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B43">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="C43">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="D43">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B44">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C44">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="1">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B45">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C45">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="1">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B46">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -1497,314 +1497,311 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="1">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C47">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="1">
+        <v>46270</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <v>90</v>
+      </c>
+      <c r="D48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="1">
         <v>46269</v>
       </c>
-      <c r="B48">
-        <v>0</v>
-      </c>
-      <c r="C48">
-        <v>0</v>
-      </c>
-      <c r="D48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:21">
-      <c r="A49" s="1">
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="1">
         <v>46268</v>
       </c>
-      <c r="B49">
+      <c r="B50">
         <v>23</v>
       </c>
-      <c r="C49">
+      <c r="C50">
         <v>74</v>
       </c>
-      <c r="D49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:21">
-      <c r="A50" s="1">
+      <c r="D50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="1">
         <v>46267</v>
       </c>
-      <c r="B50">
+      <c r="B51">
         <v>7</v>
       </c>
-      <c r="C50">
+      <c r="C51">
         <v>75</v>
       </c>
-      <c r="D50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:21">
-      <c r="A51" s="1">
+      <c r="D51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="1">
         <v>46266</v>
       </c>
-      <c r="B51">
+      <c r="B52">
         <v>17</v>
       </c>
-      <c r="C51">
-        <v>0</v>
-      </c>
-      <c r="D51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:21">
-      <c r="A52" s="1">
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="1">
         <v>46265</v>
       </c>
-      <c r="C52">
+      <c r="C53">
         <v>62</v>
       </c>
-      <c r="D52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:21">
-      <c r="A53" s="1">
+      <c r="D53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="1">
         <v>46264</v>
       </c>
-      <c r="B53">
+      <c r="B54">
         <v>5</v>
       </c>
-      <c r="C53">
-        <v>0</v>
-      </c>
-      <c r="D53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:21">
-      <c r="A54" s="1">
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="1">
         <v>46263</v>
       </c>
-      <c r="B54">
+      <c r="B55">
         <v>73</v>
       </c>
-      <c r="C54">
+      <c r="C55">
         <v>62</v>
       </c>
-      <c r="D54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:21">
-      <c r="A55" s="1">
+      <c r="D55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="1">
         <v>46262</v>
       </c>
-      <c r="B55">
+      <c r="B56">
         <v>67</v>
       </c>
-      <c r="C55">
+      <c r="C56">
         <v>54</v>
       </c>
-      <c r="D55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:21">
-      <c r="A56" s="1">
+      <c r="D56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="1">
         <v>46261</v>
       </c>
-      <c r="B56">
+      <c r="B57">
         <v>29</v>
       </c>
-      <c r="C56">
+      <c r="C57">
         <v>64</v>
       </c>
-      <c r="D56">
+      <c r="D57">
         <v>3</v>
       </c>
-      <c r="E56" s="4">
+      <c r="E57" s="4">
         <v>0.21422999999999998</v>
       </c>
     </row>
-    <row r="57" spans="1:21">
-      <c r="A57" s="1">
+    <row r="58" spans="1:5">
+      <c r="A58" s="1">
         <v>46260</v>
       </c>
-      <c r="B57">
+      <c r="B58">
         <v>85</v>
-      </c>
-      <c r="C57">
-        <v>62</v>
-      </c>
-      <c r="D57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:21">
-      <c r="A58" s="1">
-        <v>46259</v>
-      </c>
-      <c r="B58">
-        <v>13</v>
       </c>
       <c r="C58">
         <v>62</v>
       </c>
       <c r="D58">
-        <v>1</v>
-      </c>
-      <c r="E58" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B59">
+        <v>13</v>
+      </c>
+      <c r="C59">
+        <v>62</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="E59" s="4">
         <v>10.703772000000001</v>
       </c>
     </row>
-    <row r="59" spans="1:21">
-      <c r="A59" s="1">
+    <row r="60" spans="1:5">
+      <c r="A60" s="1">
         <v>46258</v>
       </c>
-      <c r="B59">
+      <c r="B60">
         <v>18</v>
       </c>
-      <c r="C59">
+      <c r="C60">
         <v>56</v>
       </c>
-      <c r="D59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:21">
-      <c r="A60" s="1">
+      <c r="D60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="1">
         <v>46257</v>
       </c>
-      <c r="B60">
+      <c r="B61">
         <v>3</v>
       </c>
-      <c r="C60">
-        <v>0</v>
-      </c>
-      <c r="D60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:21">
-      <c r="A61" s="1">
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="1">
         <v>46256</v>
       </c>
-      <c r="B61">
+      <c r="B62">
         <v>69</v>
       </c>
-      <c r="C61">
+      <c r="C62">
         <v>53</v>
       </c>
-      <c r="D61">
+      <c r="D62">
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:21">
-      <c r="A62" s="1">
+    <row r="63" spans="1:5">
+      <c r="A63" s="1">
         <v>46255</v>
       </c>
-      <c r="B62">
+      <c r="B63">
         <v>15</v>
       </c>
-      <c r="C62">
+      <c r="C63">
         <v>60</v>
       </c>
-      <c r="D62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:21">
-      <c r="A63" s="1">
+      <c r="D63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="1">
         <v>46254</v>
       </c>
-      <c r="B63">
+      <c r="B64">
         <v>48</v>
       </c>
-      <c r="C63">
+      <c r="C64">
         <v>43</v>
       </c>
-      <c r="D63">
-        <v>0</v>
-      </c>
-      <c r="E63" s="4">
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64" s="4">
         <v>8.4293359999999993</v>
       </c>
     </row>
-    <row r="64" spans="1:21">
-      <c r="A64" s="1">
+    <row r="65" spans="1:21">
+      <c r="A65" s="1">
         <v>46253</v>
       </c>
-      <c r="B64">
+      <c r="B65">
         <v>27</v>
       </c>
-      <c r="C64">
+      <c r="C65">
         <v>51</v>
       </c>
-      <c r="D64">
-        <v>1</v>
-      </c>
-      <c r="G64" s="7"/>
-      <c r="H64" s="7"/>
-      <c r="I64" s="3"/>
-      <c r="J64" s="3"/>
-      <c r="K64" s="7"/>
-      <c r="L64" s="7"/>
-      <c r="M64" s="7"/>
-      <c r="N64" s="7"/>
-      <c r="O64" s="7"/>
-      <c r="P64" s="7"/>
-      <c r="Q64" s="7"/>
-      <c r="R64" s="7"/>
-      <c r="S64" s="7"/>
-      <c r="T64" s="7"/>
-      <c r="U64" s="7"/>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="1">
+      <c r="D65">
+        <v>1</v>
+      </c>
+      <c r="G65" s="7"/>
+      <c r="H65" s="7"/>
+      <c r="I65" s="3"/>
+      <c r="J65" s="3"/>
+      <c r="K65" s="7"/>
+      <c r="L65" s="7"/>
+      <c r="M65" s="7"/>
+      <c r="N65" s="7"/>
+      <c r="O65" s="7"/>
+      <c r="P65" s="7"/>
+      <c r="Q65" s="7"/>
+      <c r="R65" s="7"/>
+      <c r="S65" s="7"/>
+      <c r="T65" s="7"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="1:21">
+      <c r="A66" s="1">
         <v>46252</v>
       </c>
-      <c r="B65">
-        <v>0</v>
-      </c>
-      <c r="C65">
-        <v>0</v>
-      </c>
-      <c r="D65">
+      <c r="B66">
+        <v>0</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66">
         <v>2</v>
       </c>
-      <c r="E65" s="4">
+      <c r="E66" s="4">
         <v>6.2419820000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="1">
+    <row r="67" spans="1:21">
+      <c r="A67" s="1">
         <v>46251</v>
-      </c>
-      <c r="B66">
-        <v>12</v>
-      </c>
-      <c r="C66">
-        <v>0</v>
-      </c>
-      <c r="D66">
-        <v>1</v>
-      </c>
-      <c r="E66" s="4">
-        <v>14.777381999999999</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="1">
-        <v>46250</v>
       </c>
       <c r="B67">
         <v>12</v>
@@ -1812,172 +1809,189 @@
       <c r="C67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:5">
+      <c r="D67">
+        <v>1</v>
+      </c>
+      <c r="E67" s="4">
+        <v>14.777381999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21">
       <c r="A68" s="1">
+        <v>46250</v>
+      </c>
+      <c r="B68">
+        <v>12</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21">
+      <c r="A69" s="1">
         <v>46249</v>
       </c>
-      <c r="C68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="1">
+      <c r="C69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21">
+      <c r="A70" s="1">
         <v>46248</v>
       </c>
-      <c r="B69">
+      <c r="B70">
         <v>7</v>
       </c>
-      <c r="C69">
+      <c r="C70">
         <v>16</v>
       </c>
-      <c r="D69">
-        <v>0</v>
-      </c>
-      <c r="E69" s="4">
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70" s="4">
         <v>20.847041999999995</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="1">
+    <row r="71" spans="1:21">
+      <c r="A71" s="1">
         <v>46247</v>
       </c>
-      <c r="B70">
+      <c r="B71">
         <v>35</v>
-      </c>
-      <c r="C70">
-        <v>21</v>
-      </c>
-      <c r="D70">
-        <v>0</v>
-      </c>
-      <c r="E70" s="4">
-        <v>5.4199330000000003</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="1">
-        <v>46246</v>
-      </c>
-      <c r="B71">
-        <v>28</v>
       </c>
       <c r="C71">
         <v>21</v>
       </c>
       <c r="D71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="E71" s="4">
+        <v>5.4199330000000003</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21">
       <c r="A72" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B72">
+        <v>28</v>
+      </c>
+      <c r="C72">
+        <v>21</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21">
+      <c r="A73" s="1">
         <v>46245</v>
       </c>
-      <c r="B72">
+      <c r="B73">
         <v>21</v>
       </c>
-      <c r="C72">
+      <c r="C73">
         <v>25</v>
       </c>
-      <c r="D72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="1">
+      <c r="D73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21">
+      <c r="A74" s="1">
         <v>46244</v>
       </c>
-      <c r="B73">
+      <c r="B74">
         <v>19</v>
       </c>
-      <c r="C73">
+      <c r="C74">
         <v>11</v>
       </c>
-      <c r="D73">
+      <c r="D74">
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="1">
+    <row r="75" spans="1:21">
+      <c r="A75" s="1">
         <v>46243</v>
       </c>
-      <c r="B74">
+      <c r="B75">
         <v>13</v>
       </c>
-      <c r="C74">
-        <v>0</v>
-      </c>
-      <c r="D74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="1">
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21">
+      <c r="A76" s="1">
         <v>46242</v>
       </c>
-      <c r="B75">
-        <v>0</v>
-      </c>
-      <c r="C75">
-        <v>0</v>
-      </c>
-      <c r="D75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="1">
+      <c r="B76">
+        <v>0</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21">
+      <c r="A77" s="1">
         <v>46241</v>
       </c>
-      <c r="B76">
+      <c r="B77">
         <v>32</v>
       </c>
-      <c r="C76">
-        <v>0</v>
-      </c>
-      <c r="D76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="1">
+      <c r="C77">
+        <v>0</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21">
+      <c r="A78" s="1">
         <v>46240</v>
       </c>
-      <c r="B77">
+      <c r="B78">
         <v>16</v>
       </c>
-      <c r="C77">
-        <v>0</v>
-      </c>
-      <c r="D77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="1">
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21">
+      <c r="A79" s="1">
         <v>46239</v>
       </c>
-      <c r="B78">
-        <v>0</v>
-      </c>
-      <c r="C78">
-        <v>0</v>
-      </c>
-      <c r="D78">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="1">
+      <c r="B79">
+        <v>0</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="D79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21">
+      <c r="A80" s="1">
         <v>46238</v>
       </c>
-      <c r="B79">
-        <v>0</v>
-      </c>
-      <c r="C79">
-        <v>0</v>
-      </c>
-      <c r="D79">
+      <c r="B80">
+        <v>0</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+      <c r="D80">
         <v>1</v>
       </c>
     </row>
@@ -1988,7 +2002,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D41FB4CD-150C-4CE3-A76E-CB540C2892DD}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
@@ -2062,7 +2076,7 @@
       </c>
       <c r="B3">
         <f>4375+SUM(B6:B500)</f>
-        <v>5216</v>
+        <v>5270</v>
       </c>
       <c r="C3">
         <f>7462+SUM(C6:C100)</f>
@@ -2074,7 +2088,7 @@
       </c>
       <c r="E3">
         <f>10+SUM(E5:E150)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <f>10+SUM(F5:F100)</f>
@@ -2082,7 +2096,7 @@
       </c>
       <c r="G3">
         <f>8+SUM(G5:G100)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3">
         <f>14+SUM(H5:H100)</f>
@@ -2090,7 +2104,7 @@
       </c>
       <c r="I3">
         <f>170+SUM(I5:I150)</f>
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J3">
         <f>1195+SUM(J5:J200)</f>
@@ -2103,7 +2117,7 @@
       </c>
       <c r="B4">
         <f>B2-B3</f>
-        <v>4481</v>
+        <v>4427</v>
       </c>
       <c r="C4">
         <f>C2-C3</f>
@@ -2115,7 +2129,7 @@
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F4">
         <f t="shared" si="0"/>
@@ -2123,7 +2137,7 @@
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H4">
         <f>H2-H3</f>
@@ -2131,7 +2145,7 @@
       </c>
       <c r="I4">
         <f>I2-I3</f>
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="J4">
         <f>J2-J3</f>
@@ -2516,6 +2530,38 @@
         <v>0</v>
       </c>
       <c r="J16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B17">
+        <v>54</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>2</v>
+      </c>
+      <c r="J17">
         <v>0</v>
       </c>
     </row>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1216" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74C61ACF-6154-4441-A247-16A623C69BBF}"/>
+  <xr:revisionPtr revIDLastSave="1276" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E94F992-1BC0-4019-B793-F9E9A0C84282}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>
@@ -53,19 +53,19 @@
     <t>ACC</t>
   </si>
   <si>
-    <t>Daily-10; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 931;Total - 5547 MT</t>
+    <t>Daily-20; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 951;Total - 5567 MT</t>
   </si>
   <si>
     <t>Boiler</t>
   </si>
   <si>
-    <t>Daily-54  - (SH-54 and RH-); Oct-1651 NDHT Balance joints - 8563 (SH - 4427; RH - 4136)</t>
+    <t>Daily-98  - (SH-86 and RH-12); Oct-1749 NDHT Balance joints - 8465 (SH - 4341; RH - 4124)</t>
   </si>
   <si>
     <t>PCP Joint</t>
   </si>
   <si>
-    <t>Daily-0; MS Joints - 74/146; MS to PRDS - 11/26; HRH - 11/95; CRH -15/87; LPBP - 11/49; HPBP-9/23; BFD- 180/661</t>
+    <t>Daily-0; MS Joints - 74/146; MS to PRDS - 11/26; HRH - 11/95; CRH -15/87; LPBP - 11/49; HPBP-10/23; BFD- 181/661</t>
   </si>
   <si>
     <t>Boiler - NDHT Joints</t>
@@ -723,7 +723,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -734,7 +734,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -745,7 +745,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -764,7 +764,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
-  <dimension ref="A1:AA80"/>
+  <dimension ref="A1:AA82"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
@@ -773,7 +773,7 @@
     <col min="5" max="6" width="11.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -790,7 +790,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -807,728 +807,801 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:27">
+    <row r="3" spans="1:5">
       <c r="A3" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B3">
+        <v>20</v>
+      </c>
+      <c r="C3">
+        <v>98</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1">
         <v>46317</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>10</v>
       </c>
-      <c r="C3">
+      <c r="C4">
         <v>54</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27">
-      <c r="A4" s="1">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1">
         <v>46316</v>
       </c>
-      <c r="B4">
+      <c r="B5">
         <v>30</v>
       </c>
-      <c r="C4">
+      <c r="C5">
         <v>32</v>
       </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27">
-      <c r="A5" s="1">
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1">
         <v>46314</v>
       </c>
-      <c r="B5">
+      <c r="B7">
         <v>6</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27">
-      <c r="A6" s="1">
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1">
         <v>46313</v>
       </c>
-      <c r="B6">
+      <c r="B8">
         <v>18</v>
       </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27">
-      <c r="A7" s="1">
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1">
         <v>46312</v>
       </c>
-      <c r="B7">
+      <c r="B9">
         <v>14</v>
       </c>
-      <c r="C7">
+      <c r="C9">
         <v>85</v>
       </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27">
-      <c r="A8" s="1">
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1">
         <v>46311</v>
       </c>
-      <c r="B8">
+      <c r="B10">
         <v>117</v>
       </c>
-      <c r="C8">
+      <c r="C10">
         <v>148</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27">
-      <c r="A9" s="1">
-        <v>46310</v>
-      </c>
-      <c r="B9">
-        <v>56</v>
-      </c>
-      <c r="C9">
-        <v>122</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" s="6">
-        <v>20.72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27">
-      <c r="A10" s="1">
-        <v>46309</v>
-      </c>
-      <c r="B10">
-        <v>23</v>
-      </c>
-      <c r="C10">
-        <v>135</v>
       </c>
       <c r="D10">
         <v>2</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B11">
+        <v>56</v>
+      </c>
+      <c r="C11">
+        <v>122</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="6">
+        <v>20.72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B12">
+        <v>23</v>
+      </c>
+      <c r="C12">
+        <v>135</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12" s="6">
         <v>16.425999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:27">
-      <c r="A11" s="1">
+    <row r="13" spans="1:5">
+      <c r="A13" s="1">
         <v>46308</v>
       </c>
-      <c r="B11">
+      <c r="B13">
         <v>44</v>
       </c>
-      <c r="C11">
+      <c r="C13">
         <v>127</v>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" s="6">
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" s="6">
         <v>18.917999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:27">
-      <c r="A12" s="1">
+    <row r="14" spans="1:5">
+      <c r="A14" s="1">
         <v>46307</v>
       </c>
-      <c r="B12">
+      <c r="B14">
         <v>102</v>
       </c>
-      <c r="C12">
+      <c r="C14">
         <v>118</v>
       </c>
-      <c r="D12">
+      <c r="D14">
         <v>3</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E14" s="6">
         <v>7.9720000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:27">
-      <c r="A13" s="1">
+    <row r="15" spans="1:5">
+      <c r="A15" s="1">
         <v>46306</v>
       </c>
-      <c r="B13">
+      <c r="B15">
         <v>21</v>
       </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13" s="6"/>
-    </row>
-    <row r="14" spans="1:27">
-      <c r="A14" s="1">
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="1">
         <v>46305</v>
       </c>
-      <c r="B14">
+      <c r="B16">
         <v>83</v>
       </c>
-      <c r="C14">
+      <c r="C16">
         <v>82</v>
       </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="6"/>
-    </row>
-    <row r="15" spans="1:27">
-      <c r="A15" s="1">
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27">
+      <c r="A17" s="1">
         <v>46304</v>
       </c>
-      <c r="B15">
+      <c r="B17">
         <v>74</v>
       </c>
-      <c r="C15">
+      <c r="C17">
         <v>130</v>
       </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="6">
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" s="6">
         <v>4.3440000000000003</v>
       </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="3"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="2"/>
-      <c r="U15" s="2"/>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="2"/>
-      <c r="Z15" s="2"/>
-      <c r="AA15" s="2"/>
-    </row>
-    <row r="16" spans="1:27">
-      <c r="A16" s="1">
+      <c r="I17" s="2"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="3"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="3"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="X17" s="3"/>
+      <c r="Y17" s="2"/>
+      <c r="Z17" s="2"/>
+      <c r="AA17" s="2"/>
+    </row>
+    <row r="18" spans="1:27">
+      <c r="A18" s="1">
         <v>46303</v>
       </c>
-      <c r="B16">
+      <c r="B18">
         <v>70</v>
       </c>
-      <c r="C16">
+      <c r="C18">
         <v>134</v>
       </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16" s="6"/>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="1">
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27">
+      <c r="A19" s="1">
         <v>46302</v>
       </c>
-      <c r="B17">
+      <c r="B19">
         <v>26</v>
       </c>
-      <c r="C17">
+      <c r="C19">
         <v>91</v>
       </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17" s="6"/>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="1">
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27">
+      <c r="A20" s="1">
         <v>46301</v>
       </c>
-      <c r="B18">
+      <c r="B20">
         <v>45</v>
       </c>
-      <c r="C18">
+      <c r="C20">
         <v>104</v>
       </c>
-      <c r="D18">
+      <c r="D20">
         <v>4</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E20" s="6">
         <v>4.5679999999999996</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="1">
+    <row r="21" spans="1:27">
+      <c r="A21" s="1">
         <v>46300</v>
       </c>
-      <c r="B19">
+      <c r="B21">
         <v>45</v>
       </c>
-      <c r="C19">
+      <c r="C21">
         <v>123</v>
       </c>
-      <c r="D19">
+      <c r="D21">
         <v>2</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E21" s="6">
         <v>6.4130000000000003</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="1">
+    <row r="22" spans="1:27">
+      <c r="A22" s="1">
         <v>46299</v>
       </c>
-      <c r="B20">
+      <c r="B22">
         <v>66</v>
       </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20" s="6">
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22" s="6">
         <v>4.3440000000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="1">
+    <row r="23" spans="1:27">
+      <c r="A23" s="1">
         <v>46298</v>
-      </c>
-      <c r="B21">
-        <v>40</v>
-      </c>
-      <c r="C21">
-        <v>65</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21" s="6"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="1">
-        <v>46297</v>
-      </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22" s="6"/>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="1">
-        <v>46296</v>
       </c>
       <c r="B23">
         <v>40</v>
       </c>
       <c r="C23">
+        <v>65</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27">
+      <c r="A24" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27">
+      <c r="A25" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B25">
+        <v>40</v>
+      </c>
+      <c r="C25">
         <v>101</v>
       </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23" s="6"/>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="1">
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27">
+      <c r="A26" s="1">
         <v>46295</v>
       </c>
-      <c r="B24">
+      <c r="B26">
         <v>321</v>
       </c>
-      <c r="C24">
+      <c r="C26">
         <v>139</v>
       </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24" s="5">
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5">
         <v>37.679307999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="1">
+    <row r="27" spans="1:27">
+      <c r="A27" s="1">
         <v>46294</v>
       </c>
-      <c r="B25">
+      <c r="B27">
         <v>200</v>
       </c>
-      <c r="C25">
+      <c r="C27">
         <v>114</v>
       </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-      <c r="E25" s="5">
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27" s="5">
         <v>33.449338000000004</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="1">
+    <row r="28" spans="1:27">
+      <c r="A28" s="1">
         <v>46293</v>
       </c>
-      <c r="B26">
+      <c r="B28">
         <v>43</v>
       </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
         <v>4</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E28" s="5">
         <v>42.041217999999994</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="1">
+    <row r="29" spans="1:27">
+      <c r="A29" s="1">
         <v>46292</v>
       </c>
-      <c r="B27">
+      <c r="B29">
         <v>13</v>
       </c>
-      <c r="C27">
-        <v>0</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-      <c r="E27" s="6"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="1">
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27">
+      <c r="A30" s="1">
         <v>46291</v>
       </c>
-      <c r="B28">
+      <c r="B30">
         <v>17</v>
       </c>
-      <c r="C28">
+      <c r="C30">
         <v>39</v>
       </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="E28" s="5">
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30" s="5">
         <v>16.912866999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="1">
+    <row r="31" spans="1:27">
+      <c r="A31" s="1">
         <v>46290</v>
       </c>
-      <c r="B29">
+      <c r="B31">
         <v>20</v>
       </c>
-      <c r="C29">
+      <c r="C31">
         <v>121</v>
       </c>
-      <c r="D29">
+      <c r="D31">
         <v>2</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E31" s="5">
         <v>11.657306</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="1">
+    <row r="32" spans="1:27">
+      <c r="A32" s="1">
         <v>46289</v>
       </c>
-      <c r="B30">
+      <c r="B32">
         <v>3</v>
       </c>
-      <c r="C30">
+      <c r="C32">
         <v>133</v>
       </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="1">
-        <v>46288</v>
-      </c>
-      <c r="B31">
-        <v>0</v>
-      </c>
-      <c r="C31">
-        <v>143</v>
-      </c>
-      <c r="D31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="1">
-        <v>46287</v>
-      </c>
-      <c r="B32">
-        <v>9</v>
-      </c>
-      <c r="C32">
-        <v>0</v>
-      </c>
       <c r="D32">
         <v>1</v>
+      </c>
+      <c r="E32" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="B33">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="B34">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C34">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="B35">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C35">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="E35" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="B36">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C36">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E36" s="5">
-        <v>30.143184999999992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1">
-        <v>46281</v>
+        <v>46284</v>
       </c>
       <c r="B37">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C37">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="D37">
+        <v>4</v>
+      </c>
+      <c r="E37" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C38">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="E38" s="5">
+        <v>30.143184999999992</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="B39">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C39">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="E39" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="B40">
         <v>3</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="B41">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C41">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="D41">
         <v>2</v>
       </c>
+      <c r="E41" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="1">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="B42">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C42">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" s="5">
-        <v>5.3833070000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="1">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B43">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="C43">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="E43" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="1">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B44">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="C44">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="E44" s="5">
+        <v>5.3833070000000003</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B45">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="C45">
-        <v>105</v>
+        <v>16</v>
       </c>
       <c r="D45">
         <v>1</v>
+      </c>
+      <c r="E45" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="1">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="B46">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C46">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="1">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="B47">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="1">
-        <v>46270</v>
+        <v>46272</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C48">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="1">
-        <v>46269</v>
+        <v>46271</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -1539,52 +1612,55 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="1">
-        <v>46268</v>
+        <v>46270</v>
       </c>
       <c r="B50">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="1">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B51">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C51">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="1">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B52">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="1">
-        <v>46265</v>
+        <v>46267</v>
+      </c>
+      <c r="B53">
+        <v>7</v>
       </c>
       <c r="C53">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -1592,24 +1668,21 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="1">
-        <v>46264</v>
+        <v>46266</v>
       </c>
       <c r="B54">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C54">
         <v>0</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="1">
-        <v>46263</v>
-      </c>
-      <c r="B55">
-        <v>73</v>
+        <v>46265</v>
       </c>
       <c r="C55">
         <v>62</v>
@@ -1620,13 +1693,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="1">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="B56">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="C56">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -1634,30 +1707,27 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="1">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="B57">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="C57">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D57">
-        <v>3</v>
-      </c>
-      <c r="E57" s="4">
-        <v>0.21422999999999998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B58">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="C58">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -1665,261 +1735,264 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="1">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B59">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C59">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E59" s="4">
-        <v>10.703772000000001</v>
+        <v>0.21422999999999998</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="1">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B60">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="C60">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="1">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B61">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E61" s="4">
+        <v>10.703772000000001</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="1">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="B62">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="C62">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D62">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="1">
-        <v>46255</v>
+        <v>46257</v>
       </c>
       <c r="B63">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C63">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="1">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="B64">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="C64">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D64">
-        <v>0</v>
-      </c>
-      <c r="E64" s="4">
-        <v>8.4293359999999993</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:21">
       <c r="A65" s="1">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B65">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C65">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D65">
         <v>1</v>
       </c>
-      <c r="G65" s="7"/>
-      <c r="H65" s="7"/>
-      <c r="I65" s="3"/>
-      <c r="J65" s="3"/>
-      <c r="K65" s="7"/>
-      <c r="L65" s="7"/>
-      <c r="M65" s="7"/>
-      <c r="N65" s="7"/>
-      <c r="O65" s="7"/>
-      <c r="P65" s="7"/>
-      <c r="Q65" s="7"/>
-      <c r="R65" s="7"/>
-      <c r="S65" s="7"/>
-      <c r="T65" s="7"/>
-      <c r="U65" s="7"/>
     </row>
     <row r="66" spans="1:21">
       <c r="A66" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B66">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="D66">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E66" s="4">
-        <v>6.2419820000000001</v>
+        <v>8.4293359999999993</v>
       </c>
     </row>
     <row r="67" spans="1:21">
       <c r="A67" s="1">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B67">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D67">
         <v>1</v>
       </c>
-      <c r="E67" s="4">
-        <v>14.777381999999999</v>
-      </c>
+      <c r="G67" s="7"/>
+      <c r="H67" s="7"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="3"/>
+      <c r="K67" s="7"/>
+      <c r="L67" s="7"/>
+      <c r="M67" s="7"/>
+      <c r="N67" s="7"/>
+      <c r="O67" s="7"/>
+      <c r="P67" s="7"/>
+      <c r="Q67" s="7"/>
+      <c r="R67" s="7"/>
+      <c r="S67" s="7"/>
+      <c r="T67" s="7"/>
+      <c r="U67" s="7"/>
     </row>
     <row r="68" spans="1:21">
       <c r="A68" s="1">
-        <v>46250</v>
+        <v>46252</v>
       </c>
       <c r="B68">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C68">
         <v>0</v>
+      </c>
+      <c r="D68">
+        <v>2</v>
+      </c>
+      <c r="E68" s="4">
+        <v>6.2419820000000001</v>
       </c>
     </row>
     <row r="69" spans="1:21">
       <c r="A69" s="1">
-        <v>46249</v>
+        <v>46251</v>
+      </c>
+      <c r="B69">
+        <v>12</v>
       </c>
       <c r="C69">
         <v>0</v>
+      </c>
+      <c r="D69">
+        <v>1</v>
+      </c>
+      <c r="E69" s="4">
+        <v>14.777381999999999</v>
       </c>
     </row>
     <row r="70" spans="1:21">
       <c r="A70" s="1">
-        <v>46248</v>
+        <v>46250</v>
       </c>
       <c r="B70">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C70">
-        <v>16</v>
-      </c>
-      <c r="D70">
-        <v>0</v>
-      </c>
-      <c r="E70" s="4">
-        <v>20.847041999999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:21">
       <c r="A71" s="1">
-        <v>46247</v>
-      </c>
-      <c r="B71">
-        <v>35</v>
+        <v>46249</v>
       </c>
       <c r="C71">
-        <v>21</v>
-      </c>
-      <c r="D71">
-        <v>0</v>
-      </c>
-      <c r="E71" s="4">
-        <v>5.4199330000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:21">
       <c r="A72" s="1">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B72">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C72">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E72" s="4">
+        <v>20.847041999999995</v>
       </c>
     </row>
     <row r="73" spans="1:21">
       <c r="A73" s="1">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B73">
+        <v>35</v>
+      </c>
+      <c r="C73">
         <v>21</v>
       </c>
-      <c r="C73">
-        <v>25</v>
-      </c>
       <c r="D73">
         <v>0</v>
+      </c>
+      <c r="E73" s="4">
+        <v>5.4199330000000003</v>
       </c>
     </row>
     <row r="74" spans="1:21">
       <c r="A74" s="1">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B74">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C74">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D74">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:21">
       <c r="A75" s="1">
-        <v>46243</v>
+        <v>46245</v>
       </c>
       <c r="B75">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -1927,24 +2000,24 @@
     </row>
     <row r="76" spans="1:21">
       <c r="A76" s="1">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:21">
       <c r="A77" s="1">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B77">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -1955,10 +2028,10 @@
     </row>
     <row r="78" spans="1:21">
       <c r="A78" s="1">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="B78">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -1969,29 +2042,57 @@
     </row>
     <row r="79" spans="1:21">
       <c r="A79" s="1">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B79">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C79">
         <v>0</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:21">
       <c r="A80" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B80">
+        <v>16</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B81">
+        <v>0</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="1">
         <v>46238</v>
       </c>
-      <c r="B80">
-        <v>0</v>
-      </c>
-      <c r="C80">
-        <v>0</v>
-      </c>
-      <c r="D80">
+      <c r="B82">
+        <v>0</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
+      <c r="D82">
         <v>1</v>
       </c>
     </row>
@@ -2002,7 +2103,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D41FB4CD-150C-4CE3-A76E-CB540C2892DD}">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
@@ -2076,11 +2177,11 @@
       </c>
       <c r="B3">
         <f>4375+SUM(B6:B500)</f>
-        <v>5270</v>
+        <v>5356</v>
       </c>
       <c r="C3">
         <f>7462+SUM(C6:C100)</f>
-        <v>7734</v>
+        <v>7746</v>
       </c>
       <c r="D3">
         <f>75+SUM(D5:D100)</f>
@@ -2096,7 +2197,7 @@
       </c>
       <c r="G3">
         <f>8+SUM(G5:G100)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H3">
         <f>14+SUM(H5:H100)</f>
@@ -2104,11 +2205,11 @@
       </c>
       <c r="I3">
         <f>170+SUM(I5:I150)</f>
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J3">
         <f>1195+SUM(J5:J200)</f>
-        <v>1284</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -2117,11 +2218,11 @@
       </c>
       <c r="B4">
         <f>B2-B3</f>
-        <v>4427</v>
+        <v>4341</v>
       </c>
       <c r="C4">
         <f>C2-C3</f>
-        <v>4136</v>
+        <v>4124</v>
       </c>
       <c r="D4">
         <f t="shared" ref="D4:G4" si="0">D2-D3</f>
@@ -2137,7 +2238,7 @@
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H4">
         <f>H2-H3</f>
@@ -2145,11 +2246,11 @@
       </c>
       <c r="I4">
         <f>I2-I3</f>
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="J4">
         <f>J2-J3</f>
-        <v>3216</v>
+        <v>3202</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -2563,6 +2664,38 @@
       </c>
       <c r="J17">
         <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B18">
+        <v>86</v>
+      </c>
+      <c r="C18">
+        <v>12</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1276" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E94F992-1BC0-4019-B793-F9E9A0C84282}"/>
+  <xr:revisionPtr revIDLastSave="1324" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D44F3511-CEB2-423D-A955-70653B42A8FB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>
@@ -53,19 +53,19 @@
     <t>ACC</t>
   </si>
   <si>
-    <t>Daily-20; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 951;Total - 5567 MT</t>
+    <t>Daily-8; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 994;Total - 5610 MT</t>
   </si>
   <si>
     <t>Boiler</t>
   </si>
   <si>
-    <t>Daily-98  - (SH-86 and RH-12); Oct-1749 NDHT Balance joints - 8465 (SH - 4341; RH - 4124)</t>
+    <t>Daily-104  - (SH-92 and RH-12); Oct-1864 NDHT Balance joints - 8350 (SH - 4248; RH - 4102)</t>
   </si>
   <si>
     <t>PCP Joint</t>
   </si>
   <si>
-    <t>Daily-0; MS Joints - 74/146; MS to PRDS - 11/26; HRH - 11/95; CRH -15/87; LPBP - 11/49; HPBP-10/23; BFD- 181/661</t>
+    <t>Daily-0; MS Joints - 76/146; MS to PRDS - 11/26; HRH - 11/95; CRH -15/87; LPBP - 11/49; HPBP-10/23; BFD- 182/661</t>
   </si>
   <si>
     <t>Boiler - NDHT Joints</t>
@@ -707,7 +707,7 @@
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="93" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -723,7 +723,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1">
-        <v>46318</v>
+        <v>46320</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -734,7 +734,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -745,7 +745,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1">
-        <v>46318</v>
+        <v>46320</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -764,7 +764,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
-  <dimension ref="A1:AA82"/>
+  <dimension ref="A1:AA84"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
@@ -809,67 +809,67 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1">
-        <v>46318</v>
+        <v>46320</v>
       </c>
       <c r="B3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C4">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1">
-        <v>46316</v>
+        <v>46318</v>
       </c>
       <c r="B5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C5">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="1">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -877,13 +877,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -894,10 +894,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="1">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="B8">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -911,13 +911,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="B9">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -928,165 +928,149 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1">
-        <v>46311</v>
+        <v>46313</v>
       </c>
       <c r="B10">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="C10">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1">
-        <v>46310</v>
+        <v>46312</v>
       </c>
       <c r="B11">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="C11">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" s="6">
-        <v>20.72</v>
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="B12">
-        <v>23</v>
+        <v>117</v>
       </c>
       <c r="C12">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="D12">
         <v>2</v>
       </c>
-      <c r="E12" s="6">
-        <v>16.425999999999998</v>
+      <c r="E12">
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="B13">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C13">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13" s="6">
-        <v>18.917999999999999</v>
+        <v>20.72</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="B14">
-        <v>102</v>
+        <v>23</v>
       </c>
       <c r="C14">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" s="6">
-        <v>7.9720000000000004</v>
+        <v>16.425999999999998</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="B15">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="6">
-        <v>0</v>
+        <v>18.917999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1">
-        <v>46305</v>
+        <v>46307</v>
       </c>
       <c r="B16">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="C16">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="6">
-        <v>0</v>
+        <v>7.9720000000000004</v>
       </c>
     </row>
     <row r="17" spans="1:27">
       <c r="A17" s="1">
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="B17">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="C17">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="6">
-        <v>4.3440000000000003</v>
-      </c>
-      <c r="I17" s="2"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="3"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="2"/>
-      <c r="Z17" s="2"/>
-      <c r="AA17" s="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="18" spans="1:27">
       <c r="A18" s="1">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="B18">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C18">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1097,95 +1081,111 @@
     </row>
     <row r="19" spans="1:27">
       <c r="A19" s="1">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="B19">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="C19">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="6">
-        <v>0</v>
-      </c>
+        <v>4.3440000000000003</v>
+      </c>
+      <c r="I19" s="2"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="3"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="3"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="X19" s="3"/>
+      <c r="Y19" s="2"/>
+      <c r="Z19" s="2"/>
+      <c r="AA19" s="2"/>
     </row>
     <row r="20" spans="1:27">
       <c r="A20" s="1">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="B20">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C20">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="D20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E20" s="6">
-        <v>4.5679999999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:27">
       <c r="A21" s="1">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="B21">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C21">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E21" s="6">
-        <v>6.4130000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:27">
       <c r="A22" s="1">
-        <v>46299</v>
+        <v>46301</v>
       </c>
       <c r="B22">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E22" s="6">
-        <v>4.3440000000000003</v>
+        <v>4.5679999999999996</v>
       </c>
     </row>
     <row r="23" spans="1:27">
       <c r="A23" s="1">
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="B23">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C23">
-        <v>65</v>
+        <v>123</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="6">
-        <v>0</v>
+        <v>6.4130000000000003</v>
       </c>
     </row>
     <row r="24" spans="1:27">
       <c r="A24" s="1">
-        <v>46297</v>
+        <v>46299</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1194,18 +1194,18 @@
         <v>0</v>
       </c>
       <c r="E24" s="6">
-        <v>0</v>
+        <v>4.3440000000000003</v>
       </c>
     </row>
     <row r="25" spans="1:27">
       <c r="A25" s="1">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="B25">
         <v>40</v>
       </c>
       <c r="C25">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1216,149 +1216,149 @@
     </row>
     <row r="26" spans="1:27">
       <c r="A26" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="B26">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
-      <c r="E26" s="5">
-        <v>37.679307999999999</v>
+      <c r="E26" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:27">
       <c r="A27" s="1">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="B27">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="C27">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
-      <c r="E27" s="5">
-        <v>33.449338000000004</v>
+      <c r="E27" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:27">
       <c r="A28" s="1">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="B28">
-        <v>43</v>
+        <v>321</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E28" s="5">
-        <v>42.041217999999994</v>
+        <v>37.679307999999999</v>
       </c>
     </row>
     <row r="29" spans="1:27">
       <c r="A29" s="1">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="B29">
-        <v>13</v>
+        <v>200</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="D29">
-        <v>0</v>
-      </c>
-      <c r="E29" s="6">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E29" s="5">
+        <v>33.449338000000004</v>
       </c>
     </row>
     <row r="30" spans="1:27">
       <c r="A30" s="1">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="B30">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C30">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E30" s="5">
-        <v>16.912866999999999</v>
+        <v>42.041217999999994</v>
       </c>
     </row>
     <row r="31" spans="1:27">
       <c r="A31" s="1">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="B31">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C31">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>2</v>
-      </c>
-      <c r="E31" s="5">
-        <v>11.657306</v>
+        <v>0</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:27">
       <c r="A32" s="1">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C32">
-        <v>133</v>
+        <v>39</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" s="5">
-        <v>0</v>
+        <v>16.912866999999999</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C33">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="5">
-        <v>0</v>
+        <v>11.657306</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B34">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1369,16 +1369,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="B35">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="5">
         <v>0</v>
@@ -1386,16 +1386,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="B36">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C36">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="5">
         <v>0</v>
@@ -1403,16 +1403,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="B37">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C37">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="D37">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E37" s="5">
         <v>0</v>
@@ -1420,33 +1420,33 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="B38">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C38">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E38" s="5">
-        <v>30.143184999999992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1">
-        <v>46281</v>
+        <v>46284</v>
       </c>
       <c r="B39">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C39">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E39" s="5">
         <v>0</v>
@@ -1454,33 +1454,33 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="B40">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C40">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E40" s="5">
-        <v>0</v>
+        <v>30.143184999999992</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="B41">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C41">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E41" s="5">
         <v>0</v>
@@ -1488,16 +1488,16 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="1">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="B42">
         <v>3</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" s="5">
         <v>0</v>
@@ -1505,13 +1505,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="1">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="B43">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C43">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -1522,33 +1522,33 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="1">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="B44">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C44">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" s="5">
-        <v>5.3833070000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="1">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B45">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="C45">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" s="5">
         <v>0</v>
@@ -1556,80 +1556,86 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="1">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B46">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="C46">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D46">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="E46" s="5">
+        <v>5.3833070000000003</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B47">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="C47">
-        <v>105</v>
+        <v>16</v>
       </c>
       <c r="D47">
         <v>1</v>
+      </c>
+      <c r="E47" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="1">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="B48">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C48">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="1">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="B49">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="1">
-        <v>46270</v>
+        <v>46272</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C50">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="1">
-        <v>46269</v>
+        <v>46271</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -1640,52 +1646,55 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="1">
-        <v>46268</v>
+        <v>46270</v>
       </c>
       <c r="B52">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="1">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B53">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="1">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B54">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="1">
-        <v>46265</v>
+        <v>46267</v>
+      </c>
+      <c r="B55">
+        <v>7</v>
       </c>
       <c r="C55">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -1693,24 +1702,21 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="1">
-        <v>46264</v>
+        <v>46266</v>
       </c>
       <c r="B56">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="1">
-        <v>46263</v>
-      </c>
-      <c r="B57">
-        <v>73</v>
+        <v>46265</v>
       </c>
       <c r="C57">
         <v>62</v>
@@ -1721,13 +1727,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="1">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="B58">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="C58">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -1735,30 +1741,27 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="1">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="B59">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="C59">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D59">
-        <v>3</v>
-      </c>
-      <c r="E59" s="4">
-        <v>0.21422999999999998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B60">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="C60">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -1766,261 +1769,264 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="1">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B61">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C61">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E61" s="4">
-        <v>10.703772000000001</v>
+        <v>0.21422999999999998</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="1">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B62">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="C62">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="1">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B63">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E63" s="4">
+        <v>10.703772000000001</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="1">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="B64">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="C64">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D64">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:21">
       <c r="A65" s="1">
-        <v>46255</v>
+        <v>46257</v>
       </c>
       <c r="B65">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C65">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:21">
       <c r="A66" s="1">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="B66">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="C66">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D66">
-        <v>0</v>
-      </c>
-      <c r="E66" s="4">
-        <v>8.4293359999999993</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:21">
       <c r="A67" s="1">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B67">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C67">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D67">
         <v>1</v>
       </c>
-      <c r="G67" s="7"/>
-      <c r="H67" s="7"/>
-      <c r="I67" s="3"/>
-      <c r="J67" s="3"/>
-      <c r="K67" s="7"/>
-      <c r="L67" s="7"/>
-      <c r="M67" s="7"/>
-      <c r="N67" s="7"/>
-      <c r="O67" s="7"/>
-      <c r="P67" s="7"/>
-      <c r="Q67" s="7"/>
-      <c r="R67" s="7"/>
-      <c r="S67" s="7"/>
-      <c r="T67" s="7"/>
-      <c r="U67" s="7"/>
     </row>
     <row r="68" spans="1:21">
       <c r="A68" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E68" s="4">
-        <v>6.2419820000000001</v>
+        <v>8.4293359999999993</v>
       </c>
     </row>
     <row r="69" spans="1:21">
       <c r="A69" s="1">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B69">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D69">
         <v>1</v>
       </c>
-      <c r="E69" s="4">
-        <v>14.777381999999999</v>
-      </c>
+      <c r="G69" s="7"/>
+      <c r="H69" s="7"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3"/>
+      <c r="K69" s="7"/>
+      <c r="L69" s="7"/>
+      <c r="M69" s="7"/>
+      <c r="N69" s="7"/>
+      <c r="O69" s="7"/>
+      <c r="P69" s="7"/>
+      <c r="Q69" s="7"/>
+      <c r="R69" s="7"/>
+      <c r="S69" s="7"/>
+      <c r="T69" s="7"/>
+      <c r="U69" s="7"/>
     </row>
     <row r="70" spans="1:21">
       <c r="A70" s="1">
-        <v>46250</v>
+        <v>46252</v>
       </c>
       <c r="B70">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C70">
         <v>0</v>
+      </c>
+      <c r="D70">
+        <v>2</v>
+      </c>
+      <c r="E70" s="4">
+        <v>6.2419820000000001</v>
       </c>
     </row>
     <row r="71" spans="1:21">
       <c r="A71" s="1">
-        <v>46249</v>
+        <v>46251</v>
+      </c>
+      <c r="B71">
+        <v>12</v>
       </c>
       <c r="C71">
         <v>0</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71" s="4">
+        <v>14.777381999999999</v>
       </c>
     </row>
     <row r="72" spans="1:21">
       <c r="A72" s="1">
-        <v>46248</v>
+        <v>46250</v>
       </c>
       <c r="B72">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C72">
-        <v>16</v>
-      </c>
-      <c r="D72">
-        <v>0</v>
-      </c>
-      <c r="E72" s="4">
-        <v>20.847041999999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:21">
       <c r="A73" s="1">
-        <v>46247</v>
-      </c>
-      <c r="B73">
-        <v>35</v>
+        <v>46249</v>
       </c>
       <c r="C73">
-        <v>21</v>
-      </c>
-      <c r="D73">
-        <v>0</v>
-      </c>
-      <c r="E73" s="4">
-        <v>5.4199330000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:21">
       <c r="A74" s="1">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B74">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C74">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E74" s="4">
+        <v>20.847041999999995</v>
       </c>
     </row>
     <row r="75" spans="1:21">
       <c r="A75" s="1">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B75">
+        <v>35</v>
+      </c>
+      <c r="C75">
         <v>21</v>
       </c>
-      <c r="C75">
-        <v>25</v>
-      </c>
       <c r="D75">
         <v>0</v>
+      </c>
+      <c r="E75" s="4">
+        <v>5.4199330000000003</v>
       </c>
     </row>
     <row r="76" spans="1:21">
       <c r="A76" s="1">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B76">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C76">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D76">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:21">
       <c r="A77" s="1">
-        <v>46243</v>
+        <v>46245</v>
       </c>
       <c r="B77">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -2028,24 +2034,24 @@
     </row>
     <row r="78" spans="1:21">
       <c r="A78" s="1">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="B78">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:21">
       <c r="A79" s="1">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B79">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2056,10 +2062,10 @@
     </row>
     <row r="80" spans="1:21">
       <c r="A80" s="1">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="B80">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2070,29 +2076,57 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="1">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B81">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C81">
         <v>0</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B82">
+        <v>16</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B83">
+        <v>0</v>
+      </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
+      <c r="D83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="1">
         <v>46238</v>
       </c>
-      <c r="B82">
-        <v>0</v>
-      </c>
-      <c r="C82">
-        <v>0</v>
-      </c>
-      <c r="D82">
+      <c r="B84">
+        <v>0</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84">
         <v>1</v>
       </c>
     </row>
@@ -2103,7 +2137,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D41FB4CD-150C-4CE3-A76E-CB540C2892DD}">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
@@ -2177,15 +2211,15 @@
       </c>
       <c r="B3">
         <f>4375+SUM(B6:B500)</f>
-        <v>5356</v>
+        <v>5448</v>
       </c>
       <c r="C3">
         <f>7462+SUM(C6:C100)</f>
-        <v>7746</v>
+        <v>7758</v>
       </c>
       <c r="D3">
         <f>75+SUM(D5:D100)</f>
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E3">
         <f>10+SUM(E5:E150)</f>
@@ -2205,11 +2239,11 @@
       </c>
       <c r="I3">
         <f>170+SUM(I5:I150)</f>
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J3">
         <f>1195+SUM(J5:J200)</f>
-        <v>1298</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -2218,15 +2252,15 @@
       </c>
       <c r="B4">
         <f>B2-B3</f>
-        <v>4341</v>
+        <v>4249</v>
       </c>
       <c r="C4">
         <f>C2-C3</f>
-        <v>4124</v>
+        <v>4112</v>
       </c>
       <c r="D4">
         <f t="shared" ref="D4:G4" si="0">D2-D3</f>
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
@@ -2246,11 +2280,11 @@
       </c>
       <c r="I4">
         <f>I2-I3</f>
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J4">
         <f>J2-J3</f>
-        <v>3202</v>
+        <v>3196</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -2696,6 +2730,70 @@
       </c>
       <c r="J18">
         <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B19">
+        <v>92</v>
+      </c>
+      <c r="C19">
+        <v>12</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="1">
+        <v>46320</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30619"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1324" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D44F3511-CEB2-423D-A955-70653B42A8FB}"/>
+  <xr:revisionPtr revIDLastSave="1355" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDF26554-54E1-4D21-8356-0FC4ED222FD6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>
@@ -53,19 +53,19 @@
     <t>ACC</t>
   </si>
   <si>
-    <t>Daily-8; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 994;Total - 5610 MT</t>
+    <t>Daily-24; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 1018;Total - 5634 MT</t>
   </si>
   <si>
     <t>Boiler</t>
   </si>
   <si>
-    <t>Daily-104  - (SH-92 and RH-12); Oct-1864 NDHT Balance joints - 8350 (SH - 4248; RH - 4102)</t>
+    <t>Daily-116  - (SH-92 and RH-24); Oct-1986 NDHT Balance joints - 8228(SH - 4150; RH - 4078)</t>
   </si>
   <si>
     <t>PCP Joint</t>
   </si>
   <si>
-    <t>Daily-0; MS Joints - 76/146; MS to PRDS - 11/26; HRH - 11/95; CRH -15/87; LPBP - 11/49; HPBP-10/23; BFD- 182/661</t>
+    <t>Daily-2; MS Joints - 78/146; MS to PRDS - 11/26; HRH - 11/95; CRH -15/87; LPBP - 11/49; HPBP-10/23; BFD- 183/661</t>
   </si>
   <si>
     <t>Boiler - NDHT Joints</t>
@@ -723,7 +723,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -734,7 +734,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -745,7 +745,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -764,7 +764,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
-  <dimension ref="A1:AA84"/>
+  <dimension ref="A1:AA85"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
@@ -809,84 +809,84 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="B3">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="B4">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="B5">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C5">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="1">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C6">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B7">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -894,13 +894,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="1">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -911,10 +911,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -928,10 +928,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B10">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -945,13 +945,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C11">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -962,118 +962,118 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B12">
-        <v>117</v>
+        <v>14</v>
       </c>
       <c r="C12">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B13">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C13">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13" s="6">
-        <v>20.72</v>
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B14">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="C14">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="6">
-        <v>16.425999999999998</v>
+        <v>20.72</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B15">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="C15">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="6">
-        <v>18.917999999999999</v>
+        <v>16.425999999999998</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B16">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="C16">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="6">
-        <v>7.9720000000000004</v>
+        <v>18.917999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:27">
       <c r="A17" s="1">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B17">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E17" s="6">
-        <v>0</v>
+        <v>7.9720000000000004</v>
       </c>
     </row>
     <row r="18" spans="1:27">
       <c r="A18" s="1">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="B18">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="C18">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="6">
         <v>0</v>
@@ -1081,66 +1081,66 @@
     </row>
     <row r="19" spans="1:27">
       <c r="A19" s="1">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B19">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C19">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="E19" s="6">
-        <v>4.3440000000000003</v>
-      </c>
-      <c r="I19" s="2"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="3"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="2"/>
-      <c r="Z19" s="2"/>
-      <c r="AA19" s="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:27">
       <c r="A20" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B20">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C20">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20" s="6">
-        <v>0</v>
-      </c>
+        <v>4.3440000000000003</v>
+      </c>
+      <c r="I20" s="2"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="3"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="X20" s="3"/>
+      <c r="Y20" s="2"/>
+      <c r="Z20" s="2"/>
+      <c r="AA20" s="2"/>
     </row>
     <row r="21" spans="1:27">
       <c r="A21" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B21">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="C21">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="6">
         <v>0</v>
@@ -1148,84 +1148,84 @@
     </row>
     <row r="22" spans="1:27">
       <c r="A22" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B22">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C22">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D22">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E22" s="6">
-        <v>4.5679999999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:27">
       <c r="A23" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B23">
         <v>45</v>
       </c>
       <c r="C23">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E23" s="6">
-        <v>6.4130000000000003</v>
+        <v>4.5679999999999996</v>
       </c>
     </row>
     <row r="24" spans="1:27">
       <c r="A24" s="1">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B24">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E24" s="6">
-        <v>4.3440000000000003</v>
+        <v>6.4130000000000003</v>
       </c>
     </row>
     <row r="25" spans="1:27">
       <c r="A25" s="1">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B25">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C25">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="6">
-        <v>0</v>
+        <v>4.3440000000000003</v>
       </c>
     </row>
     <row r="26" spans="1:27">
       <c r="A26" s="1">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="6">
         <v>0</v>
@@ -1233,16 +1233,16 @@
     </row>
     <row r="27" spans="1:27">
       <c r="A27" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B27">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="6">
         <v>0</v>
@@ -1250,132 +1250,132 @@
     </row>
     <row r="28" spans="1:27">
       <c r="A28" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B28">
-        <v>321</v>
+        <v>40</v>
       </c>
       <c r="C28">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="E28" s="5">
-        <v>37.679307999999999</v>
+        <v>1</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:27">
       <c r="A29" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B29">
-        <v>200</v>
+        <v>321</v>
       </c>
       <c r="C29">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" s="5">
-        <v>33.449338000000004</v>
+        <v>37.679307999999999</v>
       </c>
     </row>
     <row r="30" spans="1:27">
       <c r="A30" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B30">
-        <v>43</v>
+        <v>200</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="D30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E30" s="5">
-        <v>42.041217999999994</v>
+        <v>33.449338000000004</v>
       </c>
     </row>
     <row r="31" spans="1:27">
       <c r="A31" s="1">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B31">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>0</v>
-      </c>
-      <c r="E31" s="6">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="E31" s="5">
+        <v>42.041217999999994</v>
       </c>
     </row>
     <row r="32" spans="1:27">
       <c r="A32" s="1">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B32">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C32">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
-      <c r="E32" s="5">
-        <v>16.912866999999999</v>
+      <c r="E32" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B33">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C33">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E33" s="5">
-        <v>11.657306</v>
+        <v>16.912866999999999</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C34">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" s="5">
-        <v>0</v>
+        <v>11.657306</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C35">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1386,13 +1386,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B36">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1403,16 +1403,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B37">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C37">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" s="5">
         <v>0</v>
@@ -1420,13 +1420,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B38">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C38">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -1437,16 +1437,16 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B39">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C39">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D39">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E39" s="5">
         <v>0</v>
@@ -1454,7 +1454,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B40">
         <v>16</v>
@@ -1466,38 +1466,38 @@
         <v>4</v>
       </c>
       <c r="E40" s="5">
-        <v>30.143184999999992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B41">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C41">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E41" s="5">
-        <v>0</v>
+        <v>30.143184999999992</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="1">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C42">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" s="5">
         <v>0</v>
@@ -1505,16 +1505,16 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B43">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="C43">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" s="5">
         <v>0</v>
@@ -1522,16 +1522,16 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="1">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B44">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E44" s="5">
         <v>0</v>
@@ -1539,16 +1539,16 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="1">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B45">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="C45">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E45" s="5">
         <v>0</v>
@@ -1556,89 +1556,92 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="1">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B46">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="C46">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" s="5">
-        <v>5.3833070000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="1">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B47">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C47">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="D47">
         <v>1</v>
       </c>
       <c r="E47" s="5">
-        <v>0</v>
+        <v>5.3833070000000003</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="1">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B48">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="C48">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="E48" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B49">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C49">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="1">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B50">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C50">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="1">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B51">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -1646,41 +1649,41 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="1">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C52">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="1">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B53">
         <v>0</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="1">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B54">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C54">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -1688,27 +1691,27 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="1">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B55">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C55">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B56">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -1716,10 +1719,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="1">
-        <v>46265</v>
+        <v>46266</v>
+      </c>
+      <c r="B57">
+        <v>17</v>
       </c>
       <c r="C57">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -1727,233 +1733,227 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="1">
-        <v>46264</v>
-      </c>
-      <c r="B58">
-        <v>5</v>
+        <v>46265</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="1">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B59">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="C59">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="1">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B60">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C60">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B61">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C61">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D61">
-        <v>3</v>
-      </c>
-      <c r="E61" s="4">
-        <v>0.21422999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B62">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="C62">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="E62" s="4">
+        <v>0.21422999999999998</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B63">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="C63">
         <v>62</v>
       </c>
       <c r="D63">
-        <v>1</v>
-      </c>
-      <c r="E63" s="4">
-        <v>10.703772000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B64">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C64">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D64">
         <v>1</v>
+      </c>
+      <c r="E64" s="4">
+        <v>10.703772000000001</v>
       </c>
     </row>
     <row r="65" spans="1:21">
       <c r="A65" s="1">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B65">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:21">
       <c r="A66" s="1">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B66">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="C66">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:21">
       <c r="A67" s="1">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B67">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="C67">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:21">
       <c r="A68" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B68">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="C68">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D68">
-        <v>0</v>
-      </c>
-      <c r="E68" s="4">
-        <v>8.4293359999999993</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:21">
       <c r="A69" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B69">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C69">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D69">
-        <v>1</v>
-      </c>
-      <c r="G69" s="7"/>
-      <c r="H69" s="7"/>
-      <c r="I69" s="3"/>
-      <c r="J69" s="3"/>
-      <c r="K69" s="7"/>
-      <c r="L69" s="7"/>
-      <c r="M69" s="7"/>
-      <c r="N69" s="7"/>
-      <c r="O69" s="7"/>
-      <c r="P69" s="7"/>
-      <c r="Q69" s="7"/>
-      <c r="R69" s="7"/>
-      <c r="S69" s="7"/>
-      <c r="T69" s="7"/>
-      <c r="U69" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="E69" s="4">
+        <v>8.4293359999999993</v>
+      </c>
     </row>
     <row r="70" spans="1:21">
       <c r="A70" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B70">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D70">
-        <v>2</v>
-      </c>
-      <c r="E70" s="4">
-        <v>6.2419820000000001</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G70" s="7"/>
+      <c r="H70" s="7"/>
+      <c r="I70" s="3"/>
+      <c r="J70" s="3"/>
+      <c r="K70" s="7"/>
+      <c r="L70" s="7"/>
+      <c r="M70" s="7"/>
+      <c r="N70" s="7"/>
+      <c r="O70" s="7"/>
+      <c r="P70" s="7"/>
+      <c r="Q70" s="7"/>
+      <c r="R70" s="7"/>
+      <c r="S70" s="7"/>
+      <c r="T70" s="7"/>
+      <c r="U70" s="7"/>
     </row>
     <row r="71" spans="1:21">
       <c r="A71" s="1">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B71">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71" s="4">
-        <v>14.777381999999999</v>
+        <v>6.2419820000000001</v>
       </c>
     </row>
     <row r="72" spans="1:21">
       <c r="A72" s="1">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B72">
         <v>12</v>
@@ -1961,10 +1961,19 @@
       <c r="C72">
         <v>0</v>
       </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="E72" s="4">
+        <v>14.777381999999999</v>
+      </c>
     </row>
     <row r="73" spans="1:21">
       <c r="A73" s="1">
-        <v>46249</v>
+        <v>46250</v>
+      </c>
+      <c r="B73">
+        <v>12</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -1972,100 +1981,94 @@
     </row>
     <row r="74" spans="1:21">
       <c r="A74" s="1">
-        <v>46248</v>
-      </c>
-      <c r="B74">
-        <v>7</v>
+        <v>46249</v>
       </c>
       <c r="C74">
-        <v>16</v>
-      </c>
-      <c r="D74">
-        <v>0</v>
-      </c>
-      <c r="E74" s="4">
-        <v>20.847041999999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:21">
       <c r="A75" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B75">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="C75">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D75">
         <v>0</v>
       </c>
       <c r="E75" s="4">
-        <v>5.4199330000000003</v>
+        <v>20.847041999999995</v>
       </c>
     </row>
     <row r="76" spans="1:21">
       <c r="A76" s="1">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B76">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C76">
         <v>21</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E76" s="4">
+        <v>5.4199330000000003</v>
       </c>
     </row>
     <row r="77" spans="1:21">
       <c r="A77" s="1">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B77">
+        <v>28</v>
+      </c>
+      <c r="C77">
         <v>21</v>
       </c>
-      <c r="C77">
-        <v>25</v>
-      </c>
       <c r="D77">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:21">
       <c r="A78" s="1">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B78">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C78">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D78">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:21">
       <c r="A79" s="1">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B79">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:21">
       <c r="A80" s="1">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2076,10 +2079,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="1">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B81">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2090,10 +2093,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="1">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B82">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2104,29 +2107,43 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="1">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B84">
+        <v>0</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="1">
         <v>46238</v>
       </c>
-      <c r="B84">
-        <v>0</v>
-      </c>
-      <c r="C84">
-        <v>0</v>
-      </c>
-      <c r="D84">
+      <c r="B85">
+        <v>0</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="D85">
         <v>1</v>
       </c>
     </row>
@@ -2137,7 +2154,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D41FB4CD-150C-4CE3-A76E-CB540C2892DD}">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
@@ -2211,15 +2228,15 @@
       </c>
       <c r="B3">
         <f>4375+SUM(B6:B500)</f>
-        <v>5448</v>
+        <v>5540</v>
       </c>
       <c r="C3">
         <f>7462+SUM(C6:C100)</f>
-        <v>7758</v>
+        <v>7782</v>
       </c>
       <c r="D3">
         <f>75+SUM(D5:D100)</f>
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E3">
         <f>10+SUM(E5:E150)</f>
@@ -2239,7 +2256,7 @@
       </c>
       <c r="I3">
         <f>170+SUM(I5:I150)</f>
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J3">
         <f>1195+SUM(J5:J200)</f>
@@ -2252,15 +2269,15 @@
       </c>
       <c r="B4">
         <f>B2-B3</f>
-        <v>4249</v>
+        <v>4157</v>
       </c>
       <c r="C4">
         <f>C2-C3</f>
-        <v>4112</v>
+        <v>4088</v>
       </c>
       <c r="D4">
         <f t="shared" ref="D4:G4" si="0">D2-D3</f>
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
@@ -2280,7 +2297,7 @@
       </c>
       <c r="I4">
         <f>I2-I3</f>
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J4">
         <f>J2-J3</f>
@@ -2794,6 +2811,38 @@
       </c>
       <c r="J20">
         <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B21">
+        <v>92</v>
+      </c>
+      <c r="C21">
+        <v>24</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1355" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDF26554-54E1-4D21-8356-0FC4ED222FD6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1355" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDF26554-54E1-4D21-8356-0FC4ED222FD6}"/>
+  <xr:revisionPtr revIDLastSave="1395" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F920B4B-1653-43E6-A61F-47D99FE8430D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>
-    <sheet name="Critical areas" sheetId="2" r:id="rId2"/>
-    <sheet name="Joints" sheetId="5" r:id="rId3"/>
-    <sheet name="Chimney" sheetId="3" r:id="rId4"/>
+    <sheet name="Tonnage" sheetId="6" r:id="rId2"/>
+    <sheet name="Critical areas" sheetId="2" r:id="rId3"/>
+    <sheet name="Joints" sheetId="5" r:id="rId4"/>
+    <sheet name="Chimney" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
   <si>
     <t>Date</t>
   </si>
@@ -53,19 +54,46 @@
     <t>ACC</t>
   </si>
   <si>
-    <t>Daily-24; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 1018;Total - 5634 MT</t>
+    <t>Daily-21; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 1040;Total - 5655 MT</t>
   </si>
   <si>
     <t>Boiler</t>
   </si>
   <si>
-    <t>Daily-116  - (SH-92 and RH-24); Oct-1986 NDHT Balance joints - 8228(SH - 4150; RH - 4078)</t>
+    <t>Daily-141  - (SH-105 and RH-36); Oct-2127 NDHT Balance joints - 8087(SH - 4045; RH - 4042)</t>
   </si>
   <si>
     <t>PCP Joint</t>
   </si>
   <si>
-    <t>Daily-2; MS Joints - 78/146; MS to PRDS - 11/26; HRH - 11/95; CRH -15/87; LPBP - 11/49; HPBP-10/23; BFD- 183/661</t>
+    <t>Daily-2; MS Joints - 88/146; MS to PRDS - 11/26; HRH - 11/95; CRH -15/87; LPBP - 11/49; HPBP-10/23; BFD- 183/661</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Tonnage Completed</t>
+  </si>
+  <si>
+    <t>Total Tonnage</t>
+  </si>
+  <si>
+    <t>Percentage</t>
+  </si>
+  <si>
+    <t>Unit 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boiler-3 </t>
+  </si>
+  <si>
+    <t>Piping-3</t>
+  </si>
+  <si>
+    <t>ESP-3 incl control room</t>
   </si>
   <si>
     <t>Boiler - NDHT Joints</t>
@@ -138,12 +166,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -209,8 +238,20 @@
       <family val="1"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -228,8 +269,13 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF005A9C"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -237,8 +283,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="34">
+  <cellStyleXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -273,8 +334,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -293,8 +355,13 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="22" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="34" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="34">
+  <cellStyles count="35">
     <cellStyle name="20% - Accent5 9" xfId="29" xr:uid="{83B76E04-2387-4B96-B399-6CA28CB9C921}"/>
     <cellStyle name="20% - Accent5 9 98 9 51" xfId="32" xr:uid="{E9B08F62-33F7-462D-93D0-323D948290BA}"/>
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -327,6 +394,7 @@
     <cellStyle name="Normal 7_Du Detail" xfId="21" xr:uid="{CEFE62EF-08D5-4F02-9A50-430497EA831D}"/>
     <cellStyle name="Normal 8" xfId="18" xr:uid="{AEC90A00-016F-4DCF-909E-72954C023E8A}"/>
     <cellStyle name="Normal 9" xfId="2" xr:uid="{C0442E06-09A9-4EB8-A419-861957760B34}"/>
+    <cellStyle name="Percent" xfId="34" builtinId="5"/>
     <cellStyle name="Percent 2" xfId="3" xr:uid="{D4ECF4DB-59CC-49E5-B26D-B71A761533FC}"/>
     <cellStyle name="Title 2" xfId="27" xr:uid="{4CF40618-97A1-49D9-9269-557741BF9292}"/>
   </cellStyles>
@@ -723,7 +791,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -734,7 +802,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -745,7 +813,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -763,8 +831,92 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6E5BA1F-B477-478E-9D82-DB1AA3EDF6C0}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="2" max="2" width="29.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="9">
+        <v>40824</v>
+      </c>
+      <c r="D2" s="9">
+        <v>66363</v>
+      </c>
+      <c r="E2" s="10">
+        <f t="shared" ref="E2:E4" si="0">C2/D2</f>
+        <v>0.61516206319786626</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="9">
+        <v>1644</v>
+      </c>
+      <c r="D3" s="9">
+        <v>5309</v>
+      </c>
+      <c r="E3" s="10">
+        <f t="shared" si="0"/>
+        <v>0.30966283669240913</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="9">
+        <v>11284</v>
+      </c>
+      <c r="D4" s="9">
+        <v>14724</v>
+      </c>
+      <c r="E4" s="10">
+        <f t="shared" si="0"/>
+        <v>0.76636783482749249</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
-  <dimension ref="A1:AA85"/>
+  <dimension ref="A1:AA86"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
@@ -781,18 +933,18 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B2">
         <v>30</v>
@@ -809,13 +961,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="B3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C3">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -826,84 +978,84 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="B4">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="B5">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="1">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="B6">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C6">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C7">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="1">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B8">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C8">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -911,13 +1063,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -928,10 +1080,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -945,10 +1097,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B11">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -962,13 +1114,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B12">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C12">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -979,118 +1131,118 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B13">
-        <v>117</v>
+        <v>14</v>
       </c>
       <c r="C13">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B14">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C14">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="6">
-        <v>20.72</v>
+        <v>2</v>
+      </c>
+      <c r="E14">
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B15">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="C15">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="6">
-        <v>16.425999999999998</v>
+        <v>20.72</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B16">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="C16">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="6">
-        <v>18.917999999999999</v>
+        <v>16.425999999999998</v>
       </c>
     </row>
     <row r="17" spans="1:27">
       <c r="A17" s="1">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B17">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="C17">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" s="6">
-        <v>7.9720000000000004</v>
+        <v>18.917999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:27">
       <c r="A18" s="1">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B18">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E18" s="6">
-        <v>0</v>
+        <v>7.9720000000000004</v>
       </c>
     </row>
     <row r="19" spans="1:27">
       <c r="A19" s="1">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="B19">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="C19">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="6">
         <v>0</v>
@@ -1098,66 +1250,66 @@
     </row>
     <row r="20" spans="1:27">
       <c r="A20" s="1">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B20">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C20">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20" s="6">
-        <v>4.3440000000000003</v>
-      </c>
-      <c r="I20" s="2"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="3"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
-      <c r="X20" s="3"/>
-      <c r="Y20" s="2"/>
-      <c r="Z20" s="2"/>
-      <c r="AA20" s="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:27">
       <c r="A21" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B21">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C21">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
       <c r="E21" s="6">
-        <v>0</v>
-      </c>
+        <v>4.3440000000000003</v>
+      </c>
+      <c r="I21" s="2"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="3"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="3"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="X21" s="3"/>
+      <c r="Y21" s="2"/>
+      <c r="Z21" s="2"/>
+      <c r="AA21" s="2"/>
     </row>
     <row r="22" spans="1:27">
       <c r="A22" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B22">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="C22">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="6">
         <v>0</v>
@@ -1165,84 +1317,84 @@
     </row>
     <row r="23" spans="1:27">
       <c r="A23" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B23">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C23">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E23" s="6">
-        <v>4.5679999999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:27">
       <c r="A24" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B24">
         <v>45</v>
       </c>
       <c r="C24">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E24" s="6">
-        <v>6.4130000000000003</v>
+        <v>4.5679999999999996</v>
       </c>
     </row>
     <row r="25" spans="1:27">
       <c r="A25" s="1">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B25">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E25" s="6">
-        <v>4.3440000000000003</v>
+        <v>6.4130000000000003</v>
       </c>
     </row>
     <row r="26" spans="1:27">
       <c r="A26" s="1">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B26">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C26">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="6">
-        <v>0</v>
+        <v>4.3440000000000003</v>
       </c>
     </row>
     <row r="27" spans="1:27">
       <c r="A27" s="1">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="6">
         <v>0</v>
@@ -1250,16 +1402,16 @@
     </row>
     <row r="28" spans="1:27">
       <c r="A28" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B28">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="6">
         <v>0</v>
@@ -1267,132 +1419,132 @@
     </row>
     <row r="29" spans="1:27">
       <c r="A29" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B29">
-        <v>321</v>
+        <v>40</v>
       </c>
       <c r="C29">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="D29">
-        <v>0</v>
-      </c>
-      <c r="E29" s="5">
-        <v>37.679307999999999</v>
+        <v>1</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:27">
       <c r="A30" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B30">
-        <v>200</v>
+        <v>321</v>
       </c>
       <c r="C30">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="5">
-        <v>33.449338000000004</v>
+        <v>37.679307999999999</v>
       </c>
     </row>
     <row r="31" spans="1:27">
       <c r="A31" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B31">
-        <v>43</v>
+        <v>200</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="D31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E31" s="5">
-        <v>42.041217999999994</v>
+        <v>33.449338000000004</v>
       </c>
     </row>
     <row r="32" spans="1:27">
       <c r="A32" s="1">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B32">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
       <c r="D32">
-        <v>0</v>
-      </c>
-      <c r="E32" s="6">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="E32" s="5">
+        <v>42.041217999999994</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B33">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C33">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
-      <c r="E33" s="5">
-        <v>16.912866999999999</v>
+      <c r="E33" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B34">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C34">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E34" s="5">
-        <v>11.657306</v>
+        <v>16.912866999999999</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C35">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" s="5">
-        <v>0</v>
+        <v>11.657306</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C36">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1403,13 +1555,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B37">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1420,16 +1572,16 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B38">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C38">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="5">
         <v>0</v>
@@ -1437,13 +1589,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B39">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C39">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -1454,16 +1606,16 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B40">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C40">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D40">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E40" s="5">
         <v>0</v>
@@ -1471,7 +1623,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B41">
         <v>16</v>
@@ -1483,38 +1635,38 @@
         <v>4</v>
       </c>
       <c r="E41" s="5">
-        <v>30.143184999999992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="1">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B42">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C42">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E42" s="5">
-        <v>0</v>
+        <v>30.143184999999992</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="1">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C43">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" s="5">
         <v>0</v>
@@ -1522,16 +1674,16 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B44">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="C44">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" s="5">
         <v>0</v>
@@ -1539,16 +1691,16 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="1">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E45" s="5">
         <v>0</v>
@@ -1556,16 +1708,16 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="1">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B46">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="C46">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E46" s="5">
         <v>0</v>
@@ -1573,89 +1725,92 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="1">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B47">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="C47">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" s="5">
-        <v>5.3833070000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="1">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B48">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C48">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="D48">
         <v>1</v>
       </c>
       <c r="E48" s="5">
-        <v>0</v>
+        <v>5.3833070000000003</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="1">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B49">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="C49">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="E49" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B50">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C50">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="1">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B51">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C51">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="1">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B52">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -1663,41 +1818,41 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="1">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C53">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="1">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B54">
         <v>0</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="1">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B55">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C55">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -1705,27 +1860,27 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="1">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B56">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C56">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B57">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -1733,10 +1888,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="1">
-        <v>46265</v>
+        <v>46266</v>
+      </c>
+      <c r="B58">
+        <v>17</v>
       </c>
       <c r="C58">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -1744,233 +1902,227 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="1">
-        <v>46264</v>
-      </c>
-      <c r="B59">
-        <v>5</v>
+        <v>46265</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="1">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B60">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="C60">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="1">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B61">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C61">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B62">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C62">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D62">
-        <v>3</v>
-      </c>
-      <c r="E62" s="4">
-        <v>0.21422999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B63">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="C63">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="E63" s="4">
+        <v>0.21422999999999998</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B64">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="C64">
         <v>62</v>
       </c>
       <c r="D64">
-        <v>1</v>
-      </c>
-      <c r="E64" s="4">
-        <v>10.703772000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:21">
       <c r="A65" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B65">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C65">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D65">
         <v>1</v>
+      </c>
+      <c r="E65" s="4">
+        <v>10.703772000000001</v>
       </c>
     </row>
     <row r="66" spans="1:21">
       <c r="A66" s="1">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B66">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:21">
       <c r="A67" s="1">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B67">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="C67">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:21">
       <c r="A68" s="1">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B68">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="C68">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69" spans="1:21">
       <c r="A69" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B69">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="C69">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D69">
-        <v>0</v>
-      </c>
-      <c r="E69" s="4">
-        <v>8.4293359999999993</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:21">
       <c r="A70" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B70">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C70">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D70">
-        <v>1</v>
-      </c>
-      <c r="G70" s="7"/>
-      <c r="H70" s="7"/>
-      <c r="I70" s="3"/>
-      <c r="J70" s="3"/>
-      <c r="K70" s="7"/>
-      <c r="L70" s="7"/>
-      <c r="M70" s="7"/>
-      <c r="N70" s="7"/>
-      <c r="O70" s="7"/>
-      <c r="P70" s="7"/>
-      <c r="Q70" s="7"/>
-      <c r="R70" s="7"/>
-      <c r="S70" s="7"/>
-      <c r="T70" s="7"/>
-      <c r="U70" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="E70" s="4">
+        <v>8.4293359999999993</v>
+      </c>
     </row>
     <row r="71" spans="1:21">
       <c r="A71" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B71">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D71">
-        <v>2</v>
-      </c>
-      <c r="E71" s="4">
-        <v>6.2419820000000001</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G71" s="7"/>
+      <c r="H71" s="7"/>
+      <c r="I71" s="3"/>
+      <c r="J71" s="3"/>
+      <c r="K71" s="7"/>
+      <c r="L71" s="7"/>
+      <c r="M71" s="7"/>
+      <c r="N71" s="7"/>
+      <c r="O71" s="7"/>
+      <c r="P71" s="7"/>
+      <c r="Q71" s="7"/>
+      <c r="R71" s="7"/>
+      <c r="S71" s="7"/>
+      <c r="T71" s="7"/>
+      <c r="U71" s="7"/>
     </row>
     <row r="72" spans="1:21">
       <c r="A72" s="1">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B72">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" s="4">
-        <v>14.777381999999999</v>
+        <v>6.2419820000000001</v>
       </c>
     </row>
     <row r="73" spans="1:21">
       <c r="A73" s="1">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B73">
         <v>12</v>
@@ -1978,10 +2130,19 @@
       <c r="C73">
         <v>0</v>
       </c>
+      <c r="D73">
+        <v>1</v>
+      </c>
+      <c r="E73" s="4">
+        <v>14.777381999999999</v>
+      </c>
     </row>
     <row r="74" spans="1:21">
       <c r="A74" s="1">
-        <v>46249</v>
+        <v>46250</v>
+      </c>
+      <c r="B74">
+        <v>12</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -1989,100 +2150,94 @@
     </row>
     <row r="75" spans="1:21">
       <c r="A75" s="1">
-        <v>46248</v>
-      </c>
-      <c r="B75">
-        <v>7</v>
+        <v>46249</v>
       </c>
       <c r="C75">
-        <v>16</v>
-      </c>
-      <c r="D75">
-        <v>0</v>
-      </c>
-      <c r="E75" s="4">
-        <v>20.847041999999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:21">
       <c r="A76" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B76">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="C76">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D76">
         <v>0</v>
       </c>
       <c r="E76" s="4">
-        <v>5.4199330000000003</v>
+        <v>20.847041999999995</v>
       </c>
     </row>
     <row r="77" spans="1:21">
       <c r="A77" s="1">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B77">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C77">
         <v>21</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E77" s="4">
+        <v>5.4199330000000003</v>
       </c>
     </row>
     <row r="78" spans="1:21">
       <c r="A78" s="1">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B78">
+        <v>28</v>
+      </c>
+      <c r="C78">
         <v>21</v>
       </c>
-      <c r="C78">
-        <v>25</v>
-      </c>
       <c r="D78">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:21">
       <c r="A79" s="1">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B79">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C79">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D79">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:21">
       <c r="A80" s="1">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B80">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="1">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B81">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2093,10 +2248,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="1">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B82">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2107,10 +2262,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="1">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B83">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2121,29 +2276,43 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="1">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B84">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B85">
+        <v>0</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="D85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="1">
         <v>46238</v>
       </c>
-      <c r="B85">
-        <v>0</v>
-      </c>
-      <c r="C85">
-        <v>0</v>
-      </c>
-      <c r="D85">
+      <c r="B86">
+        <v>0</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86">
         <v>1</v>
       </c>
     </row>
@@ -2152,9 +2321,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D41FB4CD-150C-4CE3-A76E-CB540C2892DD}">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
@@ -2162,36 +2331,36 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="B1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" t="s">
         <v>20</v>
-      </c>
-      <c r="J1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B2">
         <v>9697</v>
@@ -2224,19 +2393,19 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <f>4375+SUM(B6:B500)</f>
-        <v>5540</v>
+        <v>5645</v>
       </c>
       <c r="C3">
         <f>7462+SUM(C6:C100)</f>
-        <v>7782</v>
+        <v>7818</v>
       </c>
       <c r="D3">
         <f>75+SUM(D5:D100)</f>
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E3">
         <f>10+SUM(E5:E150)</f>
@@ -2265,19 +2434,19 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B4">
         <f>B2-B3</f>
-        <v>4157</v>
+        <v>4052</v>
       </c>
       <c r="C4">
         <f>C2-C3</f>
-        <v>4088</v>
+        <v>4052</v>
       </c>
       <c r="D4">
         <f t="shared" ref="D4:G4" si="0">D2-D3</f>
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
@@ -2842,6 +3011,38 @@
         <v>1</v>
       </c>
       <c r="J21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B22">
+        <v>105</v>
+      </c>
+      <c r="C22">
+        <v>36</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
         <v>0</v>
       </c>
     </row>
@@ -2850,7 +3051,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E384ED-EF07-4058-B570-9E7F8CBFADFB}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
@@ -2861,7 +3062,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -2869,31 +3070,31 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B5" s="1">
         <v>46336</v>
@@ -2901,7 +3102,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B6" s="1">
         <v>46371</v>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30619"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1395" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F920B4B-1653-43E6-A61F-47D99FE8430D}"/>
+  <xr:revisionPtr revIDLastSave="1417" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39848C3C-457D-4373-B2F4-8C5E0DA06FBB}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
   <si>
     <t>Date</t>
   </si>
@@ -160,6 +160,12 @@
   </si>
   <si>
     <t>Segment-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insulation </t>
+  </si>
+  <si>
+    <t>APH</t>
   </si>
 </sst>
 </file>
@@ -167,12 +173,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -306,7 +312,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -314,13 +320,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
@@ -772,13 +778,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="95.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -789,7 +795,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A2" s="1">
         <v>46322</v>
       </c>
@@ -800,7 +806,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A3" s="1">
         <v>46322</v>
       </c>
@@ -811,7 +817,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A4" s="1">
         <v>46322</v>
       </c>
@@ -833,12 +839,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6E5BA1F-B477-478E-9D82-DB1AA3EDF6C0}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="2" max="2" width="29.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A1" s="8" t="s">
         <v>9</v>
       </c>
@@ -855,7 +861,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -873,7 +879,7 @@
         <v>0.61516206319786626</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -891,7 +897,7 @@
         <v>0.30966283669240913</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -917,7 +923,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
   <dimension ref="A1:AA86"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
@@ -925,7 +931,7 @@
     <col min="5" max="6" width="11.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -942,7 +948,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -959,7 +965,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A3" s="1">
         <v>46322</v>
       </c>
@@ -976,7 +982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A4" s="1">
         <v>46321</v>
       </c>
@@ -993,7 +999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A5" s="1">
         <v>46320</v>
       </c>
@@ -1010,7 +1016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A6" s="1">
         <v>46319</v>
       </c>
@@ -1027,7 +1033,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A7" s="1">
         <v>46318</v>
       </c>
@@ -1044,7 +1050,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A8" s="1">
         <v>46317</v>
       </c>
@@ -1061,7 +1067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A9" s="1">
         <v>46316</v>
       </c>
@@ -1078,7 +1084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A10" s="1">
         <v>46315</v>
       </c>
@@ -1095,7 +1101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A11" s="1">
         <v>46314</v>
       </c>
@@ -1112,7 +1118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A12" s="1">
         <v>46313</v>
       </c>
@@ -1129,7 +1135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A13" s="1">
         <v>46312</v>
       </c>
@@ -1146,7 +1152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A14" s="1">
         <v>46311</v>
       </c>
@@ -1163,7 +1169,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A15" s="1">
         <v>46310</v>
       </c>
@@ -1180,7 +1186,7 @@
         <v>20.72</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A16" s="1">
         <v>46309</v>
       </c>
@@ -1197,7 +1203,7 @@
         <v>16.425999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.5">
       <c r="A17" s="1">
         <v>46308</v>
       </c>
@@ -1214,7 +1220,7 @@
         <v>18.917999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:27">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.5">
       <c r="A18" s="1">
         <v>46307</v>
       </c>
@@ -1231,7 +1237,7 @@
         <v>7.9720000000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:27">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.5">
       <c r="A19" s="1">
         <v>46306</v>
       </c>
@@ -1248,7 +1254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.5">
       <c r="A20" s="1">
         <v>46305</v>
       </c>
@@ -1265,7 +1271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.5">
       <c r="A21" s="1">
         <v>46304</v>
       </c>
@@ -1298,7 +1304,7 @@
       <c r="Z21" s="2"/>
       <c r="AA21" s="2"/>
     </row>
-    <row r="22" spans="1:27">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.5">
       <c r="A22" s="1">
         <v>46303</v>
       </c>
@@ -1315,7 +1321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.5">
       <c r="A23" s="1">
         <v>46302</v>
       </c>
@@ -1332,7 +1338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.5">
       <c r="A24" s="1">
         <v>46301</v>
       </c>
@@ -1349,7 +1355,7 @@
         <v>4.5679999999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:27">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.5">
       <c r="A25" s="1">
         <v>46300</v>
       </c>
@@ -1366,7 +1372,7 @@
         <v>6.4130000000000003</v>
       </c>
     </row>
-    <row r="26" spans="1:27">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.5">
       <c r="A26" s="1">
         <v>46299</v>
       </c>
@@ -1383,7 +1389,7 @@
         <v>4.3440000000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:27">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.5">
       <c r="A27" s="1">
         <v>46298</v>
       </c>
@@ -1400,7 +1406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.5">
       <c r="A28" s="1">
         <v>46297</v>
       </c>
@@ -1417,7 +1423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.5">
       <c r="A29" s="1">
         <v>46296</v>
       </c>
@@ -1434,7 +1440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.5">
       <c r="A30" s="1">
         <v>46295</v>
       </c>
@@ -1451,7 +1457,7 @@
         <v>37.679307999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:27">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.5">
       <c r="A31" s="1">
         <v>46294</v>
       </c>
@@ -1468,7 +1474,7 @@
         <v>33.449338000000004</v>
       </c>
     </row>
-    <row r="32" spans="1:27">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.5">
       <c r="A32" s="1">
         <v>46293</v>
       </c>
@@ -1485,7 +1491,7 @@
         <v>42.041217999999994</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A33" s="1">
         <v>46292</v>
       </c>
@@ -1502,7 +1508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A34" s="1">
         <v>46291</v>
       </c>
@@ -1519,7 +1525,7 @@
         <v>16.912866999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A35" s="1">
         <v>46290</v>
       </c>
@@ -1536,7 +1542,7 @@
         <v>11.657306</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A36" s="1">
         <v>46289</v>
       </c>
@@ -1553,7 +1559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A37" s="1">
         <v>46288</v>
       </c>
@@ -1570,7 +1576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A38" s="1">
         <v>46287</v>
       </c>
@@ -1587,7 +1593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A39" s="1">
         <v>46286</v>
       </c>
@@ -1604,7 +1610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A40" s="1">
         <v>46285</v>
       </c>
@@ -1621,7 +1627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A41" s="1">
         <v>46284</v>
       </c>
@@ -1638,7 +1644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A42" s="1">
         <v>46283</v>
       </c>
@@ -1655,7 +1661,7 @@
         <v>30.143184999999992</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A43" s="1">
         <v>46281</v>
       </c>
@@ -1672,7 +1678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A44" s="1">
         <v>46280</v>
       </c>
@@ -1689,7 +1695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A45" s="1">
         <v>46279</v>
       </c>
@@ -1706,7 +1712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A46" s="1">
         <v>46278</v>
       </c>
@@ -1723,7 +1729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A47" s="1">
         <v>46277</v>
       </c>
@@ -1740,7 +1746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A48" s="1">
         <v>46276</v>
       </c>
@@ -1757,7 +1763,7 @@
         <v>5.3833070000000003</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A49" s="1">
         <v>46275</v>
       </c>
@@ -1774,7 +1780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A50" s="1">
         <v>46274</v>
       </c>
@@ -1788,7 +1794,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A51" s="1">
         <v>46273</v>
       </c>
@@ -1802,7 +1808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A52" s="1">
         <v>46272</v>
       </c>
@@ -1816,7 +1822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A53" s="1">
         <v>46271</v>
       </c>
@@ -1830,7 +1836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A54" s="1">
         <v>46270</v>
       </c>
@@ -1844,7 +1850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A55" s="1">
         <v>46269</v>
       </c>
@@ -1858,7 +1864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A56" s="1">
         <v>46268</v>
       </c>
@@ -1872,7 +1878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A57" s="1">
         <v>46267</v>
       </c>
@@ -1886,7 +1892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A58" s="1">
         <v>46266</v>
       </c>
@@ -1900,7 +1906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A59" s="1">
         <v>46265</v>
       </c>
@@ -1911,7 +1917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A60" s="1">
         <v>46264</v>
       </c>
@@ -1925,7 +1931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A61" s="1">
         <v>46263</v>
       </c>
@@ -1939,7 +1945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A62" s="1">
         <v>46262</v>
       </c>
@@ -1953,7 +1959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A63" s="1">
         <v>46261</v>
       </c>
@@ -1970,7 +1976,7 @@
         <v>0.21422999999999998</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A64" s="1">
         <v>46260</v>
       </c>
@@ -1984,7 +1990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:21">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A65" s="1">
         <v>46259</v>
       </c>
@@ -2001,7 +2007,7 @@
         <v>10.703772000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:21">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A66" s="1">
         <v>46258</v>
       </c>
@@ -2015,7 +2021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:21">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A67" s="1">
         <v>46257</v>
       </c>
@@ -2029,7 +2035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:21">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A68" s="1">
         <v>46256</v>
       </c>
@@ -2043,7 +2049,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:21">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A69" s="1">
         <v>46255</v>
       </c>
@@ -2057,7 +2063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:21">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A70" s="1">
         <v>46254</v>
       </c>
@@ -2074,7 +2080,7 @@
         <v>8.4293359999999993</v>
       </c>
     </row>
-    <row r="71" spans="1:21">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A71" s="1">
         <v>46253</v>
       </c>
@@ -2103,7 +2109,7 @@
       <c r="T71" s="7"/>
       <c r="U71" s="7"/>
     </row>
-    <row r="72" spans="1:21">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A72" s="1">
         <v>46252</v>
       </c>
@@ -2120,7 +2126,7 @@
         <v>6.2419820000000001</v>
       </c>
     </row>
-    <row r="73" spans="1:21">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A73" s="1">
         <v>46251</v>
       </c>
@@ -2137,7 +2143,7 @@
         <v>14.777381999999999</v>
       </c>
     </row>
-    <row r="74" spans="1:21">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A74" s="1">
         <v>46250</v>
       </c>
@@ -2148,7 +2154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:21">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A75" s="1">
         <v>46249</v>
       </c>
@@ -2156,7 +2162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:21">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A76" s="1">
         <v>46248</v>
       </c>
@@ -2173,7 +2179,7 @@
         <v>20.847041999999995</v>
       </c>
     </row>
-    <row r="77" spans="1:21">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A77" s="1">
         <v>46247</v>
       </c>
@@ -2190,7 +2196,7 @@
         <v>5.4199330000000003</v>
       </c>
     </row>
-    <row r="78" spans="1:21">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A78" s="1">
         <v>46246</v>
       </c>
@@ -2204,7 +2210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:21">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A79" s="1">
         <v>46245</v>
       </c>
@@ -2218,7 +2224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:21">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A80" s="1">
         <v>46244</v>
       </c>
@@ -2232,7 +2238,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A81" s="1">
         <v>46243</v>
       </c>
@@ -2246,7 +2252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A82" s="1">
         <v>46242</v>
       </c>
@@ -2260,7 +2266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A83" s="1">
         <v>46241</v>
       </c>
@@ -2274,7 +2280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A84" s="1">
         <v>46240</v>
       </c>
@@ -2288,7 +2294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A85" s="1">
         <v>46239</v>
       </c>
@@ -2302,7 +2308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A86" s="1">
         <v>46238</v>
       </c>
@@ -2323,13 +2329,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D41FB4CD-150C-4CE3-A76E-CB540C2892DD}">
-  <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <dimension ref="A1:M22"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.5">
       <c r="B1" t="s">
         <v>22</v>
       </c>
@@ -2357,8 +2363,17 @@
       <c r="J1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -2390,8 +2405,17 @@
       <c r="J2">
         <v>4500</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="K2">
+        <v>4706</v>
+      </c>
+      <c r="L2">
+        <v>1376</v>
+      </c>
+      <c r="M2">
+        <v>51849</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -2431,8 +2455,17 @@
         <f>1195+SUM(J5:J200)</f>
         <v>1304</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>9</v>
+      </c>
+      <c r="M3">
+        <v>14810</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -2472,8 +2505,20 @@
         <f>J2-J3</f>
         <v>3196</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="K4">
+        <f>K2-K3</f>
+        <v>4706</v>
+      </c>
+      <c r="L4">
+        <f>L2-L3</f>
+        <v>1367</v>
+      </c>
+      <c r="M4">
+        <f>M2-M3</f>
+        <v>37039</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A5" s="1">
         <v>46302</v>
       </c>
@@ -2504,8 +2549,11 @@
       <c r="J5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="M5">
+        <v>28.03</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A6" s="1">
         <v>46303</v>
       </c>
@@ -2536,8 +2584,11 @@
       <c r="J6" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="M6">
+        <v>27.501999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A7" s="1">
         <v>46304</v>
       </c>
@@ -2568,8 +2619,11 @@
       <c r="J7" s="6">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="M7">
+        <v>31.963000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A8" s="1">
         <v>46305</v>
       </c>
@@ -2600,8 +2654,11 @@
       <c r="J8" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="M8">
+        <v>10.138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A9" s="1">
         <v>46306</v>
       </c>
@@ -2632,8 +2689,11 @@
       <c r="J9" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="M9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A10" s="1">
         <v>46307</v>
       </c>
@@ -2664,8 +2724,11 @@
       <c r="J10" s="6">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="M10">
+        <v>36.164999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A11" s="1">
         <v>46308</v>
       </c>
@@ -2696,8 +2759,11 @@
       <c r="J11" s="6">
         <v>19</v>
       </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="M11">
+        <v>51.722999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A12" s="1">
         <v>46309</v>
       </c>
@@ -2725,8 +2791,11 @@
       <c r="J12" s="6">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="M12">
+        <v>39.198999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A13" s="1">
         <v>46310</v>
       </c>
@@ -2757,8 +2826,11 @@
       <c r="J13" s="6">
         <v>21</v>
       </c>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="M13">
+        <v>54.48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A14" s="1">
         <v>46311</v>
       </c>
@@ -2789,8 +2861,11 @@
       <c r="J14" s="6">
         <v>21</v>
       </c>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="M14">
+        <v>58.851999999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A15" s="1">
         <v>46312</v>
       </c>
@@ -2821,8 +2896,11 @@
       <c r="J15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:10">
+      <c r="M15">
+        <v>4.8529999999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A16" s="1">
         <v>46316</v>
       </c>
@@ -2853,8 +2931,12 @@
       <c r="J16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:10">
+      <c r="M16">
+        <f>5.603+33.119</f>
+        <v>38.722000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A17" s="1">
         <v>46317</v>
       </c>
@@ -2885,8 +2967,11 @@
       <c r="J17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:10">
+      <c r="M17">
+        <v>57.932000000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A18" s="1">
         <v>46318</v>
       </c>
@@ -2917,8 +3002,11 @@
       <c r="J18">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="M18">
+        <v>46.978999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A19" s="1">
         <v>46319</v>
       </c>
@@ -2949,8 +3037,11 @@
       <c r="J19">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="M19">
+        <v>60.981999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A20" s="1">
         <v>46320</v>
       </c>
@@ -2981,8 +3072,11 @@
       <c r="J20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="M20">
+        <v>63.399000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A21" s="1">
         <v>46321</v>
       </c>
@@ -3013,8 +3107,11 @@
       <c r="J21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:10">
+      <c r="M21">
+        <v>84.963999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A22" s="1">
         <v>46322</v>
       </c>
@@ -3044,6 +3141,9 @@
       </c>
       <c r="J22">
         <v>0</v>
+      </c>
+      <c r="M22">
+        <v>92.921000000000006</v>
       </c>
     </row>
   </sheetData>
@@ -3054,13 +3154,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E384ED-EF07-4058-B570-9E7F8CBFADFB}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="9.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -3068,7 +3168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -3076,7 +3176,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -3084,7 +3184,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -3092,7 +3192,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -3100,7 +3200,7 @@
         <v>46336</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
         <v>39</v>
       </c>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30619"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1417" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39848C3C-457D-4373-B2F4-8C5E0DA06FBB}"/>
+  <xr:revisionPtr revIDLastSave="1443" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EB368CC-7E89-4A68-B155-FBE9253EE692}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>
@@ -54,19 +54,19 @@
     <t>ACC</t>
   </si>
   <si>
-    <t>Daily-21; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 1040;Total - 5655 MT</t>
+    <t>Daily-12; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 1052;Total - 5668 MT</t>
   </si>
   <si>
     <t>Boiler</t>
   </si>
   <si>
-    <t>Daily-141  - (SH-105 and RH-36); Oct-2127 NDHT Balance joints - 8087(SH - 4045; RH - 4042)</t>
+    <t>Daily-148  - (SH-112 and RH-36); Oct-2275 NDHT Balance joints - 7939(SH - 3933; RH - 4006)</t>
   </si>
   <si>
     <t>PCP Joint</t>
   </si>
   <si>
-    <t>Daily-2; MS Joints - 88/146; MS to PRDS - 11/26; HRH - 11/95; CRH -15/87; LPBP - 11/49; HPBP-10/23; BFD- 183/661</t>
+    <t>Daily-0; MS Joints - 88/146; MS to PRDS - 11/26; HRH - 11/95; CRH -15/87; LPBP - 11/49; HPBP-10/23; BFD- 185/661</t>
   </si>
   <si>
     <t>Unit</t>
@@ -132,6 +132,12 @@
     <t>BFD</t>
   </si>
   <si>
+    <t xml:space="preserve">Insulation </t>
+  </si>
+  <si>
+    <t>APH</t>
+  </si>
+  <si>
     <t>Total</t>
   </si>
   <si>
@@ -160,12 +166,6 @@
   </si>
   <si>
     <t>Segment-5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insulation </t>
-  </si>
-  <si>
-    <t>APH</t>
   </si>
 </sst>
 </file>
@@ -173,12 +173,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -312,7 +312,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -320,13 +320,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
@@ -778,13 +778,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="95.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -795,9 +795,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:3">
       <c r="A2" s="1">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -806,9 +806,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:3">
       <c r="A3" s="1">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -817,9 +817,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:3">
       <c r="A4" s="1">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -839,12 +839,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6E5BA1F-B477-478E-9D82-DB1AA3EDF6C0}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="2" max="2" width="29.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:5">
       <c r="A1" s="8" t="s">
         <v>9</v>
       </c>
@@ -861,7 +861,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -879,7 +879,7 @@
         <v>0.61516206319786626</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -897,7 +897,7 @@
         <v>0.30966283669240913</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -922,8 +922,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
-  <dimension ref="A1:AA86"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:AA87"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
@@ -931,7 +931,7 @@
     <col min="5" max="6" width="11.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -948,7 +948,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -965,32 +965,32 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:5">
       <c r="A3" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B3">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>148</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1">
         <v>46322</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>21</v>
       </c>
-      <c r="C3">
+      <c r="C4">
         <v>141</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A4" s="1">
-        <v>46321</v>
-      </c>
-      <c r="B4">
-        <v>24</v>
-      </c>
-      <c r="C4">
-        <v>116</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -999,654 +999,654 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:5">
       <c r="A5" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B5">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>116</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1">
         <v>46320</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>8</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A6" s="1">
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1">
         <v>46319</v>
       </c>
-      <c r="B6">
+      <c r="B7">
         <v>35</v>
       </c>
-      <c r="C6">
+      <c r="C7">
         <v>104</v>
       </c>
-      <c r="D6">
+      <c r="D7">
         <v>2</v>
       </c>
-      <c r="E6">
+      <c r="E7">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A7" s="1">
+    <row r="8" spans="1:5">
+      <c r="A8" s="1">
         <v>46318</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>20</v>
       </c>
-      <c r="C7">
+      <c r="C8">
         <v>98</v>
       </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A8" s="1">
+    <row r="9" spans="1:5">
+      <c r="A9" s="1">
         <v>46317</v>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>10</v>
       </c>
-      <c r="C8">
+      <c r="C9">
         <v>54</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A9" s="1">
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1">
         <v>46316</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>30</v>
       </c>
-      <c r="C9">
+      <c r="C10">
         <v>32</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A10" s="1">
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1">
         <v>46315</v>
       </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A11" s="1">
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1">
         <v>46314</v>
       </c>
-      <c r="B11">
+      <c r="B12">
         <v>6</v>
       </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A12" s="1">
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="1">
         <v>46313</v>
       </c>
-      <c r="B12">
+      <c r="B13">
         <v>18</v>
       </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A13" s="1">
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="1">
         <v>46312</v>
       </c>
-      <c r="B13">
+      <c r="B14">
         <v>14</v>
       </c>
-      <c r="C13">
+      <c r="C14">
         <v>85</v>
       </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A14" s="1">
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="1">
         <v>46311</v>
       </c>
-      <c r="B14">
+      <c r="B15">
         <v>117</v>
       </c>
-      <c r="C14">
+      <c r="C15">
         <v>148</v>
       </c>
-      <c r="D14">
+      <c r="D15">
         <v>2</v>
       </c>
-      <c r="E14">
+      <c r="E15">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A15" s="1">
+    <row r="16" spans="1:5">
+      <c r="A16" s="1">
         <v>46310</v>
       </c>
-      <c r="B15">
+      <c r="B16">
         <v>56</v>
       </c>
-      <c r="C15">
+      <c r="C16">
         <v>122</v>
       </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="6">
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" s="6">
         <v>20.72</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A16" s="1">
+    <row r="17" spans="1:27">
+      <c r="A17" s="1">
         <v>46309</v>
       </c>
-      <c r="B16">
+      <c r="B17">
         <v>23</v>
       </c>
-      <c r="C16">
+      <c r="C17">
         <v>135</v>
       </c>
-      <c r="D16">
+      <c r="D17">
         <v>2</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E17" s="6">
         <v>16.425999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.5">
-      <c r="A17" s="1">
+    <row r="18" spans="1:27">
+      <c r="A18" s="1">
         <v>46308</v>
       </c>
-      <c r="B17">
+      <c r="B18">
         <v>44</v>
       </c>
-      <c r="C17">
+      <c r="C18">
         <v>127</v>
       </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17" s="6">
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" s="6">
         <v>18.917999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.5">
-      <c r="A18" s="1">
+    <row r="19" spans="1:27">
+      <c r="A19" s="1">
         <v>46307</v>
       </c>
-      <c r="B18">
+      <c r="B19">
         <v>102</v>
       </c>
-      <c r="C18">
+      <c r="C19">
         <v>118</v>
       </c>
-      <c r="D18">
+      <c r="D19">
         <v>3</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E19" s="6">
         <v>7.9720000000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.5">
-      <c r="A19" s="1">
+    <row r="20" spans="1:27">
+      <c r="A20" s="1">
         <v>46306</v>
       </c>
-      <c r="B19">
+      <c r="B20">
         <v>21</v>
       </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.5">
-      <c r="A20" s="1">
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27">
+      <c r="A21" s="1">
         <v>46305</v>
       </c>
-      <c r="B20">
+      <c r="B21">
         <v>83</v>
       </c>
-      <c r="C20">
+      <c r="C21">
         <v>82</v>
       </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.5">
-      <c r="A21" s="1">
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27">
+      <c r="A22" s="1">
         <v>46304</v>
       </c>
-      <c r="B21">
+      <c r="B22">
         <v>74</v>
       </c>
-      <c r="C21">
+      <c r="C22">
         <v>130</v>
       </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21" s="6">
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" s="6">
         <v>4.3440000000000003</v>
       </c>
-      <c r="I21" s="2"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="3"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="3"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
-      <c r="X21" s="3"/>
-      <c r="Y21" s="2"/>
-      <c r="Z21" s="2"/>
-      <c r="AA21" s="2"/>
-    </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.5">
-      <c r="A22" s="1">
+      <c r="I22" s="2"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="3"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="2"/>
+      <c r="Z22" s="2"/>
+      <c r="AA22" s="2"/>
+    </row>
+    <row r="23" spans="1:27">
+      <c r="A23" s="1">
         <v>46303</v>
       </c>
-      <c r="B22">
+      <c r="B23">
         <v>70</v>
       </c>
-      <c r="C22">
+      <c r="C23">
         <v>134</v>
       </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.5">
-      <c r="A23" s="1">
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27">
+      <c r="A24" s="1">
         <v>46302</v>
       </c>
-      <c r="B23">
+      <c r="B24">
         <v>26</v>
       </c>
-      <c r="C23">
+      <c r="C24">
         <v>91</v>
       </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.5">
-      <c r="A24" s="1">
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27">
+      <c r="A25" s="1">
         <v>46301</v>
-      </c>
-      <c r="B24">
-        <v>45</v>
-      </c>
-      <c r="C24">
-        <v>104</v>
-      </c>
-      <c r="D24">
-        <v>4</v>
-      </c>
-      <c r="E24" s="6">
-        <v>4.5679999999999996</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.5">
-      <c r="A25" s="1">
-        <v>46300</v>
       </c>
       <c r="B25">
         <v>45</v>
       </c>
       <c r="C25">
+        <v>104</v>
+      </c>
+      <c r="D25">
+        <v>4</v>
+      </c>
+      <c r="E25" s="6">
+        <v>4.5679999999999996</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27">
+      <c r="A26" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B26">
+        <v>45</v>
+      </c>
+      <c r="C26">
         <v>123</v>
       </c>
-      <c r="D25">
+      <c r="D26">
         <v>2</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E26" s="6">
         <v>6.4130000000000003</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.5">
-      <c r="A26" s="1">
+    <row r="27" spans="1:27">
+      <c r="A27" s="1">
         <v>46299</v>
       </c>
-      <c r="B26">
+      <c r="B27">
         <v>66</v>
       </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26" s="6">
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27" s="6">
         <v>4.3440000000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.5">
-      <c r="A27" s="1">
+    <row r="28" spans="1:27">
+      <c r="A28" s="1">
         <v>46298</v>
       </c>
-      <c r="B27">
+      <c r="B28">
         <v>40</v>
       </c>
-      <c r="C27">
+      <c r="C28">
         <v>65</v>
       </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-      <c r="E27" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.5">
-      <c r="A28" s="1">
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27">
+      <c r="A29" s="1">
         <v>46297</v>
       </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
-      <c r="C28">
-        <v>0</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="E28" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.5">
-      <c r="A29" s="1">
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27">
+      <c r="A30" s="1">
         <v>46296</v>
       </c>
-      <c r="B29">
+      <c r="B30">
         <v>40</v>
       </c>
-      <c r="C29">
+      <c r="C30">
         <v>101</v>
       </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-      <c r="E29" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.5">
-      <c r="A30" s="1">
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27">
+      <c r="A31" s="1">
         <v>46295</v>
       </c>
-      <c r="B30">
+      <c r="B31">
         <v>321</v>
       </c>
-      <c r="C30">
+      <c r="C31">
         <v>139</v>
       </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-      <c r="E30" s="5">
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5">
         <v>37.679307999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.5">
-      <c r="A31" s="1">
+    <row r="32" spans="1:27">
+      <c r="A32" s="1">
         <v>46294</v>
       </c>
-      <c r="B31">
+      <c r="B32">
         <v>200</v>
       </c>
-      <c r="C31">
+      <c r="C32">
         <v>114</v>
       </c>
-      <c r="D31">
-        <v>1</v>
-      </c>
-      <c r="E31" s="5">
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32" s="5">
         <v>33.449338000000004</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.5">
-      <c r="A32" s="1">
+    <row r="33" spans="1:5">
+      <c r="A33" s="1">
         <v>46293</v>
       </c>
-      <c r="B32">
+      <c r="B33">
         <v>43</v>
       </c>
-      <c r="C32">
-        <v>0</v>
-      </c>
-      <c r="D32">
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
         <v>4</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E33" s="5">
         <v>42.041217999999994</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A33" s="1">
+    <row r="34" spans="1:5">
+      <c r="A34" s="1">
         <v>46292</v>
       </c>
-      <c r="B33">
+      <c r="B34">
         <v>13</v>
       </c>
-      <c r="C33">
-        <v>0</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
-      <c r="E33" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A34" s="1">
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="1">
         <v>46291</v>
       </c>
-      <c r="B34">
+      <c r="B35">
         <v>17</v>
       </c>
-      <c r="C34">
+      <c r="C35">
         <v>39</v>
       </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
-      <c r="E34" s="5">
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35" s="5">
         <v>16.912866999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A35" s="1">
+    <row r="36" spans="1:5">
+      <c r="A36" s="1">
         <v>46290</v>
       </c>
-      <c r="B35">
+      <c r="B36">
         <v>20</v>
       </c>
-      <c r="C35">
+      <c r="C36">
         <v>121</v>
       </c>
-      <c r="D35">
+      <c r="D36">
         <v>2</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E36" s="5">
         <v>11.657306</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A36" s="1">
+    <row r="37" spans="1:5">
+      <c r="A37" s="1">
         <v>46289</v>
       </c>
-      <c r="B36">
+      <c r="B37">
         <v>3</v>
       </c>
-      <c r="C36">
+      <c r="C37">
         <v>133</v>
       </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-      <c r="E36" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A37" s="1">
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="1">
         <v>46288</v>
       </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-      <c r="C37">
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38">
         <v>143</v>
       </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-      <c r="E37" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A38" s="1">
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="1">
         <v>46287</v>
       </c>
-      <c r="B38">
+      <c r="B39">
         <v>9</v>
       </c>
-      <c r="C38">
-        <v>0</v>
-      </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
-      <c r="E38" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A39" s="1">
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="1">
         <v>46286</v>
       </c>
-      <c r="B39">
+      <c r="B40">
         <v>32</v>
       </c>
-      <c r="C39">
+      <c r="C40">
         <v>131</v>
       </c>
-      <c r="D39">
-        <v>0</v>
-      </c>
-      <c r="E39" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A40" s="1">
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="1">
         <v>46285</v>
       </c>
-      <c r="B40">
+      <c r="B41">
         <v>42</v>
       </c>
-      <c r="C40">
+      <c r="C41">
         <v>111</v>
       </c>
-      <c r="D40">
-        <v>0</v>
-      </c>
-      <c r="E40" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A41" s="1">
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="1">
         <v>46284</v>
-      </c>
-      <c r="B41">
-        <v>16</v>
-      </c>
-      <c r="C41">
-        <v>118</v>
-      </c>
-      <c r="D41">
-        <v>4</v>
-      </c>
-      <c r="E41" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A42" s="1">
-        <v>46283</v>
       </c>
       <c r="B42">
         <v>16</v>
@@ -1658,494 +1658,494 @@
         <v>4</v>
       </c>
       <c r="E42" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B43">
+        <v>16</v>
+      </c>
+      <c r="C43">
+        <v>118</v>
+      </c>
+      <c r="D43">
+        <v>4</v>
+      </c>
+      <c r="E43" s="5">
         <v>30.143184999999992</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A43" s="1">
+    <row r="44" spans="1:5">
+      <c r="A44" s="1">
         <v>46281</v>
       </c>
-      <c r="B43">
+      <c r="B44">
         <v>33</v>
       </c>
-      <c r="C43">
+      <c r="C44">
         <v>98</v>
       </c>
-      <c r="D43">
-        <v>0</v>
-      </c>
-      <c r="E43" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A44" s="1">
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="1">
         <v>46280</v>
       </c>
-      <c r="B44">
+      <c r="B45">
         <v>3</v>
       </c>
-      <c r="C44">
+      <c r="C45">
         <v>125</v>
       </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-      <c r="E44" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A45" s="1">
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="1">
         <v>46279</v>
       </c>
-      <c r="B45">
+      <c r="B46">
         <v>58</v>
       </c>
-      <c r="C45">
+      <c r="C46">
         <v>100</v>
       </c>
-      <c r="D45">
+      <c r="D46">
         <v>2</v>
       </c>
-      <c r="E45" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A46" s="1">
+      <c r="E46" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="1">
         <v>46278</v>
       </c>
-      <c r="B46">
+      <c r="B47">
         <v>3</v>
       </c>
-      <c r="C46">
-        <v>0</v>
-      </c>
-      <c r="D46">
-        <v>0</v>
-      </c>
-      <c r="E46" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A47" s="1">
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="1">
         <v>46277</v>
       </c>
-      <c r="B47">
+      <c r="B48">
         <v>63</v>
       </c>
-      <c r="C47">
+      <c r="C48">
         <v>42</v>
       </c>
-      <c r="D47">
+      <c r="D48">
         <v>2</v>
       </c>
-      <c r="E47" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A48" s="1">
+      <c r="E48" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="1">
         <v>46276</v>
       </c>
-      <c r="B48">
+      <c r="B49">
         <v>19</v>
       </c>
-      <c r="C48">
+      <c r="C49">
         <v>73</v>
       </c>
-      <c r="D48">
-        <v>1</v>
-      </c>
-      <c r="E48" s="5">
+      <c r="D49">
+        <v>1</v>
+      </c>
+      <c r="E49" s="5">
         <v>5.3833070000000003</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A49" s="1">
+    <row r="50" spans="1:5">
+      <c r="A50" s="1">
         <v>46275</v>
       </c>
-      <c r="B49">
+      <c r="B50">
         <v>21</v>
       </c>
-      <c r="C49">
+      <c r="C50">
         <v>16</v>
       </c>
-      <c r="D49">
-        <v>1</v>
-      </c>
-      <c r="E49" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A50" s="1">
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="1">
         <v>46274</v>
       </c>
-      <c r="B50">
+      <c r="B51">
         <v>47</v>
       </c>
-      <c r="C50">
+      <c r="C51">
         <v>84</v>
       </c>
-      <c r="D50">
+      <c r="D51">
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A51" s="1">
+    <row r="52" spans="1:5">
+      <c r="A52" s="1">
         <v>46273</v>
       </c>
-      <c r="B51">
+      <c r="B52">
         <v>45</v>
       </c>
-      <c r="C51">
+      <c r="C52">
         <v>105</v>
       </c>
-      <c r="D51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A52" s="1">
+      <c r="D52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="1">
         <v>46272</v>
       </c>
-      <c r="B52">
+      <c r="B53">
         <v>38</v>
       </c>
-      <c r="C52">
+      <c r="C53">
         <v>92</v>
       </c>
-      <c r="D52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A53" s="1">
+      <c r="D53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="1">
         <v>46271</v>
       </c>
-      <c r="B53">
+      <c r="B54">
         <v>13</v>
       </c>
-      <c r="C53">
-        <v>0</v>
-      </c>
-      <c r="D53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A54" s="1">
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="1">
         <v>46270</v>
       </c>
-      <c r="B54">
-        <v>0</v>
-      </c>
-      <c r="C54">
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
         <v>90</v>
       </c>
-      <c r="D54">
+      <c r="D55">
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A55" s="1">
+    <row r="56" spans="1:5">
+      <c r="A56" s="1">
         <v>46269</v>
       </c>
-      <c r="B55">
-        <v>0</v>
-      </c>
-      <c r="C55">
-        <v>0</v>
-      </c>
-      <c r="D55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A56" s="1">
+      <c r="B56">
+        <v>0</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="1">
         <v>46268</v>
       </c>
-      <c r="B56">
+      <c r="B57">
         <v>23</v>
       </c>
-      <c r="C56">
+      <c r="C57">
         <v>74</v>
       </c>
-      <c r="D56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A57" s="1">
+      <c r="D57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="1">
         <v>46267</v>
       </c>
-      <c r="B57">
+      <c r="B58">
         <v>7</v>
       </c>
-      <c r="C57">
+      <c r="C58">
         <v>75</v>
       </c>
-      <c r="D57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A58" s="1">
+      <c r="D58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="1">
         <v>46266</v>
       </c>
-      <c r="B58">
+      <c r="B59">
         <v>17</v>
       </c>
-      <c r="C58">
-        <v>0</v>
-      </c>
-      <c r="D58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A59" s="1">
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="1">
         <v>46265</v>
       </c>
-      <c r="C59">
+      <c r="C60">
         <v>62</v>
       </c>
-      <c r="D59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A60" s="1">
+      <c r="D60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="1">
         <v>46264</v>
       </c>
-      <c r="B60">
+      <c r="B61">
         <v>5</v>
       </c>
-      <c r="C60">
-        <v>0</v>
-      </c>
-      <c r="D60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A61" s="1">
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="1">
         <v>46263</v>
       </c>
-      <c r="B61">
+      <c r="B62">
         <v>73</v>
       </c>
-      <c r="C61">
+      <c r="C62">
         <v>62</v>
       </c>
-      <c r="D61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A62" s="1">
+      <c r="D62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="1">
         <v>46262</v>
       </c>
-      <c r="B62">
+      <c r="B63">
         <v>67</v>
       </c>
-      <c r="C62">
+      <c r="C63">
         <v>54</v>
       </c>
-      <c r="D62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A63" s="1">
+      <c r="D63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="1">
         <v>46261</v>
       </c>
-      <c r="B63">
+      <c r="B64">
         <v>29</v>
       </c>
-      <c r="C63">
+      <c r="C64">
         <v>64</v>
       </c>
-      <c r="D63">
+      <c r="D64">
         <v>3</v>
       </c>
-      <c r="E63" s="4">
+      <c r="E64" s="4">
         <v>0.21422999999999998</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A64" s="1">
+    <row r="65" spans="1:21">
+      <c r="A65" s="1">
         <v>46260</v>
       </c>
-      <c r="B64">
+      <c r="B65">
         <v>85</v>
-      </c>
-      <c r="C64">
-        <v>62</v>
-      </c>
-      <c r="D64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.5">
-      <c r="A65" s="1">
-        <v>46259</v>
-      </c>
-      <c r="B65">
-        <v>13</v>
       </c>
       <c r="C65">
         <v>62</v>
       </c>
       <c r="D65">
-        <v>1</v>
-      </c>
-      <c r="E65" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21">
+      <c r="A66" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B66">
+        <v>13</v>
+      </c>
+      <c r="C66">
+        <v>62</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="E66" s="4">
         <v>10.703772000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.5">
-      <c r="A66" s="1">
+    <row r="67" spans="1:21">
+      <c r="A67" s="1">
         <v>46258</v>
       </c>
-      <c r="B66">
+      <c r="B67">
         <v>18</v>
       </c>
-      <c r="C66">
+      <c r="C67">
         <v>56</v>
       </c>
-      <c r="D66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.5">
-      <c r="A67" s="1">
+      <c r="D67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21">
+      <c r="A68" s="1">
         <v>46257</v>
       </c>
-      <c r="B67">
+      <c r="B68">
         <v>3</v>
       </c>
-      <c r="C67">
-        <v>0</v>
-      </c>
-      <c r="D67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.5">
-      <c r="A68" s="1">
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21">
+      <c r="A69" s="1">
         <v>46256</v>
       </c>
-      <c r="B68">
+      <c r="B69">
         <v>69</v>
       </c>
-      <c r="C68">
+      <c r="C69">
         <v>53</v>
       </c>
-      <c r="D68">
+      <c r="D69">
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.5">
-      <c r="A69" s="1">
+    <row r="70" spans="1:21">
+      <c r="A70" s="1">
         <v>46255</v>
       </c>
-      <c r="B69">
+      <c r="B70">
         <v>15</v>
       </c>
-      <c r="C69">
+      <c r="C70">
         <v>60</v>
       </c>
-      <c r="D69">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.5">
-      <c r="A70" s="1">
+      <c r="D70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21">
+      <c r="A71" s="1">
         <v>46254</v>
       </c>
-      <c r="B70">
+      <c r="B71">
         <v>48</v>
       </c>
-      <c r="C70">
+      <c r="C71">
         <v>43</v>
       </c>
-      <c r="D70">
-        <v>0</v>
-      </c>
-      <c r="E70" s="4">
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71" s="4">
         <v>8.4293359999999993</v>
       </c>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.5">
-      <c r="A71" s="1">
+    <row r="72" spans="1:21">
+      <c r="A72" s="1">
         <v>46253</v>
       </c>
-      <c r="B71">
+      <c r="B72">
         <v>27</v>
       </c>
-      <c r="C71">
+      <c r="C72">
         <v>51</v>
       </c>
-      <c r="D71">
-        <v>1</v>
-      </c>
-      <c r="G71" s="7"/>
-      <c r="H71" s="7"/>
-      <c r="I71" s="3"/>
-      <c r="J71" s="3"/>
-      <c r="K71" s="7"/>
-      <c r="L71" s="7"/>
-      <c r="M71" s="7"/>
-      <c r="N71" s="7"/>
-      <c r="O71" s="7"/>
-      <c r="P71" s="7"/>
-      <c r="Q71" s="7"/>
-      <c r="R71" s="7"/>
-      <c r="S71" s="7"/>
-      <c r="T71" s="7"/>
-      <c r="U71" s="7"/>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.5">
-      <c r="A72" s="1">
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="G72" s="7"/>
+      <c r="H72" s="7"/>
+      <c r="I72" s="3"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="7"/>
+      <c r="L72" s="7"/>
+      <c r="M72" s="7"/>
+      <c r="N72" s="7"/>
+      <c r="O72" s="7"/>
+      <c r="P72" s="7"/>
+      <c r="Q72" s="7"/>
+      <c r="R72" s="7"/>
+      <c r="S72" s="7"/>
+      <c r="T72" s="7"/>
+      <c r="U72" s="7"/>
+    </row>
+    <row r="73" spans="1:21">
+      <c r="A73" s="1">
         <v>46252</v>
       </c>
-      <c r="B72">
-        <v>0</v>
-      </c>
-      <c r="C72">
-        <v>0</v>
-      </c>
-      <c r="D72">
+      <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
         <v>2</v>
       </c>
-      <c r="E72" s="4">
+      <c r="E73" s="4">
         <v>6.2419820000000001</v>
       </c>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.5">
-      <c r="A73" s="1">
+    <row r="74" spans="1:21">
+      <c r="A74" s="1">
         <v>46251</v>
-      </c>
-      <c r="B73">
-        <v>12</v>
-      </c>
-      <c r="C73">
-        <v>0</v>
-      </c>
-      <c r="D73">
-        <v>1</v>
-      </c>
-      <c r="E73" s="4">
-        <v>14.777381999999999</v>
-      </c>
-    </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.5">
-      <c r="A74" s="1">
-        <v>46250</v>
       </c>
       <c r="B74">
         <v>12</v>
@@ -2153,172 +2153,189 @@
       <c r="C74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.5">
+      <c r="D74">
+        <v>1</v>
+      </c>
+      <c r="E74" s="4">
+        <v>14.777381999999999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21">
       <c r="A75" s="1">
+        <v>46250</v>
+      </c>
+      <c r="B75">
+        <v>12</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21">
+      <c r="A76" s="1">
         <v>46249</v>
       </c>
-      <c r="C75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.5">
-      <c r="A76" s="1">
+      <c r="C76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21">
+      <c r="A77" s="1">
         <v>46248</v>
       </c>
-      <c r="B76">
+      <c r="B77">
         <v>7</v>
       </c>
-      <c r="C76">
+      <c r="C77">
         <v>16</v>
       </c>
-      <c r="D76">
-        <v>0</v>
-      </c>
-      <c r="E76" s="4">
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77" s="4">
         <v>20.847041999999995</v>
       </c>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.5">
-      <c r="A77" s="1">
+    <row r="78" spans="1:21">
+      <c r="A78" s="1">
         <v>46247</v>
       </c>
-      <c r="B77">
+      <c r="B78">
         <v>35</v>
-      </c>
-      <c r="C77">
-        <v>21</v>
-      </c>
-      <c r="D77">
-        <v>0</v>
-      </c>
-      <c r="E77" s="4">
-        <v>5.4199330000000003</v>
-      </c>
-    </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.5">
-      <c r="A78" s="1">
-        <v>46246</v>
-      </c>
-      <c r="B78">
-        <v>28</v>
       </c>
       <c r="C78">
         <v>21</v>
       </c>
       <c r="D78">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.5">
+        <v>0</v>
+      </c>
+      <c r="E78" s="4">
+        <v>5.4199330000000003</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21">
       <c r="A79" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B79">
+        <v>28</v>
+      </c>
+      <c r="C79">
+        <v>21</v>
+      </c>
+      <c r="D79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21">
+      <c r="A80" s="1">
         <v>46245</v>
       </c>
-      <c r="B79">
+      <c r="B80">
         <v>21</v>
       </c>
-      <c r="C79">
+      <c r="C80">
         <v>25</v>
       </c>
-      <c r="D79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.5">
-      <c r="A80" s="1">
+      <c r="D80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="1">
         <v>46244</v>
       </c>
-      <c r="B80">
+      <c r="B81">
         <v>19</v>
       </c>
-      <c r="C80">
+      <c r="C81">
         <v>11</v>
       </c>
-      <c r="D80">
+      <c r="D81">
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A81" s="1">
+    <row r="82" spans="1:4">
+      <c r="A82" s="1">
         <v>46243</v>
       </c>
-      <c r="B81">
+      <c r="B82">
         <v>13</v>
       </c>
-      <c r="C81">
-        <v>0</v>
-      </c>
-      <c r="D81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A82" s="1">
+      <c r="C82">
+        <v>0</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="1">
         <v>46242</v>
       </c>
-      <c r="B82">
-        <v>0</v>
-      </c>
-      <c r="C82">
-        <v>0</v>
-      </c>
-      <c r="D82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A83" s="1">
+      <c r="B83">
+        <v>0</v>
+      </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="1">
         <v>46241</v>
       </c>
-      <c r="B83">
+      <c r="B84">
         <v>32</v>
       </c>
-      <c r="C83">
-        <v>0</v>
-      </c>
-      <c r="D83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A84" s="1">
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="1">
         <v>46240</v>
       </c>
-      <c r="B84">
+      <c r="B85">
         <v>16</v>
       </c>
-      <c r="C84">
-        <v>0</v>
-      </c>
-      <c r="D84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A85" s="1">
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="1">
         <v>46239</v>
       </c>
-      <c r="B85">
-        <v>0</v>
-      </c>
-      <c r="C85">
-        <v>0</v>
-      </c>
-      <c r="D85">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A86" s="1">
+      <c r="B86">
+        <v>0</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="1">
         <v>46238</v>
       </c>
-      <c r="B86">
-        <v>0</v>
-      </c>
-      <c r="C86">
-        <v>0</v>
-      </c>
-      <c r="D86">
+      <c r="B87">
+        <v>0</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
         <v>1</v>
       </c>
     </row>
@@ -2329,13 +2346,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D41FB4CD-150C-4CE3-A76E-CB540C2892DD}">
-  <dimension ref="A1:M22"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:M23"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:13">
       <c r="B1" t="s">
         <v>22</v>
       </c>
@@ -2364,18 +2381,18 @@
         <v>20</v>
       </c>
       <c r="K1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L1" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="M1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B2">
         <v>9697</v>
@@ -2415,17 +2432,17 @@
         <v>51849</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3">
         <f>4375+SUM(B6:B500)</f>
-        <v>5645</v>
+        <v>5757</v>
       </c>
       <c r="C3">
         <f>7462+SUM(C6:C100)</f>
-        <v>7818</v>
+        <v>7854</v>
       </c>
       <c r="D3">
         <f>75+SUM(D5:D100)</f>
@@ -2449,11 +2466,11 @@
       </c>
       <c r="I3">
         <f>170+SUM(I5:I150)</f>
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J3">
         <f>1195+SUM(J5:J200)</f>
-        <v>1304</v>
+        <v>1316</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -2465,17 +2482,17 @@
         <v>14810</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4">
         <f>B2-B3</f>
-        <v>4052</v>
+        <v>3940</v>
       </c>
       <c r="C4">
         <f>C2-C3</f>
-        <v>4052</v>
+        <v>4016</v>
       </c>
       <c r="D4">
         <f t="shared" ref="D4:G4" si="0">D2-D3</f>
@@ -2499,11 +2516,11 @@
       </c>
       <c r="I4">
         <f>I2-I3</f>
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="J4">
         <f>J2-J3</f>
-        <v>3196</v>
+        <v>3184</v>
       </c>
       <c r="K4">
         <f>K2-K3</f>
@@ -2518,7 +2535,7 @@
         <v>37039</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:13">
       <c r="A5" s="1">
         <v>46302</v>
       </c>
@@ -2553,7 +2570,7 @@
         <v>28.03</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:13">
       <c r="A6" s="1">
         <v>46303</v>
       </c>
@@ -2588,7 +2605,7 @@
         <v>27.501999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:13">
       <c r="A7" s="1">
         <v>46304</v>
       </c>
@@ -2623,7 +2640,7 @@
         <v>31.963000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:13">
       <c r="A8" s="1">
         <v>46305</v>
       </c>
@@ -2658,7 +2675,7 @@
         <v>10.138</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:13">
       <c r="A9" s="1">
         <v>46306</v>
       </c>
@@ -2693,7 +2710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:13">
       <c r="A10" s="1">
         <v>46307</v>
       </c>
@@ -2728,7 +2745,7 @@
         <v>36.164999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:13">
       <c r="A11" s="1">
         <v>46308</v>
       </c>
@@ -2763,7 +2780,7 @@
         <v>51.722999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:13">
       <c r="A12" s="1">
         <v>46309</v>
       </c>
@@ -2795,7 +2812,7 @@
         <v>39.198999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:13">
       <c r="A13" s="1">
         <v>46310</v>
       </c>
@@ -2830,7 +2847,7 @@
         <v>54.48</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:13">
       <c r="A14" s="1">
         <v>46311</v>
       </c>
@@ -2865,7 +2882,7 @@
         <v>58.851999999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:13">
       <c r="A15" s="1">
         <v>46312</v>
       </c>
@@ -2900,7 +2917,7 @@
         <v>4.8529999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:13">
       <c r="A16" s="1">
         <v>46316</v>
       </c>
@@ -2936,7 +2953,7 @@
         <v>38.722000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:13">
       <c r="A17" s="1">
         <v>46317</v>
       </c>
@@ -2971,7 +2988,7 @@
         <v>57.932000000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:13">
       <c r="A18" s="1">
         <v>46318</v>
       </c>
@@ -3006,7 +3023,7 @@
         <v>46.978999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:13">
       <c r="A19" s="1">
         <v>46319</v>
       </c>
@@ -3041,7 +3058,7 @@
         <v>60.981999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:13">
       <c r="A20" s="1">
         <v>46320</v>
       </c>
@@ -3076,7 +3093,7 @@
         <v>63.399000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:13">
       <c r="A21" s="1">
         <v>46321</v>
       </c>
@@ -3111,7 +3128,7 @@
         <v>84.963999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:13">
       <c r="A22" s="1">
         <v>46322</v>
       </c>
@@ -3144,6 +3161,38 @@
       </c>
       <c r="M22">
         <v>92.921000000000006</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B23">
+        <v>112</v>
+      </c>
+      <c r="C23">
+        <v>36</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>2</v>
+      </c>
+      <c r="J23">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -3154,55 +3203,55 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E384ED-EF07-4058-B570-9E7F8CBFADFB}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="9.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B5" s="1">
         <v>46336</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B6" s="1">
         <v>46371</v>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1443" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EB368CC-7E89-4A68-B155-FBE9253EE692}"/>
+  <xr:revisionPtr revIDLastSave="1474" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24A955D1-4CF0-457A-BD7D-1B5C48B8EBC5}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>
@@ -54,19 +54,19 @@
     <t>ACC</t>
   </si>
   <si>
-    <t>Daily-12; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 1052;Total - 5668 MT</t>
+    <t>Daily-0; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 1052;Total - 5668 MT</t>
   </si>
   <si>
     <t>Boiler</t>
   </si>
   <si>
-    <t>Daily-148  - (SH-112 and RH-36); Oct-2275 NDHT Balance joints - 7939(SH - 3933; RH - 4006)</t>
+    <t>Daily-114  - (SH-90 and RH-24); Oct-2389 NDHT Balance joints - 7825(SH - 3843; RH - 3982)</t>
   </si>
   <si>
     <t>PCP Joint</t>
   </si>
   <si>
-    <t>Daily-0; MS Joints - 88/146; MS to PRDS - 11/26; HRH - 11/95; CRH -15/87; LPBP - 11/49; HPBP-10/23; BFD- 185/661</t>
+    <t>Daily-3; MS Joints - 90/146; MS to PRDS - 11/26; HRH - 12/95; CRH -16/87; LPBP - 11/49; HPBP-10/23; BFD- 187/661</t>
   </si>
   <si>
     <t>Unit</t>
@@ -797,7 +797,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -808,7 +808,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -819,7 +819,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -922,7 +922,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
-  <dimension ref="A1:AA87"/>
+  <dimension ref="A1:AA88"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
@@ -967,47 +967,47 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="B4">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C4">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="B5">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C5">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -1018,84 +1018,84 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="1">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="B7">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="1">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="B8">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C8">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="B9">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C9">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B10">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C10">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1103,13 +1103,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B12">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1137,10 +1137,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B13">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1154,13 +1154,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C14">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1171,118 +1171,118 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B15">
-        <v>117</v>
+        <v>14</v>
       </c>
       <c r="C15">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B16">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C16">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16" s="6">
-        <v>20.72</v>
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:27">
       <c r="A17" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B17">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="C17">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="6">
-        <v>16.425999999999998</v>
+        <v>20.72</v>
       </c>
     </row>
     <row r="18" spans="1:27">
       <c r="A18" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B18">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="C18">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="6">
-        <v>18.917999999999999</v>
+        <v>16.425999999999998</v>
       </c>
     </row>
     <row r="19" spans="1:27">
       <c r="A19" s="1">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B19">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="C19">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" s="6">
-        <v>7.9720000000000004</v>
+        <v>18.917999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:27">
       <c r="A20" s="1">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B20">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E20" s="6">
-        <v>0</v>
+        <v>7.9720000000000004</v>
       </c>
     </row>
     <row r="21" spans="1:27">
       <c r="A21" s="1">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="B21">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="C21">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="6">
         <v>0</v>
@@ -1290,66 +1290,66 @@
     </row>
     <row r="22" spans="1:27">
       <c r="A22" s="1">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B22">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C22">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="E22" s="6">
-        <v>4.3440000000000003</v>
-      </c>
-      <c r="I22" s="2"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="3"/>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="3"/>
-      <c r="T22" s="2"/>
-      <c r="U22" s="2"/>
-      <c r="X22" s="3"/>
-      <c r="Y22" s="2"/>
-      <c r="Z22" s="2"/>
-      <c r="AA22" s="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:27">
       <c r="A23" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B23">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C23">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23" s="6">
-        <v>0</v>
-      </c>
+        <v>4.3440000000000003</v>
+      </c>
+      <c r="I23" s="2"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="3"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+      <c r="X23" s="3"/>
+      <c r="Y23" s="2"/>
+      <c r="Z23" s="2"/>
+      <c r="AA23" s="2"/>
     </row>
     <row r="24" spans="1:27">
       <c r="A24" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B24">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="C24">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="6">
         <v>0</v>
@@ -1357,84 +1357,84 @@
     </row>
     <row r="25" spans="1:27">
       <c r="A25" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B25">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C25">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D25">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E25" s="6">
-        <v>4.5679999999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:27">
       <c r="A26" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B26">
         <v>45</v>
       </c>
       <c r="C26">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E26" s="6">
-        <v>6.4130000000000003</v>
+        <v>4.5679999999999996</v>
       </c>
     </row>
     <row r="27" spans="1:27">
       <c r="A27" s="1">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B27">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E27" s="6">
-        <v>4.3440000000000003</v>
+        <v>6.4130000000000003</v>
       </c>
     </row>
     <row r="28" spans="1:27">
       <c r="A28" s="1">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B28">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C28">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="6">
-        <v>0</v>
+        <v>4.3440000000000003</v>
       </c>
     </row>
     <row r="29" spans="1:27">
       <c r="A29" s="1">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="6">
         <v>0</v>
@@ -1442,16 +1442,16 @@
     </row>
     <row r="30" spans="1:27">
       <c r="A30" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B30">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="6">
         <v>0</v>
@@ -1459,132 +1459,132 @@
     </row>
     <row r="31" spans="1:27">
       <c r="A31" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B31">
-        <v>321</v>
+        <v>40</v>
       </c>
       <c r="C31">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="D31">
-        <v>0</v>
-      </c>
-      <c r="E31" s="5">
-        <v>37.679307999999999</v>
+        <v>1</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:27">
       <c r="A32" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B32">
-        <v>200</v>
+        <v>321</v>
       </c>
       <c r="C32">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" s="5">
-        <v>33.449338000000004</v>
+        <v>37.679307999999999</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B33">
-        <v>43</v>
+        <v>200</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="D33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E33" s="5">
-        <v>42.041217999999994</v>
+        <v>33.449338000000004</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B34">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C34">
         <v>0</v>
       </c>
       <c r="D34">
-        <v>0</v>
-      </c>
-      <c r="E34" s="6">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="E34" s="5">
+        <v>42.041217999999994</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B35">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C35">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
-      <c r="E35" s="5">
-        <v>16.912866999999999</v>
+      <c r="E35" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B36">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C36">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E36" s="5">
-        <v>11.657306</v>
+        <v>16.912866999999999</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C37">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" s="5">
-        <v>0</v>
+        <v>11.657306</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C38">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -1595,13 +1595,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B39">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1612,16 +1612,16 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B40">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C40">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" s="5">
         <v>0</v>
@@ -1629,13 +1629,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B41">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C41">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -1646,16 +1646,16 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="1">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B42">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C42">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D42">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E42" s="5">
         <v>0</v>
@@ -1663,7 +1663,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="1">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B43">
         <v>16</v>
@@ -1675,38 +1675,38 @@
         <v>4</v>
       </c>
       <c r="E43" s="5">
-        <v>30.143184999999992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="1">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B44">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C44">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E44" s="5">
-        <v>0</v>
+        <v>30.143184999999992</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="1">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C45">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" s="5">
         <v>0</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B46">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="C46">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46" s="5">
         <v>0</v>
@@ -1731,16 +1731,16 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="1">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B47">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E47" s="5">
         <v>0</v>
@@ -1748,16 +1748,16 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="1">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B48">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="C48">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E48" s="5">
         <v>0</v>
@@ -1765,89 +1765,92 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="1">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B49">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="C49">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="5">
-        <v>5.3833070000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="1">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B50">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C50">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="D50">
         <v>1</v>
       </c>
       <c r="E50" s="5">
-        <v>0</v>
+        <v>5.3833070000000003</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="1">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B51">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="C51">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="D51">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="E51" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B52">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C52">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="1">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B53">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C53">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="1">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B54">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -1855,41 +1858,41 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="1">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C55">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D55">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="1">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B56">
         <v>0</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="1">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B57">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C57">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -1897,27 +1900,27 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="1">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B58">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C58">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B59">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -1925,10 +1928,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="1">
-        <v>46265</v>
+        <v>46266</v>
+      </c>
+      <c r="B60">
+        <v>17</v>
       </c>
       <c r="C60">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -1936,233 +1942,227 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="1">
-        <v>46264</v>
-      </c>
-      <c r="B61">
-        <v>5</v>
+        <v>46265</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="1">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B62">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="C62">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="1">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B63">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C63">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B64">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C64">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D64">
-        <v>3</v>
-      </c>
-      <c r="E64" s="4">
-        <v>0.21422999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:21">
       <c r="A65" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B65">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="C65">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="E65" s="4">
+        <v>0.21422999999999998</v>
       </c>
     </row>
     <row r="66" spans="1:21">
       <c r="A66" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B66">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="C66">
         <v>62</v>
       </c>
       <c r="D66">
-        <v>1</v>
-      </c>
-      <c r="E66" s="4">
-        <v>10.703772000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:21">
       <c r="A67" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B67">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C67">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D67">
         <v>1</v>
+      </c>
+      <c r="E67" s="4">
+        <v>10.703772000000001</v>
       </c>
     </row>
     <row r="68" spans="1:21">
       <c r="A68" s="1">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B68">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:21">
       <c r="A69" s="1">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B69">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="C69">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D69">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:21">
       <c r="A70" s="1">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B70">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="C70">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71" spans="1:21">
       <c r="A71" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B71">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="C71">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D71">
-        <v>0</v>
-      </c>
-      <c r="E71" s="4">
-        <v>8.4293359999999993</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:21">
       <c r="A72" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B72">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C72">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D72">
-        <v>1</v>
-      </c>
-      <c r="G72" s="7"/>
-      <c r="H72" s="7"/>
-      <c r="I72" s="3"/>
-      <c r="J72" s="3"/>
-      <c r="K72" s="7"/>
-      <c r="L72" s="7"/>
-      <c r="M72" s="7"/>
-      <c r="N72" s="7"/>
-      <c r="O72" s="7"/>
-      <c r="P72" s="7"/>
-      <c r="Q72" s="7"/>
-      <c r="R72" s="7"/>
-      <c r="S72" s="7"/>
-      <c r="T72" s="7"/>
-      <c r="U72" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="E72" s="4">
+        <v>8.4293359999999993</v>
+      </c>
     </row>
     <row r="73" spans="1:21">
       <c r="A73" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D73">
-        <v>2</v>
-      </c>
-      <c r="E73" s="4">
-        <v>6.2419820000000001</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G73" s="7"/>
+      <c r="H73" s="7"/>
+      <c r="I73" s="3"/>
+      <c r="J73" s="3"/>
+      <c r="K73" s="7"/>
+      <c r="L73" s="7"/>
+      <c r="M73" s="7"/>
+      <c r="N73" s="7"/>
+      <c r="O73" s="7"/>
+      <c r="P73" s="7"/>
+      <c r="Q73" s="7"/>
+      <c r="R73" s="7"/>
+      <c r="S73" s="7"/>
+      <c r="T73" s="7"/>
+      <c r="U73" s="7"/>
     </row>
     <row r="74" spans="1:21">
       <c r="A74" s="1">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B74">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74" s="4">
-        <v>14.777381999999999</v>
+        <v>6.2419820000000001</v>
       </c>
     </row>
     <row r="75" spans="1:21">
       <c r="A75" s="1">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B75">
         <v>12</v>
@@ -2170,10 +2170,19 @@
       <c r="C75">
         <v>0</v>
       </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="E75" s="4">
+        <v>14.777381999999999</v>
+      </c>
     </row>
     <row r="76" spans="1:21">
       <c r="A76" s="1">
-        <v>46249</v>
+        <v>46250</v>
+      </c>
+      <c r="B76">
+        <v>12</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2181,100 +2190,94 @@
     </row>
     <row r="77" spans="1:21">
       <c r="A77" s="1">
-        <v>46248</v>
-      </c>
-      <c r="B77">
-        <v>7</v>
+        <v>46249</v>
       </c>
       <c r="C77">
-        <v>16</v>
-      </c>
-      <c r="D77">
-        <v>0</v>
-      </c>
-      <c r="E77" s="4">
-        <v>20.847041999999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:21">
       <c r="A78" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B78">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="C78">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D78">
         <v>0</v>
       </c>
       <c r="E78" s="4">
-        <v>5.4199330000000003</v>
+        <v>20.847041999999995</v>
       </c>
     </row>
     <row r="79" spans="1:21">
       <c r="A79" s="1">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B79">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C79">
         <v>21</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E79" s="4">
+        <v>5.4199330000000003</v>
       </c>
     </row>
     <row r="80" spans="1:21">
       <c r="A80" s="1">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B80">
+        <v>28</v>
+      </c>
+      <c r="C80">
         <v>21</v>
       </c>
-      <c r="C80">
-        <v>25</v>
-      </c>
       <c r="D80">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="1">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B81">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C81">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D81">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="1">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B82">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="1">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2285,10 +2288,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="1">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B84">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2299,10 +2302,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="1">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B85">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2313,29 +2316,43 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="1">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B86">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C86">
         <v>0</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B87">
+        <v>0</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="1">
         <v>46238</v>
       </c>
-      <c r="B87">
-        <v>0</v>
-      </c>
-      <c r="C87">
-        <v>0</v>
-      </c>
-      <c r="D87">
+      <c r="B88">
+        <v>0</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+      <c r="D88">
         <v>1</v>
       </c>
     </row>
@@ -2346,7 +2363,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D41FB4CD-150C-4CE3-A76E-CB540C2892DD}">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
@@ -2438,19 +2455,19 @@
       </c>
       <c r="B3">
         <f>4375+SUM(B6:B500)</f>
-        <v>5757</v>
+        <v>5847</v>
       </c>
       <c r="C3">
         <f>7462+SUM(C6:C100)</f>
-        <v>7854</v>
+        <v>7878</v>
       </c>
       <c r="D3">
         <f>75+SUM(D5:D100)</f>
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E3">
         <f>10+SUM(E5:E150)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3">
         <f>10+SUM(F5:F100)</f>
@@ -2462,11 +2479,11 @@
       </c>
       <c r="H3">
         <f>14+SUM(H5:H100)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I3">
         <f>170+SUM(I5:I150)</f>
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J3">
         <f>1195+SUM(J5:J200)</f>
@@ -2488,19 +2505,19 @@
       </c>
       <c r="B4">
         <f>B2-B3</f>
-        <v>3940</v>
+        <v>3850</v>
       </c>
       <c r="C4">
         <f>C2-C3</f>
-        <v>4016</v>
+        <v>3992</v>
       </c>
       <c r="D4">
         <f t="shared" ref="D4:G4" si="0">D2-D3</f>
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F4">
         <f t="shared" si="0"/>
@@ -2512,11 +2529,11 @@
       </c>
       <c r="H4">
         <f>H2-H3</f>
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I4">
         <f>I2-I3</f>
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="J4">
         <f>J2-J3</f>
@@ -3193,6 +3210,38 @@
       </c>
       <c r="J23">
         <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B24">
+        <v>90</v>
+      </c>
+      <c r="C24">
+        <v>24</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>2</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Daily-updates.xlsx
+++ b/Daily-updates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30619"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30621"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1474" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24A955D1-4CF0-457A-BD7D-1B5C48B8EBC5}"/>
+  <xr:revisionPtr revIDLastSave="1502" documentId="11_DC8F342965EF1E1694601FD3C012B93540A277E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C430D7D-BCB1-40C0-87D7-97D9792FB597}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="1" r:id="rId1"/>
@@ -54,19 +54,19 @@
     <t>ACC</t>
   </si>
   <si>
-    <t>Daily-0; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 1052;Total - 5668 MT</t>
+    <t>Daily-19; June - 1229; July - 832; Aug - 642; Sep- 1122 MT; Oct 1071;Total - 5687 MT</t>
   </si>
   <si>
     <t>Boiler</t>
   </si>
   <si>
-    <t>Daily-114  - (SH-90 and RH-24); Oct-2389 NDHT Balance joints - 7825(SH - 3843; RH - 3982)</t>
+    <t>Daily-168- (SH-134 and RH-30); Oct-25579 NDHT Balance joints - 7657(SH - 3705; RH - 3952)</t>
   </si>
   <si>
     <t>PCP Joint</t>
   </si>
   <si>
-    <t>Daily-3; MS Joints - 90/146; MS to PRDS - 11/26; HRH - 12/95; CRH -16/87; LPBP - 11/49; HPBP-10/23; BFD- 187/661</t>
+    <t>Daily-1; MS Joints - 91/146; MS to PRDS - 11/26; HRH - 12/95; CRH -16/87; LPBP - 11/49; HPBP-10/23; BFD- 187/661</t>
   </si>
   <si>
     <t>Unit</t>
@@ -797,7 +797,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -808,7 +808,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -819,7 +819,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -922,7 +922,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA68853-E44A-449A-8552-A3359B72937A}">
-  <dimension ref="A1:AA88"/>
+  <dimension ref="A1:AA89"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
@@ -967,64 +967,64 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C3">
-        <v>114</v>
+        <v>168</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="B5">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="1">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="B6">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C6">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -1035,84 +1035,84 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="1">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="B8">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="B9">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C9">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="B10">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C10">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B11">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C11">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1120,13 +1120,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1137,10 +1137,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B13">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1154,10 +1154,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B14">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1171,13 +1171,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B15">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C15">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1188,118 +1188,118 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B16">
-        <v>117</v>
+        <v>14</v>
       </c>
       <c r="C16">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:27">
       <c r="A17" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B17">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C17">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17" s="6">
-        <v>20.72</v>
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:27">
       <c r="A18" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B18">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="C18">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="6">
-        <v>16.425999999999998</v>
+        <v>20.72</v>
       </c>
     </row>
     <row r="19" spans="1:27">
       <c r="A19" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B19">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="C19">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="6">
-        <v>18.917999999999999</v>
+        <v>16.425999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:27">
       <c r="A20" s="1">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B20">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="C20">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" s="6">
-        <v>7.9720000000000004</v>
+        <v>18.917999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:27">
       <c r="A21" s="1">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B21">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E21" s="6">
-        <v>0</v>
+        <v>7.9720000000000004</v>
       </c>
     </row>
     <row r="22" spans="1:27">
       <c r="A22" s="1">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="B22">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="C22">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="6">
         <v>0</v>
@@ -1307,66 +1307,66 @@
     </row>
     <row r="23" spans="1:27">
       <c r="A23" s="1">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B23">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C23">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23" s="6">
-        <v>4.3440000000000003</v>
-      </c>
-      <c r="I23" s="2"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="3"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="3"/>
-      <c r="T23" s="2"/>
-      <c r="U23" s="2"/>
-      <c r="X23" s="3"/>
-      <c r="Y23" s="2"/>
-      <c r="Z23" s="2"/>
-      <c r="AA23" s="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:27">
       <c r="A24" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B24">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C24">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D24">
         <v>1</v>
       </c>
       <c r="E24" s="6">
-        <v>0</v>
-      </c>
+        <v>4.3440000000000003</v>
+      </c>
+      <c r="I24" s="2"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="3"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="X24" s="3"/>
+      <c r="Y24" s="2"/>
+      <c r="Z24" s="2"/>
+      <c r="AA24" s="2"/>
     </row>
     <row r="25" spans="1:27">
       <c r="A25" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B25">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="C25">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="6">
         <v>0</v>
@@ -1374,84 +1374,84 @@
     </row>
     <row r="26" spans="1:27">
       <c r="A26" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B26">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C26">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D26">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E26" s="6">
-        <v>4.5679999999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:27">
       <c r="A27" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B27">
         <v>45</v>
       </c>
       <c r="C27">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E27" s="6">
-        <v>6.4130000000000003</v>
+        <v>4.5679999999999996</v>
       </c>
     </row>
     <row r="28" spans="1:27">
       <c r="A28" s="1">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B28">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E28" s="6">
-        <v>4.3440000000000003</v>
+        <v>6.4130000000000003</v>
       </c>
     </row>
     <row r="29" spans="1:27">
       <c r="A29" s="1">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B29">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C29">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" s="6">
-        <v>0</v>
+        <v>4.3440000000000003</v>
       </c>
     </row>
     <row r="30" spans="1:27">
       <c r="A30" s="1">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="6">
         <v>0</v>
@@ -1459,16 +1459,16 @@
     </row>
     <row r="31" spans="1:27">
       <c r="A31" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B31">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" s="6">
         <v>0</v>
@@ -1476,132 +1476,132 @@
     </row>
     <row r="32" spans="1:27">
       <c r="A32" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B32">
-        <v>321</v>
+        <v>40</v>
       </c>
       <c r="C32">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="D32">
-        <v>0</v>
-      </c>
-      <c r="E32" s="5">
-        <v>37.679307999999999</v>
+        <v>1</v>
+      </c>
+      <c r="E32" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B33">
-        <v>200</v>
+        <v>321</v>
       </c>
       <c r="C33">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" s="5">
-        <v>33.449338000000004</v>
+        <v>37.679307999999999</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B34">
-        <v>43</v>
+        <v>200</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="D34">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E34" s="5">
-        <v>42.041217999999994</v>
+        <v>33.449338000000004</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B35">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35" s="6">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="E35" s="5">
+        <v>42.041217999999994</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B36">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C36">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
-      <c r="E36" s="5">
-        <v>16.912866999999999</v>
+      <c r="E36" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B37">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C37">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E37" s="5">
-        <v>11.657306</v>
+        <v>16.912866999999999</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C38">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" s="5">
-        <v>0</v>
+        <v>11.657306</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C39">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1612,13 +1612,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B40">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -1629,16 +1629,16 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B41">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C41">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" s="5">
         <v>0</v>
@@ -1646,13 +1646,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="1">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B42">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C42">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -1663,16 +1663,16 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="1">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B43">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C43">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E43" s="5">
         <v>0</v>
@@ -1680,7 +1680,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="1">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B44">
         <v>16</v>
@@ -1692,38 +1692,38 @@
         <v>4</v>
       </c>
       <c r="E44" s="5">
-        <v>30.143184999999992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="1">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B45">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C45">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E45" s="5">
-        <v>0</v>
+        <v>30.143184999999992</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="1">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C46">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" s="5">
         <v>0</v>
@@ -1731,16 +1731,16 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B47">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="C47">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" s="5">
         <v>0</v>
@@ -1748,16 +1748,16 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="1">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E48" s="5">
         <v>0</v>
@@ -1765,16 +1765,16 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="1">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B49">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="C49">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E49" s="5">
         <v>0</v>
@@ -1782,89 +1782,92 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="1">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B50">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="C50">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" s="5">
-        <v>5.3833070000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="1">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B51">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C51">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="D51">
         <v>1</v>
       </c>
       <c r="E51" s="5">
-        <v>0</v>
+        <v>5.3833070000000003</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="1">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B52">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="C52">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="D52">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="E52" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B53">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C53">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="1">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B54">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C54">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="1">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B55">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -1872,41 +1875,41 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="1">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C56">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="1">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B57">
         <v>0</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="1">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B58">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C58">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -1914,27 +1917,27 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="1">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B59">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C59">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B60">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -1942,10 +1945,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="1">
-        <v>46265</v>
+        <v>46266</v>
+      </c>
+      <c r="B61">
+        <v>17</v>
       </c>
       <c r="C61">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -1953,233 +1959,227 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="1">
-        <v>46264</v>
-      </c>
-      <c r="B62">
-        <v>5</v>
+        <v>46265</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="1">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B63">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="C63">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="1">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B64">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C64">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:21">
       <c r="A65" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B65">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C65">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D65">
-        <v>3</v>
-      </c>
-      <c r="E65" s="4">
-        <v>0.21422999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:21">
       <c r="A66" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B66">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="C66">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="E66" s="4">
+        <v>0.21422999999999998</v>
       </c>
     </row>
     <row r="67" spans="1:21">
       <c r="A67" s="1">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B67">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="C67">
         <v>62</v>
       </c>
       <c r="D67">
-        <v>1</v>
-      </c>
-      <c r="E67" s="4">
-        <v>10.703772000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:21">
       <c r="A68" s="1">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B68">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C68">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D68">
         <v>1</v>
+      </c>
+      <c r="E68" s="4">
+        <v>10.703772000000001</v>
       </c>
     </row>
     <row r="69" spans="1:21">
       <c r="A69" s="1">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:21">
       <c r="A70" s="1">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B70">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="C70">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D70">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:21">
       <c r="A71" s="1">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B71">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="C71">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72" spans="1:21">
       <c r="A72" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B72">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="C72">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D72">
-        <v>0</v>
-      </c>
-      <c r="E72" s="4">
-        <v>8.4293359999999993</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:21">
       <c r="A73" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B73">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C73">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D73">
-        <v>1</v>
-      </c>
-      <c r="G73" s="7"/>
-      <c r="H73" s="7"/>
-      <c r="I73" s="3"/>
-      <c r="J73" s="3"/>
-      <c r="K73" s="7"/>
-      <c r="L73" s="7"/>
-      <c r="M73" s="7"/>
-      <c r="N73" s="7"/>
-      <c r="O73" s="7"/>
-      <c r="P73" s="7"/>
-      <c r="Q73" s="7"/>
-      <c r="R73" s="7"/>
-      <c r="S73" s="7"/>
-      <c r="T73" s="7"/>
-      <c r="U73" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="E73" s="4">
+        <v>8.4293359999999993</v>
+      </c>
     </row>
     <row r="74" spans="1:21">
       <c r="A74" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D74">
-        <v>2</v>
-      </c>
-      <c r="E74" s="4">
-        <v>6.2419820000000001</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G74" s="7"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="3"/>
+      <c r="J74" s="3"/>
+      <c r="K74" s="7"/>
+      <c r="L74" s="7"/>
+      <c r="M74" s="7"/>
+      <c r="N74" s="7"/>
+      <c r="O74" s="7"/>
+      <c r="P74" s="7"/>
+      <c r="Q74" s="7"/>
+      <c r="R74" s="7"/>
+      <c r="S74" s="7"/>
+      <c r="T74" s="7"/>
+      <c r="U74" s="7"/>
     </row>
     <row r="75" spans="1:21">
       <c r="A75" s="1">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B75">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" s="4">
-        <v>14.777381999999999</v>
+        <v>6.2419820000000001</v>
       </c>
     </row>
     <row r="76" spans="1:21">
       <c r="A76" s="1">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B76">
         <v>12</v>
@@ -2187,10 +2187,19 @@
       <c r="C76">
         <v>0</v>
       </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76" s="4">
+        <v>14.777381999999999</v>
+      </c>
     </row>
     <row r="77" spans="1:21">
       <c r="A77" s="1">
-        <v>46249</v>
+        <v>46250</v>
+      </c>
+      <c r="B77">
+        <v>12</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2198,100 +2207,94 @@
     </row>
     <row r="78" spans="1:21">
       <c r="A78" s="1">
-        <v>46248</v>
-      </c>
-      <c r="B78">
-        <v>7</v>
+        <v>46249</v>
       </c>
       <c r="C78">
-        <v>16</v>
-      </c>
-      <c r="D78">
-        <v>0</v>
-      </c>
-      <c r="E78" s="4">
-        <v>20.847041999999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:21">
       <c r="A79" s="1">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B79">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="C79">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
       <c r="E79" s="4">
-        <v>5.4199330000000003</v>
+        <v>20.847041999999995</v>
       </c>
     </row>
     <row r="80" spans="1:21">
       <c r="A80" s="1">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B80">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C80">
         <v>21</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E80" s="4">
+        <v>5.4199330000000003</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="1">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B81">
+        <v>28</v>
+      </c>
+      <c r="C81">
         <v>21</v>
       </c>
-      <c r="C81">
-        <v>25</v>
-      </c>
       <c r="D81">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="1">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B82">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C82">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D82">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="1">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B83">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="1">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B84">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2302,10 +2305,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="1">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B85">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2316,10 +2319,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="1">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B86">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2330,29 +2333,43 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="1">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B87">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C87">
         <v>0</v>
       </c>
       <c r="D87">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B88">
+        <v>0</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+      <c r="D88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="1">
         <v>46238</v>
       </c>
-      <c r="B88">
-        <v>0</v>
-      </c>
-      <c r="C88">
-        <v>0</v>
-      </c>
-      <c r="D88">
+      <c r="B89">
+        <v>0</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
+      <c r="D89">
         <v>1</v>
       </c>
     </row>
@@ -2363,7 +2380,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D41FB4CD-150C-4CE3-A76E-CB540C2892DD}">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
@@ -2455,15 +2472,15 @@
       </c>
       <c r="B3">
         <f>4375+SUM(B6:B500)</f>
-        <v>5847</v>
+        <v>5985</v>
       </c>
       <c r="C3">
         <f>7462+SUM(C6:C100)</f>
-        <v>7878</v>
+        <v>7908</v>
       </c>
       <c r="D3">
         <f>75+SUM(D5:D100)</f>
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E3">
         <f>10+SUM(E5:E150)</f>
@@ -2487,7 +2504,7 @@
       </c>
       <c r="J3">
         <f>1195+SUM(J5:J200)</f>
-        <v>1316</v>
+        <v>1327</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -2505,15 +2522,15 @@
       </c>
       <c r="B4">
         <f>B2-B3</f>
-        <v>3850</v>
+        <v>3712</v>
       </c>
       <c r="C4">
         <f>C2-C3</f>
-        <v>3992</v>
+        <v>3962</v>
       </c>
       <c r="D4">
         <f t="shared" ref="D4:G4" si="0">D2-D3</f>
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
@@ -2537,7 +2554,7 @@
       </c>
       <c r="J4">
         <f>J2-J3</f>
-        <v>3184</v>
+        <v>3173</v>
       </c>
       <c r="K4">
         <f>K2-K3</f>
@@ -3242,6 +3259,38 @@
       </c>
       <c r="J24">
         <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B25">
+        <v>138</v>
+      </c>
+      <c r="C25">
+        <v>30</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
